--- a/Literature/Languages/Norvunic (old).xlsx
+++ b/Literature/Languages/Norvunic (old).xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="871">
   <si>
     <t>Word</t>
   </si>
@@ -69,7 +69,7 @@
     <t>nus ægi blûlr = blue very robes (very blue robes)</t>
   </si>
   <si>
-    <t>say</t>
+    <t>milk</t>
   </si>
   <si>
     <t>stode</t>
@@ -303,7 +303,7 @@
     <t>present tense -ete</t>
   </si>
   <si>
-    <t>remove -en, then add -ete</t>
+    <t>remove -en</t>
   </si>
   <si>
     <t>lybe</t>
@@ -849,6 +849,12 @@
     <t>friend, ally</t>
   </si>
   <si>
+    <t>fra</t>
+  </si>
+  <si>
+    <t>from</t>
+  </si>
+  <si>
     <t>velde</t>
   </si>
   <si>
@@ -867,6 +873,12 @@
     <t>girl</t>
   </si>
   <si>
+    <t>kofte</t>
+  </si>
+  <si>
+    <t>goat</t>
+  </si>
+  <si>
     <t>gåd</t>
   </si>
   <si>
@@ -987,6 +999,12 @@
     <t>hundred</t>
   </si>
   <si>
+    <t>rumb</t>
+  </si>
+  <si>
+    <t>hungry (adjective)</t>
+  </si>
+  <si>
     <t>meg</t>
   </si>
   <si>
@@ -1209,6 +1227,9 @@
     <t>mighty</t>
   </si>
   <si>
+    <t>greik</t>
+  </si>
+  <si>
     <t>minadd</t>
   </si>
   <si>
@@ -1795,6 +1816,12 @@
   </si>
   <si>
     <t>thing</t>
+  </si>
+  <si>
+    <t>terstig</t>
+  </si>
+  <si>
+    <t>thirsty</t>
   </si>
   <si>
     <t>tigge</t>
@@ -3154,12 +3181,12 @@
         <v>23</v>
       </c>
       <c r="G4" s="14" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:B1000, REGEXMATCH(B2:B1000, H3)), 2, TRUE)"),"talen")</f>
-        <v>talen</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:B1000, REGEXMATCH(B2:B1000, H3)), 2, TRUE)"),"greik")</f>
+        <v>greik</v>
       </c>
       <c r="H4" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"to speak, talk, or to say something")</f>
-        <v>to speak, talk, or to say something</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"milk")</f>
+        <v>milk</v>
       </c>
       <c r="I4" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("FILTER(C:C, REGEXMATCH(B:B, H3))"),"")</f>
@@ -6135,10 +6162,10 @@
       <c r="Z91" s="7"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="8" t="s">
+      <c r="A92" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="B92" s="16" t="s">
         <v>279</v>
       </c>
       <c r="C92" s="7"/>
@@ -6263,10 +6290,10 @@
       <c r="Z95" s="7"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="8" t="s">
+      <c r="A96" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="B96" s="11" t="s">
+      <c r="B96" s="16" t="s">
         <v>287</v>
       </c>
       <c r="C96" s="7"/>
@@ -6330,7 +6357,7 @@
       <c r="A98" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="B98" s="11" t="s">
         <v>291</v>
       </c>
       <c r="C98" s="7"/>
@@ -6362,7 +6389,7 @@
       <c r="A99" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="B99" s="11" t="s">
+      <c r="B99" s="8" t="s">
         <v>293</v>
       </c>
       <c r="C99" s="7"/>
@@ -6394,7 +6421,7 @@
       <c r="A100" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="B100" s="11" t="s">
+      <c r="B100" s="8" t="s">
         <v>295</v>
       </c>
       <c r="C100" s="7"/>
@@ -6458,7 +6485,7 @@
       <c r="A102" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="B102" s="8" t="s">
+      <c r="B102" s="11" t="s">
         <v>299</v>
       </c>
       <c r="C102" s="7"/>
@@ -6487,10 +6514,10 @@
       <c r="Z102" s="7"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="16" t="s">
+      <c r="A103" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="B103" s="16" t="s">
+      <c r="B103" s="11" t="s">
         <v>301</v>
       </c>
       <c r="C103" s="7"/>
@@ -6583,10 +6610,10 @@
       <c r="Z105" s="7"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="20" t="s">
+      <c r="A106" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="B106" s="20" t="s">
+      <c r="B106" s="8" t="s">
         <v>307</v>
       </c>
       <c r="C106" s="7"/>
@@ -6615,7 +6642,7 @@
       <c r="Z106" s="7"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="8" t="s">
+      <c r="A107" s="16" t="s">
         <v>308</v>
       </c>
       <c r="B107" s="16" t="s">
@@ -6647,10 +6674,10 @@
       <c r="Z107" s="7"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="8" t="s">
+      <c r="A108" s="20" t="s">
         <v>310</v>
       </c>
-      <c r="B108" s="11" t="s">
+      <c r="B108" s="20" t="s">
         <v>311</v>
       </c>
       <c r="C108" s="7"/>
@@ -6679,7 +6706,7 @@
       <c r="Z108" s="7"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="16" t="s">
+      <c r="A109" s="8" t="s">
         <v>312</v>
       </c>
       <c r="B109" s="16" t="s">
@@ -6743,10 +6770,10 @@
       <c r="Z110" s="7"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="8" t="s">
+      <c r="A111" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="B111" s="8" t="s">
+      <c r="B111" s="16" t="s">
         <v>317</v>
       </c>
       <c r="C111" s="7"/>
@@ -6778,7 +6805,7 @@
       <c r="A112" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="B112" s="8" t="s">
+      <c r="B112" s="11" t="s">
         <v>319</v>
       </c>
       <c r="C112" s="7"/>
@@ -6839,10 +6866,10 @@
       <c r="Z113" s="7"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="11" t="s">
+      <c r="A114" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="B114" s="11" t="s">
+      <c r="B114" s="8" t="s">
         <v>323</v>
       </c>
       <c r="C114" s="7"/>
@@ -6903,10 +6930,10 @@
       <c r="Z115" s="7"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="21" t="s">
+      <c r="A116" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="B116" s="20" t="s">
+      <c r="B116" s="11" t="s">
         <v>327</v>
       </c>
       <c r="C116" s="7"/>
@@ -6935,10 +6962,10 @@
       <c r="Z116" s="7"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="8" t="s">
+      <c r="A117" s="16" t="s">
         <v>328</v>
       </c>
-      <c r="B117" s="8" t="s">
+      <c r="B117" s="16" t="s">
         <v>329</v>
       </c>
       <c r="C117" s="7"/>
@@ -6970,7 +6997,7 @@
       <c r="A118" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="B118" s="11" t="s">
+      <c r="B118" s="8" t="s">
         <v>331</v>
       </c>
       <c r="C118" s="7"/>
@@ -6999,10 +7026,10 @@
       <c r="Z118" s="7"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="8" t="s">
+      <c r="A119" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="B119" s="11" t="s">
+      <c r="B119" s="20" t="s">
         <v>333</v>
       </c>
       <c r="C119" s="7"/>
@@ -7034,7 +7061,7 @@
       <c r="A120" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="B120" s="11" t="s">
+      <c r="B120" s="8" t="s">
         <v>335</v>
       </c>
       <c r="C120" s="7"/>
@@ -7063,10 +7090,10 @@
       <c r="Z120" s="7"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="20" t="s">
+      <c r="A121" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="B121" s="21" t="s">
+      <c r="B121" s="11" t="s">
         <v>337</v>
       </c>
       <c r="C121" s="7"/>
@@ -7098,7 +7125,7 @@
       <c r="A122" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="B122" s="8" t="s">
+      <c r="B122" s="11" t="s">
         <v>339</v>
       </c>
       <c r="C122" s="7"/>
@@ -7159,10 +7186,10 @@
       <c r="Z123" s="7"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="8" t="s">
+      <c r="A124" s="20" t="s">
         <v>342</v>
       </c>
-      <c r="B124" s="8" t="s">
+      <c r="B124" s="21" t="s">
         <v>343</v>
       </c>
       <c r="C124" s="7"/>
@@ -7194,7 +7221,7 @@
       <c r="A125" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="B125" s="11" t="s">
+      <c r="B125" s="8" t="s">
         <v>345</v>
       </c>
       <c r="C125" s="7"/>
@@ -7223,10 +7250,10 @@
       <c r="Z125" s="7"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="20" t="s">
+      <c r="A126" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="B126" s="21" t="s">
+      <c r="B126" s="11" t="s">
         <v>347</v>
       </c>
       <c r="C126" s="7"/>
@@ -7255,10 +7282,10 @@
       <c r="Z126" s="7"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="16" t="s">
+      <c r="A127" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="B127" s="16" t="s">
+      <c r="B127" s="8" t="s">
         <v>349</v>
       </c>
       <c r="C127" s="7"/>
@@ -7290,7 +7317,7 @@
       <c r="A128" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="B128" s="8" t="s">
+      <c r="B128" s="11" t="s">
         <v>351</v>
       </c>
       <c r="C128" s="7"/>
@@ -7319,10 +7346,10 @@
       <c r="Z128" s="7"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="8" t="s">
+      <c r="A129" s="20" t="s">
         <v>352</v>
       </c>
-      <c r="B129" s="8" t="s">
+      <c r="B129" s="21" t="s">
         <v>353</v>
       </c>
       <c r="C129" s="7"/>
@@ -7351,10 +7378,10 @@
       <c r="Z129" s="7"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="8" t="s">
+      <c r="A130" s="16" t="s">
         <v>354</v>
       </c>
-      <c r="B130" s="8" t="s">
+      <c r="B130" s="16" t="s">
         <v>355</v>
       </c>
       <c r="C130" s="7"/>
@@ -7514,7 +7541,7 @@
       <c r="A135" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="B135" s="11" t="s">
+      <c r="B135" s="8" t="s">
         <v>365</v>
       </c>
       <c r="C135" s="7"/>
@@ -7543,7 +7570,7 @@
       <c r="Z135" s="7"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="11" t="s">
+      <c r="A136" s="8" t="s">
         <v>366</v>
       </c>
       <c r="B136" s="8" t="s">
@@ -7610,7 +7637,7 @@
       <c r="A138" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="B138" s="8" t="s">
+      <c r="B138" s="11" t="s">
         <v>371</v>
       </c>
       <c r="C138" s="7"/>
@@ -7639,10 +7666,10 @@
       <c r="Z138" s="7"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="8" t="s">
+      <c r="A139" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="B139" s="11" t="s">
+      <c r="B139" s="8" t="s">
         <v>373</v>
       </c>
       <c r="C139" s="7"/>
@@ -7671,10 +7698,10 @@
       <c r="Z139" s="7"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="16" t="s">
+      <c r="A140" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="B140" s="16" t="s">
+      <c r="B140" s="8" t="s">
         <v>375</v>
       </c>
       <c r="C140" s="7"/>
@@ -7735,10 +7762,10 @@
       <c r="Z141" s="7"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="16" t="s">
+      <c r="A142" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="B142" s="16" t="s">
+      <c r="B142" s="11" t="s">
         <v>379</v>
       </c>
       <c r="C142" s="7"/>
@@ -7767,10 +7794,10 @@
       <c r="Z142" s="7"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="8" t="s">
+      <c r="A143" s="16" t="s">
         <v>380</v>
       </c>
-      <c r="B143" s="8" t="s">
+      <c r="B143" s="16" t="s">
         <v>381</v>
       </c>
       <c r="C143" s="7"/>
@@ -7831,10 +7858,10 @@
       <c r="Z144" s="7"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="8" t="s">
+      <c r="A145" s="16" t="s">
         <v>384</v>
       </c>
-      <c r="B145" s="11" t="s">
+      <c r="B145" s="16" t="s">
         <v>385</v>
       </c>
       <c r="C145" s="7"/>
@@ -7863,10 +7890,10 @@
       <c r="Z145" s="7"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="11" t="s">
+      <c r="A146" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="B146" s="11" t="s">
+      <c r="B146" s="8" t="s">
         <v>387</v>
       </c>
       <c r="C146" s="7"/>
@@ -7898,7 +7925,7 @@
       <c r="A147" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="B147" s="11" t="s">
+      <c r="B147" s="8" t="s">
         <v>389</v>
       </c>
       <c r="C147" s="7"/>
@@ -7959,10 +7986,10 @@
       <c r="Z148" s="7"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="8" t="s">
+      <c r="A149" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="B149" s="8" t="s">
+      <c r="B149" s="11" t="s">
         <v>393</v>
       </c>
       <c r="C149" s="7"/>
@@ -7991,10 +8018,10 @@
       <c r="Z149" s="7"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="16" t="s">
+      <c r="A150" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="B150" s="16" t="s">
+      <c r="B150" s="11" t="s">
         <v>395</v>
       </c>
       <c r="C150" s="7"/>
@@ -8087,10 +8114,10 @@
       <c r="Z152" s="7"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="8" t="s">
+      <c r="A153" s="16" t="s">
         <v>400</v>
       </c>
-      <c r="B153" s="8" t="s">
+      <c r="B153" s="16" t="s">
         <v>401</v>
       </c>
       <c r="C153" s="7"/>
@@ -8119,7 +8146,7 @@
       <c r="Z153" s="7"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="11" t="s">
+      <c r="A154" s="8" t="s">
         <v>402</v>
       </c>
       <c r="B154" s="11" t="s">
@@ -8151,11 +8178,11 @@
       <c r="Z154" s="7"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="8" t="s">
+      <c r="A155" s="16" t="s">
         <v>404</v>
       </c>
-      <c r="B155" s="8" t="s">
-        <v>405</v>
+      <c r="B155" s="16" t="s">
+        <v>18</v>
       </c>
       <c r="C155" s="7"/>
       <c r="D155" s="7"/>
@@ -8183,11 +8210,11 @@
       <c r="Z155" s="7"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="16" t="s">
+      <c r="A156" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="B156" s="8" t="s">
         <v>406</v>
-      </c>
-      <c r="B156" s="16" t="s">
-        <v>407</v>
       </c>
       <c r="C156" s="7"/>
       <c r="D156" s="7"/>
@@ -8215,11 +8242,11 @@
       <c r="Z156" s="7"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="11" t="s">
+      <c r="A157" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="B157" s="8" t="s">
         <v>408</v>
-      </c>
-      <c r="B157" s="8" t="s">
-        <v>409</v>
       </c>
       <c r="C157" s="7"/>
       <c r="D157" s="7"/>
@@ -8248,10 +8275,10 @@
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="B158" s="11" t="s">
         <v>410</v>
-      </c>
-      <c r="B158" s="11" t="s">
-        <v>411</v>
       </c>
       <c r="C158" s="7"/>
       <c r="D158" s="7"/>
@@ -8280,10 +8307,10 @@
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="B159" s="8" t="s">
         <v>412</v>
-      </c>
-      <c r="B159" s="8" t="s">
-        <v>413</v>
       </c>
       <c r="C159" s="7"/>
       <c r="D159" s="7"/>
@@ -8311,11 +8338,11 @@
       <c r="Z159" s="7"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="8" t="s">
+      <c r="A160" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="B160" s="16" t="s">
         <v>414</v>
-      </c>
-      <c r="B160" s="11" t="s">
-        <v>415</v>
       </c>
       <c r="C160" s="7"/>
       <c r="D160" s="7"/>
@@ -8344,10 +8371,10 @@
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="B161" s="8" t="s">
         <v>416</v>
-      </c>
-      <c r="B161" s="11" t="s">
-        <v>417</v>
       </c>
       <c r="C161" s="7"/>
       <c r="D161" s="7"/>
@@ -8375,11 +8402,11 @@
       <c r="Z161" s="7"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="8" t="s">
+      <c r="A162" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="B162" s="11" t="s">
         <v>418</v>
-      </c>
-      <c r="B162" s="8" t="s">
-        <v>419</v>
       </c>
       <c r="C162" s="7"/>
       <c r="D162" s="7"/>
@@ -8408,10 +8435,10 @@
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B163" s="8" t="s">
         <v>420</v>
-      </c>
-      <c r="B163" s="8" t="s">
-        <v>421</v>
       </c>
       <c r="C163" s="7"/>
       <c r="D163" s="7"/>
@@ -8439,11 +8466,11 @@
       <c r="Z163" s="7"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="11" t="s">
+      <c r="A164" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="B164" s="11" t="s">
         <v>422</v>
-      </c>
-      <c r="B164" s="11" t="s">
-        <v>423</v>
       </c>
       <c r="C164" s="7"/>
       <c r="D164" s="7"/>
@@ -8471,11 +8498,11 @@
       <c r="Z164" s="7"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="20" t="s">
+      <c r="A165" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="B165" s="11" t="s">
         <v>424</v>
-      </c>
-      <c r="B165" s="20" t="s">
-        <v>425</v>
       </c>
       <c r="C165" s="7"/>
       <c r="D165" s="7"/>
@@ -8503,11 +8530,11 @@
       <c r="Z165" s="7"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="16" t="s">
+      <c r="A166" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="B166" s="8" t="s">
         <v>426</v>
-      </c>
-      <c r="B166" s="16" t="s">
-        <v>427</v>
       </c>
       <c r="C166" s="7"/>
       <c r="D166" s="7"/>
@@ -8535,11 +8562,11 @@
       <c r="Z166" s="7"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="20" t="s">
+      <c r="A167" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="B167" s="8" t="s">
         <v>428</v>
-      </c>
-      <c r="B167" s="20" t="s">
-        <v>429</v>
       </c>
       <c r="C167" s="7"/>
       <c r="D167" s="7"/>
@@ -8567,11 +8594,11 @@
       <c r="Z167" s="7"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="8" t="s">
+      <c r="A168" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="B168" s="11" t="s">
         <v>430</v>
-      </c>
-      <c r="B168" s="8" t="s">
-        <v>431</v>
       </c>
       <c r="C168" s="7"/>
       <c r="D168" s="7"/>
@@ -8599,11 +8626,11 @@
       <c r="Z168" s="7"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="16" t="s">
+      <c r="A169" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="B169" s="20" t="s">
         <v>432</v>
-      </c>
-      <c r="B169" s="16" t="s">
-        <v>433</v>
       </c>
       <c r="C169" s="7"/>
       <c r="D169" s="7"/>
@@ -8631,11 +8658,11 @@
       <c r="Z169" s="7"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="8" t="s">
+      <c r="A170" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="B170" s="16" t="s">
         <v>434</v>
-      </c>
-      <c r="B170" s="8" t="s">
-        <v>435</v>
       </c>
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
@@ -8663,11 +8690,11 @@
       <c r="Z170" s="7"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="8" t="s">
+      <c r="A171" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="B171" s="20" t="s">
         <v>436</v>
-      </c>
-      <c r="B171" s="11" t="s">
-        <v>437</v>
       </c>
       <c r="C171" s="7"/>
       <c r="D171" s="7"/>
@@ -8696,10 +8723,10 @@
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="B172" s="8" t="s">
         <v>438</v>
-      </c>
-      <c r="B172" s="11" t="s">
-        <v>439</v>
       </c>
       <c r="C172" s="7"/>
       <c r="D172" s="7"/>
@@ -8727,11 +8754,11 @@
       <c r="Z172" s="7"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="8" t="s">
+      <c r="A173" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="B173" s="16" t="s">
         <v>440</v>
-      </c>
-      <c r="B173" s="11" t="s">
-        <v>441</v>
       </c>
       <c r="C173" s="7"/>
       <c r="D173" s="7"/>
@@ -8760,10 +8787,10 @@
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="B174" s="8" t="s">
         <v>442</v>
-      </c>
-      <c r="B174" s="11" t="s">
-        <v>443</v>
       </c>
       <c r="C174" s="7"/>
       <c r="D174" s="7"/>
@@ -8792,10 +8819,10 @@
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="B175" s="11" t="s">
         <v>444</v>
-      </c>
-      <c r="B175" s="11" t="s">
-        <v>445</v>
       </c>
       <c r="C175" s="7"/>
       <c r="D175" s="7"/>
@@ -8824,10 +8851,10 @@
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="B176" s="11" t="s">
         <v>446</v>
-      </c>
-      <c r="B176" s="11" t="s">
-        <v>447</v>
       </c>
       <c r="C176" s="7"/>
       <c r="D176" s="7"/>
@@ -8856,10 +8883,10 @@
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="B177" s="11" t="s">
         <v>448</v>
-      </c>
-      <c r="B177" s="11" t="s">
-        <v>449</v>
       </c>
       <c r="C177" s="7"/>
       <c r="D177" s="7"/>
@@ -8888,10 +8915,10 @@
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="B178" s="11" t="s">
         <v>450</v>
-      </c>
-      <c r="B178" s="11" t="s">
-        <v>451</v>
       </c>
       <c r="C178" s="7"/>
       <c r="D178" s="7"/>
@@ -8919,11 +8946,11 @@
       <c r="Z178" s="7"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="16" t="s">
+      <c r="A179" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="B179" s="11" t="s">
         <v>452</v>
-      </c>
-      <c r="B179" s="16" t="s">
-        <v>453</v>
       </c>
       <c r="C179" s="7"/>
       <c r="D179" s="7"/>
@@ -8952,10 +8979,10 @@
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B180" s="11" t="s">
         <v>454</v>
-      </c>
-      <c r="B180" s="11" t="s">
-        <v>455</v>
       </c>
       <c r="C180" s="7"/>
       <c r="D180" s="7"/>
@@ -8984,10 +9011,10 @@
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="B181" s="11" t="s">
         <v>456</v>
-      </c>
-      <c r="B181" s="11" t="s">
-        <v>457</v>
       </c>
       <c r="C181" s="7"/>
       <c r="D181" s="7"/>
@@ -9016,10 +9043,10 @@
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="B182" s="11" t="s">
         <v>458</v>
-      </c>
-      <c r="B182" s="11" t="s">
-        <v>459</v>
       </c>
       <c r="C182" s="7"/>
       <c r="D182" s="7"/>
@@ -9047,11 +9074,11 @@
       <c r="Z182" s="7"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="11" t="s">
+      <c r="A183" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="B183" s="16" t="s">
         <v>460</v>
-      </c>
-      <c r="B183" s="11" t="s">
-        <v>461</v>
       </c>
       <c r="C183" s="7"/>
       <c r="D183" s="7"/>
@@ -9079,11 +9106,11 @@
       <c r="Z183" s="7"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="11" t="s">
+      <c r="A184" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="B184" s="11" t="s">
         <v>462</v>
-      </c>
-      <c r="B184" s="11" t="s">
-        <v>463</v>
       </c>
       <c r="C184" s="7"/>
       <c r="D184" s="7"/>
@@ -9112,10 +9139,10 @@
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="B185" s="11" t="s">
         <v>464</v>
-      </c>
-      <c r="B185" s="11" t="s">
-        <v>465</v>
       </c>
       <c r="C185" s="7"/>
       <c r="D185" s="7"/>
@@ -9143,11 +9170,11 @@
       <c r="Z185" s="7"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="16" t="s">
+      <c r="A186" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="B186" s="11" t="s">
         <v>466</v>
-      </c>
-      <c r="B186" s="16" t="s">
-        <v>467</v>
       </c>
       <c r="C186" s="7"/>
       <c r="D186" s="7"/>
@@ -9175,11 +9202,11 @@
       <c r="Z186" s="7"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="8" t="s">
+      <c r="A187" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B187" s="11" t="s">
         <v>468</v>
-      </c>
-      <c r="B187" s="8" t="s">
-        <v>469</v>
       </c>
       <c r="C187" s="7"/>
       <c r="D187" s="7"/>
@@ -9207,11 +9234,11 @@
       <c r="Z187" s="7"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="8" t="s">
+      <c r="A188" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="B188" s="11" t="s">
         <v>470</v>
-      </c>
-      <c r="B188" s="8" t="s">
-        <v>471</v>
       </c>
       <c r="C188" s="7"/>
       <c r="D188" s="7"/>
@@ -9239,11 +9266,11 @@
       <c r="Z188" s="7"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="16" t="s">
+      <c r="A189" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="B189" s="11" t="s">
         <v>472</v>
-      </c>
-      <c r="B189" s="16" t="s">
-        <v>473</v>
       </c>
       <c r="C189" s="7"/>
       <c r="D189" s="7"/>
@@ -9272,10 +9299,10 @@
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="16" t="s">
+        <v>473</v>
+      </c>
+      <c r="B190" s="16" t="s">
         <v>474</v>
-      </c>
-      <c r="B190" s="16" t="s">
-        <v>475</v>
       </c>
       <c r="C190" s="7"/>
       <c r="D190" s="7"/>
@@ -9304,10 +9331,10 @@
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="B191" s="8" t="s">
         <v>476</v>
-      </c>
-      <c r="B191" s="8" t="s">
-        <v>477</v>
       </c>
       <c r="C191" s="7"/>
       <c r="D191" s="7"/>
@@ -9336,10 +9363,10 @@
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="B192" s="8" t="s">
         <v>478</v>
-      </c>
-      <c r="B192" s="8" t="s">
-        <v>479</v>
       </c>
       <c r="C192" s="7"/>
       <c r="D192" s="7"/>
@@ -9367,11 +9394,11 @@
       <c r="Z192" s="7"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="11" t="s">
+      <c r="A193" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="B193" s="16" t="s">
         <v>480</v>
-      </c>
-      <c r="B193" s="8" t="s">
-        <v>481</v>
       </c>
       <c r="C193" s="7"/>
       <c r="D193" s="7"/>
@@ -9399,11 +9426,11 @@
       <c r="Z193" s="7"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="8" t="s">
+      <c r="A194" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="B194" s="16" t="s">
         <v>482</v>
-      </c>
-      <c r="B194" s="11" t="s">
-        <v>483</v>
       </c>
       <c r="C194" s="7"/>
       <c r="D194" s="7"/>
@@ -9432,10 +9459,10 @@
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="B195" s="8" t="s">
         <v>484</v>
-      </c>
-      <c r="B195" s="11" t="s">
-        <v>485</v>
       </c>
       <c r="C195" s="7"/>
       <c r="D195" s="7"/>
@@ -9464,10 +9491,10 @@
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="B196" s="8" t="s">
         <v>486</v>
-      </c>
-      <c r="B196" s="8" t="s">
-        <v>487</v>
       </c>
       <c r="C196" s="7"/>
       <c r="D196" s="7"/>
@@ -9495,11 +9522,11 @@
       <c r="Z196" s="7"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="8" t="s">
+      <c r="A197" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="B197" s="8" t="s">
         <v>488</v>
-      </c>
-      <c r="B197" s="11" t="s">
-        <v>489</v>
       </c>
       <c r="C197" s="7"/>
       <c r="D197" s="7"/>
@@ -9528,10 +9555,10 @@
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="B198" s="11" t="s">
         <v>490</v>
-      </c>
-      <c r="B198" s="8" t="s">
-        <v>491</v>
       </c>
       <c r="C198" s="7"/>
       <c r="D198" s="7"/>
@@ -9559,11 +9586,11 @@
       <c r="Z198" s="7"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="16" t="s">
+      <c r="A199" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="B199" s="11" t="s">
         <v>492</v>
-      </c>
-      <c r="B199" s="16" t="s">
-        <v>493</v>
       </c>
       <c r="C199" s="7"/>
       <c r="D199" s="7"/>
@@ -9591,11 +9618,11 @@
       <c r="Z199" s="7"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="11" t="s">
+      <c r="A200" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="B200" s="8" t="s">
         <v>494</v>
-      </c>
-      <c r="B200" s="8" t="s">
-        <v>495</v>
       </c>
       <c r="C200" s="7"/>
       <c r="D200" s="7"/>
@@ -9624,10 +9651,10 @@
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="B201" s="11" t="s">
         <v>496</v>
-      </c>
-      <c r="B201" s="11" t="s">
-        <v>497</v>
       </c>
       <c r="C201" s="7"/>
       <c r="D201" s="7"/>
@@ -9655,11 +9682,11 @@
       <c r="Z201" s="7"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="20" t="s">
+      <c r="A202" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="B202" s="8" t="s">
         <v>498</v>
-      </c>
-      <c r="B202" s="21" t="s">
-        <v>499</v>
       </c>
       <c r="C202" s="7"/>
       <c r="D202" s="7"/>
@@ -9687,11 +9714,11 @@
       <c r="Z202" s="7"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="8" t="s">
+      <c r="A203" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="B203" s="16" t="s">
         <v>500</v>
-      </c>
-      <c r="B203" s="8" t="s">
-        <v>501</v>
       </c>
       <c r="C203" s="7"/>
       <c r="D203" s="7"/>
@@ -9719,11 +9746,11 @@
       <c r="Z203" s="7"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="8" t="s">
+      <c r="A204" s="11" t="s">
+        <v>501</v>
+      </c>
+      <c r="B204" s="8" t="s">
         <v>502</v>
-      </c>
-      <c r="B204" s="11" t="s">
-        <v>503</v>
       </c>
       <c r="C204" s="7"/>
       <c r="D204" s="7"/>
@@ -9752,10 +9779,10 @@
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="B205" s="11" t="s">
         <v>504</v>
-      </c>
-      <c r="B205" s="8" t="s">
-        <v>505</v>
       </c>
       <c r="C205" s="7"/>
       <c r="D205" s="7"/>
@@ -9783,11 +9810,11 @@
       <c r="Z205" s="7"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="16" t="s">
+      <c r="A206" s="20" t="s">
+        <v>505</v>
+      </c>
+      <c r="B206" s="21" t="s">
         <v>506</v>
-      </c>
-      <c r="B206" s="16" t="s">
-        <v>507</v>
       </c>
       <c r="C206" s="7"/>
       <c r="D206" s="7"/>
@@ -9816,10 +9843,10 @@
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="B207" s="8" t="s">
         <v>508</v>
-      </c>
-      <c r="B207" s="8" t="s">
-        <v>509</v>
       </c>
       <c r="C207" s="7"/>
       <c r="D207" s="7"/>
@@ -9847,11 +9874,11 @@
       <c r="Z207" s="7"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="16" t="s">
+      <c r="A208" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="B208" s="11" t="s">
         <v>510</v>
-      </c>
-      <c r="B208" s="16" t="s">
-        <v>511</v>
       </c>
       <c r="C208" s="7"/>
       <c r="D208" s="7"/>
@@ -9880,10 +9907,10 @@
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B209" s="8" t="s">
         <v>512</v>
-      </c>
-      <c r="B209" s="8" t="s">
-        <v>513</v>
       </c>
       <c r="C209" s="7"/>
       <c r="D209" s="7"/>
@@ -9911,11 +9938,11 @@
       <c r="Z209" s="7"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="8" t="s">
+      <c r="A210" s="16" t="s">
+        <v>513</v>
+      </c>
+      <c r="B210" s="16" t="s">
         <v>514</v>
-      </c>
-      <c r="B210" s="8" t="s">
-        <v>515</v>
       </c>
       <c r="C210" s="7"/>
       <c r="D210" s="7"/>
@@ -9944,10 +9971,10 @@
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="B211" s="8" t="s">
         <v>516</v>
-      </c>
-      <c r="B211" s="11" t="s">
-        <v>517</v>
       </c>
       <c r="C211" s="7"/>
       <c r="D211" s="7"/>
@@ -9975,11 +10002,11 @@
       <c r="Z211" s="7"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="11" t="s">
+      <c r="A212" s="16" t="s">
+        <v>517</v>
+      </c>
+      <c r="B212" s="16" t="s">
         <v>518</v>
-      </c>
-      <c r="B212" s="11" t="s">
-        <v>519</v>
       </c>
       <c r="C212" s="7"/>
       <c r="D212" s="7"/>
@@ -10008,10 +10035,10 @@
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="B213" s="8" t="s">
         <v>520</v>
-      </c>
-      <c r="B213" s="11" t="s">
-        <v>521</v>
       </c>
       <c r="C213" s="7"/>
       <c r="D213" s="7"/>
@@ -10039,11 +10066,11 @@
       <c r="Z213" s="7"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="16" t="s">
+      <c r="A214" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="B214" s="8" t="s">
         <v>522</v>
-      </c>
-      <c r="B214" s="16" t="s">
-        <v>523</v>
       </c>
       <c r="C214" s="7"/>
       <c r="D214" s="7"/>
@@ -10072,10 +10099,10 @@
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="B215" s="11" t="s">
         <v>524</v>
-      </c>
-      <c r="B215" s="11" t="s">
-        <v>525</v>
       </c>
       <c r="C215" s="7"/>
       <c r="D215" s="7"/>
@@ -10103,11 +10130,11 @@
       <c r="Z215" s="7"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="A216" s="16" t="s">
+      <c r="A216" s="11" t="s">
+        <v>525</v>
+      </c>
+      <c r="B216" s="11" t="s">
         <v>526</v>
-      </c>
-      <c r="B216" s="16" t="s">
-        <v>527</v>
       </c>
       <c r="C216" s="7"/>
       <c r="D216" s="7"/>
@@ -10136,10 +10163,10 @@
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="B217" s="11" t="s">
         <v>528</v>
-      </c>
-      <c r="B217" s="8" t="s">
-        <v>529</v>
       </c>
       <c r="C217" s="7"/>
       <c r="D217" s="7"/>
@@ -10167,11 +10194,11 @@
       <c r="Z217" s="7"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="8" t="s">
+      <c r="A218" s="16" t="s">
+        <v>529</v>
+      </c>
+      <c r="B218" s="16" t="s">
         <v>530</v>
-      </c>
-      <c r="B218" s="11" t="s">
-        <v>531</v>
       </c>
       <c r="C218" s="7"/>
       <c r="D218" s="7"/>
@@ -10200,10 +10227,10 @@
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="B219" s="11" t="s">
         <v>532</v>
-      </c>
-      <c r="B219" s="8" t="s">
-        <v>533</v>
       </c>
       <c r="C219" s="7"/>
       <c r="D219" s="7"/>
@@ -10231,11 +10258,11 @@
       <c r="Z219" s="7"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="11" t="s">
+      <c r="A220" s="16" t="s">
+        <v>533</v>
+      </c>
+      <c r="B220" s="16" t="s">
         <v>534</v>
-      </c>
-      <c r="B220" s="11" t="s">
-        <v>535</v>
       </c>
       <c r="C220" s="7"/>
       <c r="D220" s="7"/>
@@ -10264,10 +10291,10 @@
     </row>
     <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="B221" s="8" t="s">
         <v>536</v>
-      </c>
-      <c r="B221" s="8" t="s">
-        <v>537</v>
       </c>
       <c r="C221" s="7"/>
       <c r="D221" s="7"/>
@@ -10296,10 +10323,10 @@
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="B222" s="11" t="s">
         <v>538</v>
-      </c>
-      <c r="B222" s="8" t="s">
-        <v>539</v>
       </c>
       <c r="C222" s="7"/>
       <c r="D222" s="7"/>
@@ -10327,11 +10354,11 @@
       <c r="Z222" s="7"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="16" t="s">
+      <c r="A223" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="B223" s="8" t="s">
         <v>540</v>
-      </c>
-      <c r="B223" s="16" t="s">
-        <v>541</v>
       </c>
       <c r="C223" s="7"/>
       <c r="D223" s="7"/>
@@ -10359,11 +10386,11 @@
       <c r="Z223" s="7"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="8" t="s">
+      <c r="A224" s="11" t="s">
+        <v>541</v>
+      </c>
+      <c r="B224" s="11" t="s">
         <v>542</v>
-      </c>
-      <c r="B224" s="11" t="s">
-        <v>543</v>
       </c>
       <c r="C224" s="7"/>
       <c r="D224" s="7"/>
@@ -10392,10 +10419,10 @@
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="B225" s="8" t="s">
         <v>544</v>
-      </c>
-      <c r="B225" s="8" t="s">
-        <v>545</v>
       </c>
       <c r="C225" s="7"/>
       <c r="D225" s="7"/>
@@ -10424,10 +10451,10 @@
     </row>
     <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="B226" s="8" t="s">
         <v>546</v>
-      </c>
-      <c r="B226" s="8" t="s">
-        <v>547</v>
       </c>
       <c r="C226" s="7"/>
       <c r="D226" s="7"/>
@@ -10455,11 +10482,11 @@
       <c r="Z226" s="7"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="11" t="s">
+      <c r="A227" s="16" t="s">
+        <v>547</v>
+      </c>
+      <c r="B227" s="16" t="s">
         <v>548</v>
-      </c>
-      <c r="B227" s="8" t="s">
-        <v>549</v>
       </c>
       <c r="C227" s="7"/>
       <c r="D227" s="7"/>
@@ -10488,10 +10515,10 @@
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="B228" s="11" t="s">
         <v>550</v>
-      </c>
-      <c r="B228" s="8" t="s">
-        <v>551</v>
       </c>
       <c r="C228" s="7"/>
       <c r="D228" s="7"/>
@@ -10520,10 +10547,10 @@
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="B229" s="8" t="s">
         <v>552</v>
-      </c>
-      <c r="B229" s="8" t="s">
-        <v>553</v>
       </c>
       <c r="C229" s="7"/>
       <c r="D229" s="7"/>
@@ -10552,10 +10579,10 @@
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="B230" s="8" t="s">
         <v>554</v>
-      </c>
-      <c r="B230" s="11" t="s">
-        <v>555</v>
       </c>
       <c r="C230" s="7"/>
       <c r="D230" s="7"/>
@@ -10583,11 +10610,11 @@
       <c r="Z230" s="7"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="8" t="s">
+      <c r="A231" s="11" t="s">
+        <v>555</v>
+      </c>
+      <c r="B231" s="8" t="s">
         <v>556</v>
-      </c>
-      <c r="B231" s="11" t="s">
-        <v>557</v>
       </c>
       <c r="C231" s="7"/>
       <c r="D231" s="7"/>
@@ -10616,10 +10643,10 @@
     </row>
     <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="B232" s="8" t="s">
         <v>558</v>
-      </c>
-      <c r="B232" s="11" t="s">
-        <v>559</v>
       </c>
       <c r="C232" s="7"/>
       <c r="D232" s="7"/>
@@ -10647,11 +10674,11 @@
       <c r="Z232" s="7"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="A233" s="11" t="s">
+      <c r="A233" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="B233" s="8" t="s">
         <v>560</v>
-      </c>
-      <c r="B233" s="11" t="s">
-        <v>561</v>
       </c>
       <c r="C233" s="7"/>
       <c r="D233" s="7"/>
@@ -10680,10 +10707,10 @@
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="B234" s="11" t="s">
         <v>562</v>
-      </c>
-      <c r="B234" s="11" t="s">
-        <v>563</v>
       </c>
       <c r="C234" s="7"/>
       <c r="D234" s="7"/>
@@ -10712,10 +10739,10 @@
     </row>
     <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="8" t="s">
+        <v>563</v>
+      </c>
+      <c r="B235" s="11" t="s">
         <v>564</v>
-      </c>
-      <c r="B235" s="8" t="s">
-        <v>565</v>
       </c>
       <c r="C235" s="7"/>
       <c r="D235" s="7"/>
@@ -10744,10 +10771,10 @@
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="8" t="s">
+        <v>565</v>
+      </c>
+      <c r="B236" s="11" t="s">
         <v>566</v>
-      </c>
-      <c r="B236" s="11" t="s">
-        <v>567</v>
       </c>
       <c r="C236" s="7"/>
       <c r="D236" s="7"/>
@@ -10775,11 +10802,11 @@
       <c r="Z236" s="7"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="A237" s="8" t="s">
+      <c r="A237" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="B237" s="11" t="s">
         <v>568</v>
-      </c>
-      <c r="B237" s="11" t="s">
-        <v>569</v>
       </c>
       <c r="C237" s="7"/>
       <c r="D237" s="7"/>
@@ -10808,10 +10835,10 @@
     </row>
     <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="B238" s="11" t="s">
         <v>570</v>
-      </c>
-      <c r="B238" s="11" t="s">
-        <v>571</v>
       </c>
       <c r="C238" s="7"/>
       <c r="D238" s="7"/>
@@ -10839,11 +10866,11 @@
       <c r="Z238" s="7"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="11" t="s">
+      <c r="A239" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="B239" s="8" t="s">
         <v>572</v>
-      </c>
-      <c r="B239" s="11" t="s">
-        <v>573</v>
       </c>
       <c r="C239" s="7"/>
       <c r="D239" s="7"/>
@@ -10872,10 +10899,10 @@
     </row>
     <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="B240" s="11" t="s">
         <v>574</v>
-      </c>
-      <c r="B240" s="11" t="s">
-        <v>575</v>
       </c>
       <c r="C240" s="7"/>
       <c r="D240" s="7"/>
@@ -10904,10 +10931,10 @@
     </row>
     <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="B241" s="11" t="s">
         <v>576</v>
-      </c>
-      <c r="B241" s="11" t="s">
-        <v>577</v>
       </c>
       <c r="C241" s="7"/>
       <c r="D241" s="7"/>
@@ -10936,10 +10963,10 @@
     </row>
     <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="B242" s="11" t="s">
         <v>578</v>
-      </c>
-      <c r="B242" s="8" t="s">
-        <v>579</v>
       </c>
       <c r="C242" s="7"/>
       <c r="D242" s="7"/>
@@ -10967,11 +10994,11 @@
       <c r="Z242" s="7"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="A243" s="8" t="s">
+      <c r="A243" s="11" t="s">
+        <v>579</v>
+      </c>
+      <c r="B243" s="11" t="s">
         <v>580</v>
-      </c>
-      <c r="B243" s="11" t="s">
-        <v>581</v>
       </c>
       <c r="C243" s="7"/>
       <c r="D243" s="7"/>
@@ -10999,11 +11026,11 @@
       <c r="Z243" s="7"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="16" t="s">
+      <c r="A244" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="B244" s="11" t="s">
         <v>582</v>
-      </c>
-      <c r="B244" s="16" t="s">
-        <v>583</v>
       </c>
       <c r="C244" s="7"/>
       <c r="D244" s="7"/>
@@ -11032,10 +11059,10 @@
     </row>
     <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="B245" s="11" t="s">
         <v>584</v>
-      </c>
-      <c r="B245" s="8" t="s">
-        <v>585</v>
       </c>
       <c r="C245" s="7"/>
       <c r="D245" s="7"/>
@@ -11064,10 +11091,10 @@
     </row>
     <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="B246" s="8" t="s">
         <v>586</v>
-      </c>
-      <c r="B246" s="8" t="s">
-        <v>587</v>
       </c>
       <c r="C246" s="7"/>
       <c r="D246" s="7"/>
@@ -11096,10 +11123,10 @@
     </row>
     <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="B247" s="11" t="s">
         <v>588</v>
-      </c>
-      <c r="B247" s="8" t="s">
-        <v>589</v>
       </c>
       <c r="C247" s="7"/>
       <c r="D247" s="7"/>
@@ -11128,10 +11155,10 @@
     </row>
     <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="16" t="s">
+        <v>589</v>
+      </c>
+      <c r="B248" s="16" t="s">
         <v>590</v>
-      </c>
-      <c r="B248" s="16" t="s">
-        <v>591</v>
       </c>
       <c r="C248" s="7"/>
       <c r="D248" s="7"/>
@@ -11160,10 +11187,10 @@
     </row>
     <row r="249" ht="15.75" customHeight="1">
       <c r="A249" s="8" t="s">
+        <v>591</v>
+      </c>
+      <c r="B249" s="8" t="s">
         <v>592</v>
-      </c>
-      <c r="B249" s="8" t="s">
-        <v>593</v>
       </c>
       <c r="C249" s="7"/>
       <c r="D249" s="7"/>
@@ -11191,11 +11218,11 @@
       <c r="Z249" s="7"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="A250" s="16" t="s">
+      <c r="A250" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="B250" s="8" t="s">
         <v>594</v>
-      </c>
-      <c r="B250" s="16" t="s">
-        <v>595</v>
       </c>
       <c r="C250" s="7"/>
       <c r="D250" s="7"/>
@@ -11223,11 +11250,11 @@
       <c r="Z250" s="7"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="A251" s="16" t="s">
+      <c r="A251" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="B251" s="8" t="s">
         <v>596</v>
-      </c>
-      <c r="B251" s="16" t="s">
-        <v>597</v>
       </c>
       <c r="C251" s="7"/>
       <c r="D251" s="7"/>
@@ -11255,11 +11282,11 @@
       <c r="Z251" s="7"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="A252" s="8" t="s">
+      <c r="A252" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="B252" s="16" t="s">
         <v>598</v>
-      </c>
-      <c r="B252" s="11" t="s">
-        <v>599</v>
       </c>
       <c r="C252" s="7"/>
       <c r="D252" s="7"/>
@@ -11288,10 +11315,10 @@
     </row>
     <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="B253" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="B253" s="11" t="s">
-        <v>601</v>
       </c>
       <c r="C253" s="7"/>
       <c r="D253" s="7"/>
@@ -11319,11 +11346,11 @@
       <c r="Z253" s="7"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="8" t="s">
+      <c r="A254" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="B254" s="16" t="s">
         <v>602</v>
-      </c>
-      <c r="B254" s="8" t="s">
-        <v>603</v>
       </c>
       <c r="C254" s="7"/>
       <c r="D254" s="7"/>
@@ -11351,11 +11378,11 @@
       <c r="Z254" s="7"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="20" t="s">
+      <c r="A255" s="16" t="s">
+        <v>603</v>
+      </c>
+      <c r="B255" s="16" t="s">
         <v>604</v>
-      </c>
-      <c r="B255" s="21" t="s">
-        <v>605</v>
       </c>
       <c r="C255" s="7"/>
       <c r="D255" s="7"/>
@@ -11383,11 +11410,11 @@
       <c r="Z255" s="7"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="8" t="s">
+      <c r="A256" s="16" t="s">
+        <v>605</v>
+      </c>
+      <c r="B256" s="16" t="s">
         <v>606</v>
-      </c>
-      <c r="B256" s="11" t="s">
-        <v>607</v>
       </c>
       <c r="C256" s="7"/>
       <c r="D256" s="7"/>
@@ -11416,10 +11443,10 @@
     </row>
     <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="B257" s="11" t="s">
         <v>608</v>
-      </c>
-      <c r="B257" s="11" t="s">
-        <v>609</v>
       </c>
       <c r="C257" s="7"/>
       <c r="D257" s="7"/>
@@ -11448,10 +11475,10 @@
     </row>
     <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="B258" s="11" t="s">
         <v>610</v>
-      </c>
-      <c r="B258" s="11" t="s">
-        <v>611</v>
       </c>
       <c r="C258" s="7"/>
       <c r="D258" s="7"/>
@@ -11480,10 +11507,10 @@
     </row>
     <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="B259" s="8" t="s">
         <v>612</v>
-      </c>
-      <c r="B259" s="8" t="s">
-        <v>613</v>
       </c>
       <c r="C259" s="7"/>
       <c r="D259" s="7"/>
@@ -11511,11 +11538,11 @@
       <c r="Z259" s="7"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="16" t="s">
+      <c r="A260" s="20" t="s">
+        <v>613</v>
+      </c>
+      <c r="B260" s="21" t="s">
         <v>614</v>
-      </c>
-      <c r="B260" s="16" t="s">
-        <v>615</v>
       </c>
       <c r="C260" s="7"/>
       <c r="D260" s="7"/>
@@ -11543,11 +11570,11 @@
       <c r="Z260" s="7"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="A261" s="16" t="s">
+      <c r="A261" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="B261" s="11" t="s">
         <v>616</v>
-      </c>
-      <c r="B261" s="16" t="s">
-        <v>617</v>
       </c>
       <c r="C261" s="7"/>
       <c r="D261" s="7"/>
@@ -11576,10 +11603,10 @@
     </row>
     <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="B262" s="11" t="s">
         <v>618</v>
-      </c>
-      <c r="B262" s="11" t="s">
-        <v>619</v>
       </c>
       <c r="C262" s="7"/>
       <c r="D262" s="7"/>
@@ -11608,10 +11635,10 @@
     </row>
     <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="B263" s="11" t="s">
         <v>620</v>
-      </c>
-      <c r="B263" s="11" t="s">
-        <v>621</v>
       </c>
       <c r="C263" s="7"/>
       <c r="D263" s="7"/>
@@ -11639,11 +11666,11 @@
       <c r="Z263" s="7"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="A264" s="16" t="s">
+      <c r="A264" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="B264" s="8" t="s">
         <v>622</v>
-      </c>
-      <c r="B264" s="16" t="s">
-        <v>623</v>
       </c>
       <c r="C264" s="7"/>
       <c r="D264" s="7"/>
@@ -11671,11 +11698,11 @@
       <c r="Z264" s="7"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="A265" s="8" t="s">
+      <c r="A265" s="16" t="s">
+        <v>623</v>
+      </c>
+      <c r="B265" s="16" t="s">
         <v>624</v>
-      </c>
-      <c r="B265" s="8" t="s">
-        <v>625</v>
       </c>
       <c r="C265" s="7"/>
       <c r="D265" s="7"/>
@@ -11704,10 +11731,10 @@
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="16" t="s">
+        <v>625</v>
+      </c>
+      <c r="B266" s="16" t="s">
         <v>626</v>
-      </c>
-      <c r="B266" s="16" t="s">
-        <v>627</v>
       </c>
       <c r="C266" s="7"/>
       <c r="D266" s="7"/>
@@ -11736,10 +11763,10 @@
     </row>
     <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="B267" s="11" t="s">
         <v>628</v>
-      </c>
-      <c r="B267" s="8" t="s">
-        <v>629</v>
       </c>
       <c r="C267" s="7"/>
       <c r="D267" s="7"/>
@@ -11768,10 +11795,10 @@
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="B268" s="11" t="s">
         <v>630</v>
-      </c>
-      <c r="B268" s="8" t="s">
-        <v>631</v>
       </c>
       <c r="C268" s="7"/>
       <c r="D268" s="7"/>
@@ -11800,10 +11827,10 @@
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="16" t="s">
+        <v>631</v>
+      </c>
+      <c r="B269" s="16" t="s">
         <v>632</v>
-      </c>
-      <c r="B269" s="16" t="s">
-        <v>633</v>
       </c>
       <c r="C269" s="7"/>
       <c r="D269" s="7"/>
@@ -11831,11 +11858,11 @@
       <c r="Z269" s="7"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
-      <c r="A270" s="16" t="s">
+      <c r="A270" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="B270" s="8" t="s">
         <v>634</v>
-      </c>
-      <c r="B270" s="16" t="s">
-        <v>635</v>
       </c>
       <c r="C270" s="7"/>
       <c r="D270" s="7"/>
@@ -11863,11 +11890,11 @@
       <c r="Z270" s="7"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
-      <c r="A271" s="8" t="s">
+      <c r="A271" s="16" t="s">
+        <v>635</v>
+      </c>
+      <c r="B271" s="16" t="s">
         <v>636</v>
-      </c>
-      <c r="B271" s="8" t="s">
-        <v>637</v>
       </c>
       <c r="C271" s="7"/>
       <c r="D271" s="7"/>
@@ -11895,11 +11922,11 @@
       <c r="Z271" s="7"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
-      <c r="A272" s="16" t="s">
+      <c r="A272" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="B272" s="8" t="s">
         <v>638</v>
-      </c>
-      <c r="B272" s="16" t="s">
-        <v>639</v>
       </c>
       <c r="C272" s="7"/>
       <c r="D272" s="7"/>
@@ -11928,10 +11955,10 @@
     </row>
     <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="B273" s="8" t="s">
         <v>640</v>
-      </c>
-      <c r="B273" s="11" t="s">
-        <v>641</v>
       </c>
       <c r="C273" s="7"/>
       <c r="D273" s="7"/>
@@ -11960,10 +11987,10 @@
     </row>
     <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="16" t="s">
+        <v>641</v>
+      </c>
+      <c r="B274" s="16" t="s">
         <v>642</v>
-      </c>
-      <c r="B274" s="11" t="s">
-        <v>643</v>
       </c>
       <c r="C274" s="7"/>
       <c r="D274" s="7"/>
@@ -11991,11 +12018,11 @@
       <c r="Z274" s="7"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
-      <c r="A275" s="8" t="s">
+      <c r="A275" s="16" t="s">
+        <v>643</v>
+      </c>
+      <c r="B275" s="16" t="s">
         <v>644</v>
-      </c>
-      <c r="B275" s="11" t="s">
-        <v>645</v>
       </c>
       <c r="C275" s="7"/>
       <c r="D275" s="7"/>
@@ -12023,11 +12050,11 @@
       <c r="Z275" s="7"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="A276" s="16" t="s">
+      <c r="A276" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="B276" s="8" t="s">
         <v>646</v>
-      </c>
-      <c r="B276" s="16" t="s">
-        <v>647</v>
       </c>
       <c r="C276" s="7"/>
       <c r="D276" s="7"/>
@@ -12055,11 +12082,11 @@
       <c r="Z276" s="7"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
-      <c r="A277" s="8" t="s">
+      <c r="A277" s="16" t="s">
+        <v>647</v>
+      </c>
+      <c r="B277" s="16" t="s">
         <v>648</v>
-      </c>
-      <c r="B277" s="11" t="s">
-        <v>649</v>
       </c>
       <c r="C277" s="7"/>
       <c r="D277" s="7"/>
@@ -12088,10 +12115,10 @@
     </row>
     <row r="278" ht="15.75" customHeight="1">
       <c r="A278" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="B278" s="11" t="s">
         <v>650</v>
-      </c>
-      <c r="B278" s="11" t="s">
-        <v>651</v>
       </c>
       <c r="C278" s="7"/>
       <c r="D278" s="7"/>
@@ -12119,11 +12146,11 @@
       <c r="Z278" s="7"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="A279" s="8" t="s">
+      <c r="A279" s="16" t="s">
+        <v>651</v>
+      </c>
+      <c r="B279" s="11" t="s">
         <v>652</v>
-      </c>
-      <c r="B279" s="8" t="s">
-        <v>653</v>
       </c>
       <c r="C279" s="7"/>
       <c r="D279" s="7"/>
@@ -12151,11 +12178,11 @@
       <c r="Z279" s="7"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
-      <c r="A280" s="16" t="s">
+      <c r="A280" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="B280" s="11" t="s">
         <v>654</v>
-      </c>
-      <c r="B280" s="16" t="s">
-        <v>655</v>
       </c>
       <c r="C280" s="7"/>
       <c r="D280" s="7"/>
@@ -12183,11 +12210,11 @@
       <c r="Z280" s="7"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
-      <c r="A281" s="8" t="s">
+      <c r="A281" s="16" t="s">
+        <v>655</v>
+      </c>
+      <c r="B281" s="16" t="s">
         <v>656</v>
-      </c>
-      <c r="B281" s="8" t="s">
-        <v>657</v>
       </c>
       <c r="C281" s="7"/>
       <c r="D281" s="7"/>
@@ -12215,11 +12242,11 @@
       <c r="Z281" s="7"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="A282" s="16" t="s">
+      <c r="A282" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="B282" s="11" t="s">
         <v>658</v>
-      </c>
-      <c r="B282" s="16" t="s">
-        <v>659</v>
       </c>
       <c r="C282" s="7"/>
       <c r="D282" s="7"/>
@@ -12248,10 +12275,10 @@
     </row>
     <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="B283" s="11" t="s">
         <v>660</v>
-      </c>
-      <c r="B283" s="11" t="s">
-        <v>661</v>
       </c>
       <c r="C283" s="7"/>
       <c r="D283" s="7"/>
@@ -12280,10 +12307,10 @@
     </row>
     <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="B284" s="8" t="s">
         <v>662</v>
-      </c>
-      <c r="B284" s="11" t="s">
-        <v>663</v>
       </c>
       <c r="C284" s="7"/>
       <c r="D284" s="7"/>
@@ -12311,11 +12338,11 @@
       <c r="Z284" s="7"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="A285" s="8" t="s">
+      <c r="A285" s="16" t="s">
+        <v>663</v>
+      </c>
+      <c r="B285" s="16" t="s">
         <v>664</v>
-      </c>
-      <c r="B285" s="8" t="s">
-        <v>665</v>
       </c>
       <c r="C285" s="7"/>
       <c r="D285" s="7"/>
@@ -12344,10 +12371,10 @@
     </row>
     <row r="286" ht="15.75" customHeight="1">
       <c r="A286" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="B286" s="8" t="s">
         <v>666</v>
-      </c>
-      <c r="B286" s="11" t="s">
-        <v>667</v>
       </c>
       <c r="C286" s="7"/>
       <c r="D286" s="7"/>
@@ -12375,11 +12402,11 @@
       <c r="Z286" s="7"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="A287" s="8" t="s">
+      <c r="A287" s="16" t="s">
+        <v>667</v>
+      </c>
+      <c r="B287" s="16" t="s">
         <v>668</v>
-      </c>
-      <c r="B287" s="11" t="s">
-        <v>669</v>
       </c>
       <c r="C287" s="7"/>
       <c r="D287" s="7"/>
@@ -12408,10 +12435,10 @@
     </row>
     <row r="288" ht="15.75" customHeight="1">
       <c r="A288" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="B288" s="11" t="s">
         <v>670</v>
-      </c>
-      <c r="B288" s="11" t="s">
-        <v>671</v>
       </c>
       <c r="C288" s="7"/>
       <c r="D288" s="7"/>
@@ -12440,10 +12467,10 @@
     </row>
     <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="B289" s="11" t="s">
         <v>672</v>
-      </c>
-      <c r="B289" s="11" t="s">
-        <v>673</v>
       </c>
       <c r="C289" s="7"/>
       <c r="D289" s="7"/>
@@ -12472,10 +12499,10 @@
     </row>
     <row r="290" ht="15.75" customHeight="1">
       <c r="A290" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="B290" s="8" t="s">
         <v>674</v>
-      </c>
-      <c r="B290" s="8" t="s">
-        <v>675</v>
       </c>
       <c r="C290" s="7"/>
       <c r="D290" s="7"/>
@@ -12503,11 +12530,11 @@
       <c r="Z290" s="7"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
-      <c r="A291" s="20" t="s">
+      <c r="A291" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="B291" s="11" t="s">
         <v>676</v>
-      </c>
-      <c r="B291" s="20" t="s">
-        <v>677</v>
       </c>
       <c r="C291" s="7"/>
       <c r="D291" s="7"/>
@@ -12536,10 +12563,10 @@
     </row>
     <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="B292" s="11" t="s">
         <v>678</v>
-      </c>
-      <c r="B292" s="11" t="s">
-        <v>679</v>
       </c>
       <c r="C292" s="7"/>
       <c r="D292" s="7"/>
@@ -12568,10 +12595,10 @@
     </row>
     <row r="293" ht="15.75" customHeight="1">
       <c r="A293" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="B293" s="11" t="s">
         <v>680</v>
-      </c>
-      <c r="B293" s="11" t="s">
-        <v>681</v>
       </c>
       <c r="C293" s="7"/>
       <c r="D293" s="7"/>
@@ -12600,10 +12627,10 @@
     </row>
     <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="B294" s="11" t="s">
         <v>682</v>
-      </c>
-      <c r="B294" s="11" t="s">
-        <v>683</v>
       </c>
       <c r="C294" s="7"/>
       <c r="D294" s="7"/>
@@ -12631,11 +12658,11 @@
       <c r="Z294" s="7"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
-      <c r="A295" s="16" t="s">
+      <c r="A295" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="B295" s="8" t="s">
         <v>684</v>
-      </c>
-      <c r="B295" s="16" t="s">
-        <v>685</v>
       </c>
       <c r="C295" s="7"/>
       <c r="D295" s="7"/>
@@ -12663,11 +12690,11 @@
       <c r="Z295" s="7"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="A296" s="8" t="s">
+      <c r="A296" s="20" t="s">
+        <v>685</v>
+      </c>
+      <c r="B296" s="20" t="s">
         <v>686</v>
-      </c>
-      <c r="B296" s="11" t="s">
-        <v>687</v>
       </c>
       <c r="C296" s="7"/>
       <c r="D296" s="7"/>
@@ -12696,10 +12723,10 @@
     </row>
     <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="8" t="s">
+        <v>687</v>
+      </c>
+      <c r="B297" s="11" t="s">
         <v>688</v>
-      </c>
-      <c r="B297" s="8" t="s">
-        <v>689</v>
       </c>
       <c r="C297" s="7"/>
       <c r="D297" s="7"/>
@@ -12728,10 +12755,10 @@
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="B298" s="11" t="s">
         <v>690</v>
-      </c>
-      <c r="B298" s="11" t="s">
-        <v>691</v>
       </c>
       <c r="C298" s="7"/>
       <c r="D298" s="7"/>
@@ -12760,10 +12787,10 @@
     </row>
     <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="B299" s="11" t="s">
         <v>692</v>
-      </c>
-      <c r="B299" s="11" t="s">
-        <v>693</v>
       </c>
       <c r="C299" s="7"/>
       <c r="D299" s="7"/>
@@ -12791,11 +12818,11 @@
       <c r="Z299" s="7"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="A300" s="8" t="s">
+      <c r="A300" s="16" t="s">
+        <v>693</v>
+      </c>
+      <c r="B300" s="16" t="s">
         <v>694</v>
-      </c>
-      <c r="B300" s="11" t="s">
-        <v>695</v>
       </c>
       <c r="C300" s="7"/>
       <c r="D300" s="7"/>
@@ -12824,10 +12851,10 @@
     </row>
     <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="B301" s="11" t="s">
         <v>696</v>
-      </c>
-      <c r="B301" s="11" t="s">
-        <v>697</v>
       </c>
       <c r="C301" s="7"/>
       <c r="D301" s="7"/>
@@ -12856,10 +12883,10 @@
     </row>
     <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="B302" s="8" t="s">
         <v>698</v>
-      </c>
-      <c r="B302" s="11" t="s">
-        <v>699</v>
       </c>
       <c r="C302" s="7"/>
       <c r="D302" s="7"/>
@@ -12887,11 +12914,11 @@
       <c r="Z302" s="7"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="A303" s="20" t="s">
+      <c r="A303" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="B303" s="11" t="s">
         <v>700</v>
-      </c>
-      <c r="B303" s="21" t="s">
-        <v>701</v>
       </c>
       <c r="C303" s="7"/>
       <c r="D303" s="7"/>
@@ -12920,10 +12947,10 @@
     </row>
     <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="B304" s="11" t="s">
         <v>702</v>
-      </c>
-      <c r="B304" s="11" t="s">
-        <v>703</v>
       </c>
       <c r="C304" s="7"/>
       <c r="D304" s="7"/>
@@ -12951,11 +12978,11 @@
       <c r="Z304" s="7"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="A305" s="16" t="s">
+      <c r="A305" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="B305" s="11" t="s">
         <v>704</v>
-      </c>
-      <c r="B305" s="16" t="s">
-        <v>705</v>
       </c>
       <c r="C305" s="7"/>
       <c r="D305" s="7"/>
@@ -12983,11 +13010,11 @@
       <c r="Z305" s="7"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="A306" s="16" t="s">
+      <c r="A306" s="8" t="s">
+        <v>705</v>
+      </c>
+      <c r="B306" s="11" t="s">
         <v>706</v>
-      </c>
-      <c r="B306" s="16" t="s">
-        <v>707</v>
       </c>
       <c r="C306" s="7"/>
       <c r="D306" s="7"/>
@@ -13016,10 +13043,10 @@
     </row>
     <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="B307" s="11" t="s">
         <v>708</v>
-      </c>
-      <c r="B307" s="8" t="s">
-        <v>709</v>
       </c>
       <c r="C307" s="7"/>
       <c r="D307" s="7"/>
@@ -13047,11 +13074,11 @@
       <c r="Z307" s="7"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="A308" s="16" t="s">
+      <c r="A308" s="20" t="s">
+        <v>709</v>
+      </c>
+      <c r="B308" s="21" t="s">
         <v>710</v>
-      </c>
-      <c r="B308" s="16" t="s">
-        <v>711</v>
       </c>
       <c r="C308" s="7"/>
       <c r="D308" s="7"/>
@@ -13079,11 +13106,11 @@
       <c r="Z308" s="7"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="A309" s="23" t="s">
+      <c r="A309" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="B309" s="11" t="s">
         <v>712</v>
-      </c>
-      <c r="B309" s="24" t="s">
-        <v>713</v>
       </c>
       <c r="C309" s="7"/>
       <c r="D309" s="7"/>
@@ -13112,10 +13139,10 @@
     </row>
     <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="16" t="s">
+        <v>713</v>
+      </c>
+      <c r="B310" s="16" t="s">
         <v>714</v>
-      </c>
-      <c r="B310" s="16" t="s">
-        <v>715</v>
       </c>
       <c r="C310" s="7"/>
       <c r="D310" s="7"/>
@@ -13143,11 +13170,11 @@
       <c r="Z310" s="7"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="A311" s="8" t="s">
+      <c r="A311" s="16" t="s">
+        <v>715</v>
+      </c>
+      <c r="B311" s="16" t="s">
         <v>716</v>
-      </c>
-      <c r="B311" s="8" t="s">
-        <v>717</v>
       </c>
       <c r="C311" s="7"/>
       <c r="D311" s="7"/>
@@ -13176,10 +13203,10 @@
     </row>
     <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="8" t="s">
+        <v>717</v>
+      </c>
+      <c r="B312" s="8" t="s">
         <v>718</v>
-      </c>
-      <c r="B312" s="8" t="s">
-        <v>719</v>
       </c>
       <c r="C312" s="7"/>
       <c r="D312" s="7"/>
@@ -13207,11 +13234,11 @@
       <c r="Z312" s="7"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="A313" s="8" t="s">
+      <c r="A313" s="16" t="s">
+        <v>719</v>
+      </c>
+      <c r="B313" s="16" t="s">
         <v>720</v>
-      </c>
-      <c r="B313" s="8" t="s">
-        <v>721</v>
       </c>
       <c r="C313" s="7"/>
       <c r="D313" s="7"/>
@@ -13239,11 +13266,11 @@
       <c r="Z313" s="7"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="A314" s="8" t="s">
+      <c r="A314" s="23" t="s">
+        <v>721</v>
+      </c>
+      <c r="B314" s="24" t="s">
         <v>722</v>
-      </c>
-      <c r="B314" s="11" t="s">
-        <v>723</v>
       </c>
       <c r="C314" s="7"/>
       <c r="D314" s="7"/>
@@ -13271,11 +13298,11 @@
       <c r="Z314" s="7"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="A315" s="8" t="s">
+      <c r="A315" s="16" t="s">
+        <v>723</v>
+      </c>
+      <c r="B315" s="16" t="s">
         <v>724</v>
-      </c>
-      <c r="B315" s="8" t="s">
-        <v>725</v>
       </c>
       <c r="C315" s="7"/>
       <c r="D315" s="7"/>
@@ -13303,11 +13330,11 @@
       <c r="Z315" s="7"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="A316" s="16" t="s">
+      <c r="A316" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="B316" s="8" t="s">
         <v>726</v>
-      </c>
-      <c r="B316" s="16" t="s">
-        <v>727</v>
       </c>
       <c r="C316" s="7"/>
       <c r="D316" s="7"/>
@@ -13336,10 +13363,10 @@
     </row>
     <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="B317" s="8" t="s">
         <v>728</v>
-      </c>
-      <c r="B317" s="11" t="s">
-        <v>729</v>
       </c>
       <c r="C317" s="7"/>
       <c r="D317" s="7"/>
@@ -13368,10 +13395,10 @@
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="B318" s="8" t="s">
         <v>730</v>
-      </c>
-      <c r="B318" s="8" t="s">
-        <v>731</v>
       </c>
       <c r="C318" s="7"/>
       <c r="D318" s="7"/>
@@ -13400,10 +13427,10 @@
     </row>
     <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="B319" s="11" t="s">
         <v>732</v>
-      </c>
-      <c r="B319" s="11" t="s">
-        <v>733</v>
       </c>
       <c r="C319" s="7"/>
       <c r="D319" s="7"/>
@@ -13432,10 +13459,10 @@
     </row>
     <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="B320" s="8" t="s">
         <v>734</v>
-      </c>
-      <c r="B320" s="11" t="s">
-        <v>735</v>
       </c>
       <c r="C320" s="7"/>
       <c r="D320" s="7"/>
@@ -13463,11 +13490,11 @@
       <c r="Z320" s="7"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
-      <c r="A321" s="8" t="s">
+      <c r="A321" s="16" t="s">
+        <v>735</v>
+      </c>
+      <c r="B321" s="16" t="s">
         <v>736</v>
-      </c>
-      <c r="B321" s="8" t="s">
-        <v>737</v>
       </c>
       <c r="C321" s="7"/>
       <c r="D321" s="7"/>
@@ -13496,10 +13523,10 @@
     </row>
     <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="B322" s="11" t="s">
         <v>738</v>
-      </c>
-      <c r="B322" s="11" t="s">
-        <v>739</v>
       </c>
       <c r="C322" s="7"/>
       <c r="D322" s="7"/>
@@ -13528,10 +13555,10 @@
     </row>
     <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="8" t="s">
+        <v>739</v>
+      </c>
+      <c r="B323" s="8" t="s">
         <v>740</v>
-      </c>
-      <c r="B323" s="11" t="s">
-        <v>741</v>
       </c>
       <c r="C323" s="7"/>
       <c r="D323" s="7"/>
@@ -13559,11 +13586,11 @@
       <c r="Z323" s="7"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="A324" s="20" t="s">
+      <c r="A324" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="B324" s="11" t="s">
         <v>742</v>
-      </c>
-      <c r="B324" s="21" t="s">
-        <v>743</v>
       </c>
       <c r="C324" s="7"/>
       <c r="D324" s="7"/>
@@ -13592,10 +13619,10 @@
     </row>
     <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="B325" s="11" t="s">
         <v>744</v>
-      </c>
-      <c r="B325" s="11" t="s">
-        <v>745</v>
       </c>
       <c r="C325" s="7"/>
       <c r="D325" s="7"/>
@@ -13624,10 +13651,10 @@
     </row>
     <row r="326" ht="15.75" customHeight="1">
       <c r="A326" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="B326" s="8" t="s">
         <v>746</v>
-      </c>
-      <c r="B326" s="11" t="s">
-        <v>747</v>
       </c>
       <c r="C326" s="7"/>
       <c r="D326" s="7"/>
@@ -13656,10 +13683,10 @@
     </row>
     <row r="327" ht="15.75" customHeight="1">
       <c r="A327" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="B327" s="11" t="s">
         <v>748</v>
-      </c>
-      <c r="B327" s="8" t="s">
-        <v>749</v>
       </c>
       <c r="C327" s="7"/>
       <c r="D327" s="7"/>
@@ -13688,10 +13715,10 @@
     </row>
     <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="8" t="s">
+        <v>749</v>
+      </c>
+      <c r="B328" s="11" t="s">
         <v>750</v>
-      </c>
-      <c r="B328" s="11" t="s">
-        <v>751</v>
       </c>
       <c r="C328" s="7"/>
       <c r="D328" s="7"/>
@@ -13719,11 +13746,11 @@
       <c r="Z328" s="7"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="A329" s="8" t="s">
+      <c r="A329" s="20" t="s">
+        <v>751</v>
+      </c>
+      <c r="B329" s="21" t="s">
         <v>752</v>
-      </c>
-      <c r="B329" s="8" t="s">
-        <v>753</v>
       </c>
       <c r="C329" s="7"/>
       <c r="D329" s="7"/>
@@ -13752,10 +13779,10 @@
     </row>
     <row r="330" ht="15.75" customHeight="1">
       <c r="A330" s="8" t="s">
+        <v>753</v>
+      </c>
+      <c r="B330" s="11" t="s">
         <v>754</v>
-      </c>
-      <c r="B330" s="11" t="s">
-        <v>755</v>
       </c>
       <c r="C330" s="7"/>
       <c r="D330" s="7"/>
@@ -13784,10 +13811,10 @@
     </row>
     <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="8" t="s">
+        <v>755</v>
+      </c>
+      <c r="B331" s="11" t="s">
         <v>756</v>
-      </c>
-      <c r="B331" s="8" t="s">
-        <v>757</v>
       </c>
       <c r="C331" s="7"/>
       <c r="D331" s="7"/>
@@ -13816,10 +13843,10 @@
     </row>
     <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="B332" s="8" t="s">
         <v>758</v>
-      </c>
-      <c r="B332" s="8" t="s">
-        <v>759</v>
       </c>
       <c r="C332" s="7"/>
       <c r="D332" s="7"/>
@@ -13848,10 +13875,10 @@
     </row>
     <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="B333" s="11" t="s">
         <v>760</v>
-      </c>
-      <c r="B333" s="11" t="s">
-        <v>761</v>
       </c>
       <c r="C333" s="7"/>
       <c r="D333" s="7"/>
@@ -13880,10 +13907,10 @@
     </row>
     <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="B334" s="8" t="s">
         <v>762</v>
-      </c>
-      <c r="B334" s="11" t="s">
-        <v>763</v>
       </c>
       <c r="C334" s="7"/>
       <c r="D334" s="7"/>
@@ -13912,10 +13939,10 @@
     </row>
     <row r="335" ht="15.75" customHeight="1">
       <c r="A335" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="B335" s="11" t="s">
         <v>764</v>
-      </c>
-      <c r="B335" s="8" t="s">
-        <v>765</v>
       </c>
       <c r="C335" s="7"/>
       <c r="D335" s="7"/>
@@ -13944,10 +13971,10 @@
     </row>
     <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="8" t="s">
+        <v>765</v>
+      </c>
+      <c r="B336" s="8" t="s">
         <v>766</v>
-      </c>
-      <c r="B336" s="11" t="s">
-        <v>767</v>
       </c>
       <c r="C336" s="7"/>
       <c r="D336" s="7"/>
@@ -13976,10 +14003,10 @@
     </row>
     <row r="337" ht="15.75" customHeight="1">
       <c r="A337" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="B337" s="8" t="s">
         <v>768</v>
-      </c>
-      <c r="B337" s="11" t="s">
-        <v>769</v>
       </c>
       <c r="C337" s="7"/>
       <c r="D337" s="7"/>
@@ -14008,10 +14035,10 @@
     </row>
     <row r="338" ht="15.75" customHeight="1">
       <c r="A338" s="8" t="s">
+        <v>769</v>
+      </c>
+      <c r="B338" s="11" t="s">
         <v>770</v>
-      </c>
-      <c r="B338" s="11" t="s">
-        <v>771</v>
       </c>
       <c r="C338" s="7"/>
       <c r="D338" s="7"/>
@@ -14040,10 +14067,10 @@
     </row>
     <row r="339" ht="15.75" customHeight="1">
       <c r="A339" s="8" t="s">
+        <v>771</v>
+      </c>
+      <c r="B339" s="11" t="s">
         <v>772</v>
-      </c>
-      <c r="B339" s="8" t="s">
-        <v>773</v>
       </c>
       <c r="C339" s="7"/>
       <c r="D339" s="7"/>
@@ -14072,10 +14099,10 @@
     </row>
     <row r="340" ht="15.75" customHeight="1">
       <c r="A340" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="B340" s="8" t="s">
         <v>774</v>
-      </c>
-      <c r="B340" s="11" t="s">
-        <v>775</v>
       </c>
       <c r="C340" s="7"/>
       <c r="D340" s="7"/>
@@ -14104,10 +14131,10 @@
     </row>
     <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="B341" s="11" t="s">
         <v>776</v>
-      </c>
-      <c r="B341" s="8" t="s">
-        <v>777</v>
       </c>
       <c r="C341" s="7"/>
       <c r="D341" s="7"/>
@@ -14136,10 +14163,10 @@
     </row>
     <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="B342" s="11" t="s">
         <v>778</v>
-      </c>
-      <c r="B342" s="11" t="s">
-        <v>779</v>
       </c>
       <c r="C342" s="7"/>
       <c r="D342" s="7"/>
@@ -14168,10 +14195,10 @@
     </row>
     <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="B343" s="11" t="s">
         <v>780</v>
-      </c>
-      <c r="B343" s="11" t="s">
-        <v>781</v>
       </c>
       <c r="C343" s="7"/>
       <c r="D343" s="7"/>
@@ -14200,10 +14227,10 @@
     </row>
     <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="8" t="s">
+        <v>781</v>
+      </c>
+      <c r="B344" s="8" t="s">
         <v>782</v>
-      </c>
-      <c r="B344" s="11" t="s">
-        <v>783</v>
       </c>
       <c r="C344" s="7"/>
       <c r="D344" s="7"/>
@@ -14232,10 +14259,10 @@
     </row>
     <row r="345" ht="15.75" customHeight="1">
       <c r="A345" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="B345" s="11" t="s">
         <v>784</v>
-      </c>
-      <c r="B345" s="11" t="s">
-        <v>785</v>
       </c>
       <c r="C345" s="7"/>
       <c r="D345" s="7"/>
@@ -14264,10 +14291,10 @@
     </row>
     <row r="346" ht="15.75" customHeight="1">
       <c r="A346" s="8" t="s">
+        <v>785</v>
+      </c>
+      <c r="B346" s="8" t="s">
         <v>786</v>
-      </c>
-      <c r="B346" s="11" t="s">
-        <v>787</v>
       </c>
       <c r="C346" s="7"/>
       <c r="D346" s="7"/>
@@ -14295,11 +14322,11 @@
       <c r="Z346" s="7"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
-      <c r="A347" s="16" t="s">
+      <c r="A347" s="8" t="s">
+        <v>787</v>
+      </c>
+      <c r="B347" s="11" t="s">
         <v>788</v>
-      </c>
-      <c r="B347" s="25" t="s">
-        <v>789</v>
       </c>
       <c r="C347" s="7"/>
       <c r="D347" s="7"/>
@@ -14327,11 +14354,11 @@
       <c r="Z347" s="7"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
-      <c r="A348" s="16" t="s">
+      <c r="A348" s="8" t="s">
+        <v>789</v>
+      </c>
+      <c r="B348" s="11" t="s">
         <v>790</v>
-      </c>
-      <c r="B348" s="16" t="s">
-        <v>791</v>
       </c>
       <c r="C348" s="7"/>
       <c r="D348" s="7"/>
@@ -14360,10 +14387,10 @@
     </row>
     <row r="349" ht="15.75" customHeight="1">
       <c r="A349" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="B349" s="11" t="s">
         <v>792</v>
-      </c>
-      <c r="B349" s="11" t="s">
-        <v>793</v>
       </c>
       <c r="C349" s="7"/>
       <c r="D349" s="7"/>
@@ -14392,10 +14419,10 @@
     </row>
     <row r="350" ht="15.75" customHeight="1">
       <c r="A350" s="8" t="s">
+        <v>793</v>
+      </c>
+      <c r="B350" s="11" t="s">
         <v>794</v>
-      </c>
-      <c r="B350" s="8" t="s">
-        <v>795</v>
       </c>
       <c r="C350" s="7"/>
       <c r="D350" s="7"/>
@@ -14423,11 +14450,11 @@
       <c r="Z350" s="7"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="A351" s="16" t="s">
+      <c r="A351" s="8" t="s">
+        <v>795</v>
+      </c>
+      <c r="B351" s="11" t="s">
         <v>796</v>
-      </c>
-      <c r="B351" s="16" t="s">
-        <v>797</v>
       </c>
       <c r="C351" s="7"/>
       <c r="D351" s="7"/>
@@ -14455,11 +14482,11 @@
       <c r="Z351" s="7"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
-      <c r="A352" s="11" t="s">
+      <c r="A352" s="16" t="s">
+        <v>797</v>
+      </c>
+      <c r="B352" s="25" t="s">
         <v>798</v>
-      </c>
-      <c r="B352" s="8" t="s">
-        <v>799</v>
       </c>
       <c r="C352" s="7"/>
       <c r="D352" s="7"/>
@@ -14487,11 +14514,11 @@
       <c r="Z352" s="7"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="A353" s="8" t="s">
+      <c r="A353" s="16" t="s">
+        <v>799</v>
+      </c>
+      <c r="B353" s="16" t="s">
         <v>800</v>
-      </c>
-      <c r="B353" s="8" t="s">
-        <v>801</v>
       </c>
       <c r="C353" s="7"/>
       <c r="D353" s="7"/>
@@ -14519,11 +14546,11 @@
       <c r="Z353" s="7"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="A354" s="16" t="s">
+      <c r="A354" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="B354" s="11" t="s">
         <v>802</v>
-      </c>
-      <c r="B354" s="16" t="s">
-        <v>803</v>
       </c>
       <c r="C354" s="7"/>
       <c r="D354" s="7"/>
@@ -14551,11 +14578,11 @@
       <c r="Z354" s="7"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="A355" s="11" t="s">
+      <c r="A355" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="B355" s="8" t="s">
         <v>804</v>
-      </c>
-      <c r="B355" s="11" t="s">
-        <v>805</v>
       </c>
       <c r="C355" s="7"/>
       <c r="D355" s="7"/>
@@ -14584,10 +14611,10 @@
     </row>
     <row r="356" ht="15.75" customHeight="1">
       <c r="A356" s="16" t="s">
+        <v>805</v>
+      </c>
+      <c r="B356" s="16" t="s">
         <v>806</v>
-      </c>
-      <c r="B356" s="11" t="s">
-        <v>807</v>
       </c>
       <c r="C356" s="7"/>
       <c r="D356" s="7"/>
@@ -14615,11 +14642,11 @@
       <c r="Z356" s="7"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="A357" s="8" t="s">
+      <c r="A357" s="11" t="s">
+        <v>807</v>
+      </c>
+      <c r="B357" s="8" t="s">
         <v>808</v>
-      </c>
-      <c r="B357" s="11" t="s">
-        <v>809</v>
       </c>
       <c r="C357" s="7"/>
       <c r="D357" s="7"/>
@@ -14647,11 +14674,11 @@
       <c r="Z357" s="7"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="A358" s="11" t="s">
+      <c r="A358" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="B358" s="8" t="s">
         <v>810</v>
-      </c>
-      <c r="B358" s="11" t="s">
-        <v>811</v>
       </c>
       <c r="C358" s="7"/>
       <c r="D358" s="7"/>
@@ -14679,11 +14706,11 @@
       <c r="Z358" s="7"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="A359" s="8" t="s">
+      <c r="A359" s="16" t="s">
+        <v>811</v>
+      </c>
+      <c r="B359" s="16" t="s">
         <v>812</v>
-      </c>
-      <c r="B359" s="11" t="s">
-        <v>813</v>
       </c>
       <c r="C359" s="7"/>
       <c r="D359" s="7"/>
@@ -14711,11 +14738,11 @@
       <c r="Z359" s="7"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="A360" s="20" t="s">
+      <c r="A360" s="11" t="s">
+        <v>813</v>
+      </c>
+      <c r="B360" s="11" t="s">
         <v>814</v>
-      </c>
-      <c r="B360" s="21" t="s">
-        <v>815</v>
       </c>
       <c r="C360" s="7"/>
       <c r="D360" s="7"/>
@@ -14743,11 +14770,11 @@
       <c r="Z360" s="7"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="8" t="s">
+      <c r="A361" s="16" t="s">
+        <v>815</v>
+      </c>
+      <c r="B361" s="11" t="s">
         <v>816</v>
-      </c>
-      <c r="B361" s="8" t="s">
-        <v>817</v>
       </c>
       <c r="C361" s="7"/>
       <c r="D361" s="7"/>
@@ -14776,10 +14803,10 @@
     </row>
     <row r="362" ht="15.75" customHeight="1">
       <c r="A362" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="B362" s="11" t="s">
         <v>818</v>
-      </c>
-      <c r="B362" s="11" t="s">
-        <v>819</v>
       </c>
       <c r="C362" s="7"/>
       <c r="D362" s="7"/>
@@ -14807,11 +14834,11 @@
       <c r="Z362" s="7"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="A363" s="8" t="s">
+      <c r="A363" s="11" t="s">
+        <v>819</v>
+      </c>
+      <c r="B363" s="11" t="s">
         <v>820</v>
-      </c>
-      <c r="B363" s="8" t="s">
-        <v>821</v>
       </c>
       <c r="C363" s="7"/>
       <c r="D363" s="7"/>
@@ -14840,10 +14867,10 @@
     </row>
     <row r="364" ht="15.75" customHeight="1">
       <c r="A364" s="8" t="s">
+        <v>821</v>
+      </c>
+      <c r="B364" s="11" t="s">
         <v>822</v>
-      </c>
-      <c r="B364" s="11" t="s">
-        <v>823</v>
       </c>
       <c r="C364" s="7"/>
       <c r="D364" s="7"/>
@@ -14871,11 +14898,11 @@
       <c r="Z364" s="7"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="A365" s="11" t="s">
+      <c r="A365" s="20" t="s">
+        <v>823</v>
+      </c>
+      <c r="B365" s="21" t="s">
         <v>824</v>
-      </c>
-      <c r="B365" s="11" t="s">
-        <v>825</v>
       </c>
       <c r="C365" s="7"/>
       <c r="D365" s="7"/>
@@ -14904,10 +14931,10 @@
     </row>
     <row r="366" ht="15.75" customHeight="1">
       <c r="A366" s="8" t="s">
+        <v>825</v>
+      </c>
+      <c r="B366" s="8" t="s">
         <v>826</v>
-      </c>
-      <c r="B366" s="8" t="s">
-        <v>827</v>
       </c>
       <c r="C366" s="7"/>
       <c r="D366" s="7"/>
@@ -14936,10 +14963,10 @@
     </row>
     <row r="367" ht="15.75" customHeight="1">
       <c r="A367" s="8" t="s">
+        <v>827</v>
+      </c>
+      <c r="B367" s="11" t="s">
         <v>828</v>
-      </c>
-      <c r="B367" s="8" t="s">
-        <v>829</v>
       </c>
       <c r="C367" s="7"/>
       <c r="D367" s="7"/>
@@ -14968,10 +14995,10 @@
     </row>
     <row r="368" ht="15.75" customHeight="1">
       <c r="A368" s="8" t="s">
+        <v>829</v>
+      </c>
+      <c r="B368" s="8" t="s">
         <v>830</v>
-      </c>
-      <c r="B368" s="8" t="s">
-        <v>831</v>
       </c>
       <c r="C368" s="7"/>
       <c r="D368" s="7"/>
@@ -15000,10 +15027,10 @@
     </row>
     <row r="369" ht="15.75" customHeight="1">
       <c r="A369" s="8" t="s">
+        <v>831</v>
+      </c>
+      <c r="B369" s="11" t="s">
         <v>832</v>
-      </c>
-      <c r="B369" s="11" t="s">
-        <v>833</v>
       </c>
       <c r="C369" s="7"/>
       <c r="D369" s="7"/>
@@ -15031,11 +15058,11 @@
       <c r="Z369" s="7"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="A370" s="8" t="s">
+      <c r="A370" s="11" t="s">
+        <v>833</v>
+      </c>
+      <c r="B370" s="11" t="s">
         <v>834</v>
-      </c>
-      <c r="B370" s="8" t="s">
-        <v>835</v>
       </c>
       <c r="C370" s="7"/>
       <c r="D370" s="7"/>
@@ -15064,10 +15091,10 @@
     </row>
     <row r="371" ht="15.75" customHeight="1">
       <c r="A371" s="8" t="s">
+        <v>835</v>
+      </c>
+      <c r="B371" s="8" t="s">
         <v>836</v>
-      </c>
-      <c r="B371" s="11" t="s">
-        <v>837</v>
       </c>
       <c r="C371" s="7"/>
       <c r="D371" s="7"/>
@@ -15095,11 +15122,11 @@
       <c r="Z371" s="7"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="A372" s="16" t="s">
+      <c r="A372" s="8" t="s">
+        <v>837</v>
+      </c>
+      <c r="B372" s="8" t="s">
         <v>838</v>
-      </c>
-      <c r="B372" s="16" t="s">
-        <v>839</v>
       </c>
       <c r="C372" s="7"/>
       <c r="D372" s="7"/>
@@ -15128,10 +15155,10 @@
     </row>
     <row r="373" ht="15.75" customHeight="1">
       <c r="A373" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="B373" s="8" t="s">
         <v>840</v>
-      </c>
-      <c r="B373" s="11" t="s">
-        <v>841</v>
       </c>
       <c r="C373" s="7"/>
       <c r="D373" s="7"/>
@@ -15159,11 +15186,11 @@
       <c r="Z373" s="7"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="A374" s="16" t="s">
+      <c r="A374" s="8" t="s">
+        <v>841</v>
+      </c>
+      <c r="B374" s="11" t="s">
         <v>842</v>
-      </c>
-      <c r="B374" s="16" t="s">
-        <v>843</v>
       </c>
       <c r="C374" s="7"/>
       <c r="D374" s="7"/>
@@ -15191,11 +15218,11 @@
       <c r="Z374" s="7"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="A375" s="16" t="s">
+      <c r="A375" s="8" t="s">
+        <v>843</v>
+      </c>
+      <c r="B375" s="8" t="s">
         <v>844</v>
-      </c>
-      <c r="B375" s="16" t="s">
-        <v>845</v>
       </c>
       <c r="C375" s="7"/>
       <c r="D375" s="7"/>
@@ -15224,10 +15251,10 @@
     </row>
     <row r="376" ht="15.75" customHeight="1">
       <c r="A376" s="8" t="s">
+        <v>845</v>
+      </c>
+      <c r="B376" s="11" t="s">
         <v>846</v>
-      </c>
-      <c r="B376" s="8" t="s">
-        <v>847</v>
       </c>
       <c r="C376" s="7"/>
       <c r="D376" s="7"/>
@@ -15255,11 +15282,11 @@
       <c r="Z376" s="7"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="A377" s="8" t="s">
+      <c r="A377" s="16" t="s">
+        <v>847</v>
+      </c>
+      <c r="B377" s="16" t="s">
         <v>848</v>
-      </c>
-      <c r="B377" s="8" t="s">
-        <v>849</v>
       </c>
       <c r="C377" s="7"/>
       <c r="D377" s="7"/>
@@ -15287,11 +15314,11 @@
       <c r="Z377" s="7"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="A378" s="11" t="s">
+      <c r="A378" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="B378" s="11" t="s">
         <v>850</v>
-      </c>
-      <c r="B378" s="11" t="s">
-        <v>851</v>
       </c>
       <c r="C378" s="7"/>
       <c r="D378" s="7"/>
@@ -15319,11 +15346,11 @@
       <c r="Z378" s="7"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
-      <c r="A379" s="8" t="s">
+      <c r="A379" s="16" t="s">
+        <v>851</v>
+      </c>
+      <c r="B379" s="16" t="s">
         <v>852</v>
-      </c>
-      <c r="B379" s="8" t="s">
-        <v>853</v>
       </c>
       <c r="C379" s="7"/>
       <c r="D379" s="7"/>
@@ -15351,11 +15378,11 @@
       <c r="Z379" s="7"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="A380" s="21" t="s">
+      <c r="A380" s="16" t="s">
+        <v>853</v>
+      </c>
+      <c r="B380" s="16" t="s">
         <v>854</v>
-      </c>
-      <c r="B380" s="20" t="s">
-        <v>855</v>
       </c>
       <c r="C380" s="7"/>
       <c r="D380" s="7"/>
@@ -15384,10 +15411,10 @@
     </row>
     <row r="381" ht="15.75" customHeight="1">
       <c r="A381" s="8" t="s">
+        <v>855</v>
+      </c>
+      <c r="B381" s="8" t="s">
         <v>856</v>
-      </c>
-      <c r="B381" s="8" t="s">
-        <v>857</v>
       </c>
       <c r="C381" s="7"/>
       <c r="D381" s="7"/>
@@ -15416,10 +15443,10 @@
     </row>
     <row r="382" ht="15.75" customHeight="1">
       <c r="A382" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="B382" s="8" t="s">
         <v>858</v>
-      </c>
-      <c r="B382" s="8" t="s">
-        <v>859</v>
       </c>
       <c r="C382" s="7"/>
       <c r="D382" s="7"/>
@@ -15447,11 +15474,11 @@
       <c r="Z382" s="7"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="A383" s="8" t="s">
+      <c r="A383" s="11" t="s">
+        <v>859</v>
+      </c>
+      <c r="B383" s="11" t="s">
         <v>860</v>
-      </c>
-      <c r="B383" s="8" t="s">
-        <v>861</v>
       </c>
       <c r="C383" s="7"/>
       <c r="D383" s="7"/>
@@ -15479,6 +15506,12 @@
       <c r="Z383" s="7"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
+      <c r="A384" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="B384" s="8" t="s">
+        <v>862</v>
+      </c>
       <c r="C384" s="7"/>
       <c r="D384" s="7"/>
       <c r="E384" s="7"/>
@@ -15505,6 +15538,12 @@
       <c r="Z384" s="7"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
+      <c r="A385" s="21" t="s">
+        <v>863</v>
+      </c>
+      <c r="B385" s="20" t="s">
+        <v>864</v>
+      </c>
       <c r="C385" s="7"/>
       <c r="D385" s="7"/>
       <c r="E385" s="7"/>
@@ -15531,6 +15570,12 @@
       <c r="Z385" s="7"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
+      <c r="A386" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="B386" s="8" t="s">
+        <v>866</v>
+      </c>
       <c r="C386" s="7"/>
       <c r="D386" s="7"/>
       <c r="E386" s="7"/>
@@ -15557,6 +15602,12 @@
       <c r="Z386" s="7"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
+      <c r="A387" s="8" t="s">
+        <v>867</v>
+      </c>
+      <c r="B387" s="8" t="s">
+        <v>868</v>
+      </c>
       <c r="C387" s="7"/>
       <c r="D387" s="7"/>
       <c r="E387" s="7"/>
@@ -15583,6 +15634,12 @@
       <c r="Z387" s="7"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
+      <c r="A388" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="B388" s="8" t="s">
+        <v>870</v>
+      </c>
       <c r="C388" s="7"/>
       <c r="D388" s="7"/>
       <c r="E388" s="7"/>
@@ -15947,7 +16004,6 @@
       <c r="Z401" s="7"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="A402" s="11"/>
       <c r="B402" s="11"/>
       <c r="C402" s="7"/>
       <c r="D402" s="7"/>
@@ -15975,7 +16031,6 @@
       <c r="Z402" s="7"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="A403" s="11"/>
       <c r="B403" s="11"/>
       <c r="C403" s="7"/>
       <c r="D403" s="7"/>
@@ -16003,7 +16058,6 @@
       <c r="Z403" s="7"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="A404" s="11"/>
       <c r="B404" s="11"/>
       <c r="C404" s="7"/>
       <c r="D404" s="7"/>
@@ -16031,7 +16085,6 @@
       <c r="Z404" s="7"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="A405" s="11"/>
       <c r="B405" s="11"/>
       <c r="C405" s="7"/>
       <c r="D405" s="7"/>
@@ -16059,7 +16112,6 @@
       <c r="Z405" s="7"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
-      <c r="A406" s="11"/>
       <c r="B406" s="11"/>
       <c r="C406" s="7"/>
       <c r="D406" s="7"/>
@@ -16087,7 +16139,6 @@
       <c r="Z406" s="7"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="A407" s="11"/>
       <c r="B407" s="11"/>
       <c r="C407" s="7"/>
       <c r="D407" s="7"/>
@@ -16115,7 +16166,6 @@
       <c r="Z407" s="7"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
-      <c r="A408" s="11"/>
       <c r="B408" s="11"/>
       <c r="C408" s="7"/>
       <c r="D408" s="7"/>
@@ -16143,7 +16193,6 @@
       <c r="Z408" s="7"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
-      <c r="A409" s="11"/>
       <c r="B409" s="11"/>
       <c r="C409" s="7"/>
       <c r="D409" s="7"/>
@@ -16171,7 +16220,6 @@
       <c r="Z409" s="7"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
-      <c r="A410" s="11"/>
       <c r="B410" s="11"/>
       <c r="C410" s="7"/>
       <c r="D410" s="7"/>
@@ -16199,7 +16247,6 @@
       <c r="Z410" s="7"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="A411" s="11"/>
       <c r="B411" s="11"/>
       <c r="C411" s="7"/>
       <c r="D411" s="7"/>
@@ -16227,7 +16274,6 @@
       <c r="Z411" s="7"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
-      <c r="A412" s="11"/>
       <c r="B412" s="11"/>
       <c r="C412" s="7"/>
       <c r="D412" s="7"/>
@@ -16255,7 +16301,6 @@
       <c r="Z412" s="7"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="A413" s="11"/>
       <c r="B413" s="11"/>
       <c r="C413" s="7"/>
       <c r="D413" s="7"/>
@@ -16283,7 +16328,6 @@
       <c r="Z413" s="7"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
-      <c r="A414" s="11"/>
       <c r="B414" s="11"/>
       <c r="C414" s="7"/>
       <c r="D414" s="7"/>
@@ -16311,7 +16355,6 @@
       <c r="Z414" s="7"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="A415" s="11"/>
       <c r="B415" s="11"/>
       <c r="C415" s="7"/>
       <c r="D415" s="7"/>
@@ -16339,7 +16382,6 @@
       <c r="Z415" s="7"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="A416" s="11"/>
       <c r="B416" s="11"/>
       <c r="C416" s="7"/>
       <c r="D416" s="7"/>
@@ -16367,7 +16409,6 @@
       <c r="Z416" s="7"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
-      <c r="A417" s="11"/>
       <c r="B417" s="11"/>
       <c r="C417" s="7"/>
       <c r="D417" s="7"/>
@@ -16395,7 +16436,6 @@
       <c r="Z417" s="7"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="A418" s="11"/>
       <c r="B418" s="11"/>
       <c r="C418" s="7"/>
       <c r="D418" s="7"/>
@@ -16423,7 +16463,6 @@
       <c r="Z418" s="7"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
-      <c r="A419" s="11"/>
       <c r="B419" s="11"/>
       <c r="C419" s="7"/>
       <c r="D419" s="7"/>
@@ -16451,7 +16490,6 @@
       <c r="Z419" s="7"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
-      <c r="A420" s="11"/>
       <c r="B420" s="11"/>
       <c r="C420" s="7"/>
       <c r="D420" s="7"/>
@@ -16479,7 +16517,6 @@
       <c r="Z420" s="7"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="A421" s="11"/>
       <c r="B421" s="11"/>
       <c r="C421" s="7"/>
       <c r="D421" s="7"/>
@@ -16507,7 +16544,6 @@
       <c r="Z421" s="7"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="A422" s="11"/>
       <c r="B422" s="11"/>
       <c r="C422" s="7"/>
       <c r="D422" s="7"/>
@@ -16535,7 +16571,6 @@
       <c r="Z422" s="7"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="A423" s="11"/>
       <c r="B423" s="11"/>
       <c r="C423" s="7"/>
       <c r="D423" s="7"/>
@@ -16563,7 +16598,6 @@
       <c r="Z423" s="7"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="A424" s="11"/>
       <c r="B424" s="11"/>
       <c r="C424" s="7"/>
       <c r="D424" s="7"/>
@@ -16591,7 +16625,6 @@
       <c r="Z424" s="7"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="A425" s="11"/>
       <c r="B425" s="11"/>
       <c r="C425" s="7"/>
       <c r="D425" s="7"/>
@@ -16619,7 +16652,6 @@
       <c r="Z425" s="7"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="A426" s="11"/>
       <c r="B426" s="11"/>
       <c r="C426" s="7"/>
       <c r="D426" s="7"/>
@@ -16647,7 +16679,6 @@
       <c r="Z426" s="7"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="A427" s="11"/>
       <c r="B427" s="11"/>
       <c r="C427" s="7"/>
       <c r="D427" s="7"/>
@@ -16675,7 +16706,6 @@
       <c r="Z427" s="7"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="A428" s="11"/>
       <c r="B428" s="11"/>
       <c r="C428" s="7"/>
       <c r="D428" s="7"/>
@@ -16703,7 +16733,6 @@
       <c r="Z428" s="7"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
-      <c r="A429" s="11"/>
       <c r="B429" s="11"/>
       <c r="C429" s="7"/>
       <c r="D429" s="7"/>
@@ -16731,7 +16760,6 @@
       <c r="Z429" s="7"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="A430" s="11"/>
       <c r="B430" s="11"/>
       <c r="C430" s="7"/>
       <c r="D430" s="7"/>
@@ -16759,7 +16787,6 @@
       <c r="Z430" s="7"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="A431" s="11"/>
       <c r="B431" s="11"/>
       <c r="C431" s="7"/>
       <c r="D431" s="7"/>
@@ -16787,7 +16814,6 @@
       <c r="Z431" s="7"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="A432" s="11"/>
       <c r="B432" s="11"/>
       <c r="C432" s="7"/>
       <c r="D432" s="7"/>
@@ -16815,7 +16841,6 @@
       <c r="Z432" s="7"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="A433" s="11"/>
       <c r="B433" s="11"/>
       <c r="C433" s="7"/>
       <c r="D433" s="7"/>
@@ -16843,7 +16868,6 @@
       <c r="Z433" s="7"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="A434" s="11"/>
       <c r="B434" s="11"/>
       <c r="C434" s="7"/>
       <c r="D434" s="7"/>
@@ -16871,7 +16895,6 @@
       <c r="Z434" s="7"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="A435" s="11"/>
       <c r="B435" s="11"/>
       <c r="C435" s="7"/>
       <c r="D435" s="7"/>
@@ -16899,7 +16922,6 @@
       <c r="Z435" s="7"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="A436" s="11"/>
       <c r="B436" s="11"/>
       <c r="C436" s="7"/>
       <c r="D436" s="7"/>
@@ -16927,7 +16949,6 @@
       <c r="Z436" s="7"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="A437" s="11"/>
       <c r="B437" s="11"/>
       <c r="C437" s="7"/>
       <c r="D437" s="7"/>
@@ -16955,7 +16976,6 @@
       <c r="Z437" s="7"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="A438" s="11"/>
       <c r="B438" s="11"/>
       <c r="C438" s="7"/>
       <c r="D438" s="7"/>
@@ -16983,7 +17003,6 @@
       <c r="Z438" s="7"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="A439" s="11"/>
       <c r="B439" s="11"/>
       <c r="C439" s="7"/>
       <c r="D439" s="7"/>
@@ -17011,7 +17030,6 @@
       <c r="Z439" s="7"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="A440" s="11"/>
       <c r="B440" s="11"/>
       <c r="C440" s="7"/>
       <c r="D440" s="7"/>
@@ -17039,7 +17057,6 @@
       <c r="Z440" s="7"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="A441" s="11"/>
       <c r="B441" s="11"/>
       <c r="C441" s="7"/>
       <c r="D441" s="7"/>
@@ -17067,7 +17084,6 @@
       <c r="Z441" s="7"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="A442" s="11"/>
       <c r="B442" s="11"/>
       <c r="C442" s="7"/>
       <c r="D442" s="7"/>
@@ -17095,7 +17111,6 @@
       <c r="Z442" s="7"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="A443" s="11"/>
       <c r="B443" s="11"/>
       <c r="C443" s="7"/>
       <c r="D443" s="7"/>
@@ -17123,7 +17138,6 @@
       <c r="Z443" s="7"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="A444" s="11"/>
       <c r="B444" s="11"/>
       <c r="C444" s="7"/>
       <c r="D444" s="7"/>
@@ -17151,7 +17165,6 @@
       <c r="Z444" s="7"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="A445" s="11"/>
       <c r="B445" s="11"/>
       <c r="C445" s="7"/>
       <c r="D445" s="7"/>
@@ -17179,7 +17192,6 @@
       <c r="Z445" s="7"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="A446" s="11"/>
       <c r="B446" s="11"/>
       <c r="C446" s="7"/>
       <c r="D446" s="7"/>
@@ -17207,7 +17219,6 @@
       <c r="Z446" s="7"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
-      <c r="A447" s="11"/>
       <c r="B447" s="11"/>
       <c r="C447" s="7"/>
       <c r="D447" s="7"/>
@@ -17235,7 +17246,6 @@
       <c r="Z447" s="7"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="A448" s="11"/>
       <c r="B448" s="11"/>
       <c r="C448" s="7"/>
       <c r="D448" s="7"/>
@@ -17263,7 +17273,6 @@
       <c r="Z448" s="7"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="A449" s="11"/>
       <c r="B449" s="11"/>
       <c r="C449" s="7"/>
       <c r="D449" s="7"/>
@@ -17291,7 +17300,6 @@
       <c r="Z449" s="7"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
-      <c r="A450" s="11"/>
       <c r="B450" s="11"/>
       <c r="C450" s="7"/>
       <c r="D450" s="7"/>
@@ -17319,7 +17327,6 @@
       <c r="Z450" s="7"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="A451" s="11"/>
       <c r="B451" s="11"/>
       <c r="C451" s="7"/>
       <c r="D451" s="7"/>
@@ -17347,7 +17354,6 @@
       <c r="Z451" s="7"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
-      <c r="A452" s="11"/>
       <c r="B452" s="11"/>
       <c r="C452" s="7"/>
       <c r="D452" s="7"/>
@@ -17375,7 +17381,6 @@
       <c r="Z452" s="7"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="A453" s="11"/>
       <c r="B453" s="11"/>
       <c r="C453" s="7"/>
       <c r="D453" s="7"/>
@@ -17403,7 +17408,6 @@
       <c r="Z453" s="7"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
-      <c r="A454" s="11"/>
       <c r="B454" s="11"/>
       <c r="C454" s="7"/>
       <c r="D454" s="7"/>
@@ -17431,7 +17435,6 @@
       <c r="Z454" s="7"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
-      <c r="A455" s="11"/>
       <c r="B455" s="11"/>
       <c r="C455" s="7"/>
       <c r="D455" s="7"/>
@@ -17459,7 +17462,6 @@
       <c r="Z455" s="7"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="A456" s="11"/>
       <c r="B456" s="11"/>
       <c r="C456" s="7"/>
       <c r="D456" s="7"/>
@@ -17487,7 +17489,6 @@
       <c r="Z456" s="7"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="A457" s="11"/>
       <c r="B457" s="11"/>
       <c r="C457" s="7"/>
       <c r="D457" s="7"/>
@@ -17515,7 +17516,6 @@
       <c r="Z457" s="7"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="A458" s="11"/>
       <c r="B458" s="11"/>
       <c r="C458" s="7"/>
       <c r="D458" s="7"/>
@@ -17543,7 +17543,6 @@
       <c r="Z458" s="7"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="A459" s="11"/>
       <c r="B459" s="11"/>
       <c r="C459" s="7"/>
       <c r="D459" s="7"/>
@@ -17571,7 +17570,6 @@
       <c r="Z459" s="7"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="A460" s="11"/>
       <c r="B460" s="11"/>
       <c r="C460" s="7"/>
       <c r="D460" s="7"/>
@@ -17599,7 +17597,6 @@
       <c r="Z460" s="7"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="A461" s="11"/>
       <c r="B461" s="11"/>
       <c r="C461" s="7"/>
       <c r="D461" s="7"/>
@@ -17627,7 +17624,6 @@
       <c r="Z461" s="7"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="A462" s="11"/>
       <c r="B462" s="11"/>
       <c r="C462" s="7"/>
       <c r="D462" s="7"/>
@@ -17655,7 +17651,6 @@
       <c r="Z462" s="7"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="A463" s="11"/>
       <c r="B463" s="11"/>
       <c r="C463" s="7"/>
       <c r="D463" s="7"/>
@@ -17683,7 +17678,6 @@
       <c r="Z463" s="7"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="A464" s="11"/>
       <c r="B464" s="11"/>
       <c r="C464" s="7"/>
       <c r="D464" s="7"/>
@@ -17711,7 +17705,6 @@
       <c r="Z464" s="7"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="A465" s="11"/>
       <c r="B465" s="11"/>
       <c r="C465" s="7"/>
       <c r="D465" s="7"/>
@@ -17739,7 +17732,6 @@
       <c r="Z465" s="7"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="A466" s="11"/>
       <c r="B466" s="11"/>
       <c r="C466" s="7"/>
       <c r="D466" s="7"/>
@@ -17767,7 +17759,6 @@
       <c r="Z466" s="7"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="A467" s="11"/>
       <c r="B467" s="11"/>
       <c r="C467" s="7"/>
       <c r="D467" s="7"/>
@@ -17795,7 +17786,6 @@
       <c r="Z467" s="7"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="A468" s="11"/>
       <c r="B468" s="11"/>
       <c r="C468" s="7"/>
       <c r="D468" s="7"/>
@@ -17823,7 +17813,6 @@
       <c r="Z468" s="7"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="A469" s="11"/>
       <c r="B469" s="11"/>
       <c r="C469" s="7"/>
       <c r="D469" s="7"/>
@@ -17851,7 +17840,6 @@
       <c r="Z469" s="7"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="A470" s="11"/>
       <c r="B470" s="11"/>
       <c r="C470" s="7"/>
       <c r="D470" s="7"/>
@@ -17879,7 +17867,6 @@
       <c r="Z470" s="7"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="A471" s="11"/>
       <c r="B471" s="11"/>
       <c r="C471" s="7"/>
       <c r="D471" s="7"/>
@@ -17907,7 +17894,6 @@
       <c r="Z471" s="7"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
-      <c r="A472" s="11"/>
       <c r="B472" s="11"/>
       <c r="C472" s="7"/>
       <c r="D472" s="7"/>
@@ -17935,7 +17921,6 @@
       <c r="Z472" s="7"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="A473" s="11"/>
       <c r="B473" s="11"/>
       <c r="C473" s="7"/>
       <c r="D473" s="7"/>
@@ -17963,7 +17948,6 @@
       <c r="Z473" s="7"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
-      <c r="A474" s="11"/>
       <c r="B474" s="11"/>
       <c r="C474" s="7"/>
       <c r="D474" s="7"/>
@@ -17991,7 +17975,6 @@
       <c r="Z474" s="7"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="A475" s="11"/>
       <c r="B475" s="11"/>
       <c r="C475" s="7"/>
       <c r="D475" s="7"/>
@@ -18019,7 +18002,6 @@
       <c r="Z475" s="7"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="A476" s="11"/>
       <c r="B476" s="11"/>
       <c r="C476" s="7"/>
       <c r="D476" s="7"/>
@@ -18047,7 +18029,6 @@
       <c r="Z476" s="7"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="A477" s="11"/>
       <c r="B477" s="11"/>
       <c r="C477" s="7"/>
       <c r="D477" s="7"/>
@@ -18075,7 +18056,6 @@
       <c r="Z477" s="7"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="A478" s="11"/>
       <c r="B478" s="11"/>
       <c r="C478" s="7"/>
       <c r="D478" s="7"/>
@@ -18103,7 +18083,6 @@
       <c r="Z478" s="7"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="A479" s="11"/>
       <c r="B479" s="11"/>
       <c r="C479" s="7"/>
       <c r="D479" s="7"/>
@@ -18131,7 +18110,6 @@
       <c r="Z479" s="7"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="A480" s="11"/>
       <c r="B480" s="11"/>
       <c r="C480" s="7"/>
       <c r="D480" s="7"/>
@@ -18159,7 +18137,6 @@
       <c r="Z480" s="7"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
-      <c r="A481" s="11"/>
       <c r="B481" s="11"/>
       <c r="C481" s="7"/>
       <c r="D481" s="7"/>
@@ -18187,7 +18164,6 @@
       <c r="Z481" s="7"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="A482" s="11"/>
       <c r="B482" s="11"/>
       <c r="C482" s="7"/>
       <c r="D482" s="7"/>
@@ -18215,7 +18191,6 @@
       <c r="Z482" s="7"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
-      <c r="A483" s="11"/>
       <c r="B483" s="11"/>
       <c r="C483" s="7"/>
       <c r="D483" s="7"/>
@@ -18243,7 +18218,6 @@
       <c r="Z483" s="7"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
-      <c r="A484" s="11"/>
       <c r="B484" s="11"/>
       <c r="C484" s="7"/>
       <c r="D484" s="7"/>
@@ -18271,7 +18245,6 @@
       <c r="Z484" s="7"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="A485" s="11"/>
       <c r="B485" s="11"/>
       <c r="C485" s="7"/>
       <c r="D485" s="7"/>
@@ -18299,7 +18272,6 @@
       <c r="Z485" s="7"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="A486" s="11"/>
       <c r="B486" s="11"/>
       <c r="C486" s="7"/>
       <c r="D486" s="7"/>
@@ -18327,7 +18299,6 @@
       <c r="Z486" s="7"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
-      <c r="A487" s="11"/>
       <c r="B487" s="11"/>
       <c r="C487" s="7"/>
       <c r="D487" s="7"/>
@@ -18355,7 +18326,6 @@
       <c r="Z487" s="7"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
-      <c r="A488" s="11"/>
       <c r="B488" s="11"/>
       <c r="C488" s="7"/>
       <c r="D488" s="7"/>
@@ -18383,7 +18353,6 @@
       <c r="Z488" s="7"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="A489" s="11"/>
       <c r="B489" s="11"/>
       <c r="C489" s="7"/>
       <c r="D489" s="7"/>
@@ -18411,7 +18380,6 @@
       <c r="Z489" s="7"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
-      <c r="A490" s="11"/>
       <c r="B490" s="11"/>
       <c r="C490" s="7"/>
       <c r="D490" s="7"/>
@@ -18439,7 +18407,6 @@
       <c r="Z490" s="7"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="A491" s="11"/>
       <c r="B491" s="11"/>
       <c r="C491" s="7"/>
       <c r="D491" s="7"/>
@@ -18467,7 +18434,6 @@
       <c r="Z491" s="7"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
-      <c r="A492" s="11"/>
       <c r="B492" s="11"/>
       <c r="C492" s="7"/>
       <c r="D492" s="7"/>
@@ -18495,7 +18461,6 @@
       <c r="Z492" s="7"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
-      <c r="A493" s="11"/>
       <c r="B493" s="11"/>
       <c r="C493" s="7"/>
       <c r="D493" s="7"/>
@@ -18523,7 +18488,6 @@
       <c r="Z493" s="7"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
-      <c r="A494" s="11"/>
       <c r="B494" s="11"/>
       <c r="C494" s="7"/>
       <c r="D494" s="7"/>
@@ -18551,7 +18515,6 @@
       <c r="Z494" s="7"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
-      <c r="A495" s="11"/>
       <c r="B495" s="11"/>
       <c r="C495" s="7"/>
       <c r="D495" s="7"/>
@@ -18579,7 +18542,6 @@
       <c r="Z495" s="7"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="A496" s="11"/>
       <c r="B496" s="11"/>
       <c r="C496" s="7"/>
       <c r="D496" s="7"/>
@@ -18607,7 +18569,6 @@
       <c r="Z496" s="7"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
-      <c r="A497" s="11"/>
       <c r="B497" s="11"/>
       <c r="C497" s="7"/>
       <c r="D497" s="7"/>
@@ -18635,7 +18596,6 @@
       <c r="Z497" s="7"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
-      <c r="A498" s="11"/>
       <c r="B498" s="11"/>
       <c r="C498" s="7"/>
       <c r="D498" s="7"/>
@@ -18663,7 +18623,6 @@
       <c r="Z498" s="7"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
-      <c r="A499" s="11"/>
       <c r="B499" s="11"/>
       <c r="C499" s="7"/>
       <c r="D499" s="7"/>
@@ -18691,7 +18650,6 @@
       <c r="Z499" s="7"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
-      <c r="A500" s="11"/>
       <c r="B500" s="11"/>
       <c r="C500" s="7"/>
       <c r="D500" s="7"/>
@@ -18719,7 +18677,6 @@
       <c r="Z500" s="7"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
-      <c r="A501" s="11"/>
       <c r="B501" s="11"/>
       <c r="C501" s="7"/>
       <c r="D501" s="7"/>
@@ -18747,7 +18704,6 @@
       <c r="Z501" s="7"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
-      <c r="A502" s="11"/>
       <c r="B502" s="11"/>
       <c r="C502" s="7"/>
       <c r="D502" s="7"/>
@@ -18775,7 +18731,6 @@
       <c r="Z502" s="7"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
-      <c r="A503" s="11"/>
       <c r="B503" s="11"/>
       <c r="C503" s="7"/>
       <c r="D503" s="7"/>
@@ -18803,7 +18758,6 @@
       <c r="Z503" s="7"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
-      <c r="A504" s="11"/>
       <c r="B504" s="11"/>
       <c r="C504" s="7"/>
       <c r="D504" s="7"/>
@@ -18831,7 +18785,6 @@
       <c r="Z504" s="7"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
-      <c r="A505" s="11"/>
       <c r="B505" s="11"/>
       <c r="C505" s="7"/>
       <c r="D505" s="7"/>
@@ -18859,7 +18812,6 @@
       <c r="Z505" s="7"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
-      <c r="A506" s="11"/>
       <c r="B506" s="11"/>
       <c r="C506" s="7"/>
       <c r="D506" s="7"/>
@@ -18887,7 +18839,6 @@
       <c r="Z506" s="7"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
-      <c r="A507" s="11"/>
       <c r="B507" s="11"/>
       <c r="C507" s="7"/>
       <c r="D507" s="7"/>
@@ -18915,7 +18866,6 @@
       <c r="Z507" s="7"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
-      <c r="A508" s="11"/>
       <c r="B508" s="11"/>
       <c r="C508" s="7"/>
       <c r="D508" s="7"/>
@@ -18943,7 +18893,6 @@
       <c r="Z508" s="7"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
-      <c r="A509" s="11"/>
       <c r="B509" s="11"/>
       <c r="C509" s="7"/>
       <c r="D509" s="7"/>
@@ -18971,7 +18920,6 @@
       <c r="Z509" s="7"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
-      <c r="A510" s="11"/>
       <c r="B510" s="11"/>
       <c r="C510" s="7"/>
       <c r="D510" s="7"/>
@@ -18999,7 +18947,6 @@
       <c r="Z510" s="7"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
-      <c r="A511" s="11"/>
       <c r="B511" s="11"/>
       <c r="C511" s="7"/>
       <c r="D511" s="7"/>
@@ -19027,7 +18974,6 @@
       <c r="Z511" s="7"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
-      <c r="A512" s="11"/>
       <c r="B512" s="11"/>
       <c r="C512" s="7"/>
       <c r="D512" s="7"/>
@@ -19055,7 +19001,6 @@
       <c r="Z512" s="7"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
-      <c r="A513" s="11"/>
       <c r="B513" s="11"/>
       <c r="C513" s="7"/>
       <c r="D513" s="7"/>
@@ -19083,7 +19028,6 @@
       <c r="Z513" s="7"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
-      <c r="A514" s="11"/>
       <c r="B514" s="11"/>
       <c r="C514" s="7"/>
       <c r="D514" s="7"/>
@@ -19111,7 +19055,6 @@
       <c r="Z514" s="7"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
-      <c r="A515" s="11"/>
       <c r="B515" s="11"/>
       <c r="C515" s="7"/>
       <c r="D515" s="7"/>
@@ -19139,7 +19082,6 @@
       <c r="Z515" s="7"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
-      <c r="A516" s="11"/>
       <c r="B516" s="11"/>
       <c r="C516" s="7"/>
       <c r="D516" s="7"/>
@@ -19167,7 +19109,6 @@
       <c r="Z516" s="7"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
-      <c r="A517" s="11"/>
       <c r="B517" s="11"/>
       <c r="C517" s="7"/>
       <c r="D517" s="7"/>
@@ -19195,7 +19136,6 @@
       <c r="Z517" s="7"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
-      <c r="A518" s="11"/>
       <c r="B518" s="11"/>
       <c r="C518" s="7"/>
       <c r="D518" s="7"/>
@@ -19223,7 +19163,6 @@
       <c r="Z518" s="7"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
-      <c r="A519" s="11"/>
       <c r="B519" s="11"/>
       <c r="C519" s="7"/>
       <c r="D519" s="7"/>
@@ -19251,7 +19190,6 @@
       <c r="Z519" s="7"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="A520" s="11"/>
       <c r="B520" s="11"/>
       <c r="C520" s="7"/>
       <c r="D520" s="7"/>
@@ -19279,7 +19217,6 @@
       <c r="Z520" s="7"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
-      <c r="A521" s="11"/>
       <c r="B521" s="11"/>
       <c r="C521" s="7"/>
       <c r="D521" s="7"/>
@@ -19307,7 +19244,6 @@
       <c r="Z521" s="7"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
-      <c r="A522" s="11"/>
       <c r="B522" s="11"/>
       <c r="C522" s="7"/>
       <c r="D522" s="7"/>
@@ -19335,7 +19271,6 @@
       <c r="Z522" s="7"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
-      <c r="A523" s="11"/>
       <c r="B523" s="11"/>
       <c r="C523" s="7"/>
       <c r="D523" s="7"/>
@@ -19363,7 +19298,6 @@
       <c r="Z523" s="7"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
-      <c r="A524" s="11"/>
       <c r="B524" s="11"/>
       <c r="C524" s="7"/>
       <c r="D524" s="7"/>
@@ -19391,7 +19325,6 @@
       <c r="Z524" s="7"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
-      <c r="A525" s="11"/>
       <c r="B525" s="11"/>
       <c r="C525" s="7"/>
       <c r="D525" s="7"/>
@@ -19419,7 +19352,6 @@
       <c r="Z525" s="7"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
-      <c r="A526" s="11"/>
       <c r="B526" s="11"/>
       <c r="C526" s="7"/>
       <c r="D526" s="7"/>
@@ -19447,7 +19379,6 @@
       <c r="Z526" s="7"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
-      <c r="A527" s="11"/>
       <c r="B527" s="11"/>
       <c r="C527" s="7"/>
       <c r="D527" s="7"/>
@@ -19475,7 +19406,6 @@
       <c r="Z527" s="7"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
-      <c r="A528" s="11"/>
       <c r="B528" s="11"/>
       <c r="C528" s="7"/>
       <c r="D528" s="7"/>
@@ -19503,7 +19433,6 @@
       <c r="Z528" s="7"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
-      <c r="A529" s="11"/>
       <c r="B529" s="11"/>
       <c r="C529" s="7"/>
       <c r="D529" s="7"/>
@@ -19531,7 +19460,6 @@
       <c r="Z529" s="7"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
-      <c r="A530" s="11"/>
       <c r="B530" s="11"/>
       <c r="C530" s="7"/>
       <c r="D530" s="7"/>
@@ -19559,7 +19487,6 @@
       <c r="Z530" s="7"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
-      <c r="A531" s="11"/>
       <c r="B531" s="11"/>
       <c r="C531" s="7"/>
       <c r="D531" s="7"/>
@@ -19587,7 +19514,6 @@
       <c r="Z531" s="7"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
-      <c r="A532" s="11"/>
       <c r="B532" s="11"/>
       <c r="C532" s="7"/>
       <c r="D532" s="7"/>
@@ -19615,7 +19541,6 @@
       <c r="Z532" s="7"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
-      <c r="A533" s="11"/>
       <c r="B533" s="11"/>
       <c r="C533" s="7"/>
       <c r="D533" s="7"/>
@@ -19643,7 +19568,6 @@
       <c r="Z533" s="7"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
-      <c r="A534" s="11"/>
       <c r="B534" s="11"/>
       <c r="C534" s="7"/>
       <c r="D534" s="7"/>
@@ -19671,7 +19595,6 @@
       <c r="Z534" s="7"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
-      <c r="A535" s="11"/>
       <c r="B535" s="11"/>
       <c r="C535" s="7"/>
       <c r="D535" s="7"/>
@@ -19699,7 +19622,6 @@
       <c r="Z535" s="7"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
-      <c r="A536" s="11"/>
       <c r="B536" s="11"/>
       <c r="C536" s="7"/>
       <c r="D536" s="7"/>
@@ -19727,7 +19649,6 @@
       <c r="Z536" s="7"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
-      <c r="A537" s="11"/>
       <c r="B537" s="11"/>
       <c r="C537" s="7"/>
       <c r="D537" s="7"/>
@@ -19755,7 +19676,6 @@
       <c r="Z537" s="7"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
-      <c r="A538" s="11"/>
       <c r="B538" s="11"/>
       <c r="C538" s="7"/>
       <c r="D538" s="7"/>
@@ -19783,7 +19703,6 @@
       <c r="Z538" s="7"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
-      <c r="A539" s="11"/>
       <c r="B539" s="11"/>
       <c r="C539" s="7"/>
       <c r="D539" s="7"/>
@@ -19811,7 +19730,6 @@
       <c r="Z539" s="7"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
-      <c r="A540" s="11"/>
       <c r="B540" s="11"/>
       <c r="C540" s="7"/>
       <c r="D540" s="7"/>
@@ -19839,7 +19757,6 @@
       <c r="Z540" s="7"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
-      <c r="A541" s="11"/>
       <c r="B541" s="11"/>
       <c r="C541" s="7"/>
       <c r="D541" s="7"/>
@@ -19867,7 +19784,6 @@
       <c r="Z541" s="7"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
-      <c r="A542" s="11"/>
       <c r="B542" s="11"/>
       <c r="C542" s="7"/>
       <c r="D542" s="7"/>
@@ -19895,7 +19811,6 @@
       <c r="Z542" s="7"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
-      <c r="A543" s="11"/>
       <c r="B543" s="11"/>
       <c r="C543" s="7"/>
       <c r="D543" s="7"/>
@@ -19923,7 +19838,6 @@
       <c r="Z543" s="7"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="A544" s="11"/>
       <c r="B544" s="11"/>
       <c r="C544" s="7"/>
       <c r="D544" s="7"/>
@@ -19951,7 +19865,6 @@
       <c r="Z544" s="7"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="A545" s="11"/>
       <c r="B545" s="11"/>
       <c r="C545" s="7"/>
       <c r="D545" s="7"/>
@@ -19979,7 +19892,6 @@
       <c r="Z545" s="7"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
-      <c r="A546" s="11"/>
       <c r="B546" s="11"/>
       <c r="C546" s="7"/>
       <c r="D546" s="7"/>
@@ -20007,7 +19919,6 @@
       <c r="Z546" s="7"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
-      <c r="A547" s="11"/>
       <c r="B547" s="11"/>
       <c r="C547" s="7"/>
       <c r="D547" s="7"/>
@@ -20035,7 +19946,6 @@
       <c r="Z547" s="7"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
-      <c r="A548" s="11"/>
       <c r="B548" s="11"/>
       <c r="C548" s="7"/>
       <c r="D548" s="7"/>
@@ -20063,7 +19973,6 @@
       <c r="Z548" s="7"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
-      <c r="A549" s="11"/>
       <c r="B549" s="11"/>
       <c r="C549" s="7"/>
       <c r="D549" s="7"/>
@@ -20091,7 +20000,6 @@
       <c r="Z549" s="7"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
-      <c r="A550" s="11"/>
       <c r="B550" s="11"/>
       <c r="C550" s="7"/>
       <c r="D550" s="7"/>
@@ -20119,7 +20027,6 @@
       <c r="Z550" s="7"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
-      <c r="A551" s="11"/>
       <c r="B551" s="11"/>
       <c r="C551" s="7"/>
       <c r="D551" s="7"/>
@@ -20147,7 +20054,6 @@
       <c r="Z551" s="7"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
-      <c r="A552" s="11"/>
       <c r="B552" s="11"/>
       <c r="C552" s="7"/>
       <c r="D552" s="7"/>
@@ -20175,7 +20081,6 @@
       <c r="Z552" s="7"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
-      <c r="A553" s="11"/>
       <c r="B553" s="11"/>
       <c r="C553" s="7"/>
       <c r="D553" s="7"/>
@@ -20203,7 +20108,6 @@
       <c r="Z553" s="7"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
-      <c r="A554" s="11"/>
       <c r="B554" s="11"/>
       <c r="C554" s="7"/>
       <c r="D554" s="7"/>
@@ -20231,7 +20135,6 @@
       <c r="Z554" s="7"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
-      <c r="A555" s="11"/>
       <c r="B555" s="11"/>
       <c r="C555" s="7"/>
       <c r="D555" s="7"/>
@@ -20259,7 +20162,6 @@
       <c r="Z555" s="7"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
-      <c r="A556" s="11"/>
       <c r="B556" s="11"/>
       <c r="C556" s="7"/>
       <c r="D556" s="7"/>
@@ -20287,7 +20189,6 @@
       <c r="Z556" s="7"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
-      <c r="A557" s="11"/>
       <c r="B557" s="11"/>
       <c r="C557" s="7"/>
       <c r="D557" s="7"/>
@@ -20315,7 +20216,6 @@
       <c r="Z557" s="7"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
-      <c r="A558" s="11"/>
       <c r="B558" s="11"/>
       <c r="C558" s="7"/>
       <c r="D558" s="7"/>
@@ -20343,7 +20243,6 @@
       <c r="Z558" s="7"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
-      <c r="A559" s="11"/>
       <c r="B559" s="11"/>
       <c r="C559" s="7"/>
       <c r="D559" s="7"/>
@@ -20371,7 +20270,6 @@
       <c r="Z559" s="7"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
-      <c r="A560" s="11"/>
       <c r="B560" s="11"/>
       <c r="C560" s="7"/>
       <c r="D560" s="7"/>
@@ -20399,7 +20297,6 @@
       <c r="Z560" s="7"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
-      <c r="A561" s="11"/>
       <c r="B561" s="11"/>
       <c r="C561" s="7"/>
       <c r="D561" s="7"/>
@@ -20427,7 +20324,6 @@
       <c r="Z561" s="7"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
-      <c r="A562" s="11"/>
       <c r="B562" s="11"/>
       <c r="C562" s="7"/>
       <c r="D562" s="7"/>
@@ -20455,7 +20351,6 @@
       <c r="Z562" s="7"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
-      <c r="A563" s="11"/>
       <c r="B563" s="11"/>
       <c r="C563" s="7"/>
       <c r="D563" s="7"/>
@@ -20483,7 +20378,6 @@
       <c r="Z563" s="7"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
-      <c r="A564" s="11"/>
       <c r="B564" s="11"/>
       <c r="C564" s="7"/>
       <c r="D564" s="7"/>
@@ -20511,7 +20405,6 @@
       <c r="Z564" s="7"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
-      <c r="A565" s="11"/>
       <c r="B565" s="11"/>
       <c r="C565" s="7"/>
       <c r="D565" s="7"/>
@@ -20539,7 +20432,6 @@
       <c r="Z565" s="7"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
-      <c r="A566" s="11"/>
       <c r="B566" s="11"/>
       <c r="C566" s="7"/>
       <c r="D566" s="7"/>
@@ -20567,7 +20459,6 @@
       <c r="Z566" s="7"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
-      <c r="A567" s="11"/>
       <c r="B567" s="11"/>
       <c r="C567" s="7"/>
       <c r="D567" s="7"/>
@@ -20595,7 +20486,6 @@
       <c r="Z567" s="7"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
-      <c r="A568" s="11"/>
       <c r="B568" s="11"/>
       <c r="C568" s="7"/>
       <c r="D568" s="7"/>
@@ -20623,7 +20513,6 @@
       <c r="Z568" s="7"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
-      <c r="A569" s="11"/>
       <c r="B569" s="11"/>
       <c r="C569" s="7"/>
       <c r="D569" s="7"/>
@@ -20651,7 +20540,6 @@
       <c r="Z569" s="7"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
-      <c r="A570" s="11"/>
       <c r="B570" s="11"/>
       <c r="C570" s="7"/>
       <c r="D570" s="7"/>
@@ -20679,7 +20567,6 @@
       <c r="Z570" s="7"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
-      <c r="A571" s="11"/>
       <c r="B571" s="11"/>
       <c r="C571" s="7"/>
       <c r="D571" s="7"/>
@@ -20707,7 +20594,6 @@
       <c r="Z571" s="7"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
-      <c r="A572" s="11"/>
       <c r="B572" s="11"/>
       <c r="C572" s="7"/>
       <c r="D572" s="7"/>
@@ -20735,7 +20621,6 @@
       <c r="Z572" s="7"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
-      <c r="A573" s="11"/>
       <c r="B573" s="11"/>
       <c r="C573" s="7"/>
       <c r="D573" s="7"/>
@@ -20763,7 +20648,6 @@
       <c r="Z573" s="7"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
-      <c r="A574" s="11"/>
       <c r="B574" s="11"/>
       <c r="C574" s="7"/>
       <c r="D574" s="7"/>
@@ -20791,7 +20675,6 @@
       <c r="Z574" s="7"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
-      <c r="A575" s="11"/>
       <c r="B575" s="11"/>
       <c r="C575" s="7"/>
       <c r="D575" s="7"/>
@@ -20819,7 +20702,6 @@
       <c r="Z575" s="7"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
-      <c r="A576" s="11"/>
       <c r="B576" s="11"/>
       <c r="C576" s="7"/>
       <c r="D576" s="7"/>
@@ -20847,7 +20729,6 @@
       <c r="Z576" s="7"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
-      <c r="A577" s="11"/>
       <c r="B577" s="11"/>
       <c r="C577" s="7"/>
       <c r="D577" s="7"/>
@@ -20875,7 +20756,6 @@
       <c r="Z577" s="7"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
-      <c r="A578" s="11"/>
       <c r="B578" s="11"/>
       <c r="C578" s="7"/>
       <c r="D578" s="7"/>
@@ -20903,7 +20783,6 @@
       <c r="Z578" s="7"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
-      <c r="A579" s="11"/>
       <c r="B579" s="11"/>
       <c r="C579" s="7"/>
       <c r="D579" s="7"/>
@@ -20931,7 +20810,6 @@
       <c r="Z579" s="7"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
-      <c r="A580" s="11"/>
       <c r="B580" s="11"/>
       <c r="C580" s="7"/>
       <c r="D580" s="7"/>
@@ -20959,7 +20837,6 @@
       <c r="Z580" s="7"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
-      <c r="A581" s="11"/>
       <c r="B581" s="11"/>
       <c r="C581" s="7"/>
       <c r="D581" s="7"/>
@@ -20987,7 +20864,6 @@
       <c r="Z581" s="7"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
-      <c r="A582" s="11"/>
       <c r="B582" s="11"/>
       <c r="C582" s="7"/>
       <c r="D582" s="7"/>
@@ -21015,7 +20891,6 @@
       <c r="Z582" s="7"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
-      <c r="A583" s="11"/>
       <c r="B583" s="11"/>
       <c r="C583" s="7"/>
       <c r="D583" s="7"/>
@@ -21043,7 +20918,6 @@
       <c r="Z583" s="7"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
-      <c r="A584" s="11"/>
       <c r="B584" s="11"/>
       <c r="C584" s="7"/>
       <c r="D584" s="7"/>
@@ -21071,7 +20945,6 @@
       <c r="Z584" s="7"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
-      <c r="A585" s="11"/>
       <c r="B585" s="11"/>
       <c r="C585" s="7"/>
       <c r="D585" s="7"/>
@@ -21099,7 +20972,6 @@
       <c r="Z585" s="7"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
-      <c r="A586" s="11"/>
       <c r="B586" s="11"/>
       <c r="C586" s="7"/>
       <c r="D586" s="7"/>
@@ -21127,7 +20999,6 @@
       <c r="Z586" s="7"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
-      <c r="A587" s="11"/>
       <c r="B587" s="11"/>
       <c r="C587" s="7"/>
       <c r="D587" s="7"/>
@@ -21155,7 +21026,6 @@
       <c r="Z587" s="7"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
-      <c r="A588" s="11"/>
       <c r="B588" s="11"/>
       <c r="C588" s="7"/>
       <c r="D588" s="7"/>
@@ -21183,7 +21053,6 @@
       <c r="Z588" s="7"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
-      <c r="A589" s="11"/>
       <c r="B589" s="11"/>
       <c r="C589" s="7"/>
       <c r="D589" s="7"/>
@@ -21211,7 +21080,6 @@
       <c r="Z589" s="7"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="A590" s="11"/>
       <c r="B590" s="11"/>
       <c r="C590" s="7"/>
       <c r="D590" s="7"/>
@@ -21239,7 +21107,6 @@
       <c r="Z590" s="7"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
-      <c r="A591" s="11"/>
       <c r="B591" s="11"/>
       <c r="C591" s="7"/>
       <c r="D591" s="7"/>
@@ -21267,7 +21134,6 @@
       <c r="Z591" s="7"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
-      <c r="A592" s="11"/>
       <c r="B592" s="11"/>
       <c r="C592" s="7"/>
       <c r="D592" s="7"/>
@@ -21295,7 +21161,6 @@
       <c r="Z592" s="7"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
-      <c r="A593" s="11"/>
       <c r="B593" s="11"/>
       <c r="C593" s="7"/>
       <c r="D593" s="7"/>
@@ -21323,7 +21188,6 @@
       <c r="Z593" s="7"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
-      <c r="A594" s="11"/>
       <c r="B594" s="11"/>
       <c r="C594" s="7"/>
       <c r="D594" s="7"/>
@@ -21351,7 +21215,6 @@
       <c r="Z594" s="7"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
-      <c r="A595" s="11"/>
       <c r="B595" s="11"/>
       <c r="C595" s="7"/>
       <c r="D595" s="7"/>
@@ -21379,7 +21242,6 @@
       <c r="Z595" s="7"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
-      <c r="A596" s="11"/>
       <c r="B596" s="11"/>
       <c r="C596" s="7"/>
       <c r="D596" s="7"/>
@@ -21407,7 +21269,6 @@
       <c r="Z596" s="7"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
-      <c r="A597" s="11"/>
       <c r="B597" s="11"/>
       <c r="C597" s="7"/>
       <c r="D597" s="7"/>
@@ -21435,1615 +21296,1212 @@
       <c r="Z597" s="7"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="A598" s="26"/>
       <c r="B598" s="26"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="A599" s="26"/>
       <c r="B599" s="26"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="A600" s="26"/>
       <c r="B600" s="26"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="A601" s="26"/>
       <c r="B601" s="26"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="A602" s="26"/>
       <c r="B602" s="26"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="A603" s="26"/>
       <c r="B603" s="26"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="A604" s="26"/>
       <c r="B604" s="26"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="A605" s="26"/>
       <c r="B605" s="26"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="A606" s="26"/>
       <c r="B606" s="26"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="A607" s="26"/>
       <c r="B607" s="26"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="A608" s="26"/>
       <c r="B608" s="26"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="A609" s="26"/>
       <c r="B609" s="26"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="A610" s="26"/>
       <c r="B610" s="26"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="A611" s="26"/>
       <c r="B611" s="26"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="A612" s="26"/>
       <c r="B612" s="26"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="A613" s="26"/>
       <c r="B613" s="26"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="A614" s="26"/>
       <c r="B614" s="26"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="A615" s="26"/>
       <c r="B615" s="26"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="A616" s="26"/>
       <c r="B616" s="26"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="A617" s="26"/>
       <c r="B617" s="26"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="A618" s="26"/>
       <c r="B618" s="26"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="A619" s="26"/>
       <c r="B619" s="26"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="A620" s="26"/>
       <c r="B620" s="26"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="A621" s="26"/>
       <c r="B621" s="26"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="A622" s="26"/>
       <c r="B622" s="26"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="A623" s="26"/>
       <c r="B623" s="26"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="A624" s="26"/>
       <c r="B624" s="26"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="A625" s="26"/>
       <c r="B625" s="26"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="A626" s="26"/>
       <c r="B626" s="26"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="A627" s="26"/>
       <c r="B627" s="26"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="A628" s="26"/>
       <c r="B628" s="26"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="A629" s="26"/>
       <c r="B629" s="26"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="A630" s="26"/>
       <c r="B630" s="26"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="A631" s="26"/>
       <c r="B631" s="26"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="A632" s="26"/>
       <c r="B632" s="26"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="A633" s="26"/>
       <c r="B633" s="26"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="A634" s="26"/>
       <c r="B634" s="26"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="A635" s="26"/>
       <c r="B635" s="26"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="A636" s="26"/>
       <c r="B636" s="26"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="A637" s="26"/>
       <c r="B637" s="26"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="A638" s="26"/>
       <c r="B638" s="26"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="A639" s="26"/>
       <c r="B639" s="26"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="A640" s="26"/>
       <c r="B640" s="26"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="A641" s="26"/>
       <c r="B641" s="26"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="A642" s="26"/>
       <c r="B642" s="26"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="A643" s="26"/>
       <c r="B643" s="26"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="A644" s="26"/>
       <c r="B644" s="26"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="A645" s="26"/>
       <c r="B645" s="26"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="A646" s="26"/>
       <c r="B646" s="26"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="A647" s="26"/>
       <c r="B647" s="26"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="A648" s="26"/>
       <c r="B648" s="26"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="A649" s="26"/>
       <c r="B649" s="26"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="A650" s="26"/>
       <c r="B650" s="26"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="A651" s="26"/>
       <c r="B651" s="26"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="A652" s="26"/>
       <c r="B652" s="26"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="A653" s="26"/>
       <c r="B653" s="26"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="A654" s="26"/>
       <c r="B654" s="26"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="A655" s="26"/>
       <c r="B655" s="26"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="A656" s="26"/>
       <c r="B656" s="26"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="A657" s="26"/>
       <c r="B657" s="26"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="A658" s="26"/>
       <c r="B658" s="26"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="A659" s="26"/>
       <c r="B659" s="26"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="A660" s="26"/>
       <c r="B660" s="26"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="A661" s="26"/>
       <c r="B661" s="26"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="A662" s="26"/>
       <c r="B662" s="26"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="A663" s="26"/>
       <c r="B663" s="26"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="A664" s="26"/>
       <c r="B664" s="26"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="A665" s="26"/>
       <c r="B665" s="26"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="A666" s="26"/>
       <c r="B666" s="26"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="A667" s="26"/>
       <c r="B667" s="26"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="A668" s="26"/>
       <c r="B668" s="26"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="A669" s="26"/>
       <c r="B669" s="26"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="A670" s="26"/>
       <c r="B670" s="26"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="A671" s="26"/>
       <c r="B671" s="26"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="A672" s="26"/>
       <c r="B672" s="26"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="A673" s="26"/>
       <c r="B673" s="26"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="A674" s="26"/>
       <c r="B674" s="26"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="A675" s="26"/>
       <c r="B675" s="26"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="A676" s="26"/>
       <c r="B676" s="26"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="A677" s="26"/>
       <c r="B677" s="26"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="A678" s="26"/>
       <c r="B678" s="26"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="A679" s="26"/>
       <c r="B679" s="26"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="A680" s="26"/>
       <c r="B680" s="26"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="A681" s="26"/>
       <c r="B681" s="26"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="A682" s="26"/>
       <c r="B682" s="26"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="A683" s="26"/>
       <c r="B683" s="26"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="A684" s="26"/>
       <c r="B684" s="26"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="A685" s="26"/>
       <c r="B685" s="26"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="A686" s="26"/>
       <c r="B686" s="26"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="A687" s="26"/>
       <c r="B687" s="26"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="A688" s="26"/>
       <c r="B688" s="26"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="A689" s="26"/>
       <c r="B689" s="26"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="A690" s="26"/>
       <c r="B690" s="26"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="A691" s="26"/>
       <c r="B691" s="26"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="A692" s="26"/>
       <c r="B692" s="26"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="A693" s="26"/>
       <c r="B693" s="26"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="A694" s="26"/>
       <c r="B694" s="26"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="A695" s="26"/>
       <c r="B695" s="26"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="A696" s="26"/>
       <c r="B696" s="26"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="A697" s="26"/>
       <c r="B697" s="26"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="A698" s="26"/>
       <c r="B698" s="26"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="A699" s="26"/>
       <c r="B699" s="26"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="A700" s="26"/>
       <c r="B700" s="26"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="A701" s="26"/>
       <c r="B701" s="26"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="A702" s="26"/>
       <c r="B702" s="26"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="A703" s="26"/>
       <c r="B703" s="26"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="A704" s="26"/>
       <c r="B704" s="26"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="A705" s="26"/>
       <c r="B705" s="26"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="A706" s="26"/>
       <c r="B706" s="26"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="A707" s="26"/>
       <c r="B707" s="26"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="A708" s="26"/>
       <c r="B708" s="26"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="A709" s="26"/>
       <c r="B709" s="26"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="A710" s="26"/>
       <c r="B710" s="26"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="A711" s="26"/>
       <c r="B711" s="26"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="A712" s="26"/>
       <c r="B712" s="26"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="A713" s="26"/>
       <c r="B713" s="26"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="A714" s="26"/>
       <c r="B714" s="26"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="A715" s="26"/>
       <c r="B715" s="26"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="A716" s="26"/>
       <c r="B716" s="26"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="A717" s="26"/>
       <c r="B717" s="26"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="A718" s="26"/>
       <c r="B718" s="26"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="A719" s="26"/>
       <c r="B719" s="26"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="A720" s="26"/>
       <c r="B720" s="26"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="A721" s="26"/>
       <c r="B721" s="26"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="A722" s="26"/>
       <c r="B722" s="26"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="A723" s="26"/>
       <c r="B723" s="26"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="A724" s="26"/>
       <c r="B724" s="26"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="A725" s="26"/>
       <c r="B725" s="26"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="A726" s="26"/>
       <c r="B726" s="26"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="A727" s="26"/>
       <c r="B727" s="26"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="A728" s="26"/>
       <c r="B728" s="26"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="A729" s="26"/>
       <c r="B729" s="26"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="A730" s="26"/>
       <c r="B730" s="26"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="A731" s="26"/>
       <c r="B731" s="26"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="A732" s="26"/>
       <c r="B732" s="26"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="A733" s="26"/>
       <c r="B733" s="26"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="A734" s="26"/>
       <c r="B734" s="26"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="A735" s="26"/>
       <c r="B735" s="26"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="A736" s="26"/>
       <c r="B736" s="26"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="A737" s="26"/>
       <c r="B737" s="26"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="A738" s="26"/>
       <c r="B738" s="26"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="A739" s="26"/>
       <c r="B739" s="26"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="A740" s="26"/>
       <c r="B740" s="26"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="A741" s="26"/>
       <c r="B741" s="26"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="A742" s="26"/>
       <c r="B742" s="26"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="A743" s="26"/>
       <c r="B743" s="26"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="A744" s="26"/>
       <c r="B744" s="26"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="A745" s="26"/>
       <c r="B745" s="26"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="A746" s="26"/>
       <c r="B746" s="26"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="A747" s="26"/>
       <c r="B747" s="26"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="A748" s="26"/>
       <c r="B748" s="26"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="A749" s="26"/>
       <c r="B749" s="26"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="A750" s="26"/>
       <c r="B750" s="26"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="A751" s="26"/>
       <c r="B751" s="26"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="A752" s="26"/>
       <c r="B752" s="26"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="A753" s="26"/>
       <c r="B753" s="26"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="A754" s="26"/>
       <c r="B754" s="26"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="A755" s="26"/>
       <c r="B755" s="26"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="A756" s="26"/>
       <c r="B756" s="26"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="A757" s="26"/>
       <c r="B757" s="26"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="A758" s="26"/>
       <c r="B758" s="26"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="A759" s="26"/>
       <c r="B759" s="26"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="A760" s="26"/>
       <c r="B760" s="26"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="A761" s="26"/>
       <c r="B761" s="26"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="A762" s="26"/>
       <c r="B762" s="26"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="A763" s="26"/>
       <c r="B763" s="26"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="A764" s="26"/>
       <c r="B764" s="26"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="A765" s="26"/>
       <c r="B765" s="26"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="A766" s="26"/>
       <c r="B766" s="26"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="A767" s="26"/>
       <c r="B767" s="26"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="A768" s="26"/>
       <c r="B768" s="26"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="A769" s="26"/>
       <c r="B769" s="26"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="A770" s="26"/>
       <c r="B770" s="26"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="A771" s="26"/>
       <c r="B771" s="26"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="A772" s="26"/>
       <c r="B772" s="26"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="A773" s="26"/>
       <c r="B773" s="26"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="A774" s="26"/>
       <c r="B774" s="26"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="A775" s="26"/>
       <c r="B775" s="26"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="A776" s="26"/>
       <c r="B776" s="26"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="A777" s="26"/>
       <c r="B777" s="26"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="A778" s="26"/>
       <c r="B778" s="26"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="A779" s="26"/>
       <c r="B779" s="26"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="A780" s="26"/>
       <c r="B780" s="26"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="A781" s="26"/>
       <c r="B781" s="26"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="A782" s="26"/>
       <c r="B782" s="26"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="A783" s="26"/>
       <c r="B783" s="26"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="A784" s="26"/>
       <c r="B784" s="26"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="A785" s="26"/>
       <c r="B785" s="26"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="A786" s="26"/>
       <c r="B786" s="26"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="A787" s="26"/>
       <c r="B787" s="26"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="A788" s="26"/>
       <c r="B788" s="26"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="A789" s="26"/>
       <c r="B789" s="26"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="A790" s="26"/>
       <c r="B790" s="26"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="A791" s="26"/>
       <c r="B791" s="26"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="A792" s="26"/>
       <c r="B792" s="26"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="A793" s="26"/>
       <c r="B793" s="26"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="A794" s="26"/>
       <c r="B794" s="26"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="A795" s="26"/>
       <c r="B795" s="26"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="A796" s="26"/>
       <c r="B796" s="26"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="A797" s="26"/>
       <c r="B797" s="26"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="A798" s="26"/>
       <c r="B798" s="26"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="A799" s="26"/>
       <c r="B799" s="26"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="A800" s="26"/>
       <c r="B800" s="26"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="A801" s="26"/>
       <c r="B801" s="26"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="A802" s="26"/>
       <c r="B802" s="26"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="A803" s="26"/>
       <c r="B803" s="26"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="A804" s="26"/>
       <c r="B804" s="26"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="A805" s="26"/>
       <c r="B805" s="26"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="A806" s="26"/>
       <c r="B806" s="26"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="A807" s="26"/>
       <c r="B807" s="26"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="A808" s="26"/>
       <c r="B808" s="26"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="A809" s="26"/>
       <c r="B809" s="26"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="A810" s="26"/>
       <c r="B810" s="26"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="A811" s="26"/>
       <c r="B811" s="26"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="A812" s="26"/>
       <c r="B812" s="26"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="A813" s="26"/>
       <c r="B813" s="26"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="A814" s="26"/>
       <c r="B814" s="26"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="A815" s="26"/>
       <c r="B815" s="26"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="A816" s="26"/>
       <c r="B816" s="26"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="A817" s="26"/>
       <c r="B817" s="26"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="A818" s="26"/>
       <c r="B818" s="26"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="A819" s="26"/>
       <c r="B819" s="26"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="A820" s="26"/>
       <c r="B820" s="26"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="A821" s="26"/>
       <c r="B821" s="26"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="A822" s="26"/>
       <c r="B822" s="26"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="A823" s="26"/>
       <c r="B823" s="26"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="A824" s="26"/>
       <c r="B824" s="26"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="A825" s="26"/>
       <c r="B825" s="26"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="A826" s="26"/>
       <c r="B826" s="26"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="A827" s="26"/>
       <c r="B827" s="26"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="A828" s="26"/>
       <c r="B828" s="26"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="A829" s="26"/>
       <c r="B829" s="26"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="A830" s="26"/>
       <c r="B830" s="26"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="A831" s="26"/>
       <c r="B831" s="26"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="A832" s="26"/>
       <c r="B832" s="26"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="A833" s="26"/>
       <c r="B833" s="26"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="A834" s="26"/>
       <c r="B834" s="26"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="A835" s="26"/>
       <c r="B835" s="26"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="A836" s="26"/>
       <c r="B836" s="26"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="A837" s="26"/>
       <c r="B837" s="26"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="A838" s="26"/>
       <c r="B838" s="26"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="A839" s="26"/>
       <c r="B839" s="26"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="A840" s="26"/>
       <c r="B840" s="26"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="A841" s="26"/>
       <c r="B841" s="26"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="A842" s="26"/>
       <c r="B842" s="26"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="A843" s="26"/>
       <c r="B843" s="26"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="A844" s="26"/>
       <c r="B844" s="26"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="A845" s="26"/>
       <c r="B845" s="26"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="A846" s="26"/>
       <c r="B846" s="26"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="A847" s="26"/>
       <c r="B847" s="26"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="A848" s="26"/>
       <c r="B848" s="26"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="A849" s="26"/>
       <c r="B849" s="26"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="A850" s="26"/>
       <c r="B850" s="26"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="A851" s="26"/>
       <c r="B851" s="26"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="A852" s="26"/>
       <c r="B852" s="26"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="A853" s="26"/>
       <c r="B853" s="26"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="A854" s="26"/>
       <c r="B854" s="26"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="A855" s="26"/>
       <c r="B855" s="26"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="A856" s="26"/>
       <c r="B856" s="26"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="A857" s="26"/>
       <c r="B857" s="26"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="A858" s="26"/>
       <c r="B858" s="26"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="A859" s="26"/>
       <c r="B859" s="26"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="A860" s="26"/>
       <c r="B860" s="26"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="A861" s="26"/>
       <c r="B861" s="26"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="A862" s="26"/>
       <c r="B862" s="26"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="A863" s="26"/>
       <c r="B863" s="26"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="A864" s="26"/>
       <c r="B864" s="26"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="A865" s="26"/>
       <c r="B865" s="26"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="A866" s="26"/>
       <c r="B866" s="26"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="A867" s="26"/>
       <c r="B867" s="26"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="A868" s="26"/>
       <c r="B868" s="26"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="A869" s="26"/>
       <c r="B869" s="26"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="A870" s="26"/>
       <c r="B870" s="26"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="A871" s="26"/>
       <c r="B871" s="26"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="A872" s="26"/>
       <c r="B872" s="26"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="A873" s="26"/>
       <c r="B873" s="26"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="A874" s="26"/>
       <c r="B874" s="26"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="A875" s="26"/>
       <c r="B875" s="26"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="A876" s="26"/>
       <c r="B876" s="26"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="A877" s="26"/>
       <c r="B877" s="26"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="A878" s="26"/>
       <c r="B878" s="26"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="A879" s="26"/>
       <c r="B879" s="26"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="A880" s="26"/>
       <c r="B880" s="26"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="A881" s="26"/>
       <c r="B881" s="26"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="A882" s="26"/>
       <c r="B882" s="26"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="A883" s="26"/>
       <c r="B883" s="26"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="A884" s="26"/>
       <c r="B884" s="26"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="A885" s="26"/>
       <c r="B885" s="26"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="A886" s="26"/>
       <c r="B886" s="26"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="A887" s="26"/>
       <c r="B887" s="26"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="A888" s="26"/>
       <c r="B888" s="26"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="A889" s="26"/>
       <c r="B889" s="26"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="A890" s="26"/>
       <c r="B890" s="26"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="A891" s="26"/>
       <c r="B891" s="26"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="A892" s="26"/>
       <c r="B892" s="26"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="A893" s="26"/>
       <c r="B893" s="26"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="A894" s="26"/>
       <c r="B894" s="26"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="A895" s="26"/>
       <c r="B895" s="26"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="A896" s="26"/>
       <c r="B896" s="26"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="A897" s="26"/>
       <c r="B897" s="26"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="A898" s="26"/>
       <c r="B898" s="26"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="A899" s="26"/>
       <c r="B899" s="26"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="A900" s="26"/>
       <c r="B900" s="26"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="A901" s="26"/>
       <c r="B901" s="26"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="A902" s="26"/>
       <c r="B902" s="26"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="A903" s="26"/>
       <c r="B903" s="26"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="A904" s="26"/>
       <c r="B904" s="26"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="A905" s="26"/>
       <c r="B905" s="26"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="A906" s="26"/>
       <c r="B906" s="26"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="A907" s="26"/>
       <c r="B907" s="26"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="A908" s="26"/>
       <c r="B908" s="26"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="A909" s="26"/>
       <c r="B909" s="26"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="A910" s="26"/>
       <c r="B910" s="26"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="A911" s="26"/>
       <c r="B911" s="26"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="A912" s="26"/>
       <c r="B912" s="26"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="A913" s="26"/>
       <c r="B913" s="26"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="A914" s="26"/>
       <c r="B914" s="26"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="A915" s="26"/>
       <c r="B915" s="26"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="A916" s="26"/>
       <c r="B916" s="26"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="A917" s="26"/>
       <c r="B917" s="26"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="A918" s="26"/>
       <c r="B918" s="26"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="A919" s="26"/>
       <c r="B919" s="26"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="A920" s="26"/>
       <c r="B920" s="26"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="A921" s="26"/>
       <c r="B921" s="26"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="A922" s="26"/>
       <c r="B922" s="26"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="A923" s="26"/>
       <c r="B923" s="26"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="A924" s="26"/>
       <c r="B924" s="26"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="A925" s="26"/>
       <c r="B925" s="26"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="A926" s="26"/>
       <c r="B926" s="26"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="A927" s="26"/>
       <c r="B927" s="26"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="A928" s="26"/>
       <c r="B928" s="26"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="A929" s="26"/>
       <c r="B929" s="26"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="A930" s="26"/>
       <c r="B930" s="26"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="A931" s="26"/>
       <c r="B931" s="26"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="A932" s="26"/>
       <c r="B932" s="26"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="A933" s="26"/>
       <c r="B933" s="26"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="A934" s="26"/>
       <c r="B934" s="26"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="A935" s="26"/>
       <c r="B935" s="26"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="A936" s="26"/>
       <c r="B936" s="26"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="A937" s="26"/>
       <c r="B937" s="26"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="A938" s="26"/>
       <c r="B938" s="26"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="A939" s="26"/>
       <c r="B939" s="26"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="A940" s="26"/>
       <c r="B940" s="26"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="A941" s="26"/>
       <c r="B941" s="26"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="A942" s="26"/>
       <c r="B942" s="26"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="A943" s="26"/>
       <c r="B943" s="26"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="A944" s="26"/>
       <c r="B944" s="26"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="A945" s="26"/>
       <c r="B945" s="26"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="A946" s="26"/>
       <c r="B946" s="26"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="A947" s="26"/>
       <c r="B947" s="26"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="A948" s="26"/>
       <c r="B948" s="26"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="A949" s="26"/>
       <c r="B949" s="26"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="A950" s="26"/>
       <c r="B950" s="26"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="A951" s="26"/>
       <c r="B951" s="26"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="A952" s="26"/>
       <c r="B952" s="26"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="A953" s="26"/>
       <c r="B953" s="26"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="A954" s="26"/>
       <c r="B954" s="26"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="A955" s="26"/>
       <c r="B955" s="26"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="A956" s="26"/>
       <c r="B956" s="26"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="A957" s="26"/>
       <c r="B957" s="26"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="A958" s="26"/>
       <c r="B958" s="26"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="A959" s="26"/>
       <c r="B959" s="26"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="A960" s="26"/>
       <c r="B960" s="26"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="A961" s="26"/>
       <c r="B961" s="26"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="A962" s="26"/>
       <c r="B962" s="26"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="A963" s="26"/>
       <c r="B963" s="26"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="A964" s="26"/>
       <c r="B964" s="26"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="A965" s="26"/>
       <c r="B965" s="26"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="A966" s="26"/>
       <c r="B966" s="26"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="A967" s="26"/>
       <c r="B967" s="26"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="A968" s="26"/>
       <c r="B968" s="26"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="A969" s="26"/>
       <c r="B969" s="26"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="A970" s="26"/>
       <c r="B970" s="26"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="A971" s="26"/>
       <c r="B971" s="26"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="A972" s="26"/>
       <c r="B972" s="26"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="A973" s="26"/>
       <c r="B973" s="26"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="A974" s="26"/>
       <c r="B974" s="26"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="A975" s="26"/>
       <c r="B975" s="26"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="A976" s="26"/>
       <c r="B976" s="26"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="A977" s="26"/>
       <c r="B977" s="26"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="A978" s="26"/>
       <c r="B978" s="26"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="A979" s="26"/>
       <c r="B979" s="26"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="A980" s="26"/>
       <c r="B980" s="26"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="A981" s="26"/>
       <c r="B981" s="26"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="A982" s="26"/>
       <c r="B982" s="26"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="A983" s="26"/>
       <c r="B983" s="26"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="A984" s="26"/>
       <c r="B984" s="26"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="A985" s="26"/>
       <c r="B985" s="26"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="A986" s="26"/>
       <c r="B986" s="26"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="A987" s="26"/>
       <c r="B987" s="26"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="A988" s="26"/>
       <c r="B988" s="26"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="A989" s="26"/>
       <c r="B989" s="26"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="A990" s="26"/>
       <c r="B990" s="26"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="A991" s="26"/>
       <c r="B991" s="26"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="A992" s="26"/>
       <c r="B992" s="26"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="A993" s="26"/>
       <c r="B993" s="26"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="A994" s="26"/>
       <c r="B994" s="26"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="A995" s="26"/>
       <c r="B995" s="26"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="A996" s="26"/>
       <c r="B996" s="26"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="26"/>
       <c r="B997" s="26"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="A998" s="26"/>
       <c r="B998" s="26"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="26"/>
       <c r="B999" s="26"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="26"/>
       <c r="B1000" s="26"/>
     </row>
   </sheetData>

--- a/Literature/Languages/Norvunic (old).xlsx
+++ b/Literature/Languages/Norvunic (old).xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="871">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="878">
   <si>
     <t>Word</t>
   </si>
@@ -69,1167 +69,1176 @@
     <t>nus ægi blûlr = blue very robes (very blue robes)</t>
   </si>
   <si>
+    <t>any</t>
+  </si>
+  <si>
+    <t>stode</t>
+  </si>
+  <si>
+    <t>a place, or location</t>
+  </si>
+  <si>
+    <t>past tense/ed (-de)</t>
+  </si>
+  <si>
+    <t>suffix</t>
+  </si>
+  <si>
+    <t>davde = ran</t>
+  </si>
+  <si>
+    <t>plåk</t>
+  </si>
+  <si>
+    <t>a plank of wood</t>
+  </si>
+  <si>
+    <t>present tense/ing (-an)</t>
+  </si>
+  <si>
+    <t>davan = run currently (running), -nan if ends with vowel</t>
+  </si>
+  <si>
+    <t>bote</t>
+  </si>
+  <si>
+    <t>a shoe or boot</t>
+  </si>
+  <si>
+    <t>future tense/will (hav)</t>
+  </si>
+  <si>
+    <t>hav dav = will run</t>
+  </si>
+  <si>
+    <t>ralme</t>
+  </si>
+  <si>
+    <t>a sprout, or shoot of a plant</t>
+  </si>
+  <si>
+    <t>plural/s (-le)</t>
+  </si>
+  <si>
+    <t>atelgle = apples</t>
+  </si>
+  <si>
+    <t>gef</t>
+  </si>
+  <si>
+    <t>a stick</t>
+  </si>
+  <si>
+    <t>singular/a (ein)</t>
+  </si>
+  <si>
+    <t>ûn atelg = one apple (an apple)</t>
+  </si>
+  <si>
+    <t>kan</t>
+  </si>
+  <si>
+    <t>able to do something</t>
+  </si>
+  <si>
+    <t>possessive (telg)</t>
+  </si>
+  <si>
+    <t>after pronoun</t>
+  </si>
+  <si>
+    <t>eg telg sig heim = i own this house</t>
+  </si>
+  <si>
+    <t>ag</t>
+  </si>
+  <si>
+    <t>about something, or the properties of</t>
+  </si>
+  <si>
+    <t>nationality (lat) (like -ian, -ic, -ish, -ese, -i, -an)</t>
+  </si>
+  <si>
+    <t>after nation</t>
+  </si>
+  <si>
+    <t>norvun lat = norvun like (norvunic), eng lat = england like (english)</t>
+  </si>
+  <si>
+    <t>vjøl</t>
+  </si>
+  <si>
+    <t>ale, beer</t>
+  </si>
+  <si>
+    <t>language (lægi) (same thing as above)</t>
+  </si>
+  <si>
+    <t>norvunlægi = norvun speak (norvunic), englægi = england speak (english)</t>
+  </si>
+  <si>
+    <t>dyr</t>
+  </si>
+  <si>
+    <t>an animal</t>
+  </si>
+  <si>
+    <t>likeness/ness or ful (lat)</t>
+  </si>
+  <si>
+    <t>ru jeg leif lat = you be beauty like (you are beautiful)</t>
+  </si>
+  <si>
+    <t>aplege</t>
+  </si>
+  <si>
+    <t>an apple</t>
+  </si>
+  <si>
+    <t>likeness/ly (ri)</t>
+  </si>
+  <si>
+    <t>after adj or adv</t>
+  </si>
+  <si>
+    <t>fjolri = quickly</t>
+  </si>
+  <si>
+    <t>arve</t>
+  </si>
+  <si>
+    <t>an arrow for a bow</t>
+  </si>
+  <si>
+    <t>weather/ing (sorp)</t>
+  </si>
+  <si>
+    <t>pe jû jeg sorp parri = the rainwater be falling (it's raining)</t>
+  </si>
+  <si>
+    <t>uks</t>
+  </si>
+  <si>
+    <t>an axe (weapon)</t>
+  </si>
+  <si>
+    <t>ready ('ap)</t>
+  </si>
+  <si>
+    <t>hagt'ap skog = battle-for axe (axe for battle)</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>and</t>
+  </si>
+  <si>
+    <t>klæddvin</t>
+  </si>
+  <si>
+    <t>any cloth attire, or apparel; clothing</t>
+  </si>
+  <si>
+    <t>I shift</t>
+  </si>
+  <si>
+    <t>A, Å, Æ =&gt; E | E =&gt; EI | O =&gt; Ø | Ø =&gt; I | EI, I =&gt; Y | U =&gt; U</t>
+  </si>
+  <si>
+    <t>antul</t>
+  </si>
+  <si>
+    <t>any type of armor</t>
+  </si>
+  <si>
+    <t>borg</t>
+  </si>
+  <si>
+    <t>any type of fortified structure, mostly used to refer castles</t>
+  </si>
+  <si>
+    <t>mirste</t>
+  </si>
+  <si>
+    <t>any type of metal</t>
+  </si>
+  <si>
+    <t>definitive -en</t>
+  </si>
+  <si>
+    <t>add -en to word. if ends with -e, use -n. if ends with other vowel, add -nen</t>
+  </si>
+  <si>
+    <t>nem</t>
+  </si>
+  <si>
+    <t>any, some</t>
+  </si>
+  <si>
+    <t>plural -ir</t>
+  </si>
+  <si>
+    <t>add -ir to word. if ends with -e, remove the -e and add -ir. if ends with other vowel, add -nir</t>
+  </si>
+  <si>
+    <t>blogvir</t>
+  </si>
+  <si>
+    <t>around</t>
+  </si>
+  <si>
+    <t>past tense -de</t>
+  </si>
+  <si>
+    <t>remove -en, then add -de. if after removing the ending, and it ends with two different consonants (or -t or -d) (excluding consonants are r, n, m, and l), apply i shift and double the consonant | gjårken =&gt; gjårkde | akresten =&gt; akreisdde | hæsten =&gt; hesdde  (-ten is replaced with -den)</t>
+  </si>
+  <si>
+    <t>å</t>
+  </si>
+  <si>
+    <t>at</t>
+  </si>
+  <si>
+    <t>present tense -ete</t>
+  </si>
+  <si>
+    <t>remove -en</t>
+  </si>
+  <si>
+    <t>væg</t>
+  </si>
+  <si>
+    <t>away</t>
+  </si>
+  <si>
+    <t>past participle -den, -edet</t>
+  </si>
+  <si>
+    <t>remove -en, then add -den. if after removing the ending, and it ends with two different consonants (or -t or -d) (excluding consonants are r, n, m, and l), apply i shift and add -ende | gjårken =&gt; gjårkden | akresten =&gt; akreistende | hæsten =&gt; hestende  (-ten is replaced with -den)</t>
+  </si>
+  <si>
+    <t>lybe</t>
+  </si>
+  <si>
+    <t>baby</t>
+  </si>
+  <si>
+    <t>present participle -inde</t>
+  </si>
+  <si>
+    <t>remove -en, then add -inde</t>
+  </si>
+  <si>
+    <t>dym</t>
+  </si>
+  <si>
+    <t>bad</t>
+  </si>
+  <si>
+    <t>noun form of verb -inge</t>
+  </si>
+  <si>
+    <t>remove -en, then add -inge</t>
+  </si>
+  <si>
+    <t>bal</t>
+  </si>
+  <si>
+    <t>ball, sphere</t>
+  </si>
+  <si>
+    <t>imperative</t>
+  </si>
+  <si>
+    <t>remove the -n</t>
+  </si>
+  <si>
+    <t>bavked</t>
+  </si>
+  <si>
+    <t>bastard (insult)</t>
+  </si>
+  <si>
+    <t>likeness -likden</t>
+  </si>
+  <si>
+    <t>add -likden</t>
+  </si>
+  <si>
+    <t>bagt</t>
+  </si>
+  <si>
+    <t>battle, or any large-scale fight</t>
+  </si>
+  <si>
+    <t>Pronunciation</t>
+  </si>
+  <si>
+    <t>Sound</t>
+  </si>
+  <si>
+    <t>Special</t>
+  </si>
+  <si>
+    <t>dul</t>
+  </si>
+  <si>
+    <t>bean</t>
+  </si>
+  <si>
+    <t>VOWELS</t>
+  </si>
+  <si>
+    <t>A Å Æ E I O Ø U Y</t>
+  </si>
+  <si>
+    <t>byr</t>
+  </si>
+  <si>
+    <t>bear</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>/a/</t>
+  </si>
+  <si>
+    <t>kødde</t>
+  </si>
+  <si>
+    <t>bed</t>
+  </si>
+  <si>
+    <t>Å</t>
+  </si>
+  <si>
+    <t>/ɒ/</t>
+  </si>
+  <si>
+    <t>glof</t>
+  </si>
+  <si>
+    <t>being fat</t>
+  </si>
+  <si>
+    <t>Æ</t>
+  </si>
+  <si>
+    <t>/aː/</t>
+  </si>
+  <si>
+    <t>tuvig</t>
+  </si>
+  <si>
+    <t>being heavy</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>/ɛ/</t>
+  </si>
+  <si>
+    <t>berre</t>
+  </si>
+  <si>
+    <t>berry</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>/ɪ/</t>
+  </si>
+  <si>
+    <t>bag</t>
+  </si>
+  <si>
+    <t>big, vast, massive, or great</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>/ɔ/</t>
+  </si>
+  <si>
+    <t>årke</t>
+  </si>
+  <si>
+    <t>bird</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>/u/</t>
+  </si>
+  <si>
+    <t>blæke</t>
+  </si>
+  <si>
+    <t>black</t>
+  </si>
+  <si>
+    <t>bladd</t>
+  </si>
+  <si>
+    <t>blade</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>/i/</t>
+  </si>
+  <si>
+    <t>blod</t>
+  </si>
+  <si>
+    <t>blood</t>
+  </si>
+  <si>
+    <t>EA</t>
+  </si>
+  <si>
+    <t>/aːɒː/</t>
+  </si>
+  <si>
+    <t>blor</t>
+  </si>
+  <si>
+    <t>blue</t>
+  </si>
+  <si>
+    <t>EO</t>
+  </si>
+  <si>
+    <t>/ɛoː/</t>
+  </si>
+  <si>
+    <t>skått</t>
+  </si>
+  <si>
+    <t>boat</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>/r/</t>
+  </si>
+  <si>
+    <t>buv</t>
+  </si>
+  <si>
+    <t>bow (weapon)</t>
+  </si>
+  <si>
+    <t>L when its after the vowel in a syllable</t>
+  </si>
+  <si>
+    <t>/l̪/</t>
+  </si>
+  <si>
+    <t>gutte</t>
+  </si>
+  <si>
+    <t>boy</t>
+  </si>
+  <si>
+    <t>balde</t>
+  </si>
+  <si>
+    <t>brave, bold</t>
+  </si>
+  <si>
+    <t>brod</t>
+  </si>
+  <si>
+    <t>bread</t>
+  </si>
+  <si>
+    <t>glant</t>
+  </si>
+  <si>
+    <t>bright, shiny</t>
+  </si>
+  <si>
+    <t>adjectives go before nouns</t>
+  </si>
+  <si>
+    <t>ænne</t>
+  </si>
+  <si>
+    <t>but, still, or yet</t>
+  </si>
+  <si>
+    <t>adverbs go after verbs</t>
+  </si>
+  <si>
+    <t>kogve</t>
+  </si>
+  <si>
+    <t>cart, wagon</t>
+  </si>
+  <si>
+    <t>kåte</t>
+  </si>
+  <si>
+    <t>cat</t>
+  </si>
+  <si>
+    <t>question example</t>
+  </si>
+  <si>
+    <t>vil du som matig?</t>
+  </si>
+  <si>
+    <t>kuve</t>
+  </si>
+  <si>
+    <t>cattle, bull, cow</t>
+  </si>
+  <si>
+    <t>auxiliary example</t>
+  </si>
+  <si>
+    <t>eg vil eten som matig.</t>
+  </si>
+  <si>
+    <t>maille</t>
+  </si>
+  <si>
+    <t>chain mail, maille</t>
+  </si>
+  <si>
+    <t>kjele</t>
+  </si>
+  <si>
+    <t>chemise, night gown, underdress; a long undertunic for women</t>
+  </si>
+  <si>
+    <t>kopinne</t>
+  </si>
+  <si>
+    <t>chicken</t>
+  </si>
+  <si>
+    <t>møtol</t>
+  </si>
+  <si>
+    <t>cloak</t>
+  </si>
+  <si>
+    <t>klædd</t>
+  </si>
+  <si>
+    <t>cloth</t>
+  </si>
+  <si>
+    <t>stelke</t>
+  </si>
+  <si>
+    <t>cooked meat</t>
+  </si>
+  <si>
+    <t>kopper</t>
+  </si>
+  <si>
+    <t>copper</t>
+  </si>
+  <si>
+    <t>ritte</t>
+  </si>
+  <si>
+    <t>correct, right, or true</t>
+  </si>
+  <si>
+    <t>bulte</t>
+  </si>
+  <si>
+    <t>crossbow bolt</t>
+  </si>
+  <si>
+    <t>trøng</t>
+  </si>
+  <si>
+    <t>crowd, throng</t>
+  </si>
+  <si>
+    <t>krone</t>
+  </si>
+  <si>
+    <t>crown, circlet</t>
+  </si>
+  <si>
+    <t>dære</t>
+  </si>
+  <si>
+    <t>death</t>
+  </si>
+  <si>
+    <t>dir</t>
+  </si>
+  <si>
+    <t>deer</t>
+  </si>
+  <si>
+    <t>helfulg</t>
+  </si>
+  <si>
+    <t>demon</t>
+  </si>
+  <si>
+    <t>graste</t>
+  </si>
+  <si>
+    <t>disgust, or gross</t>
+  </si>
+  <si>
+    <t>beig</t>
+  </si>
+  <si>
+    <t>dog</t>
+  </si>
+  <si>
+    <t>dor</t>
+  </si>
+  <si>
+    <t>door</t>
+  </si>
+  <si>
+    <t>blomse</t>
+  </si>
+  <si>
+    <t>dress, gown</t>
+  </si>
+  <si>
+    <t>drikke</t>
+  </si>
+  <si>
+    <t>drink, beverage</t>
+  </si>
+  <si>
+    <t>galk</t>
+  </si>
+  <si>
+    <t>duck</t>
+  </si>
+  <si>
+    <t>feig</t>
+  </si>
+  <si>
+    <t>early</t>
+  </si>
+  <si>
+    <t>søt</t>
+  </si>
+  <si>
+    <t>earth, dirt, soil</t>
+  </si>
+  <si>
+    <t>alt</t>
+  </si>
+  <si>
+    <t>eight</t>
+  </si>
+  <si>
+    <t>tåge en</t>
+  </si>
+  <si>
+    <t>eleven</t>
+  </si>
+  <si>
+    <t>beste</t>
+  </si>
+  <si>
+    <t>equivalent to best</t>
+  </si>
+  <si>
+    <t>dag</t>
+  </si>
+  <si>
+    <t>equivalent to day</t>
+  </si>
+  <si>
+    <t>fæde</t>
+  </si>
+  <si>
+    <t>equivalent to fire</t>
+  </si>
+  <si>
+    <t>vydel</t>
+  </si>
+  <si>
+    <t>equivalent to sharp</t>
+  </si>
+  <si>
+    <t>alle</t>
+  </si>
+  <si>
+    <t>every, or all</t>
+  </si>
+  <si>
+    <t>tal</t>
+  </si>
+  <si>
+    <t>far, or far away</t>
+  </si>
+  <si>
+    <t>kave</t>
+  </si>
+  <si>
+    <t>fast, or quick</t>
+  </si>
+  <si>
+    <t>fellog</t>
+  </si>
+  <si>
+    <t>fate</t>
+  </si>
+  <si>
+    <t>fåde</t>
+  </si>
+  <si>
+    <t>feather, quill</t>
+  </si>
+  <si>
+    <t>hæsten</t>
+  </si>
+  <si>
+    <t>find, search</t>
+  </si>
+  <si>
+    <t>fiske</t>
+  </si>
+  <si>
+    <t>fish</t>
+  </si>
+  <si>
+    <t>falde</t>
+  </si>
+  <si>
+    <t>five</t>
+  </si>
+  <si>
+    <t>matte</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>skjorg</t>
+  </si>
+  <si>
+    <t>forest</t>
+  </si>
+  <si>
+    <t>fir</t>
+  </si>
+  <si>
+    <t>four</t>
+  </si>
+  <si>
+    <t>balbeig</t>
+  </si>
+  <si>
+    <t>fox</t>
+  </si>
+  <si>
+    <t>vin</t>
+  </si>
+  <si>
+    <t>friend, ally</t>
+  </si>
+  <si>
+    <t>fra</t>
+  </si>
+  <si>
+    <t>from</t>
+  </si>
+  <si>
+    <t>velde</t>
+  </si>
+  <si>
+    <t>fur</t>
+  </si>
+  <si>
+    <t>spåke</t>
+  </si>
+  <si>
+    <t>ghost, spirit</t>
+  </si>
+  <si>
+    <t>kirle</t>
+  </si>
+  <si>
+    <t>girl</t>
+  </si>
+  <si>
+    <t>kofte</t>
+  </si>
+  <si>
+    <t>goat</t>
+  </si>
+  <si>
+    <t>gåd</t>
+  </si>
+  <si>
+    <t>god</t>
+  </si>
+  <si>
+    <t>gleidd</t>
+  </si>
+  <si>
+    <t>gold</t>
+  </si>
+  <si>
+    <t>gode</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>gub</t>
+  </si>
+  <si>
+    <t>goose</t>
+  </si>
+  <si>
+    <t>grasse</t>
+  </si>
+  <si>
+    <t>grass</t>
+  </si>
+  <si>
+    <t>grår</t>
+  </si>
+  <si>
+    <t>gray, or grey</t>
+  </si>
+  <si>
+    <t>grene</t>
+  </si>
+  <si>
+    <t>green</t>
+  </si>
+  <si>
+    <t>gest</t>
+  </si>
+  <si>
+    <t>guest</t>
+  </si>
+  <si>
+    <t>hær</t>
+  </si>
+  <si>
+    <t>hair</t>
+  </si>
+  <si>
+    <t>hål</t>
+  </si>
+  <si>
+    <t>hallway</t>
+  </si>
+  <si>
+    <t>hese</t>
+  </si>
+  <si>
+    <t>he, him (accusative)</t>
+  </si>
+  <si>
+    <t>han</t>
+  </si>
+  <si>
+    <t>he, him (nominative)</t>
+  </si>
+  <si>
+    <t>hes</t>
+  </si>
+  <si>
+    <t>he, him (possessive)</t>
+  </si>
+  <si>
+    <t>hel</t>
+  </si>
+  <si>
+    <t>hell</t>
+  </si>
+  <si>
+    <t>hålvel</t>
+  </si>
+  <si>
+    <t>hello, hi</t>
+  </si>
+  <si>
+    <t>sære</t>
+  </si>
+  <si>
+    <t>here</t>
+  </si>
+  <si>
+    <t>hest</t>
+  </si>
+  <si>
+    <t>horse</t>
+  </si>
+  <si>
+    <t>høs</t>
+  </si>
+  <si>
+    <t>house</t>
+  </si>
+  <si>
+    <t>håg</t>
+  </si>
+  <si>
+    <t>how</t>
+  </si>
+  <si>
+    <t>halga</t>
+  </si>
+  <si>
+    <t>hundred</t>
+  </si>
+  <si>
+    <t>rumb</t>
+  </si>
+  <si>
+    <t>hungry (adjective)</t>
+  </si>
+  <si>
+    <t>meg</t>
+  </si>
+  <si>
+    <t>i, me (accusative)</t>
+  </si>
+  <si>
+    <t>eg</t>
+  </si>
+  <si>
+    <t>i, me (nominative)</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>i, me (possessive)</t>
+  </si>
+  <si>
+    <t>isk</t>
+  </si>
+  <si>
+    <t>ice</t>
+  </si>
+  <si>
+    <t>ef</t>
+  </si>
+  <si>
+    <t>if, in case, or on a condition</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>in, or into</t>
+  </si>
+  <si>
+    <t>ferk</t>
+  </si>
+  <si>
+    <t>incorrect, wrong, or false</t>
+  </si>
+  <si>
+    <t>gesthos</t>
+  </si>
+  <si>
+    <t>inn, hoten</t>
+  </si>
+  <si>
+    <t>jern</t>
+  </si>
+  <si>
+    <t>iron</t>
+  </si>
+  <si>
+    <t>er</t>
+  </si>
+  <si>
+    <t>is, am, are</t>
+  </si>
+  <si>
+    <t>sjådd</t>
+  </si>
+  <si>
+    <t>jade</t>
+  </si>
+  <si>
+    <t>lepen</t>
+  </si>
+  <si>
+    <t>jump</t>
+  </si>
+  <si>
+    <t>tøse</t>
+  </si>
+  <si>
+    <t>kid, child</t>
+  </si>
+  <si>
+    <t>kånge</t>
+  </si>
+  <si>
+    <t>king</t>
+  </si>
+  <si>
+    <t>kångelorvet</t>
+  </si>
+  <si>
+    <t>kingdom</t>
+  </si>
+  <si>
+    <t>nif</t>
+  </si>
+  <si>
+    <t>knife, dagger, dirk (weapon)</t>
+  </si>
+  <si>
+    <t>vitte</t>
+  </si>
+  <si>
+    <t>knowledge, wisdom</t>
+  </si>
+  <si>
+    <t>fryne</t>
+  </si>
+  <si>
+    <t>lady, maiden</t>
+  </si>
+  <si>
+    <t>lånde</t>
+  </si>
+  <si>
+    <t>land</t>
+  </si>
+  <si>
+    <t>mal</t>
+  </si>
+  <si>
+    <t>language</t>
+  </si>
+  <si>
+    <t>spål</t>
+  </si>
+  <si>
+    <t>late</t>
+  </si>
+  <si>
+    <t>saf</t>
+  </si>
+  <si>
+    <t>leaf</t>
+  </si>
+  <si>
+    <t>luft</t>
+  </si>
+  <si>
+    <t>left (direction)</t>
+  </si>
+  <si>
+    <t>lif</t>
+  </si>
+  <si>
+    <t>life (noun), alive (adjective)</t>
+  </si>
+  <si>
+    <t>fædinge</t>
+  </si>
+  <si>
+    <t>lightning</t>
+  </si>
+  <si>
+    <t>lang</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>jurl</t>
+  </si>
+  <si>
+    <t>lord, jarl, earl</t>
+  </si>
+  <si>
+    <t>skrøsa</t>
+  </si>
+  <si>
+    <t>lute</t>
+  </si>
+  <si>
+    <t>grøl</t>
+  </si>
+  <si>
+    <t>mace</t>
+  </si>
+  <si>
+    <t>mand</t>
+  </si>
+  <si>
+    <t>man</t>
+  </si>
+  <si>
+    <t>maf</t>
+  </si>
+  <si>
+    <t>many, much, several, or a lot of</t>
+  </si>
+  <si>
+    <t>mobre</t>
+  </si>
+  <si>
+    <t>marble</t>
+  </si>
+  <si>
+    <t>mægere</t>
+  </si>
+  <si>
+    <t>maybe, might be, or could be</t>
+  </si>
+  <si>
+    <t>mjød</t>
+  </si>
+  <si>
+    <t>mead</t>
+  </si>
+  <si>
+    <t>månt</t>
+  </si>
+  <si>
+    <t>meal</t>
+  </si>
+  <si>
+    <t>prand</t>
+  </si>
+  <si>
+    <t>message, letter</t>
+  </si>
+  <si>
+    <t>valtig</t>
+  </si>
+  <si>
+    <t>mighty</t>
+  </si>
+  <si>
+    <t>greik</t>
+  </si>
+  <si>
     <t>milk</t>
   </si>
   <si>
-    <t>stode</t>
-  </si>
-  <si>
-    <t>a place, or location</t>
-  </si>
-  <si>
-    <t>past tense/ed (-de)</t>
-  </si>
-  <si>
-    <t>suffix</t>
-  </si>
-  <si>
-    <t>davde = ran</t>
-  </si>
-  <si>
-    <t>plåk</t>
-  </si>
-  <si>
-    <t>a plank of wood</t>
-  </si>
-  <si>
-    <t>present tense/ing (-an)</t>
-  </si>
-  <si>
-    <t>davan = run currently (running), -nan if ends with vowel</t>
-  </si>
-  <si>
-    <t>bote</t>
-  </si>
-  <si>
-    <t>a shoe or boot</t>
-  </si>
-  <si>
-    <t>future tense/will (hav)</t>
-  </si>
-  <si>
-    <t>hav dav = will run</t>
-  </si>
-  <si>
-    <t>ralme</t>
-  </si>
-  <si>
-    <t>a sprout, or shoot of a plant</t>
-  </si>
-  <si>
-    <t>plural/s (-le)</t>
-  </si>
-  <si>
-    <t>atelgle = apples</t>
-  </si>
-  <si>
-    <t>gef</t>
-  </si>
-  <si>
-    <t>a stick</t>
-  </si>
-  <si>
-    <t>singular/a (ein)</t>
-  </si>
-  <si>
-    <t>ûn atelg = one apple (an apple)</t>
-  </si>
-  <si>
-    <t>kan</t>
-  </si>
-  <si>
-    <t>able to do something</t>
-  </si>
-  <si>
-    <t>possessive (telg)</t>
-  </si>
-  <si>
-    <t>after pronoun</t>
-  </si>
-  <si>
-    <t>eg telg sig heim = i own this house</t>
-  </si>
-  <si>
-    <t>ag</t>
-  </si>
-  <si>
-    <t>about something, or the properties of</t>
-  </si>
-  <si>
-    <t>nationality (lat) (like -ian, -ic, -ish, -ese, -i, -an)</t>
-  </si>
-  <si>
-    <t>after nation</t>
-  </si>
-  <si>
-    <t>norvun lat = norvun like (norvunic), eng lat = england like (english)</t>
-  </si>
-  <si>
-    <t>vjøl</t>
-  </si>
-  <si>
-    <t>ale, beer</t>
-  </si>
-  <si>
-    <t>language (lægi) (same thing as above)</t>
-  </si>
-  <si>
-    <t>norvunlægi = norvun speak (norvunic), englægi = england speak (english)</t>
-  </si>
-  <si>
-    <t>dyr</t>
-  </si>
-  <si>
-    <t>an animal</t>
-  </si>
-  <si>
-    <t>likeness/ness or ful (lat)</t>
-  </si>
-  <si>
-    <t>ru jeg leif lat = you be beauty like (you are beautiful)</t>
-  </si>
-  <si>
-    <t>aplege</t>
-  </si>
-  <si>
-    <t>an apple</t>
-  </si>
-  <si>
-    <t>likeness/ly (ri)</t>
-  </si>
-  <si>
-    <t>after adj or adv</t>
-  </si>
-  <si>
-    <t>fjolri = quickly</t>
-  </si>
-  <si>
-    <t>arve</t>
-  </si>
-  <si>
-    <t>an arrow for a bow</t>
-  </si>
-  <si>
-    <t>weather/ing (sorp)</t>
-  </si>
-  <si>
-    <t>pe jû jeg sorp parri = the rainwater be falling (it's raining)</t>
-  </si>
-  <si>
-    <t>uks</t>
-  </si>
-  <si>
-    <t>an axe (weapon)</t>
-  </si>
-  <si>
-    <t>ready ('ap)</t>
-  </si>
-  <si>
-    <t>hagt'ap skog = battle-for axe (axe for battle)</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>and</t>
-  </si>
-  <si>
-    <t>klæddvin</t>
-  </si>
-  <si>
-    <t>any cloth attire, or apparel; clothing</t>
-  </si>
-  <si>
-    <t>I shift</t>
-  </si>
-  <si>
-    <t>A, Å, Æ =&gt; E | E =&gt; EI | O =&gt; Ø | Ø =&gt; I | EI, I =&gt; Y | U =&gt; U</t>
-  </si>
-  <si>
-    <t>antul</t>
-  </si>
-  <si>
-    <t>any type of armor</t>
-  </si>
-  <si>
-    <t>borg</t>
-  </si>
-  <si>
-    <t>any type of fortified structure, mostly used to refer castles</t>
-  </si>
-  <si>
-    <t>mirste</t>
-  </si>
-  <si>
-    <t>any type of metal</t>
-  </si>
-  <si>
-    <t>definitive -en</t>
-  </si>
-  <si>
-    <t>add -en to word. if ends with -e, use -n. if ends with other vowel, add -nen</t>
-  </si>
-  <si>
-    <t>blogvir</t>
-  </si>
-  <si>
-    <t>around</t>
-  </si>
-  <si>
-    <t>plural -ir</t>
-  </si>
-  <si>
-    <t>add -ir to word. if ends with -e, remove the -e and add -ir. if ends with other vowel, add -nir</t>
-  </si>
-  <si>
-    <t>å</t>
-  </si>
-  <si>
-    <t>at</t>
-  </si>
-  <si>
-    <t>past tense -de</t>
-  </si>
-  <si>
-    <t>remove -en, then add -de. if after removing the ending, and it ends with two different consonants (or -t or -d) (excluding consonants are r, n, m, and l), apply i shift and double the consonant | gjårken =&gt; gjårkde | akresten =&gt; akreisdde | hæsten =&gt; hesdde  (-ten is replaced with -den)</t>
-  </si>
-  <si>
-    <t>væg</t>
-  </si>
-  <si>
-    <t>away</t>
-  </si>
-  <si>
-    <t>present tense -ete</t>
-  </si>
-  <si>
-    <t>remove -en</t>
-  </si>
-  <si>
-    <t>lybe</t>
-  </si>
-  <si>
-    <t>baby</t>
-  </si>
-  <si>
-    <t>past participle -den, -edet</t>
-  </si>
-  <si>
-    <t>remove -en, then add -den. if after removing the ending, and it ends with two different consonants (or -t or -d) (excluding consonants are r, n, m, and l), apply i shift and add -ende | gjårken =&gt; gjårkden | akresten =&gt; akreistende | hæsten =&gt; hestende  (-ten is replaced with -den)</t>
-  </si>
-  <si>
-    <t>dym</t>
-  </si>
-  <si>
-    <t>bad</t>
-  </si>
-  <si>
-    <t>present participle -inde</t>
-  </si>
-  <si>
-    <t>remove -en, then add -inde</t>
-  </si>
-  <si>
-    <t>bal</t>
-  </si>
-  <si>
-    <t>ball, sphere</t>
-  </si>
-  <si>
-    <t>noun form of verb -inge</t>
-  </si>
-  <si>
-    <t>remove -en, then add -inge</t>
-  </si>
-  <si>
-    <t>bavked</t>
-  </si>
-  <si>
-    <t>bastard (insult)</t>
-  </si>
-  <si>
-    <t>imperative</t>
-  </si>
-  <si>
-    <t>remove the -n</t>
-  </si>
-  <si>
-    <t>bagt</t>
-  </si>
-  <si>
-    <t>battle, or any large-scale fight</t>
-  </si>
-  <si>
-    <t>likeness -likden</t>
-  </si>
-  <si>
-    <t>add -likden</t>
-  </si>
-  <si>
-    <t>dul</t>
-  </si>
-  <si>
-    <t>bean</t>
-  </si>
-  <si>
-    <t>Pronunciation</t>
-  </si>
-  <si>
-    <t>Sound</t>
-  </si>
-  <si>
-    <t>Special</t>
-  </si>
-  <si>
-    <t>byr</t>
-  </si>
-  <si>
-    <t>bear</t>
-  </si>
-  <si>
-    <t>VOWELS</t>
-  </si>
-  <si>
-    <t>A Å Æ E I O Ø U Y</t>
-  </si>
-  <si>
-    <t>kødde</t>
-  </si>
-  <si>
-    <t>bed</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>/a/</t>
-  </si>
-  <si>
-    <t>glof</t>
-  </si>
-  <si>
-    <t>being fat</t>
-  </si>
-  <si>
-    <t>Å</t>
-  </si>
-  <si>
-    <t>/ɒ/</t>
-  </si>
-  <si>
-    <t>tuvig</t>
-  </si>
-  <si>
-    <t>being heavy</t>
-  </si>
-  <si>
-    <t>Æ</t>
-  </si>
-  <si>
-    <t>/aː/</t>
-  </si>
-  <si>
-    <t>berre</t>
-  </si>
-  <si>
-    <t>berry</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>/ɛ/</t>
-  </si>
-  <si>
-    <t>bag</t>
-  </si>
-  <si>
-    <t>big, vast, massive, or great</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>/ɪ/</t>
-  </si>
-  <si>
-    <t>årke</t>
-  </si>
-  <si>
-    <t>bird</t>
-  </si>
-  <si>
-    <t>O</t>
-  </si>
-  <si>
-    <t>/ɔ/</t>
-  </si>
-  <si>
-    <t>blæke</t>
-  </si>
-  <si>
-    <t>black</t>
-  </si>
-  <si>
-    <t>U</t>
-  </si>
-  <si>
-    <t>/u/</t>
-  </si>
-  <si>
-    <t>bladd</t>
-  </si>
-  <si>
-    <t>blade</t>
-  </si>
-  <si>
-    <t>blod</t>
-  </si>
-  <si>
-    <t>blood</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>/i/</t>
-  </si>
-  <si>
-    <t>blor</t>
-  </si>
-  <si>
-    <t>blue</t>
-  </si>
-  <si>
-    <t>EA</t>
-  </si>
-  <si>
-    <t>/aːɒː/</t>
-  </si>
-  <si>
-    <t>skått</t>
-  </si>
-  <si>
-    <t>boat</t>
-  </si>
-  <si>
-    <t>EO</t>
-  </si>
-  <si>
-    <t>/ɛoː/</t>
-  </si>
-  <si>
-    <t>buv</t>
-  </si>
-  <si>
-    <t>bow (weapon)</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>/r/</t>
-  </si>
-  <si>
-    <t>gutte</t>
-  </si>
-  <si>
-    <t>boy</t>
-  </si>
-  <si>
-    <t>L when its after the vowel in a syllable</t>
-  </si>
-  <si>
-    <t>/l̪/</t>
-  </si>
-  <si>
-    <t>balde</t>
-  </si>
-  <si>
-    <t>brave, bold</t>
-  </si>
-  <si>
-    <t>brod</t>
-  </si>
-  <si>
-    <t>bread</t>
-  </si>
-  <si>
-    <t>glant</t>
-  </si>
-  <si>
-    <t>bright, shiny</t>
-  </si>
-  <si>
-    <t>ænne</t>
-  </si>
-  <si>
-    <t>but, still, or yet</t>
-  </si>
-  <si>
-    <t>adjectives go before nouns</t>
-  </si>
-  <si>
-    <t>kogve</t>
-  </si>
-  <si>
-    <t>cart, wagon</t>
-  </si>
-  <si>
-    <t>adverbs go after verbs</t>
-  </si>
-  <si>
-    <t>kåte</t>
-  </si>
-  <si>
-    <t>cat</t>
-  </si>
-  <si>
-    <t>kuve</t>
-  </si>
-  <si>
-    <t>cattle, bull, cow</t>
-  </si>
-  <si>
-    <t>question example</t>
-  </si>
-  <si>
-    <t>vil du som matig?</t>
-  </si>
-  <si>
-    <t>maille</t>
-  </si>
-  <si>
-    <t>chain mail, maille</t>
-  </si>
-  <si>
-    <t>auxiliary example</t>
-  </si>
-  <si>
-    <t>eg vil eten som matig.</t>
-  </si>
-  <si>
-    <t>kjele</t>
-  </si>
-  <si>
-    <t>chemise, night gown, underdress; a long undertunic for women</t>
-  </si>
-  <si>
-    <t>kopinne</t>
-  </si>
-  <si>
-    <t>chicken</t>
-  </si>
-  <si>
-    <t>møtol</t>
-  </si>
-  <si>
-    <t>cloak</t>
-  </si>
-  <si>
-    <t>klædd</t>
-  </si>
-  <si>
-    <t>cloth</t>
-  </si>
-  <si>
-    <t>stelke</t>
-  </si>
-  <si>
-    <t>cooked meat</t>
-  </si>
-  <si>
-    <t>kopper</t>
-  </si>
-  <si>
-    <t>copper</t>
-  </si>
-  <si>
-    <t>ritte</t>
-  </si>
-  <si>
-    <t>correct, right, or true</t>
-  </si>
-  <si>
-    <t>bulte</t>
-  </si>
-  <si>
-    <t>crossbow bolt</t>
-  </si>
-  <si>
-    <t>trøng</t>
-  </si>
-  <si>
-    <t>crowd, throng</t>
-  </si>
-  <si>
-    <t>krone</t>
-  </si>
-  <si>
-    <t>crown, circlet</t>
-  </si>
-  <si>
-    <t>dære</t>
-  </si>
-  <si>
-    <t>death</t>
-  </si>
-  <si>
-    <t>dir</t>
-  </si>
-  <si>
-    <t>deer</t>
-  </si>
-  <si>
-    <t>helfulg</t>
-  </si>
-  <si>
-    <t>demon</t>
-  </si>
-  <si>
-    <t>graste</t>
-  </si>
-  <si>
-    <t>disgust, or gross</t>
-  </si>
-  <si>
-    <t>beig</t>
-  </si>
-  <si>
-    <t>dog</t>
-  </si>
-  <si>
-    <t>dor</t>
-  </si>
-  <si>
-    <t>door</t>
-  </si>
-  <si>
-    <t>blomse</t>
-  </si>
-  <si>
-    <t>dress, gown</t>
-  </si>
-  <si>
-    <t>drikke</t>
-  </si>
-  <si>
-    <t>drink, beverage</t>
-  </si>
-  <si>
-    <t>galk</t>
-  </si>
-  <si>
-    <t>duck</t>
-  </si>
-  <si>
-    <t>feig</t>
-  </si>
-  <si>
-    <t>early</t>
-  </si>
-  <si>
-    <t>søt</t>
-  </si>
-  <si>
-    <t>earth, dirt, soil</t>
-  </si>
-  <si>
-    <t>alt</t>
-  </si>
-  <si>
-    <t>eight</t>
-  </si>
-  <si>
-    <t>tåge en</t>
-  </si>
-  <si>
-    <t>eleven</t>
-  </si>
-  <si>
-    <t>beste</t>
-  </si>
-  <si>
-    <t>equivalent to best</t>
-  </si>
-  <si>
-    <t>dag</t>
-  </si>
-  <si>
-    <t>equivalent to day</t>
-  </si>
-  <si>
-    <t>fæde</t>
-  </si>
-  <si>
-    <t>equivalent to fire</t>
-  </si>
-  <si>
-    <t>vydel</t>
-  </si>
-  <si>
-    <t>equivalent to sharp</t>
-  </si>
-  <si>
-    <t>alle</t>
-  </si>
-  <si>
-    <t>every, or all</t>
-  </si>
-  <si>
-    <t>tal</t>
-  </si>
-  <si>
-    <t>far, or far away</t>
-  </si>
-  <si>
-    <t>kave</t>
-  </si>
-  <si>
-    <t>fast, or quick</t>
-  </si>
-  <si>
-    <t>fellog</t>
-  </si>
-  <si>
-    <t>fate</t>
-  </si>
-  <si>
-    <t>fåde</t>
-  </si>
-  <si>
-    <t>feather, quill</t>
-  </si>
-  <si>
-    <t>hæsten</t>
-  </si>
-  <si>
-    <t>find, search</t>
-  </si>
-  <si>
-    <t>fiske</t>
-  </si>
-  <si>
-    <t>fish</t>
-  </si>
-  <si>
-    <t>falde</t>
-  </si>
-  <si>
-    <t>five</t>
-  </si>
-  <si>
-    <t>matte</t>
-  </si>
-  <si>
-    <t>food</t>
-  </si>
-  <si>
-    <t>skjorg</t>
-  </si>
-  <si>
-    <t>forest</t>
-  </si>
-  <si>
-    <t>fir</t>
-  </si>
-  <si>
-    <t>four</t>
-  </si>
-  <si>
-    <t>balbeig</t>
-  </si>
-  <si>
-    <t>fox</t>
-  </si>
-  <si>
-    <t>vin</t>
-  </si>
-  <si>
-    <t>friend, ally</t>
-  </si>
-  <si>
-    <t>fra</t>
-  </si>
-  <si>
-    <t>from</t>
-  </si>
-  <si>
-    <t>velde</t>
-  </si>
-  <si>
-    <t>fur</t>
-  </si>
-  <si>
-    <t>spåke</t>
-  </si>
-  <si>
-    <t>ghost, spirit</t>
-  </si>
-  <si>
-    <t>kirle</t>
-  </si>
-  <si>
-    <t>girl</t>
-  </si>
-  <si>
-    <t>kofte</t>
-  </si>
-  <si>
-    <t>goat</t>
-  </si>
-  <si>
-    <t>gåd</t>
-  </si>
-  <si>
-    <t>god</t>
-  </si>
-  <si>
-    <t>gleidd</t>
-  </si>
-  <si>
-    <t>gold</t>
-  </si>
-  <si>
-    <t>gode</t>
-  </si>
-  <si>
-    <t>good</t>
-  </si>
-  <si>
-    <t>gub</t>
-  </si>
-  <si>
-    <t>goose</t>
-  </si>
-  <si>
-    <t>grasse</t>
-  </si>
-  <si>
-    <t>grass</t>
-  </si>
-  <si>
-    <t>grår</t>
-  </si>
-  <si>
-    <t>gray, or grey</t>
-  </si>
-  <si>
-    <t>grene</t>
-  </si>
-  <si>
-    <t>green</t>
-  </si>
-  <si>
-    <t>gest</t>
-  </si>
-  <si>
-    <t>guest</t>
-  </si>
-  <si>
-    <t>hær</t>
-  </si>
-  <si>
-    <t>hair</t>
-  </si>
-  <si>
-    <t>hål</t>
-  </si>
-  <si>
-    <t>hallway</t>
-  </si>
-  <si>
-    <t>hese</t>
-  </si>
-  <si>
-    <t>he, him (accusative)</t>
-  </si>
-  <si>
-    <t>han</t>
-  </si>
-  <si>
-    <t>he, him (nominative)</t>
-  </si>
-  <si>
-    <t>hes</t>
-  </si>
-  <si>
-    <t>he, him (possessive)</t>
-  </si>
-  <si>
-    <t>hel</t>
-  </si>
-  <si>
-    <t>hell</t>
-  </si>
-  <si>
-    <t>hålvel</t>
-  </si>
-  <si>
-    <t>hello, hi</t>
-  </si>
-  <si>
-    <t>sære</t>
-  </si>
-  <si>
-    <t>here</t>
-  </si>
-  <si>
-    <t>hest</t>
-  </si>
-  <si>
-    <t>horse</t>
-  </si>
-  <si>
-    <t>høs</t>
-  </si>
-  <si>
-    <t>house</t>
-  </si>
-  <si>
-    <t>håg</t>
-  </si>
-  <si>
-    <t>how</t>
-  </si>
-  <si>
-    <t>halga</t>
-  </si>
-  <si>
-    <t>hundred</t>
-  </si>
-  <si>
-    <t>rumb</t>
-  </si>
-  <si>
-    <t>hungry (adjective)</t>
-  </si>
-  <si>
-    <t>meg</t>
-  </si>
-  <si>
-    <t>i, me (accusative)</t>
-  </si>
-  <si>
-    <t>eg</t>
-  </si>
-  <si>
-    <t>i, me (nominative)</t>
-  </si>
-  <si>
-    <t>min</t>
-  </si>
-  <si>
-    <t>i, me (possessive)</t>
-  </si>
-  <si>
-    <t>isk</t>
-  </si>
-  <si>
-    <t>ice</t>
-  </si>
-  <si>
-    <t>ef</t>
-  </si>
-  <si>
-    <t>if, in case, or on a condition</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>in, or into</t>
-  </si>
-  <si>
-    <t>ferk</t>
-  </si>
-  <si>
-    <t>incorrect, wrong, or false</t>
-  </si>
-  <si>
-    <t>gesthos</t>
-  </si>
-  <si>
-    <t>inn, hoten</t>
-  </si>
-  <si>
-    <t>jern</t>
-  </si>
-  <si>
-    <t>iron</t>
-  </si>
-  <si>
-    <t>er</t>
-  </si>
-  <si>
-    <t>is, am, are</t>
-  </si>
-  <si>
-    <t>sjådd</t>
-  </si>
-  <si>
-    <t>jade</t>
-  </si>
-  <si>
-    <t>lepen</t>
-  </si>
-  <si>
-    <t>jump</t>
-  </si>
-  <si>
-    <t>tøse</t>
-  </si>
-  <si>
-    <t>kid, child</t>
-  </si>
-  <si>
-    <t>kånge</t>
-  </si>
-  <si>
-    <t>king</t>
-  </si>
-  <si>
-    <t>kångelorvet</t>
-  </si>
-  <si>
-    <t>kingdom</t>
-  </si>
-  <si>
-    <t>nif</t>
-  </si>
-  <si>
-    <t>knife, dagger, dirk (weapon)</t>
-  </si>
-  <si>
-    <t>vitte</t>
-  </si>
-  <si>
-    <t>knowledge, wisdom</t>
-  </si>
-  <si>
-    <t>fryne</t>
-  </si>
-  <si>
-    <t>lady, maiden</t>
-  </si>
-  <si>
-    <t>lånde</t>
-  </si>
-  <si>
-    <t>land</t>
-  </si>
-  <si>
-    <t>mal</t>
-  </si>
-  <si>
-    <t>language</t>
-  </si>
-  <si>
-    <t>spål</t>
-  </si>
-  <si>
-    <t>late</t>
-  </si>
-  <si>
-    <t>saf</t>
-  </si>
-  <si>
-    <t>leaf</t>
-  </si>
-  <si>
-    <t>luft</t>
-  </si>
-  <si>
-    <t>left (direction)</t>
-  </si>
-  <si>
-    <t>lif</t>
-  </si>
-  <si>
-    <t>life (noun), alive (adjective)</t>
-  </si>
-  <si>
-    <t>fædinge</t>
-  </si>
-  <si>
-    <t>lightning</t>
-  </si>
-  <si>
-    <t>lang</t>
-  </si>
-  <si>
-    <t>long</t>
-  </si>
-  <si>
-    <t>jurl</t>
-  </si>
-  <si>
-    <t>lord, jarl, earl</t>
-  </si>
-  <si>
-    <t>skrøsa</t>
-  </si>
-  <si>
-    <t>lute</t>
-  </si>
-  <si>
-    <t>grøl</t>
-  </si>
-  <si>
-    <t>mace</t>
-  </si>
-  <si>
-    <t>mand</t>
-  </si>
-  <si>
-    <t>man</t>
-  </si>
-  <si>
-    <t>maf</t>
-  </si>
-  <si>
-    <t>many, much, several, or a lot of</t>
-  </si>
-  <si>
-    <t>mobre</t>
-  </si>
-  <si>
-    <t>marble</t>
-  </si>
-  <si>
-    <t>mægere</t>
-  </si>
-  <si>
-    <t>maybe, might be, or could be</t>
-  </si>
-  <si>
-    <t>mjød</t>
-  </si>
-  <si>
-    <t>mead</t>
-  </si>
-  <si>
-    <t>månt</t>
-  </si>
-  <si>
-    <t>meal</t>
-  </si>
-  <si>
-    <t>prand</t>
-  </si>
-  <si>
-    <t>message, letter</t>
-  </si>
-  <si>
-    <t>valtig</t>
-  </si>
-  <si>
-    <t>mighty</t>
-  </si>
-  <si>
-    <t>greik</t>
-  </si>
-  <si>
     <t>minadd</t>
   </si>
   <si>
@@ -2550,10 +2559,22 @@
     <t>where</t>
   </si>
   <si>
+    <t>hvest</t>
+  </si>
+  <si>
+    <t>which</t>
+  </si>
+  <si>
     <t>vætte</t>
   </si>
   <si>
     <t>white</t>
+  </si>
+  <si>
+    <t>hve</t>
+  </si>
+  <si>
+    <t>who, whom</t>
   </si>
   <si>
     <t>vig</t>
@@ -3181,12 +3202,12 @@
         <v>23</v>
       </c>
       <c r="G4" s="14" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:B1000, REGEXMATCH(B2:B1000, H3)), 2, TRUE)"),"greik")</f>
-        <v>greik</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:B1000, REGEXMATCH(B2:B1000, H3)), 2, TRUE)"),"klæddvin")</f>
+        <v>klæddvin</v>
       </c>
       <c r="H4" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"milk")</f>
-        <v>milk</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"any cloth attire, or apparel; clothing")</f>
+        <v>any cloth attire, or apparel; clothing</v>
       </c>
       <c r="I4" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("FILTER(C:C, REGEXMATCH(B:B, H3))"),"")</f>
@@ -3227,8 +3248,14 @@
       <c r="F5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
+      <c r="G5" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"antul")</f>
+        <v>antul</v>
+      </c>
+      <c r="H5" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"any type of armor")</f>
+        <v>any type of armor</v>
+      </c>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
@@ -3265,8 +3292,14 @@
       <c r="F6" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
+      <c r="G6" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"borg")</f>
+        <v>borg</v>
+      </c>
+      <c r="H6" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"any type of fortified structure, mostly used to refer castles")</f>
+        <v>any type of fortified structure, mostly used to refer castles</v>
+      </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -3303,8 +3336,14 @@
       <c r="F7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
+      <c r="G7" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"mirste")</f>
+        <v>mirste</v>
+      </c>
+      <c r="H7" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"any type of metal")</f>
+        <v>any type of metal</v>
+      </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -3341,8 +3380,14 @@
       <c r="F8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+      <c r="G8" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"nem")</f>
+        <v>nem</v>
+      </c>
+      <c r="H8" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"any, some")</f>
+        <v>any, some</v>
+      </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -3379,8 +3424,14 @@
       <c r="F9" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
+      <c r="G9" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"bagt")</f>
+        <v>bagt</v>
+      </c>
+      <c r="H9" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"battle, or any large-scale fight")</f>
+        <v>battle, or any large-scale fight</v>
+      </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
@@ -3417,8 +3468,14 @@
       <c r="F10" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
+      <c r="G10" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"maf")</f>
+        <v>maf</v>
+      </c>
+      <c r="H10" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"many, much, several, or a lot of")</f>
+        <v>many, much, several, or a lot of</v>
+      </c>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -3455,8 +3512,14 @@
       <c r="F11" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+      <c r="G11" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"håle")</f>
+        <v>håle</v>
+      </c>
+      <c r="H11" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"the sea, ocean, or any giant body of water")</f>
+        <v>the sea, ocean, or any giant body of water</v>
+      </c>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
@@ -3493,8 +3556,14 @@
       <c r="F12" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="G12" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"gånde")</f>
+        <v>gånde</v>
+      </c>
+      <c r="H12" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"used to describe any type of magic")</f>
+        <v>used to describe any type of magic</v>
+      </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
@@ -3790,10 +3859,10 @@
       <c r="Z20" s="7"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="16" t="s">
         <v>86</v>
       </c>
       <c r="C21" s="7"/>
@@ -3826,10 +3895,10 @@
       <c r="Z21" s="7"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="11" t="s">
         <v>90</v>
       </c>
       <c r="C22" s="7"/>
@@ -3862,10 +3931,10 @@
       <c r="Z22" s="7"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="16" t="s">
         <v>94</v>
       </c>
       <c r="C23" s="7"/>
@@ -3898,10 +3967,10 @@
       <c r="Z23" s="7"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="11" t="s">
         <v>98</v>
       </c>
       <c r="C24" s="7"/>
@@ -3934,10 +4003,10 @@
       <c r="Z24" s="7"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="16" t="s">
         <v>102</v>
       </c>
       <c r="C25" s="7"/>
@@ -4042,10 +4111,10 @@
       <c r="Z27" s="7"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="8" t="s">
         <v>114</v>
       </c>
       <c r="C28" s="7"/>
@@ -4077,10 +4146,10 @@
       <c r="Z28" s="7"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="11" t="s">
         <v>118</v>
       </c>
       <c r="C29" s="7"/>
@@ -4115,10 +4184,10 @@
       <c r="Z29" s="7"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="8" t="s">
         <v>123</v>
       </c>
       <c r="C30" s="7"/>
@@ -4150,10 +4219,10 @@
       <c r="Z30" s="7"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="11" t="s">
         <v>127</v>
       </c>
       <c r="C31" s="7"/>
@@ -4186,10 +4255,10 @@
       <c r="Z31" s="7"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="8" t="s">
         <v>131</v>
       </c>
       <c r="C32" s="7"/>
@@ -4222,7 +4291,7 @@
       <c r="Z32" s="7"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="11" t="s">
         <v>134</v>
       </c>
       <c r="B33" s="11" t="s">
@@ -4261,7 +4330,7 @@
       <c r="A34" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="11" t="s">
         <v>139</v>
       </c>
       <c r="C34" s="7"/>
@@ -4294,10 +4363,10 @@
       <c r="Z34" s="7"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="8" t="s">
         <v>143</v>
       </c>
       <c r="C35" s="7"/>
@@ -4330,10 +4399,10 @@
       <c r="Z35" s="7"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="11" t="s">
         <v>147</v>
       </c>
       <c r="C36" s="7"/>
@@ -4437,7 +4506,7 @@
       <c r="A39" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="8" t="s">
         <v>157</v>
       </c>
       <c r="C39" s="7"/>
@@ -4470,10 +4539,10 @@
       <c r="Z39" s="7"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="11" t="s">
         <v>161</v>
       </c>
       <c r="C40" s="7"/>
@@ -4506,10 +4575,10 @@
       <c r="Z40" s="7"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="16" t="s">
         <v>165</v>
       </c>
       <c r="C41" s="7"/>
@@ -4649,7 +4718,7 @@
       <c r="A45" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="8" t="s">
         <v>179</v>
       </c>
       <c r="C45" s="7"/>
@@ -4681,7 +4750,7 @@
       <c r="A46" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="11" t="s">
         <v>181</v>
       </c>
       <c r="C46" s="7"/>
@@ -4713,7 +4782,7 @@
       <c r="A47" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="8" t="s">
         <v>183</v>
       </c>
       <c r="C47" s="7"/>
@@ -4747,7 +4816,7 @@
       <c r="A48" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="11" t="s">
         <v>186</v>
       </c>
       <c r="C48" s="7"/>
@@ -4946,10 +5015,10 @@
       <c r="Z53" s="7"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="16" t="s">
+      <c r="A54" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="8" t="s">
         <v>203</v>
       </c>
       <c r="C54" s="7"/>
@@ -4978,10 +5047,10 @@
       <c r="Z54" s="7"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="16" t="s">
         <v>205</v>
       </c>
       <c r="C55" s="7"/>
@@ -5013,7 +5082,7 @@
       <c r="A56" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="11" t="s">
         <v>207</v>
       </c>
       <c r="C56" s="7"/>
@@ -5074,10 +5143,10 @@
       <c r="Z57" s="7"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="20" t="s">
+      <c r="A58" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="B58" s="21" t="s">
+      <c r="B58" s="8" t="s">
         <v>211</v>
       </c>
       <c r="C58" s="7"/>
@@ -5106,10 +5175,10 @@
       <c r="Z58" s="7"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="21" t="s">
         <v>213</v>
       </c>
       <c r="C59" s="7"/>
@@ -5138,10 +5207,10 @@
       <c r="Z59" s="7"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="16" t="s">
+      <c r="A60" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="B60" s="16" t="s">
+      <c r="B60" s="8" t="s">
         <v>215</v>
       </c>
       <c r="C60" s="7"/>
@@ -5202,10 +5271,10 @@
       <c r="Z61" s="7"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="B62" s="11" t="s">
+      <c r="B62" s="16" t="s">
         <v>219</v>
       </c>
       <c r="C62" s="7"/>
@@ -5266,10 +5335,10 @@
       <c r="Z63" s="7"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="11" t="s">
         <v>223</v>
       </c>
       <c r="C64" s="7"/>
@@ -5298,10 +5367,10 @@
       <c r="Z64" s="7"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="8" t="s">
         <v>225</v>
       </c>
       <c r="C65" s="7"/>
@@ -5330,10 +5399,10 @@
       <c r="Z65" s="7"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="11" t="s">
         <v>227</v>
       </c>
       <c r="C66" s="7"/>
@@ -5362,7 +5431,7 @@
       <c r="Z66" s="7"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="11" t="s">
         <v>228</v>
       </c>
       <c r="B67" s="8" t="s">
@@ -5426,10 +5495,10 @@
       <c r="Z68" s="7"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="B69" s="16" t="s">
+      <c r="B69" s="8" t="s">
         <v>233</v>
       </c>
       <c r="C69" s="7"/>
@@ -5458,10 +5527,10 @@
       <c r="Z69" s="7"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="11" t="s">
+      <c r="A70" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="16" t="s">
         <v>235</v>
       </c>
       <c r="C70" s="7"/>
@@ -5490,10 +5559,10 @@
       <c r="Z70" s="7"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="B71" s="11" t="s">
+      <c r="B71" s="8" t="s">
         <v>237</v>
       </c>
       <c r="C71" s="7"/>
@@ -5522,10 +5591,10 @@
       <c r="Z71" s="7"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="16" t="s">
+      <c r="A72" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="B72" s="16" t="s">
+      <c r="B72" s="11" t="s">
         <v>239</v>
       </c>
       <c r="C72" s="7"/>
@@ -5554,10 +5623,10 @@
       <c r="Z72" s="7"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="B73" s="16" t="s">
         <v>241</v>
       </c>
       <c r="C73" s="7"/>
@@ -5810,13 +5879,13 @@
       <c r="Z80" s="7"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="20" t="s">
+      <c r="A81" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="B81" s="21" t="s">
+      <c r="B81" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="C81" s="22"/>
+      <c r="C81" s="7"/>
       <c r="D81" s="7"/>
       <c r="E81" s="7"/>
       <c r="F81" s="7"/>
@@ -5842,13 +5911,13 @@
       <c r="Z81" s="7"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="8" t="s">
+      <c r="A82" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B82" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="C82" s="7"/>
+      <c r="C82" s="22"/>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
       <c r="F82" s="7"/>
@@ -5909,7 +5978,7 @@
       <c r="A84" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="8" t="s">
         <v>263</v>
       </c>
       <c r="C84" s="7"/>
@@ -5941,7 +6010,7 @@
       <c r="A85" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B85" s="11" t="s">
         <v>265</v>
       </c>
       <c r="C85" s="7"/>
@@ -5973,7 +6042,7 @@
       <c r="A86" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="8" t="s">
         <v>267</v>
       </c>
       <c r="C86" s="7"/>
@@ -6005,7 +6074,7 @@
       <c r="A87" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="11" t="s">
         <v>269</v>
       </c>
       <c r="C87" s="7"/>
@@ -6066,10 +6135,10 @@
       <c r="Z88" s="7"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="11" t="s">
+      <c r="A89" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="8" t="s">
         <v>273</v>
       </c>
       <c r="C89" s="7"/>
@@ -6101,7 +6170,7 @@
       <c r="A90" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B90" s="11" t="s">
         <v>275</v>
       </c>
       <c r="C90" s="7"/>
@@ -6130,7 +6199,7 @@
       <c r="Z90" s="7"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="8" t="s">
+      <c r="A91" s="11" t="s">
         <v>276</v>
       </c>
       <c r="B91" s="8" t="s">
@@ -6162,10 +6231,10 @@
       <c r="Z91" s="7"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="16" t="s">
+      <c r="A92" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="B92" s="16" t="s">
+      <c r="B92" s="8" t="s">
         <v>279</v>
       </c>
       <c r="C92" s="7"/>
@@ -6194,10 +6263,10 @@
       <c r="Z92" s="7"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="8" t="s">
+      <c r="A93" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="B93" s="16" t="s">
         <v>281</v>
       </c>
       <c r="C93" s="7"/>
@@ -6290,10 +6359,10 @@
       <c r="Z95" s="7"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="16" t="s">
+      <c r="A96" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="B96" s="16" t="s">
+      <c r="B96" s="8" t="s">
         <v>287</v>
       </c>
       <c r="C96" s="7"/>
@@ -6322,10 +6391,10 @@
       <c r="Z96" s="7"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="16" t="s">
         <v>288</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B97" s="16" t="s">
         <v>289</v>
       </c>
       <c r="C97" s="7"/>
@@ -6357,7 +6426,7 @@
       <c r="A98" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="B98" s="11" t="s">
+      <c r="B98" s="8" t="s">
         <v>291</v>
       </c>
       <c r="C98" s="7"/>
@@ -6389,7 +6458,7 @@
       <c r="A99" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="B99" s="11" t="s">
         <v>293</v>
       </c>
       <c r="C99" s="7"/>
@@ -6453,7 +6522,7 @@
       <c r="A101" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="B101" s="11" t="s">
+      <c r="B101" s="8" t="s">
         <v>297</v>
       </c>
       <c r="C101" s="7"/>
@@ -6549,7 +6618,7 @@
       <c r="A104" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B104" s="8" t="s">
+      <c r="B104" s="11" t="s">
         <v>303</v>
       </c>
       <c r="C104" s="7"/>
@@ -6578,10 +6647,10 @@
       <c r="Z104" s="7"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="16" t="s">
+      <c r="A105" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="B105" s="16" t="s">
+      <c r="B105" s="8" t="s">
         <v>305</v>
       </c>
       <c r="C105" s="7"/>
@@ -6610,10 +6679,10 @@
       <c r="Z105" s="7"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="8" t="s">
+      <c r="A106" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="B106" s="8" t="s">
+      <c r="B106" s="16" t="s">
         <v>307</v>
       </c>
       <c r="C106" s="7"/>
@@ -6642,10 +6711,10 @@
       <c r="Z106" s="7"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="16" t="s">
+      <c r="A107" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="B107" s="16" t="s">
+      <c r="B107" s="8" t="s">
         <v>309</v>
       </c>
       <c r="C107" s="7"/>
@@ -6674,10 +6743,10 @@
       <c r="Z107" s="7"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="20" t="s">
+      <c r="A108" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="B108" s="20" t="s">
+      <c r="B108" s="16" t="s">
         <v>311</v>
       </c>
       <c r="C108" s="7"/>
@@ -6706,10 +6775,10 @@
       <c r="Z108" s="7"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="8" t="s">
+      <c r="A109" s="20" t="s">
         <v>312</v>
       </c>
-      <c r="B109" s="16" t="s">
+      <c r="B109" s="20" t="s">
         <v>313</v>
       </c>
       <c r="C109" s="7"/>
@@ -6741,7 +6810,7 @@
       <c r="A110" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="B110" s="11" t="s">
+      <c r="B110" s="16" t="s">
         <v>315</v>
       </c>
       <c r="C110" s="7"/>
@@ -6770,10 +6839,10 @@
       <c r="Z110" s="7"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="16" t="s">
+      <c r="A111" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="B111" s="16" t="s">
+      <c r="B111" s="11" t="s">
         <v>317</v>
       </c>
       <c r="C111" s="7"/>
@@ -6802,10 +6871,10 @@
       <c r="Z111" s="7"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="8" t="s">
+      <c r="A112" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="B112" s="11" t="s">
+      <c r="B112" s="16" t="s">
         <v>319</v>
       </c>
       <c r="C112" s="7"/>
@@ -6837,7 +6906,7 @@
       <c r="A113" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="B113" s="8" t="s">
+      <c r="B113" s="11" t="s">
         <v>321</v>
       </c>
       <c r="C113" s="7"/>
@@ -6930,10 +6999,10 @@
       <c r="Z115" s="7"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="11" t="s">
+      <c r="A116" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="B116" s="11" t="s">
+      <c r="B116" s="8" t="s">
         <v>327</v>
       </c>
       <c r="C116" s="7"/>
@@ -6962,10 +7031,10 @@
       <c r="Z116" s="7"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="16" t="s">
+      <c r="A117" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="B117" s="16" t="s">
+      <c r="B117" s="11" t="s">
         <v>329</v>
       </c>
       <c r="C117" s="7"/>
@@ -6994,10 +7063,10 @@
       <c r="Z117" s="7"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="8" t="s">
+      <c r="A118" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="B118" s="8" t="s">
+      <c r="B118" s="16" t="s">
         <v>331</v>
       </c>
       <c r="C118" s="7"/>
@@ -7026,10 +7095,10 @@
       <c r="Z118" s="7"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="21" t="s">
+      <c r="A119" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="B119" s="20" t="s">
+      <c r="B119" s="8" t="s">
         <v>333</v>
       </c>
       <c r="C119" s="7"/>
@@ -7058,10 +7127,10 @@
       <c r="Z119" s="7"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="8" t="s">
+      <c r="A120" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="B120" s="8" t="s">
+      <c r="B120" s="20" t="s">
         <v>335</v>
       </c>
       <c r="C120" s="7"/>
@@ -7093,7 +7162,7 @@
       <c r="A121" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="B121" s="11" t="s">
+      <c r="B121" s="8" t="s">
         <v>337</v>
       </c>
       <c r="C121" s="7"/>
@@ -7186,10 +7255,10 @@
       <c r="Z123" s="7"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="20" t="s">
+      <c r="A124" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="B124" s="21" t="s">
+      <c r="B124" s="11" t="s">
         <v>343</v>
       </c>
       <c r="C124" s="7"/>
@@ -7218,10 +7287,10 @@
       <c r="Z124" s="7"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="8" t="s">
+      <c r="A125" s="20" t="s">
         <v>344</v>
       </c>
-      <c r="B125" s="8" t="s">
+      <c r="B125" s="21" t="s">
         <v>345</v>
       </c>
       <c r="C125" s="7"/>
@@ -7253,7 +7322,7 @@
       <c r="A126" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="B126" s="11" t="s">
+      <c r="B126" s="8" t="s">
         <v>347</v>
       </c>
       <c r="C126" s="7"/>
@@ -7285,7 +7354,7 @@
       <c r="A127" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="B127" s="8" t="s">
+      <c r="B127" s="11" t="s">
         <v>349</v>
       </c>
       <c r="C127" s="7"/>
@@ -7317,7 +7386,7 @@
       <c r="A128" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="B128" s="11" t="s">
+      <c r="B128" s="8" t="s">
         <v>351</v>
       </c>
       <c r="C128" s="7"/>
@@ -7346,10 +7415,10 @@
       <c r="Z128" s="7"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="20" t="s">
+      <c r="A129" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="B129" s="21" t="s">
+      <c r="B129" s="11" t="s">
         <v>353</v>
       </c>
       <c r="C129" s="7"/>
@@ -7378,10 +7447,10 @@
       <c r="Z129" s="7"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="16" t="s">
+      <c r="A130" s="20" t="s">
         <v>354</v>
       </c>
-      <c r="B130" s="16" t="s">
+      <c r="B130" s="21" t="s">
         <v>355</v>
       </c>
       <c r="C130" s="7"/>
@@ -7410,10 +7479,10 @@
       <c r="Z130" s="7"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="8" t="s">
+      <c r="A131" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="B131" s="8" t="s">
+      <c r="B131" s="16" t="s">
         <v>357</v>
       </c>
       <c r="C131" s="7"/>
@@ -7637,7 +7706,7 @@
       <c r="A138" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="B138" s="11" t="s">
+      <c r="B138" s="8" t="s">
         <v>371</v>
       </c>
       <c r="C138" s="7"/>
@@ -7666,10 +7735,10 @@
       <c r="Z138" s="7"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="11" t="s">
+      <c r="A139" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="B139" s="8" t="s">
+      <c r="B139" s="11" t="s">
         <v>373</v>
       </c>
       <c r="C139" s="7"/>
@@ -7698,7 +7767,7 @@
       <c r="Z139" s="7"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="8" t="s">
+      <c r="A140" s="11" t="s">
         <v>374</v>
       </c>
       <c r="B140" s="8" t="s">
@@ -7765,7 +7834,7 @@
       <c r="A142" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="B142" s="11" t="s">
+      <c r="B142" s="8" t="s">
         <v>379</v>
       </c>
       <c r="C142" s="7"/>
@@ -7794,10 +7863,10 @@
       <c r="Z142" s="7"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="16" t="s">
+      <c r="A143" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="B143" s="16" t="s">
+      <c r="B143" s="11" t="s">
         <v>381</v>
       </c>
       <c r="C143" s="7"/>
@@ -7826,10 +7895,10 @@
       <c r="Z143" s="7"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="8" t="s">
+      <c r="A144" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="B144" s="8" t="s">
+      <c r="B144" s="16" t="s">
         <v>383</v>
       </c>
       <c r="C144" s="7"/>
@@ -7858,10 +7927,10 @@
       <c r="Z144" s="7"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="16" t="s">
+      <c r="A145" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="B145" s="16" t="s">
+      <c r="B145" s="8" t="s">
         <v>385</v>
       </c>
       <c r="C145" s="7"/>
@@ -7890,10 +7959,10 @@
       <c r="Z145" s="7"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="8" t="s">
+      <c r="A146" s="16" t="s">
         <v>386</v>
       </c>
-      <c r="B146" s="8" t="s">
+      <c r="B146" s="16" t="s">
         <v>387</v>
       </c>
       <c r="C146" s="7"/>
@@ -7957,7 +8026,7 @@
       <c r="A148" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="B148" s="11" t="s">
+      <c r="B148" s="8" t="s">
         <v>391</v>
       </c>
       <c r="C148" s="7"/>
@@ -7986,7 +8055,7 @@
       <c r="Z148" s="7"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="11" t="s">
+      <c r="A149" s="8" t="s">
         <v>392</v>
       </c>
       <c r="B149" s="11" t="s">
@@ -8018,7 +8087,7 @@
       <c r="Z149" s="7"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="8" t="s">
+      <c r="A150" s="11" t="s">
         <v>394</v>
       </c>
       <c r="B150" s="11" t="s">
@@ -8085,7 +8154,7 @@
       <c r="A152" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="B152" s="8" t="s">
+      <c r="B152" s="11" t="s">
         <v>399</v>
       </c>
       <c r="C152" s="7"/>
@@ -8114,10 +8183,10 @@
       <c r="Z152" s="7"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="16" t="s">
+      <c r="A153" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="B153" s="16" t="s">
+      <c r="B153" s="8" t="s">
         <v>401</v>
       </c>
       <c r="C153" s="7"/>
@@ -8146,10 +8215,10 @@
       <c r="Z153" s="7"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="8" t="s">
+      <c r="A154" s="16" t="s">
         <v>402</v>
       </c>
-      <c r="B154" s="11" t="s">
+      <c r="B154" s="16" t="s">
         <v>403</v>
       </c>
       <c r="C154" s="7"/>
@@ -8178,11 +8247,11 @@
       <c r="Z154" s="7"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="16" t="s">
+      <c r="A155" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="B155" s="16" t="s">
-        <v>18</v>
+      <c r="B155" s="11" t="s">
+        <v>405</v>
       </c>
       <c r="C155" s="7"/>
       <c r="D155" s="7"/>
@@ -8210,11 +8279,11 @@
       <c r="Z155" s="7"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="8" t="s">
-        <v>405</v>
-      </c>
-      <c r="B156" s="8" t="s">
+      <c r="A156" s="16" t="s">
         <v>406</v>
+      </c>
+      <c r="B156" s="16" t="s">
+        <v>407</v>
       </c>
       <c r="C156" s="7"/>
       <c r="D156" s="7"/>
@@ -8243,10 +8312,10 @@
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="8" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C157" s="7"/>
       <c r="D157" s="7"/>
@@ -8274,11 +8343,11 @@
       <c r="Z157" s="7"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="11" t="s">
-        <v>409</v>
-      </c>
-      <c r="B158" s="11" t="s">
+      <c r="A158" s="8" t="s">
         <v>410</v>
+      </c>
+      <c r="B158" s="8" t="s">
+        <v>411</v>
       </c>
       <c r="C158" s="7"/>
       <c r="D158" s="7"/>
@@ -8306,11 +8375,11 @@
       <c r="Z158" s="7"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="B159" s="8" t="s">
+      <c r="A159" s="11" t="s">
         <v>412</v>
+      </c>
+      <c r="B159" s="11" t="s">
+        <v>413</v>
       </c>
       <c r="C159" s="7"/>
       <c r="D159" s="7"/>
@@ -8338,11 +8407,11 @@
       <c r="Z159" s="7"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="16" t="s">
-        <v>413</v>
-      </c>
-      <c r="B160" s="16" t="s">
+      <c r="A160" s="8" t="s">
         <v>414</v>
+      </c>
+      <c r="B160" s="8" t="s">
+        <v>415</v>
       </c>
       <c r="C160" s="7"/>
       <c r="D160" s="7"/>
@@ -8370,11 +8439,11 @@
       <c r="Z160" s="7"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="11" t="s">
-        <v>415</v>
-      </c>
-      <c r="B161" s="8" t="s">
+      <c r="A161" s="16" t="s">
         <v>416</v>
+      </c>
+      <c r="B161" s="16" t="s">
+        <v>417</v>
       </c>
       <c r="C161" s="7"/>
       <c r="D161" s="7"/>
@@ -8403,10 +8472,10 @@
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="11" t="s">
-        <v>417</v>
-      </c>
-      <c r="B162" s="11" t="s">
         <v>418</v>
+      </c>
+      <c r="B162" s="8" t="s">
+        <v>419</v>
       </c>
       <c r="C162" s="7"/>
       <c r="D162" s="7"/>
@@ -8434,11 +8503,11 @@
       <c r="Z162" s="7"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="B163" s="8" t="s">
+      <c r="A163" s="11" t="s">
         <v>420</v>
+      </c>
+      <c r="B163" s="11" t="s">
+        <v>421</v>
       </c>
       <c r="C163" s="7"/>
       <c r="D163" s="7"/>
@@ -8467,10 +8536,10 @@
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="B164" s="11" t="s">
         <v>422</v>
+      </c>
+      <c r="B164" s="8" t="s">
+        <v>423</v>
       </c>
       <c r="C164" s="7"/>
       <c r="D164" s="7"/>
@@ -8498,11 +8567,11 @@
       <c r="Z164" s="7"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="11" t="s">
-        <v>423</v>
+      <c r="A165" s="8" t="s">
+        <v>424</v>
       </c>
       <c r="B165" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C165" s="7"/>
       <c r="D165" s="7"/>
@@ -8530,11 +8599,11 @@
       <c r="Z165" s="7"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="8" t="s">
-        <v>425</v>
-      </c>
-      <c r="B166" s="8" t="s">
+      <c r="A166" s="11" t="s">
         <v>426</v>
+      </c>
+      <c r="B166" s="11" t="s">
+        <v>427</v>
       </c>
       <c r="C166" s="7"/>
       <c r="D166" s="7"/>
@@ -8563,10 +8632,10 @@
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="8" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C167" s="7"/>
       <c r="D167" s="7"/>
@@ -8594,11 +8663,11 @@
       <c r="Z167" s="7"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="11" t="s">
-        <v>429</v>
-      </c>
-      <c r="B168" s="11" t="s">
+      <c r="A168" s="8" t="s">
         <v>430</v>
+      </c>
+      <c r="B168" s="8" t="s">
+        <v>431</v>
       </c>
       <c r="C168" s="7"/>
       <c r="D168" s="7"/>
@@ -8626,11 +8695,11 @@
       <c r="Z168" s="7"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="20" t="s">
-        <v>431</v>
-      </c>
-      <c r="B169" s="20" t="s">
+      <c r="A169" s="11" t="s">
         <v>432</v>
+      </c>
+      <c r="B169" s="11" t="s">
+        <v>433</v>
       </c>
       <c r="C169" s="7"/>
       <c r="D169" s="7"/>
@@ -8658,11 +8727,11 @@
       <c r="Z169" s="7"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="B170" s="16" t="s">
+      <c r="A170" s="20" t="s">
         <v>434</v>
+      </c>
+      <c r="B170" s="20" t="s">
+        <v>435</v>
       </c>
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
@@ -8690,11 +8759,11 @@
       <c r="Z170" s="7"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="20" t="s">
-        <v>435</v>
-      </c>
-      <c r="B171" s="20" t="s">
+      <c r="A171" s="16" t="s">
         <v>436</v>
+      </c>
+      <c r="B171" s="16" t="s">
+        <v>437</v>
       </c>
       <c r="C171" s="7"/>
       <c r="D171" s="7"/>
@@ -8722,11 +8791,11 @@
       <c r="Z171" s="7"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="B172" s="8" t="s">
+      <c r="A172" s="20" t="s">
         <v>438</v>
+      </c>
+      <c r="B172" s="20" t="s">
+        <v>439</v>
       </c>
       <c r="C172" s="7"/>
       <c r="D172" s="7"/>
@@ -8754,11 +8823,11 @@
       <c r="Z172" s="7"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="16" t="s">
-        <v>439</v>
-      </c>
-      <c r="B173" s="16" t="s">
+      <c r="A173" s="8" t="s">
         <v>440</v>
+      </c>
+      <c r="B173" s="8" t="s">
+        <v>441</v>
       </c>
       <c r="C173" s="7"/>
       <c r="D173" s="7"/>
@@ -8786,11 +8855,11 @@
       <c r="Z173" s="7"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="B174" s="8" t="s">
+      <c r="A174" s="16" t="s">
         <v>442</v>
+      </c>
+      <c r="B174" s="16" t="s">
+        <v>443</v>
       </c>
       <c r="C174" s="7"/>
       <c r="D174" s="7"/>
@@ -8819,10 +8888,10 @@
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="B175" s="11" t="s">
         <v>444</v>
+      </c>
+      <c r="B175" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="C175" s="7"/>
       <c r="D175" s="7"/>
@@ -8851,10 +8920,10 @@
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="8" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B176" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C176" s="7"/>
       <c r="D176" s="7"/>
@@ -8883,10 +8952,10 @@
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B177" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C177" s="7"/>
       <c r="D177" s="7"/>
@@ -8915,10 +8984,10 @@
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="8" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C178" s="7"/>
       <c r="D178" s="7"/>
@@ -8947,10 +9016,10 @@
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="8" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B179" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C179" s="7"/>
       <c r="D179" s="7"/>
@@ -8979,10 +9048,10 @@
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="8" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B180" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C180" s="7"/>
       <c r="D180" s="7"/>
@@ -9011,10 +9080,10 @@
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="8" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B181" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C181" s="7"/>
       <c r="D181" s="7"/>
@@ -9043,10 +9112,10 @@
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="8" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B182" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C182" s="7"/>
       <c r="D182" s="7"/>
@@ -9074,11 +9143,11 @@
       <c r="Z182" s="7"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="16" t="s">
-        <v>459</v>
-      </c>
-      <c r="B183" s="16" t="s">
+      <c r="A183" s="8" t="s">
         <v>460</v>
+      </c>
+      <c r="B183" s="11" t="s">
+        <v>461</v>
       </c>
       <c r="C183" s="7"/>
       <c r="D183" s="7"/>
@@ -9106,11 +9175,11 @@
       <c r="Z183" s="7"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="B184" s="11" t="s">
+      <c r="A184" s="16" t="s">
         <v>462</v>
+      </c>
+      <c r="B184" s="16" t="s">
+        <v>463</v>
       </c>
       <c r="C184" s="7"/>
       <c r="D184" s="7"/>
@@ -9139,10 +9208,10 @@
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="8" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B185" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C185" s="7"/>
       <c r="D185" s="7"/>
@@ -9171,10 +9240,10 @@
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="8" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B186" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C186" s="7"/>
       <c r="D186" s="7"/>
@@ -9202,11 +9271,11 @@
       <c r="Z186" s="7"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="11" t="s">
-        <v>467</v>
+      <c r="A187" s="8" t="s">
+        <v>468</v>
       </c>
       <c r="B187" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C187" s="7"/>
       <c r="D187" s="7"/>
@@ -9235,10 +9304,10 @@
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C188" s="7"/>
       <c r="D188" s="7"/>
@@ -9266,11 +9335,11 @@
       <c r="Z188" s="7"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="8" t="s">
-        <v>471</v>
+      <c r="A189" s="11" t="s">
+        <v>472</v>
       </c>
       <c r="B189" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C189" s="7"/>
       <c r="D189" s="7"/>
@@ -9298,11 +9367,11 @@
       <c r="Z189" s="7"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="16" t="s">
-        <v>473</v>
-      </c>
-      <c r="B190" s="16" t="s">
+      <c r="A190" s="8" t="s">
         <v>474</v>
+      </c>
+      <c r="B190" s="11" t="s">
+        <v>475</v>
       </c>
       <c r="C190" s="7"/>
       <c r="D190" s="7"/>
@@ -9330,11 +9399,11 @@
       <c r="Z190" s="7"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="8" t="s">
-        <v>475</v>
-      </c>
-      <c r="B191" s="8" t="s">
+      <c r="A191" s="16" t="s">
         <v>476</v>
+      </c>
+      <c r="B191" s="16" t="s">
+        <v>477</v>
       </c>
       <c r="C191" s="7"/>
       <c r="D191" s="7"/>
@@ -9363,10 +9432,10 @@
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="8" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B192" s="8" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C192" s="7"/>
       <c r="D192" s="7"/>
@@ -9394,11 +9463,11 @@
       <c r="Z192" s="7"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="16" t="s">
-        <v>479</v>
-      </c>
-      <c r="B193" s="16" t="s">
+      <c r="A193" s="8" t="s">
         <v>480</v>
+      </c>
+      <c r="B193" s="8" t="s">
+        <v>481</v>
       </c>
       <c r="C193" s="7"/>
       <c r="D193" s="7"/>
@@ -9427,10 +9496,10 @@
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="16" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B194" s="16" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C194" s="7"/>
       <c r="D194" s="7"/>
@@ -9458,11 +9527,11 @@
       <c r="Z194" s="7"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="B195" s="8" t="s">
+      <c r="A195" s="16" t="s">
         <v>484</v>
+      </c>
+      <c r="B195" s="16" t="s">
+        <v>485</v>
       </c>
       <c r="C195" s="7"/>
       <c r="D195" s="7"/>
@@ -9491,10 +9560,10 @@
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="8" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C196" s="7"/>
       <c r="D196" s="7"/>
@@ -9522,11 +9591,11 @@
       <c r="Z196" s="7"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="11" t="s">
-        <v>487</v>
+      <c r="A197" s="8" t="s">
+        <v>488</v>
       </c>
       <c r="B197" s="8" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C197" s="7"/>
       <c r="D197" s="7"/>
@@ -9554,11 +9623,11 @@
       <c r="Z197" s="7"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="8" t="s">
-        <v>489</v>
-      </c>
-      <c r="B198" s="11" t="s">
+      <c r="A198" s="11" t="s">
         <v>490</v>
+      </c>
+      <c r="B198" s="8" t="s">
+        <v>491</v>
       </c>
       <c r="C198" s="7"/>
       <c r="D198" s="7"/>
@@ -9587,10 +9656,10 @@
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="8" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B199" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C199" s="7"/>
       <c r="D199" s="7"/>
@@ -9619,10 +9688,10 @@
     </row>
     <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="8" t="s">
-        <v>493</v>
-      </c>
-      <c r="B200" s="8" t="s">
         <v>494</v>
+      </c>
+      <c r="B200" s="11" t="s">
+        <v>495</v>
       </c>
       <c r="C200" s="7"/>
       <c r="D200" s="7"/>
@@ -9651,10 +9720,10 @@
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="8" t="s">
-        <v>495</v>
-      </c>
-      <c r="B201" s="11" t="s">
         <v>496</v>
+      </c>
+      <c r="B201" s="8" t="s">
+        <v>497</v>
       </c>
       <c r="C201" s="7"/>
       <c r="D201" s="7"/>
@@ -9683,10 +9752,10 @@
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="B202" s="8" t="s">
         <v>498</v>
+      </c>
+      <c r="B202" s="11" t="s">
+        <v>499</v>
       </c>
       <c r="C202" s="7"/>
       <c r="D202" s="7"/>
@@ -9714,11 +9783,11 @@
       <c r="Z202" s="7"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="16" t="s">
-        <v>499</v>
-      </c>
-      <c r="B203" s="16" t="s">
+      <c r="A203" s="8" t="s">
         <v>500</v>
+      </c>
+      <c r="B203" s="8" t="s">
+        <v>501</v>
       </c>
       <c r="C203" s="7"/>
       <c r="D203" s="7"/>
@@ -9746,11 +9815,11 @@
       <c r="Z203" s="7"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="11" t="s">
-        <v>501</v>
-      </c>
-      <c r="B204" s="8" t="s">
+      <c r="A204" s="16" t="s">
         <v>502</v>
+      </c>
+      <c r="B204" s="16" t="s">
+        <v>503</v>
       </c>
       <c r="C204" s="7"/>
       <c r="D204" s="7"/>
@@ -9778,11 +9847,11 @@
       <c r="Z204" s="7"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="8" t="s">
-        <v>503</v>
-      </c>
-      <c r="B205" s="11" t="s">
+      <c r="A205" s="11" t="s">
         <v>504</v>
+      </c>
+      <c r="B205" s="8" t="s">
+        <v>505</v>
       </c>
       <c r="C205" s="7"/>
       <c r="D205" s="7"/>
@@ -9810,11 +9879,11 @@
       <c r="Z205" s="7"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="20" t="s">
-        <v>505</v>
-      </c>
-      <c r="B206" s="21" t="s">
+      <c r="A206" s="8" t="s">
         <v>506</v>
+      </c>
+      <c r="B206" s="11" t="s">
+        <v>507</v>
       </c>
       <c r="C206" s="7"/>
       <c r="D206" s="7"/>
@@ -9842,11 +9911,11 @@
       <c r="Z206" s="7"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="8" t="s">
-        <v>507</v>
-      </c>
-      <c r="B207" s="8" t="s">
+      <c r="A207" s="20" t="s">
         <v>508</v>
+      </c>
+      <c r="B207" s="21" t="s">
+        <v>509</v>
       </c>
       <c r="C207" s="7"/>
       <c r="D207" s="7"/>
@@ -9875,10 +9944,10 @@
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="8" t="s">
-        <v>509</v>
-      </c>
-      <c r="B208" s="11" t="s">
         <v>510</v>
+      </c>
+      <c r="B208" s="8" t="s">
+        <v>511</v>
       </c>
       <c r="C208" s="7"/>
       <c r="D208" s="7"/>
@@ -9907,10 +9976,10 @@
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="8" t="s">
-        <v>511</v>
-      </c>
-      <c r="B209" s="8" t="s">
         <v>512</v>
+      </c>
+      <c r="B209" s="11" t="s">
+        <v>513</v>
       </c>
       <c r="C209" s="7"/>
       <c r="D209" s="7"/>
@@ -9938,11 +10007,11 @@
       <c r="Z209" s="7"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="16" t="s">
-        <v>513</v>
-      </c>
-      <c r="B210" s="16" t="s">
+      <c r="A210" s="8" t="s">
         <v>514</v>
+      </c>
+      <c r="B210" s="8" t="s">
+        <v>515</v>
       </c>
       <c r="C210" s="7"/>
       <c r="D210" s="7"/>
@@ -9970,11 +10039,11 @@
       <c r="Z210" s="7"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="B211" s="8" t="s">
+      <c r="A211" s="16" t="s">
         <v>516</v>
+      </c>
+      <c r="B211" s="16" t="s">
+        <v>517</v>
       </c>
       <c r="C211" s="7"/>
       <c r="D211" s="7"/>
@@ -10002,11 +10071,11 @@
       <c r="Z211" s="7"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="16" t="s">
-        <v>517</v>
-      </c>
-      <c r="B212" s="16" t="s">
+      <c r="A212" s="8" t="s">
         <v>518</v>
+      </c>
+      <c r="B212" s="8" t="s">
+        <v>519</v>
       </c>
       <c r="C212" s="7"/>
       <c r="D212" s="7"/>
@@ -10034,11 +10103,11 @@
       <c r="Z212" s="7"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="8" t="s">
-        <v>519</v>
-      </c>
-      <c r="B213" s="8" t="s">
+      <c r="A213" s="16" t="s">
         <v>520</v>
+      </c>
+      <c r="B213" s="16" t="s">
+        <v>521</v>
       </c>
       <c r="C213" s="7"/>
       <c r="D213" s="7"/>
@@ -10067,10 +10136,10 @@
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="8" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B214" s="8" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C214" s="7"/>
       <c r="D214" s="7"/>
@@ -10099,10 +10168,10 @@
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="8" t="s">
-        <v>523</v>
-      </c>
-      <c r="B215" s="11" t="s">
         <v>524</v>
+      </c>
+      <c r="B215" s="8" t="s">
+        <v>525</v>
       </c>
       <c r="C215" s="7"/>
       <c r="D215" s="7"/>
@@ -10130,11 +10199,11 @@
       <c r="Z215" s="7"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="A216" s="11" t="s">
-        <v>525</v>
+      <c r="A216" s="8" t="s">
+        <v>526</v>
       </c>
       <c r="B216" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C216" s="7"/>
       <c r="D216" s="7"/>
@@ -10162,11 +10231,11 @@
       <c r="Z216" s="7"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="A217" s="8" t="s">
-        <v>527</v>
+      <c r="A217" s="11" t="s">
+        <v>528</v>
       </c>
       <c r="B217" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C217" s="7"/>
       <c r="D217" s="7"/>
@@ -10194,11 +10263,11 @@
       <c r="Z217" s="7"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="16" t="s">
-        <v>529</v>
-      </c>
-      <c r="B218" s="16" t="s">
+      <c r="A218" s="8" t="s">
         <v>530</v>
+      </c>
+      <c r="B218" s="11" t="s">
+        <v>531</v>
       </c>
       <c r="C218" s="7"/>
       <c r="D218" s="7"/>
@@ -10226,11 +10295,11 @@
       <c r="Z218" s="7"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="B219" s="11" t="s">
+      <c r="A219" s="16" t="s">
         <v>532</v>
+      </c>
+      <c r="B219" s="16" t="s">
+        <v>533</v>
       </c>
       <c r="C219" s="7"/>
       <c r="D219" s="7"/>
@@ -10258,11 +10327,11 @@
       <c r="Z219" s="7"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="16" t="s">
-        <v>533</v>
-      </c>
-      <c r="B220" s="16" t="s">
+      <c r="A220" s="8" t="s">
         <v>534</v>
+      </c>
+      <c r="B220" s="11" t="s">
+        <v>535</v>
       </c>
       <c r="C220" s="7"/>
       <c r="D220" s="7"/>
@@ -10290,11 +10359,11 @@
       <c r="Z220" s="7"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="8" t="s">
-        <v>535</v>
-      </c>
-      <c r="B221" s="8" t="s">
+      <c r="A221" s="16" t="s">
         <v>536</v>
+      </c>
+      <c r="B221" s="16" t="s">
+        <v>537</v>
       </c>
       <c r="C221" s="7"/>
       <c r="D221" s="7"/>
@@ -10323,10 +10392,10 @@
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="8" t="s">
-        <v>537</v>
-      </c>
-      <c r="B222" s="11" t="s">
         <v>538</v>
+      </c>
+      <c r="B222" s="8" t="s">
+        <v>539</v>
       </c>
       <c r="C222" s="7"/>
       <c r="D222" s="7"/>
@@ -10355,10 +10424,10 @@
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="8" t="s">
-        <v>539</v>
-      </c>
-      <c r="B223" s="8" t="s">
         <v>540</v>
+      </c>
+      <c r="B223" s="11" t="s">
+        <v>541</v>
       </c>
       <c r="C223" s="7"/>
       <c r="D223" s="7"/>
@@ -10386,11 +10455,11 @@
       <c r="Z223" s="7"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="11" t="s">
-        <v>541</v>
-      </c>
-      <c r="B224" s="11" t="s">
+      <c r="A224" s="8" t="s">
         <v>542</v>
+      </c>
+      <c r="B224" s="8" t="s">
+        <v>543</v>
       </c>
       <c r="C224" s="7"/>
       <c r="D224" s="7"/>
@@ -10418,11 +10487,11 @@
       <c r="Z224" s="7"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="8" t="s">
-        <v>543</v>
-      </c>
-      <c r="B225" s="8" t="s">
+      <c r="A225" s="11" t="s">
         <v>544</v>
+      </c>
+      <c r="B225" s="11" t="s">
+        <v>545</v>
       </c>
       <c r="C225" s="7"/>
       <c r="D225" s="7"/>
@@ -10451,10 +10520,10 @@
     </row>
     <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="8" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B226" s="8" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C226" s="7"/>
       <c r="D226" s="7"/>
@@ -10482,11 +10551,11 @@
       <c r="Z226" s="7"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="16" t="s">
-        <v>547</v>
-      </c>
-      <c r="B227" s="16" t="s">
+      <c r="A227" s="8" t="s">
         <v>548</v>
+      </c>
+      <c r="B227" s="8" t="s">
+        <v>549</v>
       </c>
       <c r="C227" s="7"/>
       <c r="D227" s="7"/>
@@ -10514,11 +10583,11 @@
       <c r="Z227" s="7"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="A228" s="8" t="s">
-        <v>549</v>
-      </c>
-      <c r="B228" s="11" t="s">
+      <c r="A228" s="16" t="s">
         <v>550</v>
+      </c>
+      <c r="B228" s="16" t="s">
+        <v>551</v>
       </c>
       <c r="C228" s="7"/>
       <c r="D228" s="7"/>
@@ -10547,10 +10616,10 @@
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="8" t="s">
-        <v>551</v>
-      </c>
-      <c r="B229" s="8" t="s">
         <v>552</v>
+      </c>
+      <c r="B229" s="11" t="s">
+        <v>553</v>
       </c>
       <c r="C229" s="7"/>
       <c r="D229" s="7"/>
@@ -10579,10 +10648,10 @@
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="8" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B230" s="8" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C230" s="7"/>
       <c r="D230" s="7"/>
@@ -10610,11 +10679,11 @@
       <c r="Z230" s="7"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="11" t="s">
-        <v>555</v>
+      <c r="A231" s="8" t="s">
+        <v>556</v>
       </c>
       <c r="B231" s="8" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C231" s="7"/>
       <c r="D231" s="7"/>
@@ -10642,11 +10711,11 @@
       <c r="Z231" s="7"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="A232" s="8" t="s">
-        <v>557</v>
+      <c r="A232" s="11" t="s">
+        <v>558</v>
       </c>
       <c r="B232" s="8" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C232" s="7"/>
       <c r="D232" s="7"/>
@@ -10675,10 +10744,10 @@
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="8" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B233" s="8" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C233" s="7"/>
       <c r="D233" s="7"/>
@@ -10707,10 +10776,10 @@
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="8" t="s">
-        <v>561</v>
-      </c>
-      <c r="B234" s="11" t="s">
         <v>562</v>
+      </c>
+      <c r="B234" s="8" t="s">
+        <v>563</v>
       </c>
       <c r="C234" s="7"/>
       <c r="D234" s="7"/>
@@ -10739,10 +10808,10 @@
     </row>
     <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="8" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B235" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C235" s="7"/>
       <c r="D235" s="7"/>
@@ -10771,10 +10840,10 @@
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="8" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B236" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C236" s="7"/>
       <c r="D236" s="7"/>
@@ -10802,11 +10871,11 @@
       <c r="Z236" s="7"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="A237" s="11" t="s">
-        <v>567</v>
+      <c r="A237" s="8" t="s">
+        <v>568</v>
       </c>
       <c r="B237" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C237" s="7"/>
       <c r="D237" s="7"/>
@@ -10834,11 +10903,11 @@
       <c r="Z237" s="7"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="8" t="s">
-        <v>569</v>
+      <c r="A238" s="11" t="s">
+        <v>570</v>
       </c>
       <c r="B238" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C238" s="7"/>
       <c r="D238" s="7"/>
@@ -10867,10 +10936,10 @@
     </row>
     <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="8" t="s">
-        <v>571</v>
-      </c>
-      <c r="B239" s="8" t="s">
         <v>572</v>
+      </c>
+      <c r="B239" s="11" t="s">
+        <v>573</v>
       </c>
       <c r="C239" s="7"/>
       <c r="D239" s="7"/>
@@ -10899,10 +10968,10 @@
     </row>
     <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="8" t="s">
-        <v>573</v>
-      </c>
-      <c r="B240" s="11" t="s">
         <v>574</v>
+      </c>
+      <c r="B240" s="8" t="s">
+        <v>575</v>
       </c>
       <c r="C240" s="7"/>
       <c r="D240" s="7"/>
@@ -10931,10 +11000,10 @@
     </row>
     <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="8" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B241" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C241" s="7"/>
       <c r="D241" s="7"/>
@@ -10963,10 +11032,10 @@
     </row>
     <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="8" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B242" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C242" s="7"/>
       <c r="D242" s="7"/>
@@ -10994,11 +11063,11 @@
       <c r="Z242" s="7"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="A243" s="11" t="s">
-        <v>579</v>
+      <c r="A243" s="8" t="s">
+        <v>580</v>
       </c>
       <c r="B243" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C243" s="7"/>
       <c r="D243" s="7"/>
@@ -11026,11 +11095,11 @@
       <c r="Z243" s="7"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="8" t="s">
-        <v>581</v>
+      <c r="A244" s="11" t="s">
+        <v>582</v>
       </c>
       <c r="B244" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C244" s="7"/>
       <c r="D244" s="7"/>
@@ -11059,10 +11128,10 @@
     </row>
     <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="8" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B245" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C245" s="7"/>
       <c r="D245" s="7"/>
@@ -11091,10 +11160,10 @@
     </row>
     <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="8" t="s">
-        <v>585</v>
-      </c>
-      <c r="B246" s="8" t="s">
         <v>586</v>
+      </c>
+      <c r="B246" s="11" t="s">
+        <v>587</v>
       </c>
       <c r="C246" s="7"/>
       <c r="D246" s="7"/>
@@ -11123,10 +11192,10 @@
     </row>
     <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="8" t="s">
-        <v>587</v>
-      </c>
-      <c r="B247" s="11" t="s">
         <v>588</v>
+      </c>
+      <c r="B247" s="8" t="s">
+        <v>589</v>
       </c>
       <c r="C247" s="7"/>
       <c r="D247" s="7"/>
@@ -11154,11 +11223,11 @@
       <c r="Z247" s="7"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="16" t="s">
-        <v>589</v>
-      </c>
-      <c r="B248" s="16" t="s">
+      <c r="A248" s="8" t="s">
         <v>590</v>
+      </c>
+      <c r="B248" s="11" t="s">
+        <v>591</v>
       </c>
       <c r="C248" s="7"/>
       <c r="D248" s="7"/>
@@ -11186,11 +11255,11 @@
       <c r="Z248" s="7"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="8" t="s">
-        <v>591</v>
-      </c>
-      <c r="B249" s="8" t="s">
+      <c r="A249" s="16" t="s">
         <v>592</v>
+      </c>
+      <c r="B249" s="16" t="s">
+        <v>593</v>
       </c>
       <c r="C249" s="7"/>
       <c r="D249" s="7"/>
@@ -11219,10 +11288,10 @@
     </row>
     <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="8" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B250" s="8" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C250" s="7"/>
       <c r="D250" s="7"/>
@@ -11251,10 +11320,10 @@
     </row>
     <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="8" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B251" s="8" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C251" s="7"/>
       <c r="D251" s="7"/>
@@ -11282,11 +11351,11 @@
       <c r="Z251" s="7"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="A252" s="16" t="s">
-        <v>597</v>
-      </c>
-      <c r="B252" s="16" t="s">
+      <c r="A252" s="8" t="s">
         <v>598</v>
+      </c>
+      <c r="B252" s="8" t="s">
+        <v>599</v>
       </c>
       <c r="C252" s="7"/>
       <c r="D252" s="7"/>
@@ -11314,11 +11383,11 @@
       <c r="Z252" s="7"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="A253" s="8" t="s">
-        <v>599</v>
-      </c>
-      <c r="B253" s="8" t="s">
+      <c r="A253" s="16" t="s">
         <v>600</v>
+      </c>
+      <c r="B253" s="16" t="s">
+        <v>601</v>
       </c>
       <c r="C253" s="7"/>
       <c r="D253" s="7"/>
@@ -11346,11 +11415,11 @@
       <c r="Z253" s="7"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="16" t="s">
-        <v>601</v>
-      </c>
-      <c r="B254" s="16" t="s">
+      <c r="A254" s="8" t="s">
         <v>602</v>
+      </c>
+      <c r="B254" s="8" t="s">
+        <v>603</v>
       </c>
       <c r="C254" s="7"/>
       <c r="D254" s="7"/>
@@ -11379,10 +11448,10 @@
     </row>
     <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="16" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B255" s="16" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C255" s="7"/>
       <c r="D255" s="7"/>
@@ -11411,10 +11480,10 @@
     </row>
     <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="16" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B256" s="16" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C256" s="7"/>
       <c r="D256" s="7"/>
@@ -11442,11 +11511,11 @@
       <c r="Z256" s="7"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="8" t="s">
-        <v>607</v>
-      </c>
-      <c r="B257" s="11" t="s">
+      <c r="A257" s="16" t="s">
         <v>608</v>
+      </c>
+      <c r="B257" s="16" t="s">
+        <v>609</v>
       </c>
       <c r="C257" s="7"/>
       <c r="D257" s="7"/>
@@ -11475,10 +11544,10 @@
     </row>
     <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="8" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B258" s="11" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C258" s="7"/>
       <c r="D258" s="7"/>
@@ -11507,10 +11576,10 @@
     </row>
     <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="8" t="s">
-        <v>611</v>
-      </c>
-      <c r="B259" s="8" t="s">
         <v>612</v>
+      </c>
+      <c r="B259" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="C259" s="7"/>
       <c r="D259" s="7"/>
@@ -11538,11 +11607,11 @@
       <c r="Z259" s="7"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="20" t="s">
-        <v>613</v>
-      </c>
-      <c r="B260" s="21" t="s">
+      <c r="A260" s="8" t="s">
         <v>614</v>
+      </c>
+      <c r="B260" s="8" t="s">
+        <v>615</v>
       </c>
       <c r="C260" s="7"/>
       <c r="D260" s="7"/>
@@ -11570,11 +11639,11 @@
       <c r="Z260" s="7"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="A261" s="8" t="s">
-        <v>615</v>
-      </c>
-      <c r="B261" s="11" t="s">
+      <c r="A261" s="20" t="s">
         <v>616</v>
+      </c>
+      <c r="B261" s="21" t="s">
+        <v>617</v>
       </c>
       <c r="C261" s="7"/>
       <c r="D261" s="7"/>
@@ -11603,10 +11672,10 @@
     </row>
     <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="8" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B262" s="11" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C262" s="7"/>
       <c r="D262" s="7"/>
@@ -11635,10 +11704,10 @@
     </row>
     <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="8" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B263" s="11" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C263" s="7"/>
       <c r="D263" s="7"/>
@@ -11667,10 +11736,10 @@
     </row>
     <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="8" t="s">
-        <v>621</v>
-      </c>
-      <c r="B264" s="8" t="s">
         <v>622</v>
+      </c>
+      <c r="B264" s="11" t="s">
+        <v>623</v>
       </c>
       <c r="C264" s="7"/>
       <c r="D264" s="7"/>
@@ -11698,11 +11767,11 @@
       <c r="Z264" s="7"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="A265" s="16" t="s">
-        <v>623</v>
-      </c>
-      <c r="B265" s="16" t="s">
+      <c r="A265" s="8" t="s">
         <v>624</v>
+      </c>
+      <c r="B265" s="8" t="s">
+        <v>625</v>
       </c>
       <c r="C265" s="7"/>
       <c r="D265" s="7"/>
@@ -11731,10 +11800,10 @@
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="16" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B266" s="16" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C266" s="7"/>
       <c r="D266" s="7"/>
@@ -11762,11 +11831,11 @@
       <c r="Z266" s="7"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="A267" s="8" t="s">
-        <v>627</v>
-      </c>
-      <c r="B267" s="11" t="s">
+      <c r="A267" s="16" t="s">
         <v>628</v>
+      </c>
+      <c r="B267" s="16" t="s">
+        <v>629</v>
       </c>
       <c r="C267" s="7"/>
       <c r="D267" s="7"/>
@@ -11795,10 +11864,10 @@
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="8" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B268" s="11" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C268" s="7"/>
       <c r="D268" s="7"/>
@@ -11826,11 +11895,11 @@
       <c r="Z268" s="7"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
-      <c r="A269" s="16" t="s">
-        <v>631</v>
-      </c>
-      <c r="B269" s="16" t="s">
+      <c r="A269" s="8" t="s">
         <v>632</v>
+      </c>
+      <c r="B269" s="11" t="s">
+        <v>633</v>
       </c>
       <c r="C269" s="7"/>
       <c r="D269" s="7"/>
@@ -11858,11 +11927,11 @@
       <c r="Z269" s="7"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
-      <c r="A270" s="8" t="s">
-        <v>633</v>
-      </c>
-      <c r="B270" s="8" t="s">
+      <c r="A270" s="16" t="s">
         <v>634</v>
+      </c>
+      <c r="B270" s="16" t="s">
+        <v>635</v>
       </c>
       <c r="C270" s="7"/>
       <c r="D270" s="7"/>
@@ -11890,11 +11959,11 @@
       <c r="Z270" s="7"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
-      <c r="A271" s="16" t="s">
-        <v>635</v>
-      </c>
-      <c r="B271" s="16" t="s">
+      <c r="A271" s="8" t="s">
         <v>636</v>
+      </c>
+      <c r="B271" s="8" t="s">
+        <v>637</v>
       </c>
       <c r="C271" s="7"/>
       <c r="D271" s="7"/>
@@ -11922,11 +11991,11 @@
       <c r="Z271" s="7"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
-      <c r="A272" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="B272" s="8" t="s">
+      <c r="A272" s="16" t="s">
         <v>638</v>
+      </c>
+      <c r="B272" s="16" t="s">
+        <v>639</v>
       </c>
       <c r="C272" s="7"/>
       <c r="D272" s="7"/>
@@ -11955,10 +12024,10 @@
     </row>
     <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="8" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B273" s="8" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C273" s="7"/>
       <c r="D273" s="7"/>
@@ -11986,11 +12055,11 @@
       <c r="Z273" s="7"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
-      <c r="A274" s="16" t="s">
-        <v>641</v>
-      </c>
-      <c r="B274" s="16" t="s">
+      <c r="A274" s="8" t="s">
         <v>642</v>
+      </c>
+      <c r="B274" s="8" t="s">
+        <v>643</v>
       </c>
       <c r="C274" s="7"/>
       <c r="D274" s="7"/>
@@ -12019,10 +12088,10 @@
     </row>
     <row r="275" ht="15.75" customHeight="1">
       <c r="A275" s="16" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B275" s="16" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C275" s="7"/>
       <c r="D275" s="7"/>
@@ -12050,11 +12119,11 @@
       <c r="Z275" s="7"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="A276" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="B276" s="8" t="s">
+      <c r="A276" s="16" t="s">
         <v>646</v>
+      </c>
+      <c r="B276" s="16" t="s">
+        <v>647</v>
       </c>
       <c r="C276" s="7"/>
       <c r="D276" s="7"/>
@@ -12082,11 +12151,11 @@
       <c r="Z276" s="7"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
-      <c r="A277" s="16" t="s">
-        <v>647</v>
-      </c>
-      <c r="B277" s="16" t="s">
+      <c r="A277" s="8" t="s">
         <v>648</v>
+      </c>
+      <c r="B277" s="8" t="s">
+        <v>649</v>
       </c>
       <c r="C277" s="7"/>
       <c r="D277" s="7"/>
@@ -12114,11 +12183,11 @@
       <c r="Z277" s="7"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
-      <c r="A278" s="8" t="s">
-        <v>649</v>
-      </c>
-      <c r="B278" s="11" t="s">
+      <c r="A278" s="16" t="s">
         <v>650</v>
+      </c>
+      <c r="B278" s="16" t="s">
+        <v>651</v>
       </c>
       <c r="C278" s="7"/>
       <c r="D278" s="7"/>
@@ -12146,11 +12215,11 @@
       <c r="Z278" s="7"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="A279" s="16" t="s">
-        <v>651</v>
+      <c r="A279" s="8" t="s">
+        <v>652</v>
       </c>
       <c r="B279" s="11" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C279" s="7"/>
       <c r="D279" s="7"/>
@@ -12178,11 +12247,11 @@
       <c r="Z279" s="7"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
-      <c r="A280" s="8" t="s">
-        <v>653</v>
+      <c r="A280" s="16" t="s">
+        <v>654</v>
       </c>
       <c r="B280" s="11" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C280" s="7"/>
       <c r="D280" s="7"/>
@@ -12210,11 +12279,11 @@
       <c r="Z280" s="7"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
-      <c r="A281" s="16" t="s">
-        <v>655</v>
-      </c>
-      <c r="B281" s="16" t="s">
+      <c r="A281" s="8" t="s">
         <v>656</v>
+      </c>
+      <c r="B281" s="11" t="s">
+        <v>657</v>
       </c>
       <c r="C281" s="7"/>
       <c r="D281" s="7"/>
@@ -12242,11 +12311,11 @@
       <c r="Z281" s="7"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="A282" s="8" t="s">
-        <v>657</v>
-      </c>
-      <c r="B282" s="11" t="s">
+      <c r="A282" s="16" t="s">
         <v>658</v>
+      </c>
+      <c r="B282" s="16" t="s">
+        <v>659</v>
       </c>
       <c r="C282" s="7"/>
       <c r="D282" s="7"/>
@@ -12275,10 +12344,10 @@
     </row>
     <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="8" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B283" s="11" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C283" s="7"/>
       <c r="D283" s="7"/>
@@ -12307,10 +12376,10 @@
     </row>
     <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="8" t="s">
-        <v>661</v>
-      </c>
-      <c r="B284" s="8" t="s">
         <v>662</v>
+      </c>
+      <c r="B284" s="11" t="s">
+        <v>663</v>
       </c>
       <c r="C284" s="7"/>
       <c r="D284" s="7"/>
@@ -12338,11 +12407,11 @@
       <c r="Z284" s="7"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="A285" s="16" t="s">
-        <v>663</v>
-      </c>
-      <c r="B285" s="16" t="s">
+      <c r="A285" s="8" t="s">
         <v>664</v>
+      </c>
+      <c r="B285" s="8" t="s">
+        <v>665</v>
       </c>
       <c r="C285" s="7"/>
       <c r="D285" s="7"/>
@@ -12370,11 +12439,11 @@
       <c r="Z285" s="7"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
-      <c r="A286" s="8" t="s">
-        <v>665</v>
-      </c>
-      <c r="B286" s="8" t="s">
+      <c r="A286" s="16" t="s">
         <v>666</v>
+      </c>
+      <c r="B286" s="16" t="s">
+        <v>667</v>
       </c>
       <c r="C286" s="7"/>
       <c r="D286" s="7"/>
@@ -12402,11 +12471,11 @@
       <c r="Z286" s="7"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="A287" s="16" t="s">
-        <v>667</v>
-      </c>
-      <c r="B287" s="16" t="s">
+      <c r="A287" s="8" t="s">
         <v>668</v>
+      </c>
+      <c r="B287" s="8" t="s">
+        <v>669</v>
       </c>
       <c r="C287" s="7"/>
       <c r="D287" s="7"/>
@@ -12434,11 +12503,11 @@
       <c r="Z287" s="7"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="A288" s="8" t="s">
-        <v>669</v>
-      </c>
-      <c r="B288" s="11" t="s">
+      <c r="A288" s="16" t="s">
         <v>670</v>
+      </c>
+      <c r="B288" s="16" t="s">
+        <v>671</v>
       </c>
       <c r="C288" s="7"/>
       <c r="D288" s="7"/>
@@ -12467,10 +12536,10 @@
     </row>
     <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="8" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B289" s="11" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C289" s="7"/>
       <c r="D289" s="7"/>
@@ -12499,10 +12568,10 @@
     </row>
     <row r="290" ht="15.75" customHeight="1">
       <c r="A290" s="8" t="s">
-        <v>673</v>
-      </c>
-      <c r="B290" s="8" t="s">
         <v>674</v>
+      </c>
+      <c r="B290" s="11" t="s">
+        <v>675</v>
       </c>
       <c r="C290" s="7"/>
       <c r="D290" s="7"/>
@@ -12531,10 +12600,10 @@
     </row>
     <row r="291" ht="15.75" customHeight="1">
       <c r="A291" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="B291" s="11" t="s">
         <v>676</v>
+      </c>
+      <c r="B291" s="8" t="s">
+        <v>677</v>
       </c>
       <c r="C291" s="7"/>
       <c r="D291" s="7"/>
@@ -12563,10 +12632,10 @@
     </row>
     <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="8" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B292" s="11" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C292" s="7"/>
       <c r="D292" s="7"/>
@@ -12595,10 +12664,10 @@
     </row>
     <row r="293" ht="15.75" customHeight="1">
       <c r="A293" s="8" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B293" s="11" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C293" s="7"/>
       <c r="D293" s="7"/>
@@ -12627,10 +12696,10 @@
     </row>
     <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="8" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B294" s="11" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C294" s="7"/>
       <c r="D294" s="7"/>
@@ -12659,10 +12728,10 @@
     </row>
     <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="8" t="s">
-        <v>683</v>
-      </c>
-      <c r="B295" s="8" t="s">
         <v>684</v>
+      </c>
+      <c r="B295" s="11" t="s">
+        <v>685</v>
       </c>
       <c r="C295" s="7"/>
       <c r="D295" s="7"/>
@@ -12690,11 +12759,11 @@
       <c r="Z295" s="7"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="A296" s="20" t="s">
-        <v>685</v>
-      </c>
-      <c r="B296" s="20" t="s">
+      <c r="A296" s="8" t="s">
         <v>686</v>
+      </c>
+      <c r="B296" s="8" t="s">
+        <v>687</v>
       </c>
       <c r="C296" s="7"/>
       <c r="D296" s="7"/>
@@ -12722,11 +12791,11 @@
       <c r="Z296" s="7"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
-      <c r="A297" s="8" t="s">
-        <v>687</v>
-      </c>
-      <c r="B297" s="11" t="s">
+      <c r="A297" s="20" t="s">
         <v>688</v>
+      </c>
+      <c r="B297" s="20" t="s">
+        <v>689</v>
       </c>
       <c r="C297" s="7"/>
       <c r="D297" s="7"/>
@@ -12755,10 +12824,10 @@
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="8" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B298" s="11" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C298" s="7"/>
       <c r="D298" s="7"/>
@@ -12787,10 +12856,10 @@
     </row>
     <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="8" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B299" s="11" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C299" s="7"/>
       <c r="D299" s="7"/>
@@ -12818,11 +12887,11 @@
       <c r="Z299" s="7"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="A300" s="16" t="s">
-        <v>693</v>
-      </c>
-      <c r="B300" s="16" t="s">
+      <c r="A300" s="8" t="s">
         <v>694</v>
+      </c>
+      <c r="B300" s="11" t="s">
+        <v>695</v>
       </c>
       <c r="C300" s="7"/>
       <c r="D300" s="7"/>
@@ -12850,11 +12919,11 @@
       <c r="Z300" s="7"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
-      <c r="A301" s="8" t="s">
-        <v>695</v>
-      </c>
-      <c r="B301" s="11" t="s">
+      <c r="A301" s="16" t="s">
         <v>696</v>
+      </c>
+      <c r="B301" s="16" t="s">
+        <v>697</v>
       </c>
       <c r="C301" s="7"/>
       <c r="D301" s="7"/>
@@ -12883,10 +12952,10 @@
     </row>
     <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="8" t="s">
-        <v>697</v>
-      </c>
-      <c r="B302" s="8" t="s">
         <v>698</v>
+      </c>
+      <c r="B302" s="11" t="s">
+        <v>699</v>
       </c>
       <c r="C302" s="7"/>
       <c r="D302" s="7"/>
@@ -12915,10 +12984,10 @@
     </row>
     <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="8" t="s">
-        <v>699</v>
-      </c>
-      <c r="B303" s="11" t="s">
         <v>700</v>
+      </c>
+      <c r="B303" s="8" t="s">
+        <v>701</v>
       </c>
       <c r="C303" s="7"/>
       <c r="D303" s="7"/>
@@ -12947,10 +13016,10 @@
     </row>
     <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="8" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B304" s="11" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C304" s="7"/>
       <c r="D304" s="7"/>
@@ -12979,10 +13048,10 @@
     </row>
     <row r="305" ht="15.75" customHeight="1">
       <c r="A305" s="8" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B305" s="11" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C305" s="7"/>
       <c r="D305" s="7"/>
@@ -13011,10 +13080,10 @@
     </row>
     <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="8" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B306" s="11" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C306" s="7"/>
       <c r="D306" s="7"/>
@@ -13043,10 +13112,10 @@
     </row>
     <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="8" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B307" s="11" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C307" s="7"/>
       <c r="D307" s="7"/>
@@ -13074,11 +13143,11 @@
       <c r="Z307" s="7"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="A308" s="20" t="s">
-        <v>709</v>
-      </c>
-      <c r="B308" s="21" t="s">
+      <c r="A308" s="8" t="s">
         <v>710</v>
+      </c>
+      <c r="B308" s="11" t="s">
+        <v>711</v>
       </c>
       <c r="C308" s="7"/>
       <c r="D308" s="7"/>
@@ -13106,11 +13175,11 @@
       <c r="Z308" s="7"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="A309" s="8" t="s">
-        <v>711</v>
-      </c>
-      <c r="B309" s="11" t="s">
+      <c r="A309" s="20" t="s">
         <v>712</v>
+      </c>
+      <c r="B309" s="21" t="s">
+        <v>713</v>
       </c>
       <c r="C309" s="7"/>
       <c r="D309" s="7"/>
@@ -13138,11 +13207,11 @@
       <c r="Z309" s="7"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="A310" s="16" t="s">
-        <v>713</v>
-      </c>
-      <c r="B310" s="16" t="s">
+      <c r="A310" s="8" t="s">
         <v>714</v>
+      </c>
+      <c r="B310" s="11" t="s">
+        <v>715</v>
       </c>
       <c r="C310" s="7"/>
       <c r="D310" s="7"/>
@@ -13171,10 +13240,10 @@
     </row>
     <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="16" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B311" s="16" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C311" s="7"/>
       <c r="D311" s="7"/>
@@ -13202,11 +13271,11 @@
       <c r="Z311" s="7"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="A312" s="8" t="s">
-        <v>717</v>
-      </c>
-      <c r="B312" s="8" t="s">
+      <c r="A312" s="16" t="s">
         <v>718</v>
+      </c>
+      <c r="B312" s="16" t="s">
+        <v>719</v>
       </c>
       <c r="C312" s="7"/>
       <c r="D312" s="7"/>
@@ -13234,11 +13303,11 @@
       <c r="Z312" s="7"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="A313" s="16" t="s">
-        <v>719</v>
-      </c>
-      <c r="B313" s="16" t="s">
+      <c r="A313" s="8" t="s">
         <v>720</v>
+      </c>
+      <c r="B313" s="8" t="s">
+        <v>721</v>
       </c>
       <c r="C313" s="7"/>
       <c r="D313" s="7"/>
@@ -13266,11 +13335,11 @@
       <c r="Z313" s="7"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="A314" s="23" t="s">
-        <v>721</v>
-      </c>
-      <c r="B314" s="24" t="s">
+      <c r="A314" s="16" t="s">
         <v>722</v>
+      </c>
+      <c r="B314" s="16" t="s">
+        <v>723</v>
       </c>
       <c r="C314" s="7"/>
       <c r="D314" s="7"/>
@@ -13298,11 +13367,11 @@
       <c r="Z314" s="7"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="A315" s="16" t="s">
-        <v>723</v>
-      </c>
-      <c r="B315" s="16" t="s">
+      <c r="A315" s="23" t="s">
         <v>724</v>
+      </c>
+      <c r="B315" s="24" t="s">
+        <v>725</v>
       </c>
       <c r="C315" s="7"/>
       <c r="D315" s="7"/>
@@ -13330,11 +13399,11 @@
       <c r="Z315" s="7"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="A316" s="8" t="s">
-        <v>725</v>
-      </c>
-      <c r="B316" s="8" t="s">
+      <c r="A316" s="16" t="s">
         <v>726</v>
+      </c>
+      <c r="B316" s="16" t="s">
+        <v>727</v>
       </c>
       <c r="C316" s="7"/>
       <c r="D316" s="7"/>
@@ -13363,10 +13432,10 @@
     </row>
     <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="8" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B317" s="8" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C317" s="7"/>
       <c r="D317" s="7"/>
@@ -13395,10 +13464,10 @@
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="8" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B318" s="8" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C318" s="7"/>
       <c r="D318" s="7"/>
@@ -13427,10 +13496,10 @@
     </row>
     <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="8" t="s">
-        <v>731</v>
-      </c>
-      <c r="B319" s="11" t="s">
         <v>732</v>
+      </c>
+      <c r="B319" s="8" t="s">
+        <v>733</v>
       </c>
       <c r="C319" s="7"/>
       <c r="D319" s="7"/>
@@ -13459,10 +13528,10 @@
     </row>
     <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="8" t="s">
-        <v>733</v>
-      </c>
-      <c r="B320" s="8" t="s">
         <v>734</v>
+      </c>
+      <c r="B320" s="11" t="s">
+        <v>735</v>
       </c>
       <c r="C320" s="7"/>
       <c r="D320" s="7"/>
@@ -13490,11 +13559,11 @@
       <c r="Z320" s="7"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
-      <c r="A321" s="16" t="s">
-        <v>735</v>
-      </c>
-      <c r="B321" s="16" t="s">
+      <c r="A321" s="8" t="s">
         <v>736</v>
+      </c>
+      <c r="B321" s="8" t="s">
+        <v>737</v>
       </c>
       <c r="C321" s="7"/>
       <c r="D321" s="7"/>
@@ -13522,11 +13591,11 @@
       <c r="Z321" s="7"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="A322" s="8" t="s">
-        <v>737</v>
-      </c>
-      <c r="B322" s="11" t="s">
+      <c r="A322" s="16" t="s">
         <v>738</v>
+      </c>
+      <c r="B322" s="16" t="s">
+        <v>739</v>
       </c>
       <c r="C322" s="7"/>
       <c r="D322" s="7"/>
@@ -13555,10 +13624,10 @@
     </row>
     <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="8" t="s">
-        <v>739</v>
-      </c>
-      <c r="B323" s="8" t="s">
         <v>740</v>
+      </c>
+      <c r="B323" s="11" t="s">
+        <v>741</v>
       </c>
       <c r="C323" s="7"/>
       <c r="D323" s="7"/>
@@ -13587,10 +13656,10 @@
     </row>
     <row r="324" ht="15.75" customHeight="1">
       <c r="A324" s="8" t="s">
-        <v>741</v>
-      </c>
-      <c r="B324" s="11" t="s">
         <v>742</v>
+      </c>
+      <c r="B324" s="8" t="s">
+        <v>743</v>
       </c>
       <c r="C324" s="7"/>
       <c r="D324" s="7"/>
@@ -13619,10 +13688,10 @@
     </row>
     <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="8" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B325" s="11" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C325" s="7"/>
       <c r="D325" s="7"/>
@@ -13651,10 +13720,10 @@
     </row>
     <row r="326" ht="15.75" customHeight="1">
       <c r="A326" s="8" t="s">
-        <v>745</v>
-      </c>
-      <c r="B326" s="8" t="s">
         <v>746</v>
+      </c>
+      <c r="B326" s="11" t="s">
+        <v>747</v>
       </c>
       <c r="C326" s="7"/>
       <c r="D326" s="7"/>
@@ -13683,10 +13752,10 @@
     </row>
     <row r="327" ht="15.75" customHeight="1">
       <c r="A327" s="8" t="s">
-        <v>747</v>
-      </c>
-      <c r="B327" s="11" t="s">
         <v>748</v>
+      </c>
+      <c r="B327" s="8" t="s">
+        <v>749</v>
       </c>
       <c r="C327" s="7"/>
       <c r="D327" s="7"/>
@@ -13715,10 +13784,10 @@
     </row>
     <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="8" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B328" s="11" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C328" s="7"/>
       <c r="D328" s="7"/>
@@ -13746,11 +13815,11 @@
       <c r="Z328" s="7"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="A329" s="20" t="s">
-        <v>751</v>
-      </c>
-      <c r="B329" s="21" t="s">
+      <c r="A329" s="8" t="s">
         <v>752</v>
+      </c>
+      <c r="B329" s="11" t="s">
+        <v>753</v>
       </c>
       <c r="C329" s="7"/>
       <c r="D329" s="7"/>
@@ -13778,11 +13847,11 @@
       <c r="Z329" s="7"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="A330" s="8" t="s">
-        <v>753</v>
-      </c>
-      <c r="B330" s="11" t="s">
+      <c r="A330" s="20" t="s">
         <v>754</v>
+      </c>
+      <c r="B330" s="21" t="s">
+        <v>755</v>
       </c>
       <c r="C330" s="7"/>
       <c r="D330" s="7"/>
@@ -13811,10 +13880,10 @@
     </row>
     <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="8" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B331" s="11" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C331" s="7"/>
       <c r="D331" s="7"/>
@@ -13843,10 +13912,10 @@
     </row>
     <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="B332" s="8" t="s">
         <v>758</v>
+      </c>
+      <c r="B332" s="11" t="s">
+        <v>759</v>
       </c>
       <c r="C332" s="7"/>
       <c r="D332" s="7"/>
@@ -13875,10 +13944,10 @@
     </row>
     <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="8" t="s">
-        <v>759</v>
-      </c>
-      <c r="B333" s="11" t="s">
         <v>760</v>
+      </c>
+      <c r="B333" s="8" t="s">
+        <v>761</v>
       </c>
       <c r="C333" s="7"/>
       <c r="D333" s="7"/>
@@ -13907,10 +13976,10 @@
     </row>
     <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="8" t="s">
-        <v>761</v>
-      </c>
-      <c r="B334" s="8" t="s">
         <v>762</v>
+      </c>
+      <c r="B334" s="11" t="s">
+        <v>763</v>
       </c>
       <c r="C334" s="7"/>
       <c r="D334" s="7"/>
@@ -13939,10 +14008,10 @@
     </row>
     <row r="335" ht="15.75" customHeight="1">
       <c r="A335" s="8" t="s">
-        <v>763</v>
-      </c>
-      <c r="B335" s="11" t="s">
         <v>764</v>
+      </c>
+      <c r="B335" s="8" t="s">
+        <v>765</v>
       </c>
       <c r="C335" s="7"/>
       <c r="D335" s="7"/>
@@ -13971,10 +14040,10 @@
     </row>
     <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="8" t="s">
-        <v>765</v>
-      </c>
-      <c r="B336" s="8" t="s">
         <v>766</v>
+      </c>
+      <c r="B336" s="11" t="s">
+        <v>767</v>
       </c>
       <c r="C336" s="7"/>
       <c r="D336" s="7"/>
@@ -14003,10 +14072,10 @@
     </row>
     <row r="337" ht="15.75" customHeight="1">
       <c r="A337" s="8" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B337" s="8" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C337" s="7"/>
       <c r="D337" s="7"/>
@@ -14035,10 +14104,10 @@
     </row>
     <row r="338" ht="15.75" customHeight="1">
       <c r="A338" s="8" t="s">
-        <v>769</v>
-      </c>
-      <c r="B338" s="11" t="s">
         <v>770</v>
+      </c>
+      <c r="B338" s="8" t="s">
+        <v>771</v>
       </c>
       <c r="C338" s="7"/>
       <c r="D338" s="7"/>
@@ -14067,10 +14136,10 @@
     </row>
     <row r="339" ht="15.75" customHeight="1">
       <c r="A339" s="8" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B339" s="11" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C339" s="7"/>
       <c r="D339" s="7"/>
@@ -14099,10 +14168,10 @@
     </row>
     <row r="340" ht="15.75" customHeight="1">
       <c r="A340" s="8" t="s">
-        <v>773</v>
-      </c>
-      <c r="B340" s="8" t="s">
         <v>774</v>
+      </c>
+      <c r="B340" s="11" t="s">
+        <v>775</v>
       </c>
       <c r="C340" s="7"/>
       <c r="D340" s="7"/>
@@ -14131,10 +14200,10 @@
     </row>
     <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="8" t="s">
-        <v>775</v>
-      </c>
-      <c r="B341" s="11" t="s">
         <v>776</v>
+      </c>
+      <c r="B341" s="8" t="s">
+        <v>777</v>
       </c>
       <c r="C341" s="7"/>
       <c r="D341" s="7"/>
@@ -14163,10 +14232,10 @@
     </row>
     <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="8" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B342" s="11" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C342" s="7"/>
       <c r="D342" s="7"/>
@@ -14195,10 +14264,10 @@
     </row>
     <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="8" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B343" s="11" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C343" s="7"/>
       <c r="D343" s="7"/>
@@ -14227,10 +14296,10 @@
     </row>
     <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="8" t="s">
-        <v>781</v>
-      </c>
-      <c r="B344" s="8" t="s">
         <v>782</v>
+      </c>
+      <c r="B344" s="11" t="s">
+        <v>783</v>
       </c>
       <c r="C344" s="7"/>
       <c r="D344" s="7"/>
@@ -14259,10 +14328,10 @@
     </row>
     <row r="345" ht="15.75" customHeight="1">
       <c r="A345" s="8" t="s">
-        <v>783</v>
-      </c>
-      <c r="B345" s="11" t="s">
         <v>784</v>
+      </c>
+      <c r="B345" s="8" t="s">
+        <v>785</v>
       </c>
       <c r="C345" s="7"/>
       <c r="D345" s="7"/>
@@ -14291,10 +14360,10 @@
     </row>
     <row r="346" ht="15.75" customHeight="1">
       <c r="A346" s="8" t="s">
-        <v>785</v>
-      </c>
-      <c r="B346" s="8" t="s">
         <v>786</v>
+      </c>
+      <c r="B346" s="11" t="s">
+        <v>787</v>
       </c>
       <c r="C346" s="7"/>
       <c r="D346" s="7"/>
@@ -14323,10 +14392,10 @@
     </row>
     <row r="347" ht="15.75" customHeight="1">
       <c r="A347" s="8" t="s">
-        <v>787</v>
-      </c>
-      <c r="B347" s="11" t="s">
         <v>788</v>
+      </c>
+      <c r="B347" s="8" t="s">
+        <v>789</v>
       </c>
       <c r="C347" s="7"/>
       <c r="D347" s="7"/>
@@ -14355,10 +14424,10 @@
     </row>
     <row r="348" ht="15.75" customHeight="1">
       <c r="A348" s="8" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B348" s="11" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C348" s="7"/>
       <c r="D348" s="7"/>
@@ -14387,10 +14456,10 @@
     </row>
     <row r="349" ht="15.75" customHeight="1">
       <c r="A349" s="8" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B349" s="11" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C349" s="7"/>
       <c r="D349" s="7"/>
@@ -14419,10 +14488,10 @@
     </row>
     <row r="350" ht="15.75" customHeight="1">
       <c r="A350" s="8" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B350" s="11" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C350" s="7"/>
       <c r="D350" s="7"/>
@@ -14451,10 +14520,10 @@
     </row>
     <row r="351" ht="15.75" customHeight="1">
       <c r="A351" s="8" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B351" s="11" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C351" s="7"/>
       <c r="D351" s="7"/>
@@ -14482,11 +14551,11 @@
       <c r="Z351" s="7"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
-      <c r="A352" s="16" t="s">
-        <v>797</v>
-      </c>
-      <c r="B352" s="25" t="s">
+      <c r="A352" s="8" t="s">
         <v>798</v>
+      </c>
+      <c r="B352" s="11" t="s">
+        <v>799</v>
       </c>
       <c r="C352" s="7"/>
       <c r="D352" s="7"/>
@@ -14515,10 +14584,10 @@
     </row>
     <row r="353" ht="15.75" customHeight="1">
       <c r="A353" s="16" t="s">
-        <v>799</v>
-      </c>
-      <c r="B353" s="16" t="s">
         <v>800</v>
+      </c>
+      <c r="B353" s="25" t="s">
+        <v>801</v>
       </c>
       <c r="C353" s="7"/>
       <c r="D353" s="7"/>
@@ -14546,11 +14615,11 @@
       <c r="Z353" s="7"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="A354" s="8" t="s">
-        <v>801</v>
-      </c>
-      <c r="B354" s="11" t="s">
+      <c r="A354" s="16" t="s">
         <v>802</v>
+      </c>
+      <c r="B354" s="16" t="s">
+        <v>803</v>
       </c>
       <c r="C354" s="7"/>
       <c r="D354" s="7"/>
@@ -14579,10 +14648,10 @@
     </row>
     <row r="355" ht="15.75" customHeight="1">
       <c r="A355" s="8" t="s">
-        <v>803</v>
-      </c>
-      <c r="B355" s="8" t="s">
         <v>804</v>
+      </c>
+      <c r="B355" s="11" t="s">
+        <v>805</v>
       </c>
       <c r="C355" s="7"/>
       <c r="D355" s="7"/>
@@ -14610,11 +14679,11 @@
       <c r="Z355" s="7"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="A356" s="16" t="s">
-        <v>805</v>
-      </c>
-      <c r="B356" s="16" t="s">
+      <c r="A356" s="8" t="s">
         <v>806</v>
+      </c>
+      <c r="B356" s="8" t="s">
+        <v>807</v>
       </c>
       <c r="C356" s="7"/>
       <c r="D356" s="7"/>
@@ -14642,11 +14711,11 @@
       <c r="Z356" s="7"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="A357" s="11" t="s">
-        <v>807</v>
-      </c>
-      <c r="B357" s="8" t="s">
+      <c r="A357" s="16" t="s">
         <v>808</v>
+      </c>
+      <c r="B357" s="16" t="s">
+        <v>809</v>
       </c>
       <c r="C357" s="7"/>
       <c r="D357" s="7"/>
@@ -14674,11 +14743,11 @@
       <c r="Z357" s="7"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="A358" s="8" t="s">
-        <v>809</v>
+      <c r="A358" s="11" t="s">
+        <v>810</v>
       </c>
       <c r="B358" s="8" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C358" s="7"/>
       <c r="D358" s="7"/>
@@ -14706,11 +14775,11 @@
       <c r="Z358" s="7"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="A359" s="16" t="s">
-        <v>811</v>
-      </c>
-      <c r="B359" s="16" t="s">
+      <c r="A359" s="8" t="s">
         <v>812</v>
+      </c>
+      <c r="B359" s="8" t="s">
+        <v>813</v>
       </c>
       <c r="C359" s="7"/>
       <c r="D359" s="7"/>
@@ -14738,11 +14807,11 @@
       <c r="Z359" s="7"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="A360" s="11" t="s">
-        <v>813</v>
-      </c>
-      <c r="B360" s="11" t="s">
+      <c r="A360" s="16" t="s">
         <v>814</v>
+      </c>
+      <c r="B360" s="16" t="s">
+        <v>815</v>
       </c>
       <c r="C360" s="7"/>
       <c r="D360" s="7"/>
@@ -14770,11 +14839,11 @@
       <c r="Z360" s="7"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="16" t="s">
-        <v>815</v>
+      <c r="A361" s="11" t="s">
+        <v>816</v>
       </c>
       <c r="B361" s="11" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C361" s="7"/>
       <c r="D361" s="7"/>
@@ -14802,11 +14871,11 @@
       <c r="Z361" s="7"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="A362" s="8" t="s">
-        <v>817</v>
+      <c r="A362" s="16" t="s">
+        <v>818</v>
       </c>
       <c r="B362" s="11" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C362" s="7"/>
       <c r="D362" s="7"/>
@@ -14834,11 +14903,11 @@
       <c r="Z362" s="7"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="A363" s="11" t="s">
-        <v>819</v>
+      <c r="A363" s="8" t="s">
+        <v>820</v>
       </c>
       <c r="B363" s="11" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C363" s="7"/>
       <c r="D363" s="7"/>
@@ -14866,11 +14935,11 @@
       <c r="Z363" s="7"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="A364" s="8" t="s">
-        <v>821</v>
+      <c r="A364" s="11" t="s">
+        <v>822</v>
       </c>
       <c r="B364" s="11" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C364" s="7"/>
       <c r="D364" s="7"/>
@@ -14898,11 +14967,11 @@
       <c r="Z364" s="7"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="A365" s="20" t="s">
-        <v>823</v>
-      </c>
-      <c r="B365" s="21" t="s">
+      <c r="A365" s="8" t="s">
         <v>824</v>
+      </c>
+      <c r="B365" s="11" t="s">
+        <v>825</v>
       </c>
       <c r="C365" s="7"/>
       <c r="D365" s="7"/>
@@ -14930,11 +14999,11 @@
       <c r="Z365" s="7"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="A366" s="8" t="s">
-        <v>825</v>
-      </c>
-      <c r="B366" s="8" t="s">
+      <c r="A366" s="20" t="s">
         <v>826</v>
+      </c>
+      <c r="B366" s="21" t="s">
+        <v>827</v>
       </c>
       <c r="C366" s="7"/>
       <c r="D366" s="7"/>
@@ -14963,10 +15032,10 @@
     </row>
     <row r="367" ht="15.75" customHeight="1">
       <c r="A367" s="8" t="s">
-        <v>827</v>
-      </c>
-      <c r="B367" s="11" t="s">
         <v>828</v>
+      </c>
+      <c r="B367" s="8" t="s">
+        <v>829</v>
       </c>
       <c r="C367" s="7"/>
       <c r="D367" s="7"/>
@@ -14995,10 +15064,10 @@
     </row>
     <row r="368" ht="15.75" customHeight="1">
       <c r="A368" s="8" t="s">
-        <v>829</v>
-      </c>
-      <c r="B368" s="8" t="s">
         <v>830</v>
+      </c>
+      <c r="B368" s="11" t="s">
+        <v>831</v>
       </c>
       <c r="C368" s="7"/>
       <c r="D368" s="7"/>
@@ -15027,10 +15096,10 @@
     </row>
     <row r="369" ht="15.75" customHeight="1">
       <c r="A369" s="8" t="s">
-        <v>831</v>
-      </c>
-      <c r="B369" s="11" t="s">
         <v>832</v>
+      </c>
+      <c r="B369" s="8" t="s">
+        <v>833</v>
       </c>
       <c r="C369" s="7"/>
       <c r="D369" s="7"/>
@@ -15058,11 +15127,11 @@
       <c r="Z369" s="7"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="A370" s="11" t="s">
-        <v>833</v>
+      <c r="A370" s="8" t="s">
+        <v>834</v>
       </c>
       <c r="B370" s="11" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C370" s="7"/>
       <c r="D370" s="7"/>
@@ -15090,11 +15159,11 @@
       <c r="Z370" s="7"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="A371" s="8" t="s">
-        <v>835</v>
-      </c>
-      <c r="B371" s="8" t="s">
+      <c r="A371" s="11" t="s">
         <v>836</v>
+      </c>
+      <c r="B371" s="11" t="s">
+        <v>837</v>
       </c>
       <c r="C371" s="7"/>
       <c r="D371" s="7"/>
@@ -15123,10 +15192,10 @@
     </row>
     <row r="372" ht="15.75" customHeight="1">
       <c r="A372" s="8" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B372" s="8" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C372" s="7"/>
       <c r="D372" s="7"/>
@@ -15155,10 +15224,10 @@
     </row>
     <row r="373" ht="15.75" customHeight="1">
       <c r="A373" s="8" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B373" s="8" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C373" s="7"/>
       <c r="D373" s="7"/>
@@ -15187,10 +15256,10 @@
     </row>
     <row r="374" ht="15.75" customHeight="1">
       <c r="A374" s="8" t="s">
-        <v>841</v>
-      </c>
-      <c r="B374" s="11" t="s">
         <v>842</v>
+      </c>
+      <c r="B374" s="8" t="s">
+        <v>843</v>
       </c>
       <c r="C374" s="7"/>
       <c r="D374" s="7"/>
@@ -15219,10 +15288,10 @@
     </row>
     <row r="375" ht="15.75" customHeight="1">
       <c r="A375" s="8" t="s">
-        <v>843</v>
-      </c>
-      <c r="B375" s="8" t="s">
         <v>844</v>
+      </c>
+      <c r="B375" s="11" t="s">
+        <v>845</v>
       </c>
       <c r="C375" s="7"/>
       <c r="D375" s="7"/>
@@ -15251,10 +15320,10 @@
     </row>
     <row r="376" ht="15.75" customHeight="1">
       <c r="A376" s="8" t="s">
-        <v>845</v>
-      </c>
-      <c r="B376" s="11" t="s">
         <v>846</v>
+      </c>
+      <c r="B376" s="8" t="s">
+        <v>847</v>
       </c>
       <c r="C376" s="7"/>
       <c r="D376" s="7"/>
@@ -15283,10 +15352,10 @@
     </row>
     <row r="377" ht="15.75" customHeight="1">
       <c r="A377" s="16" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B377" s="16" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C377" s="7"/>
       <c r="D377" s="7"/>
@@ -15315,10 +15384,10 @@
     </row>
     <row r="378" ht="15.75" customHeight="1">
       <c r="A378" s="8" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B378" s="11" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C378" s="7"/>
       <c r="D378" s="7"/>
@@ -15347,10 +15416,10 @@
     </row>
     <row r="379" ht="15.75" customHeight="1">
       <c r="A379" s="16" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B379" s="16" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C379" s="7"/>
       <c r="D379" s="7"/>
@@ -15379,10 +15448,10 @@
     </row>
     <row r="380" ht="15.75" customHeight="1">
       <c r="A380" s="16" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B380" s="16" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C380" s="7"/>
       <c r="D380" s="7"/>
@@ -15411,10 +15480,10 @@
     </row>
     <row r="381" ht="15.75" customHeight="1">
       <c r="A381" s="8" t="s">
-        <v>855</v>
-      </c>
-      <c r="B381" s="8" t="s">
         <v>856</v>
+      </c>
+      <c r="B381" s="11" t="s">
+        <v>857</v>
       </c>
       <c r="C381" s="7"/>
       <c r="D381" s="7"/>
@@ -15442,11 +15511,11 @@
       <c r="Z381" s="7"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="A382" s="8" t="s">
-        <v>857</v>
-      </c>
-      <c r="B382" s="8" t="s">
+      <c r="A382" s="16" t="s">
         <v>858</v>
+      </c>
+      <c r="B382" s="16" t="s">
+        <v>859</v>
       </c>
       <c r="C382" s="7"/>
       <c r="D382" s="7"/>
@@ -15474,11 +15543,11 @@
       <c r="Z382" s="7"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="A383" s="11" t="s">
-        <v>859</v>
-      </c>
-      <c r="B383" s="11" t="s">
+      <c r="A383" s="16" t="s">
         <v>860</v>
+      </c>
+      <c r="B383" s="16" t="s">
+        <v>861</v>
       </c>
       <c r="C383" s="7"/>
       <c r="D383" s="7"/>
@@ -15507,10 +15576,10 @@
     </row>
     <row r="384" ht="15.75" customHeight="1">
       <c r="A384" s="8" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B384" s="8" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C384" s="7"/>
       <c r="D384" s="7"/>
@@ -15538,11 +15607,11 @@
       <c r="Z384" s="7"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="A385" s="21" t="s">
-        <v>863</v>
-      </c>
-      <c r="B385" s="20" t="s">
+      <c r="A385" s="8" t="s">
         <v>864</v>
+      </c>
+      <c r="B385" s="8" t="s">
+        <v>865</v>
       </c>
       <c r="C385" s="7"/>
       <c r="D385" s="7"/>
@@ -15570,11 +15639,11 @@
       <c r="Z385" s="7"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="A386" s="8" t="s">
-        <v>865</v>
-      </c>
-      <c r="B386" s="8" t="s">
+      <c r="A386" s="11" t="s">
         <v>866</v>
+      </c>
+      <c r="B386" s="11" t="s">
+        <v>867</v>
       </c>
       <c r="C386" s="7"/>
       <c r="D386" s="7"/>
@@ -15603,10 +15672,10 @@
     </row>
     <row r="387" ht="15.75" customHeight="1">
       <c r="A387" s="8" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B387" s="8" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C387" s="7"/>
       <c r="D387" s="7"/>
@@ -15634,11 +15703,11 @@
       <c r="Z387" s="7"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="A388" s="8" t="s">
-        <v>869</v>
-      </c>
-      <c r="B388" s="8" t="s">
+      <c r="A388" s="21" t="s">
         <v>870</v>
+      </c>
+      <c r="B388" s="20" t="s">
+        <v>871</v>
       </c>
       <c r="C388" s="7"/>
       <c r="D388" s="7"/>
@@ -15666,6 +15735,12 @@
       <c r="Z388" s="7"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
+      <c r="A389" s="8" t="s">
+        <v>872</v>
+      </c>
+      <c r="B389" s="8" t="s">
+        <v>873</v>
+      </c>
       <c r="C389" s="7"/>
       <c r="D389" s="7"/>
       <c r="E389" s="7"/>
@@ -15692,6 +15767,12 @@
       <c r="Z389" s="7"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
+      <c r="A390" s="8" t="s">
+        <v>874</v>
+      </c>
+      <c r="B390" s="8" t="s">
+        <v>875</v>
+      </c>
       <c r="C390" s="7"/>
       <c r="D390" s="7"/>
       <c r="E390" s="7"/>
@@ -15718,6 +15799,12 @@
       <c r="Z390" s="7"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
+      <c r="A391" s="8" t="s">
+        <v>876</v>
+      </c>
+      <c r="B391" s="8" t="s">
+        <v>877</v>
+      </c>
       <c r="C391" s="7"/>
       <c r="D391" s="7"/>
       <c r="E391" s="7"/>

--- a/Literature/Languages/Norvunic (old).xlsx
+++ b/Literature/Languages/Norvunic (old).xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="882">
   <si>
     <t>Word</t>
   </si>
@@ -69,7 +69,7 @@
     <t>nus ægi blûlr = blue very robes (very blue robes)</t>
   </si>
   <si>
-    <t>any</t>
+    <t>adv</t>
   </si>
   <si>
     <t>stode</t>
@@ -2013,6 +2013,12 @@
     <t>to eat or consume, åte = past tense</t>
   </si>
   <si>
+    <t>hæsskrymen</t>
+  </si>
+  <si>
+    <t>to explore</t>
+  </si>
+  <si>
     <t>mørknen</t>
   </si>
   <si>
@@ -2265,6 +2271,12 @@
     <t>to ride</t>
   </si>
   <si>
+    <t>skrymen</t>
+  </si>
+  <si>
+    <t>to roam, to wander</t>
+  </si>
+  <si>
     <t>råten</t>
   </si>
   <si>
@@ -2433,7 +2445,7 @@
     <t>to write, or print</t>
   </si>
   <si>
-    <t>fel</t>
+    <t>til</t>
   </si>
   <si>
     <t>to, towards, for</t>
@@ -2753,7 +2765,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2826,9 +2838,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
@@ -3202,12 +3211,12 @@
         <v>23</v>
       </c>
       <c r="G4" s="14" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:B1000, REGEXMATCH(B2:B1000, H3)), 2, TRUE)"),"klæddvin")</f>
-        <v>klæddvin</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:B1000, REGEXMATCH(B2:B1000, H3)), 2, TRUE)"),"øt")</f>
+        <v>øt</v>
       </c>
       <c r="H4" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"any cloth attire, or apparel; clothing")</f>
-        <v>any cloth attire, or apparel; clothing</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"only, just, merely (adverb, adjective)")</f>
+        <v>only, just, merely (adverb, adjective)</v>
       </c>
       <c r="I4" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("FILTER(C:C, REGEXMATCH(B:B, H3))"),"")</f>
@@ -3249,12 +3258,12 @@
         <v>27</v>
       </c>
       <c r="G5" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"antul")</f>
-        <v>antul</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"tampt")</f>
+        <v>tampt</v>
       </c>
       <c r="H5" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"any type of armor")</f>
-        <v>any type of armor</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"something that was done again (adverb)")</f>
+        <v>something that was done again (adverb)</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
@@ -3293,12 +3302,12 @@
         <v>31</v>
       </c>
       <c r="G6" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"borg")</f>
-        <v>borg</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"bovt")</f>
+        <v>bovt</v>
       </c>
       <c r="H6" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"any type of fortified structure, mostly used to refer castles")</f>
-        <v>any type of fortified structure, mostly used to refer castles</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"to be curious, or adventurous")</f>
+        <v>to be curious, or adventurous</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -3337,12 +3346,12 @@
         <v>35</v>
       </c>
       <c r="G7" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"mirste")</f>
-        <v>mirste</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"vel")</f>
+        <v>vel</v>
       </c>
       <c r="H7" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"any type of metal")</f>
-        <v>any type of metal</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"well (adverb)")</f>
+        <v>well (adverb)</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
@@ -3380,14 +3389,8 @@
       <c r="F8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"nem")</f>
-        <v>nem</v>
-      </c>
-      <c r="H8" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"any, some")</f>
-        <v>any, some</v>
-      </c>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -3424,14 +3427,8 @@
       <c r="F9" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"bagt")</f>
-        <v>bagt</v>
-      </c>
-      <c r="H9" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"battle, or any large-scale fight")</f>
-        <v>battle, or any large-scale fight</v>
-      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
@@ -3468,14 +3465,8 @@
       <c r="F10" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"maf")</f>
-        <v>maf</v>
-      </c>
-      <c r="H10" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"many, much, several, or a lot of")</f>
-        <v>many, much, several, or a lot of</v>
-      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -3512,14 +3503,8 @@
       <c r="F11" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"håle")</f>
-        <v>håle</v>
-      </c>
-      <c r="H11" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"the sea, ocean, or any giant body of water")</f>
-        <v>the sea, ocean, or any giant body of water</v>
-      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
@@ -3556,14 +3541,8 @@
       <c r="F12" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"gånde")</f>
-        <v>gånde</v>
-      </c>
-      <c r="H12" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"used to describe any type of magic")</f>
-        <v>used to describe any type of magic</v>
-      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
@@ -12471,10 +12450,10 @@
       <c r="Z286" s="7"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="A287" s="8" t="s">
+      <c r="A287" s="16" t="s">
         <v>668</v>
       </c>
-      <c r="B287" s="8" t="s">
+      <c r="B287" s="16" t="s">
         <v>669</v>
       </c>
       <c r="C287" s="7"/>
@@ -12503,10 +12482,10 @@
       <c r="Z287" s="7"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="A288" s="16" t="s">
+      <c r="A288" s="8" t="s">
         <v>670</v>
       </c>
-      <c r="B288" s="16" t="s">
+      <c r="B288" s="8" t="s">
         <v>671</v>
       </c>
       <c r="C288" s="7"/>
@@ -12535,10 +12514,10 @@
       <c r="Z288" s="7"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
-      <c r="A289" s="8" t="s">
+      <c r="A289" s="16" t="s">
         <v>672</v>
       </c>
-      <c r="B289" s="11" t="s">
+      <c r="B289" s="16" t="s">
         <v>673</v>
       </c>
       <c r="C289" s="7"/>
@@ -12602,7 +12581,7 @@
       <c r="A291" s="8" t="s">
         <v>676</v>
       </c>
-      <c r="B291" s="8" t="s">
+      <c r="B291" s="11" t="s">
         <v>677</v>
       </c>
       <c r="C291" s="7"/>
@@ -12634,7 +12613,7 @@
       <c r="A292" s="8" t="s">
         <v>678</v>
       </c>
-      <c r="B292" s="11" t="s">
+      <c r="B292" s="8" t="s">
         <v>679</v>
       </c>
       <c r="C292" s="7"/>
@@ -12762,7 +12741,7 @@
       <c r="A296" s="8" t="s">
         <v>686</v>
       </c>
-      <c r="B296" s="8" t="s">
+      <c r="B296" s="11" t="s">
         <v>687</v>
       </c>
       <c r="C296" s="7"/>
@@ -12791,10 +12770,10 @@
       <c r="Z296" s="7"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
-      <c r="A297" s="20" t="s">
+      <c r="A297" s="8" t="s">
         <v>688</v>
       </c>
-      <c r="B297" s="20" t="s">
+      <c r="B297" s="8" t="s">
         <v>689</v>
       </c>
       <c r="C297" s="7"/>
@@ -12823,10 +12802,10 @@
       <c r="Z297" s="7"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
-      <c r="A298" s="8" t="s">
+      <c r="A298" s="20" t="s">
         <v>690</v>
       </c>
-      <c r="B298" s="11" t="s">
+      <c r="B298" s="20" t="s">
         <v>691</v>
       </c>
       <c r="C298" s="7"/>
@@ -12919,10 +12898,10 @@
       <c r="Z300" s="7"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
-      <c r="A301" s="16" t="s">
+      <c r="A301" s="8" t="s">
         <v>696</v>
       </c>
-      <c r="B301" s="16" t="s">
+      <c r="B301" s="11" t="s">
         <v>697</v>
       </c>
       <c r="C301" s="7"/>
@@ -12951,10 +12930,10 @@
       <c r="Z301" s="7"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="A302" s="8" t="s">
+      <c r="A302" s="16" t="s">
         <v>698</v>
       </c>
-      <c r="B302" s="11" t="s">
+      <c r="B302" s="16" t="s">
         <v>699</v>
       </c>
       <c r="C302" s="7"/>
@@ -12986,7 +12965,7 @@
       <c r="A303" s="8" t="s">
         <v>700</v>
       </c>
-      <c r="B303" s="8" t="s">
+      <c r="B303" s="11" t="s">
         <v>701</v>
       </c>
       <c r="C303" s="7"/>
@@ -13018,7 +12997,7 @@
       <c r="A304" s="8" t="s">
         <v>702</v>
       </c>
-      <c r="B304" s="11" t="s">
+      <c r="B304" s="8" t="s">
         <v>703</v>
       </c>
       <c r="C304" s="7"/>
@@ -13175,10 +13154,10 @@
       <c r="Z308" s="7"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="A309" s="20" t="s">
+      <c r="A309" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="B309" s="21" t="s">
+      <c r="B309" s="11" t="s">
         <v>713</v>
       </c>
       <c r="C309" s="7"/>
@@ -13207,10 +13186,10 @@
       <c r="Z309" s="7"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="A310" s="8" t="s">
+      <c r="A310" s="20" t="s">
         <v>714</v>
       </c>
-      <c r="B310" s="11" t="s">
+      <c r="B310" s="21" t="s">
         <v>715</v>
       </c>
       <c r="C310" s="7"/>
@@ -13239,10 +13218,10 @@
       <c r="Z310" s="7"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="A311" s="16" t="s">
+      <c r="A311" s="8" t="s">
         <v>716</v>
       </c>
-      <c r="B311" s="16" t="s">
+      <c r="B311" s="11" t="s">
         <v>717</v>
       </c>
       <c r="C311" s="7"/>
@@ -13303,10 +13282,10 @@
       <c r="Z312" s="7"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="A313" s="8" t="s">
+      <c r="A313" s="16" t="s">
         <v>720</v>
       </c>
-      <c r="B313" s="8" t="s">
+      <c r="B313" s="16" t="s">
         <v>721</v>
       </c>
       <c r="C313" s="7"/>
@@ -13335,10 +13314,10 @@
       <c r="Z313" s="7"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="A314" s="16" t="s">
+      <c r="A314" s="8" t="s">
         <v>722</v>
       </c>
-      <c r="B314" s="16" t="s">
+      <c r="B314" s="8" t="s">
         <v>723</v>
       </c>
       <c r="C314" s="7"/>
@@ -13367,10 +13346,10 @@
       <c r="Z314" s="7"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="A315" s="23" t="s">
+      <c r="A315" s="16" t="s">
         <v>724</v>
       </c>
-      <c r="B315" s="24" t="s">
+      <c r="B315" s="16" t="s">
         <v>725</v>
       </c>
       <c r="C315" s="7"/>
@@ -13399,10 +13378,10 @@
       <c r="Z315" s="7"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="A316" s="16" t="s">
+      <c r="A316" s="23" t="s">
         <v>726</v>
       </c>
-      <c r="B316" s="16" t="s">
+      <c r="B316" s="24" t="s">
         <v>727</v>
       </c>
       <c r="C316" s="7"/>
@@ -13431,10 +13410,10 @@
       <c r="Z316" s="7"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="A317" s="8" t="s">
+      <c r="A317" s="16" t="s">
         <v>728</v>
       </c>
-      <c r="B317" s="8" t="s">
+      <c r="B317" s="16" t="s">
         <v>729</v>
       </c>
       <c r="C317" s="7"/>
@@ -13530,7 +13509,7 @@
       <c r="A320" s="8" t="s">
         <v>734</v>
       </c>
-      <c r="B320" s="11" t="s">
+      <c r="B320" s="8" t="s">
         <v>735</v>
       </c>
       <c r="C320" s="7"/>
@@ -13562,7 +13541,7 @@
       <c r="A321" s="8" t="s">
         <v>736</v>
       </c>
-      <c r="B321" s="8" t="s">
+      <c r="B321" s="11" t="s">
         <v>737</v>
       </c>
       <c r="C321" s="7"/>
@@ -13591,10 +13570,10 @@
       <c r="Z321" s="7"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="A322" s="16" t="s">
+      <c r="A322" s="8" t="s">
         <v>738</v>
       </c>
-      <c r="B322" s="16" t="s">
+      <c r="B322" s="8" t="s">
         <v>739</v>
       </c>
       <c r="C322" s="7"/>
@@ -13623,10 +13602,10 @@
       <c r="Z322" s="7"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="A323" s="8" t="s">
+      <c r="A323" s="16" t="s">
         <v>740</v>
       </c>
-      <c r="B323" s="11" t="s">
+      <c r="B323" s="16" t="s">
         <v>741</v>
       </c>
       <c r="C323" s="7"/>
@@ -13658,7 +13637,7 @@
       <c r="A324" s="8" t="s">
         <v>742</v>
       </c>
-      <c r="B324" s="8" t="s">
+      <c r="B324" s="11" t="s">
         <v>743</v>
       </c>
       <c r="C324" s="7"/>
@@ -13690,7 +13669,7 @@
       <c r="A325" s="8" t="s">
         <v>744</v>
       </c>
-      <c r="B325" s="11" t="s">
+      <c r="B325" s="8" t="s">
         <v>745</v>
       </c>
       <c r="C325" s="7"/>
@@ -13754,7 +13733,7 @@
       <c r="A327" s="8" t="s">
         <v>748</v>
       </c>
-      <c r="B327" s="8" t="s">
+      <c r="B327" s="11" t="s">
         <v>749</v>
       </c>
       <c r="C327" s="7"/>
@@ -13786,7 +13765,7 @@
       <c r="A328" s="8" t="s">
         <v>750</v>
       </c>
-      <c r="B328" s="11" t="s">
+      <c r="B328" s="8" t="s">
         <v>751</v>
       </c>
       <c r="C328" s="7"/>
@@ -13815,10 +13794,10 @@
       <c r="Z328" s="7"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="A329" s="8" t="s">
+      <c r="A329" s="16" t="s">
         <v>752</v>
       </c>
-      <c r="B329" s="11" t="s">
+      <c r="B329" s="16" t="s">
         <v>753</v>
       </c>
       <c r="C329" s="7"/>
@@ -13847,10 +13826,10 @@
       <c r="Z329" s="7"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="A330" s="20" t="s">
+      <c r="A330" s="8" t="s">
         <v>754</v>
       </c>
-      <c r="B330" s="21" t="s">
+      <c r="B330" s="11" t="s">
         <v>755</v>
       </c>
       <c r="C330" s="7"/>
@@ -13911,10 +13890,10 @@
       <c r="Z331" s="7"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="A332" s="8" t="s">
+      <c r="A332" s="20" t="s">
         <v>758</v>
       </c>
-      <c r="B332" s="11" t="s">
+      <c r="B332" s="21" t="s">
         <v>759</v>
       </c>
       <c r="C332" s="7"/>
@@ -13946,7 +13925,7 @@
       <c r="A333" s="8" t="s">
         <v>760</v>
       </c>
-      <c r="B333" s="8" t="s">
+      <c r="B333" s="11" t="s">
         <v>761</v>
       </c>
       <c r="C333" s="7"/>
@@ -14106,7 +14085,7 @@
       <c r="A338" s="8" t="s">
         <v>770</v>
       </c>
-      <c r="B338" s="8" t="s">
+      <c r="B338" s="11" t="s">
         <v>771</v>
       </c>
       <c r="C338" s="7"/>
@@ -14138,7 +14117,7 @@
       <c r="A339" s="8" t="s">
         <v>772</v>
       </c>
-      <c r="B339" s="11" t="s">
+      <c r="B339" s="8" t="s">
         <v>773</v>
       </c>
       <c r="C339" s="7"/>
@@ -14170,7 +14149,7 @@
       <c r="A340" s="8" t="s">
         <v>774</v>
       </c>
-      <c r="B340" s="11" t="s">
+      <c r="B340" s="8" t="s">
         <v>775</v>
       </c>
       <c r="C340" s="7"/>
@@ -14202,7 +14181,7 @@
       <c r="A341" s="8" t="s">
         <v>776</v>
       </c>
-      <c r="B341" s="8" t="s">
+      <c r="B341" s="11" t="s">
         <v>777</v>
       </c>
       <c r="C341" s="7"/>
@@ -14266,7 +14245,7 @@
       <c r="A343" s="8" t="s">
         <v>780</v>
       </c>
-      <c r="B343" s="11" t="s">
+      <c r="B343" s="8" t="s">
         <v>781</v>
       </c>
       <c r="C343" s="7"/>
@@ -14330,7 +14309,7 @@
       <c r="A345" s="8" t="s">
         <v>784</v>
       </c>
-      <c r="B345" s="8" t="s">
+      <c r="B345" s="11" t="s">
         <v>785</v>
       </c>
       <c r="C345" s="7"/>
@@ -14458,7 +14437,7 @@
       <c r="A349" s="8" t="s">
         <v>792</v>
       </c>
-      <c r="B349" s="11" t="s">
+      <c r="B349" s="8" t="s">
         <v>793</v>
       </c>
       <c r="C349" s="7"/>
@@ -14583,10 +14562,10 @@
       <c r="Z352" s="7"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="A353" s="16" t="s">
+      <c r="A353" s="8" t="s">
         <v>800</v>
       </c>
-      <c r="B353" s="25" t="s">
+      <c r="B353" s="11" t="s">
         <v>801</v>
       </c>
       <c r="C353" s="7"/>
@@ -14615,10 +14594,10 @@
       <c r="Z353" s="7"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="A354" s="16" t="s">
+      <c r="A354" s="8" t="s">
         <v>802</v>
       </c>
-      <c r="B354" s="16" t="s">
+      <c r="B354" s="11" t="s">
         <v>803</v>
       </c>
       <c r="C354" s="7"/>
@@ -14647,10 +14626,10 @@
       <c r="Z354" s="7"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="A355" s="8" t="s">
+      <c r="A355" s="16" t="s">
         <v>804</v>
       </c>
-      <c r="B355" s="11" t="s">
+      <c r="B355" s="16" t="s">
         <v>805</v>
       </c>
       <c r="C355" s="7"/>
@@ -14679,10 +14658,10 @@
       <c r="Z355" s="7"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="A356" s="8" t="s">
+      <c r="A356" s="16" t="s">
         <v>806</v>
       </c>
-      <c r="B356" s="8" t="s">
+      <c r="B356" s="16" t="s">
         <v>807</v>
       </c>
       <c r="C356" s="7"/>
@@ -14711,10 +14690,10 @@
       <c r="Z356" s="7"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="A357" s="16" t="s">
+      <c r="A357" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="B357" s="16" t="s">
+      <c r="B357" s="11" t="s">
         <v>809</v>
       </c>
       <c r="C357" s="7"/>
@@ -14743,7 +14722,7 @@
       <c r="Z357" s="7"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="A358" s="11" t="s">
+      <c r="A358" s="8" t="s">
         <v>810</v>
       </c>
       <c r="B358" s="8" t="s">
@@ -14775,10 +14754,10 @@
       <c r="Z358" s="7"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="A359" s="8" t="s">
+      <c r="A359" s="16" t="s">
         <v>812</v>
       </c>
-      <c r="B359" s="8" t="s">
+      <c r="B359" s="16" t="s">
         <v>813</v>
       </c>
       <c r="C359" s="7"/>
@@ -14807,10 +14786,10 @@
       <c r="Z359" s="7"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="A360" s="16" t="s">
+      <c r="A360" s="11" t="s">
         <v>814</v>
       </c>
-      <c r="B360" s="16" t="s">
+      <c r="B360" s="8" t="s">
         <v>815</v>
       </c>
       <c r="C360" s="7"/>
@@ -14839,10 +14818,10 @@
       <c r="Z360" s="7"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="11" t="s">
+      <c r="A361" s="8" t="s">
         <v>816</v>
       </c>
-      <c r="B361" s="11" t="s">
+      <c r="B361" s="8" t="s">
         <v>817</v>
       </c>
       <c r="C361" s="7"/>
@@ -14874,7 +14853,7 @@
       <c r="A362" s="16" t="s">
         <v>818</v>
       </c>
-      <c r="B362" s="11" t="s">
+      <c r="B362" s="16" t="s">
         <v>819</v>
       </c>
       <c r="C362" s="7"/>
@@ -14903,7 +14882,7 @@
       <c r="Z362" s="7"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="A363" s="8" t="s">
+      <c r="A363" s="11" t="s">
         <v>820</v>
       </c>
       <c r="B363" s="11" t="s">
@@ -14935,7 +14914,7 @@
       <c r="Z363" s="7"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="A364" s="11" t="s">
+      <c r="A364" s="16" t="s">
         <v>822</v>
       </c>
       <c r="B364" s="11" t="s">
@@ -14999,10 +14978,10 @@
       <c r="Z365" s="7"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="A366" s="20" t="s">
+      <c r="A366" s="11" t="s">
         <v>826</v>
       </c>
-      <c r="B366" s="21" t="s">
+      <c r="B366" s="11" t="s">
         <v>827</v>
       </c>
       <c r="C366" s="7"/>
@@ -15034,7 +15013,7 @@
       <c r="A367" s="8" t="s">
         <v>828</v>
       </c>
-      <c r="B367" s="8" t="s">
+      <c r="B367" s="11" t="s">
         <v>829</v>
       </c>
       <c r="C367" s="7"/>
@@ -15063,10 +15042,10 @@
       <c r="Z367" s="7"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="A368" s="8" t="s">
+      <c r="A368" s="20" t="s">
         <v>830</v>
       </c>
-      <c r="B368" s="11" t="s">
+      <c r="B368" s="21" t="s">
         <v>831</v>
       </c>
       <c r="C368" s="7"/>
@@ -15159,10 +15138,10 @@
       <c r="Z370" s="7"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="A371" s="11" t="s">
+      <c r="A371" s="8" t="s">
         <v>836</v>
       </c>
-      <c r="B371" s="11" t="s">
+      <c r="B371" s="8" t="s">
         <v>837</v>
       </c>
       <c r="C371" s="7"/>
@@ -15194,7 +15173,7 @@
       <c r="A372" s="8" t="s">
         <v>838</v>
       </c>
-      <c r="B372" s="8" t="s">
+      <c r="B372" s="11" t="s">
         <v>839</v>
       </c>
       <c r="C372" s="7"/>
@@ -15223,10 +15202,10 @@
       <c r="Z372" s="7"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="A373" s="8" t="s">
+      <c r="A373" s="11" t="s">
         <v>840</v>
       </c>
-      <c r="B373" s="8" t="s">
+      <c r="B373" s="11" t="s">
         <v>841</v>
       </c>
       <c r="C373" s="7"/>
@@ -15290,7 +15269,7 @@
       <c r="A375" s="8" t="s">
         <v>844</v>
       </c>
-      <c r="B375" s="11" t="s">
+      <c r="B375" s="8" t="s">
         <v>845</v>
       </c>
       <c r="C375" s="7"/>
@@ -15351,10 +15330,10 @@
       <c r="Z376" s="7"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="A377" s="16" t="s">
+      <c r="A377" s="8" t="s">
         <v>848</v>
       </c>
-      <c r="B377" s="16" t="s">
+      <c r="B377" s="11" t="s">
         <v>849</v>
       </c>
       <c r="C377" s="7"/>
@@ -15386,7 +15365,7 @@
       <c r="A378" s="8" t="s">
         <v>850</v>
       </c>
-      <c r="B378" s="11" t="s">
+      <c r="B378" s="8" t="s">
         <v>851</v>
       </c>
       <c r="C378" s="7"/>
@@ -15447,10 +15426,10 @@
       <c r="Z379" s="7"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="A380" s="16" t="s">
+      <c r="A380" s="8" t="s">
         <v>854</v>
       </c>
-      <c r="B380" s="16" t="s">
+      <c r="B380" s="11" t="s">
         <v>855</v>
       </c>
       <c r="C380" s="7"/>
@@ -15479,10 +15458,10 @@
       <c r="Z380" s="7"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="A381" s="8" t="s">
+      <c r="A381" s="16" t="s">
         <v>856</v>
       </c>
-      <c r="B381" s="11" t="s">
+      <c r="B381" s="16" t="s">
         <v>857</v>
       </c>
       <c r="C381" s="7"/>
@@ -15543,10 +15522,10 @@
       <c r="Z382" s="7"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="A383" s="16" t="s">
+      <c r="A383" s="8" t="s">
         <v>860</v>
       </c>
-      <c r="B383" s="16" t="s">
+      <c r="B383" s="11" t="s">
         <v>861</v>
       </c>
       <c r="C383" s="7"/>
@@ -15575,10 +15554,10 @@
       <c r="Z383" s="7"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
-      <c r="A384" s="8" t="s">
+      <c r="A384" s="16" t="s">
         <v>862</v>
       </c>
-      <c r="B384" s="8" t="s">
+      <c r="B384" s="16" t="s">
         <v>863</v>
       </c>
       <c r="C384" s="7"/>
@@ -15607,10 +15586,10 @@
       <c r="Z384" s="7"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="A385" s="8" t="s">
+      <c r="A385" s="16" t="s">
         <v>864</v>
       </c>
-      <c r="B385" s="8" t="s">
+      <c r="B385" s="16" t="s">
         <v>865</v>
       </c>
       <c r="C385" s="7"/>
@@ -15639,10 +15618,10 @@
       <c r="Z385" s="7"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="A386" s="11" t="s">
+      <c r="A386" s="8" t="s">
         <v>866</v>
       </c>
-      <c r="B386" s="11" t="s">
+      <c r="B386" s="8" t="s">
         <v>867</v>
       </c>
       <c r="C386" s="7"/>
@@ -15703,10 +15682,10 @@
       <c r="Z387" s="7"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="A388" s="21" t="s">
+      <c r="A388" s="11" t="s">
         <v>870</v>
       </c>
-      <c r="B388" s="20" t="s">
+      <c r="B388" s="11" t="s">
         <v>871</v>
       </c>
       <c r="C388" s="7"/>
@@ -15767,10 +15746,10 @@
       <c r="Z389" s="7"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="A390" s="8" t="s">
+      <c r="A390" s="21" t="s">
         <v>874</v>
       </c>
-      <c r="B390" s="8" t="s">
+      <c r="B390" s="20" t="s">
         <v>875</v>
       </c>
       <c r="C390" s="7"/>
@@ -15831,6 +15810,12 @@
       <c r="Z391" s="7"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
+      <c r="A392" s="8" t="s">
+        <v>878</v>
+      </c>
+      <c r="B392" s="8" t="s">
+        <v>879</v>
+      </c>
       <c r="C392" s="7"/>
       <c r="D392" s="7"/>
       <c r="E392" s="7"/>
@@ -15857,6 +15842,12 @@
       <c r="Z392" s="7"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
+      <c r="A393" s="8" t="s">
+        <v>880</v>
+      </c>
+      <c r="B393" s="8" t="s">
+        <v>881</v>
+      </c>
       <c r="C393" s="7"/>
       <c r="D393" s="7"/>
       <c r="E393" s="7"/>
@@ -21383,1213 +21374,1213 @@
       <c r="Z597" s="7"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="B598" s="26"/>
+      <c r="B598" s="25"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="B599" s="26"/>
+      <c r="B599" s="25"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="B600" s="26"/>
+      <c r="B600" s="25"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="B601" s="26"/>
+      <c r="B601" s="25"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="B602" s="26"/>
+      <c r="B602" s="25"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="B603" s="26"/>
+      <c r="B603" s="25"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="B604" s="26"/>
+      <c r="B604" s="25"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="B605" s="26"/>
+      <c r="B605" s="25"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="B606" s="26"/>
+      <c r="B606" s="25"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="B607" s="26"/>
+      <c r="B607" s="25"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="B608" s="26"/>
+      <c r="B608" s="25"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="B609" s="26"/>
+      <c r="B609" s="25"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="B610" s="26"/>
+      <c r="B610" s="25"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="B611" s="26"/>
+      <c r="B611" s="25"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="B612" s="26"/>
+      <c r="B612" s="25"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="B613" s="26"/>
+      <c r="B613" s="25"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="B614" s="26"/>
+      <c r="B614" s="25"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="B615" s="26"/>
+      <c r="B615" s="25"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="B616" s="26"/>
+      <c r="B616" s="25"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="B617" s="26"/>
+      <c r="B617" s="25"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="B618" s="26"/>
+      <c r="B618" s="25"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="B619" s="26"/>
+      <c r="B619" s="25"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="B620" s="26"/>
+      <c r="B620" s="25"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="B621" s="26"/>
+      <c r="B621" s="25"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="B622" s="26"/>
+      <c r="B622" s="25"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="B623" s="26"/>
+      <c r="B623" s="25"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="B624" s="26"/>
+      <c r="B624" s="25"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="B625" s="26"/>
+      <c r="B625" s="25"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="B626" s="26"/>
+      <c r="B626" s="25"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="B627" s="26"/>
+      <c r="B627" s="25"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="B628" s="26"/>
+      <c r="B628" s="25"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="B629" s="26"/>
+      <c r="B629" s="25"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="B630" s="26"/>
+      <c r="B630" s="25"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="B631" s="26"/>
+      <c r="B631" s="25"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="B632" s="26"/>
+      <c r="B632" s="25"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="B633" s="26"/>
+      <c r="B633" s="25"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="B634" s="26"/>
+      <c r="B634" s="25"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="B635" s="26"/>
+      <c r="B635" s="25"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="B636" s="26"/>
+      <c r="B636" s="25"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="B637" s="26"/>
+      <c r="B637" s="25"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="B638" s="26"/>
+      <c r="B638" s="25"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="B639" s="26"/>
+      <c r="B639" s="25"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="B640" s="26"/>
+      <c r="B640" s="25"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="B641" s="26"/>
+      <c r="B641" s="25"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="B642" s="26"/>
+      <c r="B642" s="25"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="B643" s="26"/>
+      <c r="B643" s="25"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="B644" s="26"/>
+      <c r="B644" s="25"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="B645" s="26"/>
+      <c r="B645" s="25"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="B646" s="26"/>
+      <c r="B646" s="25"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="B647" s="26"/>
+      <c r="B647" s="25"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="B648" s="26"/>
+      <c r="B648" s="25"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="B649" s="26"/>
+      <c r="B649" s="25"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="B650" s="26"/>
+      <c r="B650" s="25"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="B651" s="26"/>
+      <c r="B651" s="25"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="B652" s="26"/>
+      <c r="B652" s="25"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="B653" s="26"/>
+      <c r="B653" s="25"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="B654" s="26"/>
+      <c r="B654" s="25"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="B655" s="26"/>
+      <c r="B655" s="25"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="B656" s="26"/>
+      <c r="B656" s="25"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="B657" s="26"/>
+      <c r="B657" s="25"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="B658" s="26"/>
+      <c r="B658" s="25"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="B659" s="26"/>
+      <c r="B659" s="25"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="B660" s="26"/>
+      <c r="B660" s="25"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="B661" s="26"/>
+      <c r="B661" s="25"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="B662" s="26"/>
+      <c r="B662" s="25"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="B663" s="26"/>
+      <c r="B663" s="25"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="B664" s="26"/>
+      <c r="B664" s="25"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="B665" s="26"/>
+      <c r="B665" s="25"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="B666" s="26"/>
+      <c r="B666" s="25"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="B667" s="26"/>
+      <c r="B667" s="25"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="B668" s="26"/>
+      <c r="B668" s="25"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="B669" s="26"/>
+      <c r="B669" s="25"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="B670" s="26"/>
+      <c r="B670" s="25"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="B671" s="26"/>
+      <c r="B671" s="25"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="B672" s="26"/>
+      <c r="B672" s="25"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="B673" s="26"/>
+      <c r="B673" s="25"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="B674" s="26"/>
+      <c r="B674" s="25"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="B675" s="26"/>
+      <c r="B675" s="25"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="B676" s="26"/>
+      <c r="B676" s="25"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="B677" s="26"/>
+      <c r="B677" s="25"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="B678" s="26"/>
+      <c r="B678" s="25"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="B679" s="26"/>
+      <c r="B679" s="25"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="B680" s="26"/>
+      <c r="B680" s="25"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="B681" s="26"/>
+      <c r="B681" s="25"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="B682" s="26"/>
+      <c r="B682" s="25"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="B683" s="26"/>
+      <c r="B683" s="25"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="B684" s="26"/>
+      <c r="B684" s="25"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="B685" s="26"/>
+      <c r="B685" s="25"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="B686" s="26"/>
+      <c r="B686" s="25"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="B687" s="26"/>
+      <c r="B687" s="25"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="B688" s="26"/>
+      <c r="B688" s="25"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="B689" s="26"/>
+      <c r="B689" s="25"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="B690" s="26"/>
+      <c r="B690" s="25"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="B691" s="26"/>
+      <c r="B691" s="25"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="B692" s="26"/>
+      <c r="B692" s="25"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="B693" s="26"/>
+      <c r="B693" s="25"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="B694" s="26"/>
+      <c r="B694" s="25"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="B695" s="26"/>
+      <c r="B695" s="25"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="B696" s="26"/>
+      <c r="B696" s="25"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="B697" s="26"/>
+      <c r="B697" s="25"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="B698" s="26"/>
+      <c r="B698" s="25"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="B699" s="26"/>
+      <c r="B699" s="25"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="B700" s="26"/>
+      <c r="B700" s="25"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="B701" s="26"/>
+      <c r="B701" s="25"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="B702" s="26"/>
+      <c r="B702" s="25"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="B703" s="26"/>
+      <c r="B703" s="25"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="B704" s="26"/>
+      <c r="B704" s="25"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="B705" s="26"/>
+      <c r="B705" s="25"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="B706" s="26"/>
+      <c r="B706" s="25"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="B707" s="26"/>
+      <c r="B707" s="25"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="B708" s="26"/>
+      <c r="B708" s="25"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="B709" s="26"/>
+      <c r="B709" s="25"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="B710" s="26"/>
+      <c r="B710" s="25"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="B711" s="26"/>
+      <c r="B711" s="25"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="B712" s="26"/>
+      <c r="B712" s="25"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="B713" s="26"/>
+      <c r="B713" s="25"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="B714" s="26"/>
+      <c r="B714" s="25"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="B715" s="26"/>
+      <c r="B715" s="25"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="B716" s="26"/>
+      <c r="B716" s="25"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="B717" s="26"/>
+      <c r="B717" s="25"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="B718" s="26"/>
+      <c r="B718" s="25"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="B719" s="26"/>
+      <c r="B719" s="25"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="B720" s="26"/>
+      <c r="B720" s="25"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="B721" s="26"/>
+      <c r="B721" s="25"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="B722" s="26"/>
+      <c r="B722" s="25"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="B723" s="26"/>
+      <c r="B723" s="25"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="B724" s="26"/>
+      <c r="B724" s="25"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="B725" s="26"/>
+      <c r="B725" s="25"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="B726" s="26"/>
+      <c r="B726" s="25"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="B727" s="26"/>
+      <c r="B727" s="25"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="B728" s="26"/>
+      <c r="B728" s="25"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="B729" s="26"/>
+      <c r="B729" s="25"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="B730" s="26"/>
+      <c r="B730" s="25"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="B731" s="26"/>
+      <c r="B731" s="25"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="B732" s="26"/>
+      <c r="B732" s="25"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="B733" s="26"/>
+      <c r="B733" s="25"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="B734" s="26"/>
+      <c r="B734" s="25"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="B735" s="26"/>
+      <c r="B735" s="25"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="B736" s="26"/>
+      <c r="B736" s="25"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="B737" s="26"/>
+      <c r="B737" s="25"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="B738" s="26"/>
+      <c r="B738" s="25"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="B739" s="26"/>
+      <c r="B739" s="25"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="B740" s="26"/>
+      <c r="B740" s="25"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="B741" s="26"/>
+      <c r="B741" s="25"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="B742" s="26"/>
+      <c r="B742" s="25"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="B743" s="26"/>
+      <c r="B743" s="25"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="B744" s="26"/>
+      <c r="B744" s="25"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="B745" s="26"/>
+      <c r="B745" s="25"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="B746" s="26"/>
+      <c r="B746" s="25"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="B747" s="26"/>
+      <c r="B747" s="25"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="B748" s="26"/>
+      <c r="B748" s="25"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="B749" s="26"/>
+      <c r="B749" s="25"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="B750" s="26"/>
+      <c r="B750" s="25"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="B751" s="26"/>
+      <c r="B751" s="25"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="B752" s="26"/>
+      <c r="B752" s="25"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="B753" s="26"/>
+      <c r="B753" s="25"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="B754" s="26"/>
+      <c r="B754" s="25"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="B755" s="26"/>
+      <c r="B755" s="25"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="B756" s="26"/>
+      <c r="B756" s="25"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="B757" s="26"/>
+      <c r="B757" s="25"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="B758" s="26"/>
+      <c r="B758" s="25"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="B759" s="26"/>
+      <c r="B759" s="25"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="B760" s="26"/>
+      <c r="B760" s="25"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="B761" s="26"/>
+      <c r="B761" s="25"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="B762" s="26"/>
+      <c r="B762" s="25"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="B763" s="26"/>
+      <c r="B763" s="25"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="B764" s="26"/>
+      <c r="B764" s="25"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="B765" s="26"/>
+      <c r="B765" s="25"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="B766" s="26"/>
+      <c r="B766" s="25"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="B767" s="26"/>
+      <c r="B767" s="25"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="B768" s="26"/>
+      <c r="B768" s="25"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="B769" s="26"/>
+      <c r="B769" s="25"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="B770" s="26"/>
+      <c r="B770" s="25"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="B771" s="26"/>
+      <c r="B771" s="25"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="B772" s="26"/>
+      <c r="B772" s="25"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="B773" s="26"/>
+      <c r="B773" s="25"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="B774" s="26"/>
+      <c r="B774" s="25"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="B775" s="26"/>
+      <c r="B775" s="25"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="B776" s="26"/>
+      <c r="B776" s="25"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="B777" s="26"/>
+      <c r="B777" s="25"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="B778" s="26"/>
+      <c r="B778" s="25"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="B779" s="26"/>
+      <c r="B779" s="25"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="B780" s="26"/>
+      <c r="B780" s="25"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="B781" s="26"/>
+      <c r="B781" s="25"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="B782" s="26"/>
+      <c r="B782" s="25"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="B783" s="26"/>
+      <c r="B783" s="25"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="B784" s="26"/>
+      <c r="B784" s="25"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="B785" s="26"/>
+      <c r="B785" s="25"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="B786" s="26"/>
+      <c r="B786" s="25"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="B787" s="26"/>
+      <c r="B787" s="25"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="B788" s="26"/>
+      <c r="B788" s="25"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="B789" s="26"/>
+      <c r="B789" s="25"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="B790" s="26"/>
+      <c r="B790" s="25"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="B791" s="26"/>
+      <c r="B791" s="25"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="B792" s="26"/>
+      <c r="B792" s="25"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="B793" s="26"/>
+      <c r="B793" s="25"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="B794" s="26"/>
+      <c r="B794" s="25"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="B795" s="26"/>
+      <c r="B795" s="25"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="B796" s="26"/>
+      <c r="B796" s="25"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="B797" s="26"/>
+      <c r="B797" s="25"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="B798" s="26"/>
+      <c r="B798" s="25"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="B799" s="26"/>
+      <c r="B799" s="25"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="B800" s="26"/>
+      <c r="B800" s="25"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="B801" s="26"/>
+      <c r="B801" s="25"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="B802" s="26"/>
+      <c r="B802" s="25"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="B803" s="26"/>
+      <c r="B803" s="25"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="B804" s="26"/>
+      <c r="B804" s="25"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="B805" s="26"/>
+      <c r="B805" s="25"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="B806" s="26"/>
+      <c r="B806" s="25"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="B807" s="26"/>
+      <c r="B807" s="25"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="B808" s="26"/>
+      <c r="B808" s="25"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="B809" s="26"/>
+      <c r="B809" s="25"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="B810" s="26"/>
+      <c r="B810" s="25"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="B811" s="26"/>
+      <c r="B811" s="25"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="B812" s="26"/>
+      <c r="B812" s="25"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="B813" s="26"/>
+      <c r="B813" s="25"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="B814" s="26"/>
+      <c r="B814" s="25"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="B815" s="26"/>
+      <c r="B815" s="25"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="B816" s="26"/>
+      <c r="B816" s="25"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="B817" s="26"/>
+      <c r="B817" s="25"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="B818" s="26"/>
+      <c r="B818" s="25"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="B819" s="26"/>
+      <c r="B819" s="25"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="B820" s="26"/>
+      <c r="B820" s="25"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="B821" s="26"/>
+      <c r="B821" s="25"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="B822" s="26"/>
+      <c r="B822" s="25"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="B823" s="26"/>
+      <c r="B823" s="25"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="B824" s="26"/>
+      <c r="B824" s="25"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="B825" s="26"/>
+      <c r="B825" s="25"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="B826" s="26"/>
+      <c r="B826" s="25"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="B827" s="26"/>
+      <c r="B827" s="25"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="B828" s="26"/>
+      <c r="B828" s="25"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="B829" s="26"/>
+      <c r="B829" s="25"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="B830" s="26"/>
+      <c r="B830" s="25"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="B831" s="26"/>
+      <c r="B831" s="25"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="B832" s="26"/>
+      <c r="B832" s="25"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="B833" s="26"/>
+      <c r="B833" s="25"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="B834" s="26"/>
+      <c r="B834" s="25"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="B835" s="26"/>
+      <c r="B835" s="25"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="B836" s="26"/>
+      <c r="B836" s="25"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="B837" s="26"/>
+      <c r="B837" s="25"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="B838" s="26"/>
+      <c r="B838" s="25"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="B839" s="26"/>
+      <c r="B839" s="25"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="B840" s="26"/>
+      <c r="B840" s="25"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="B841" s="26"/>
+      <c r="B841" s="25"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="B842" s="26"/>
+      <c r="B842" s="25"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="B843" s="26"/>
+      <c r="B843" s="25"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="B844" s="26"/>
+      <c r="B844" s="25"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="B845" s="26"/>
+      <c r="B845" s="25"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="B846" s="26"/>
+      <c r="B846" s="25"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="B847" s="26"/>
+      <c r="B847" s="25"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="B848" s="26"/>
+      <c r="B848" s="25"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="B849" s="26"/>
+      <c r="B849" s="25"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="B850" s="26"/>
+      <c r="B850" s="25"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="B851" s="26"/>
+      <c r="B851" s="25"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="B852" s="26"/>
+      <c r="B852" s="25"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="B853" s="26"/>
+      <c r="B853" s="25"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="B854" s="26"/>
+      <c r="B854" s="25"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="B855" s="26"/>
+      <c r="B855" s="25"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="B856" s="26"/>
+      <c r="B856" s="25"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="B857" s="26"/>
+      <c r="B857" s="25"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="B858" s="26"/>
+      <c r="B858" s="25"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="B859" s="26"/>
+      <c r="B859" s="25"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="B860" s="26"/>
+      <c r="B860" s="25"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="B861" s="26"/>
+      <c r="B861" s="25"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="B862" s="26"/>
+      <c r="B862" s="25"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="B863" s="26"/>
+      <c r="B863" s="25"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="B864" s="26"/>
+      <c r="B864" s="25"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="B865" s="26"/>
+      <c r="B865" s="25"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="B866" s="26"/>
+      <c r="B866" s="25"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="B867" s="26"/>
+      <c r="B867" s="25"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="B868" s="26"/>
+      <c r="B868" s="25"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="B869" s="26"/>
+      <c r="B869" s="25"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="B870" s="26"/>
+      <c r="B870" s="25"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="B871" s="26"/>
+      <c r="B871" s="25"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="B872" s="26"/>
+      <c r="B872" s="25"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="B873" s="26"/>
+      <c r="B873" s="25"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="B874" s="26"/>
+      <c r="B874" s="25"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="B875" s="26"/>
+      <c r="B875" s="25"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="B876" s="26"/>
+      <c r="B876" s="25"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="B877" s="26"/>
+      <c r="B877" s="25"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="B878" s="26"/>
+      <c r="B878" s="25"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="B879" s="26"/>
+      <c r="B879" s="25"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="B880" s="26"/>
+      <c r="B880" s="25"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="B881" s="26"/>
+      <c r="B881" s="25"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="B882" s="26"/>
+      <c r="B882" s="25"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="B883" s="26"/>
+      <c r="B883" s="25"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="B884" s="26"/>
+      <c r="B884" s="25"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="B885" s="26"/>
+      <c r="B885" s="25"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="B886" s="26"/>
+      <c r="B886" s="25"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="B887" s="26"/>
+      <c r="B887" s="25"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="B888" s="26"/>
+      <c r="B888" s="25"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="B889" s="26"/>
+      <c r="B889" s="25"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="B890" s="26"/>
+      <c r="B890" s="25"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="B891" s="26"/>
+      <c r="B891" s="25"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="B892" s="26"/>
+      <c r="B892" s="25"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="B893" s="26"/>
+      <c r="B893" s="25"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="B894" s="26"/>
+      <c r="B894" s="25"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="B895" s="26"/>
+      <c r="B895" s="25"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="B896" s="26"/>
+      <c r="B896" s="25"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="B897" s="26"/>
+      <c r="B897" s="25"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="B898" s="26"/>
+      <c r="B898" s="25"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="B899" s="26"/>
+      <c r="B899" s="25"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="B900" s="26"/>
+      <c r="B900" s="25"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="B901" s="26"/>
+      <c r="B901" s="25"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="B902" s="26"/>
+      <c r="B902" s="25"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="B903" s="26"/>
+      <c r="B903" s="25"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="B904" s="26"/>
+      <c r="B904" s="25"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="B905" s="26"/>
+      <c r="B905" s="25"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="B906" s="26"/>
+      <c r="B906" s="25"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="B907" s="26"/>
+      <c r="B907" s="25"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="B908" s="26"/>
+      <c r="B908" s="25"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="B909" s="26"/>
+      <c r="B909" s="25"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="B910" s="26"/>
+      <c r="B910" s="25"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="B911" s="26"/>
+      <c r="B911" s="25"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="B912" s="26"/>
+      <c r="B912" s="25"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="B913" s="26"/>
+      <c r="B913" s="25"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="B914" s="26"/>
+      <c r="B914" s="25"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="B915" s="26"/>
+      <c r="B915" s="25"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="B916" s="26"/>
+      <c r="B916" s="25"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="B917" s="26"/>
+      <c r="B917" s="25"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="B918" s="26"/>
+      <c r="B918" s="25"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="B919" s="26"/>
+      <c r="B919" s="25"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="B920" s="26"/>
+      <c r="B920" s="25"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="B921" s="26"/>
+      <c r="B921" s="25"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="B922" s="26"/>
+      <c r="B922" s="25"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="B923" s="26"/>
+      <c r="B923" s="25"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="B924" s="26"/>
+      <c r="B924" s="25"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="B925" s="26"/>
+      <c r="B925" s="25"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="B926" s="26"/>
+      <c r="B926" s="25"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="B927" s="26"/>
+      <c r="B927" s="25"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="B928" s="26"/>
+      <c r="B928" s="25"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="B929" s="26"/>
+      <c r="B929" s="25"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="B930" s="26"/>
+      <c r="B930" s="25"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="B931" s="26"/>
+      <c r="B931" s="25"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="B932" s="26"/>
+      <c r="B932" s="25"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="B933" s="26"/>
+      <c r="B933" s="25"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="B934" s="26"/>
+      <c r="B934" s="25"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="B935" s="26"/>
+      <c r="B935" s="25"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="B936" s="26"/>
+      <c r="B936" s="25"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="B937" s="26"/>
+      <c r="B937" s="25"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="B938" s="26"/>
+      <c r="B938" s="25"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="B939" s="26"/>
+      <c r="B939" s="25"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="B940" s="26"/>
+      <c r="B940" s="25"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="B941" s="26"/>
+      <c r="B941" s="25"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="B942" s="26"/>
+      <c r="B942" s="25"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="B943" s="26"/>
+      <c r="B943" s="25"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="B944" s="26"/>
+      <c r="B944" s="25"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="B945" s="26"/>
+      <c r="B945" s="25"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="B946" s="26"/>
+      <c r="B946" s="25"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="B947" s="26"/>
+      <c r="B947" s="25"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="B948" s="26"/>
+      <c r="B948" s="25"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="B949" s="26"/>
+      <c r="B949" s="25"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="B950" s="26"/>
+      <c r="B950" s="25"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="B951" s="26"/>
+      <c r="B951" s="25"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="B952" s="26"/>
+      <c r="B952" s="25"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="B953" s="26"/>
+      <c r="B953" s="25"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="B954" s="26"/>
+      <c r="B954" s="25"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="B955" s="26"/>
+      <c r="B955" s="25"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="B956" s="26"/>
+      <c r="B956" s="25"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="B957" s="26"/>
+      <c r="B957" s="25"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="B958" s="26"/>
+      <c r="B958" s="25"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="B959" s="26"/>
+      <c r="B959" s="25"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="B960" s="26"/>
+      <c r="B960" s="25"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="B961" s="26"/>
+      <c r="B961" s="25"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="B962" s="26"/>
+      <c r="B962" s="25"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="B963" s="26"/>
+      <c r="B963" s="25"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="B964" s="26"/>
+      <c r="B964" s="25"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="B965" s="26"/>
+      <c r="B965" s="25"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="B966" s="26"/>
+      <c r="B966" s="25"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="B967" s="26"/>
+      <c r="B967" s="25"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="B968" s="26"/>
+      <c r="B968" s="25"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="B969" s="26"/>
+      <c r="B969" s="25"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="B970" s="26"/>
+      <c r="B970" s="25"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="B971" s="26"/>
+      <c r="B971" s="25"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="B972" s="26"/>
+      <c r="B972" s="25"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="B973" s="26"/>
+      <c r="B973" s="25"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="B974" s="26"/>
+      <c r="B974" s="25"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="B975" s="26"/>
+      <c r="B975" s="25"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="B976" s="26"/>
+      <c r="B976" s="25"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="B977" s="26"/>
+      <c r="B977" s="25"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="B978" s="26"/>
+      <c r="B978" s="25"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="B979" s="26"/>
+      <c r="B979" s="25"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="B980" s="26"/>
+      <c r="B980" s="25"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="B981" s="26"/>
+      <c r="B981" s="25"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="B982" s="26"/>
+      <c r="B982" s="25"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="B983" s="26"/>
+      <c r="B983" s="25"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="B984" s="26"/>
+      <c r="B984" s="25"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="B985" s="26"/>
+      <c r="B985" s="25"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="B986" s="26"/>
+      <c r="B986" s="25"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="B987" s="26"/>
+      <c r="B987" s="25"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="B988" s="26"/>
+      <c r="B988" s="25"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="B989" s="26"/>
+      <c r="B989" s="25"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="B990" s="26"/>
+      <c r="B990" s="25"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="B991" s="26"/>
+      <c r="B991" s="25"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="B992" s="26"/>
+      <c r="B992" s="25"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="B993" s="26"/>
+      <c r="B993" s="25"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="B994" s="26"/>
+      <c r="B994" s="25"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="B995" s="26"/>
+      <c r="B995" s="25"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="B996" s="26"/>
+      <c r="B996" s="25"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="B997" s="26"/>
+      <c r="B997" s="25"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="B998" s="26"/>
+      <c r="B998" s="25"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="B999" s="26"/>
+      <c r="B999" s="25"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="B1000" s="26"/>
+      <c r="B1000" s="25"/>
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$C$1000">

--- a/Literature/Languages/Norvunic (old).xlsx
+++ b/Literature/Languages/Norvunic (old).xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="897">
   <si>
     <t>Word</t>
   </si>
@@ -69,7 +69,7 @@
     <t>nus ægi blûlr = blue very robes (very blue robes)</t>
   </si>
   <si>
-    <t>clean</t>
+    <t>spoil</t>
   </si>
   <si>
     <t>stode</t>
@@ -135,19 +135,34 @@
     <t>ûn atelg = one apple (an apple)</t>
   </si>
   <si>
+    <t>fjåg</t>
+  </si>
+  <si>
+    <t>a swear word, a cuss word</t>
+  </si>
+  <si>
+    <t>possessive (telg)</t>
+  </si>
+  <si>
+    <t>after pronoun</t>
+  </si>
+  <si>
+    <t>eg telg sig heim = i own this house</t>
+  </si>
+  <si>
     <t>kan</t>
   </si>
   <si>
     <t>able to do something</t>
   </si>
   <si>
-    <t>possessive (telg)</t>
-  </si>
-  <si>
-    <t>after pronoun</t>
-  </si>
-  <si>
-    <t>eg telg sig heim = i own this house</t>
+    <t>nationality (lat) (like -ian, -ic, -ish, -ese, -i, -an)</t>
+  </si>
+  <si>
+    <t>after nation</t>
+  </si>
+  <si>
+    <t>norvun lat = norvun like (norvunic), eng lat = england like (english)</t>
   </si>
   <si>
     <t>ag</t>
@@ -156,13 +171,10 @@
     <t>about something, or the properties of</t>
   </si>
   <si>
-    <t>nationality (lat) (like -ian, -ic, -ish, -ese, -i, -an)</t>
-  </si>
-  <si>
-    <t>after nation</t>
-  </si>
-  <si>
-    <t>norvun lat = norvun like (norvunic), eng lat = england like (english)</t>
+    <t>language (lægi) (same thing as above)</t>
+  </si>
+  <si>
+    <t>norvunlægi = norvun speak (norvunic), englægi = england speak (english)</t>
   </si>
   <si>
     <t>vjøl</t>
@@ -171,10 +183,10 @@
     <t>ale, beer</t>
   </si>
   <si>
-    <t>language (lægi) (same thing as above)</t>
-  </si>
-  <si>
-    <t>norvunlægi = norvun speak (norvunic), englægi = england speak (english)</t>
+    <t>likeness/ness or ful (lat)</t>
+  </si>
+  <si>
+    <t>ru jeg leif lat = you be beauty like (you are beautiful)</t>
   </si>
   <si>
     <t>dyr</t>
@@ -183,10 +195,13 @@
     <t>an animal</t>
   </si>
   <si>
-    <t>likeness/ness or ful (lat)</t>
-  </si>
-  <si>
-    <t>ru jeg leif lat = you be beauty like (you are beautiful)</t>
+    <t>likeness/ly (ri)</t>
+  </si>
+  <si>
+    <t>after adj or adv</t>
+  </si>
+  <si>
+    <t>fjolri = quickly</t>
   </si>
   <si>
     <t>aplege</t>
@@ -195,13 +210,10 @@
     <t>an apple</t>
   </si>
   <si>
-    <t>likeness/ly (ri)</t>
-  </si>
-  <si>
-    <t>after adj or adv</t>
-  </si>
-  <si>
-    <t>fjolri = quickly</t>
+    <t>weather/ing (sorp)</t>
+  </si>
+  <si>
+    <t>pe jû jeg sorp parri = the rainwater be falling (it's raining)</t>
   </si>
   <si>
     <t>arve</t>
@@ -210,10 +222,10 @@
     <t>an arrow for a bow</t>
   </si>
   <si>
-    <t>weather/ing (sorp)</t>
-  </si>
-  <si>
-    <t>pe jû jeg sorp parri = the rainwater be falling (it's raining)</t>
+    <t>ready ('ap)</t>
+  </si>
+  <si>
+    <t>hagt'ap skog = battle-for axe (axe for battle)</t>
   </si>
   <si>
     <t>uks</t>
@@ -222,30 +234,24 @@
     <t>an axe (weapon)</t>
   </si>
   <si>
-    <t>ready ('ap)</t>
-  </si>
-  <si>
-    <t>hagt'ap skog = battle-for axe (axe for battle)</t>
-  </si>
-  <si>
     <t>ok</t>
   </si>
   <si>
     <t>and</t>
   </si>
   <si>
+    <t>I shift</t>
+  </si>
+  <si>
+    <t>A, Å, Æ =&gt; E | E =&gt; EI | O =&gt; Ø | Ø =&gt; I | EI, I =&gt; Y | U =&gt; U</t>
+  </si>
+  <si>
     <t>klæddvin</t>
   </si>
   <si>
     <t>any cloth attire, or apparel; clothing</t>
   </si>
   <si>
-    <t>I shift</t>
-  </si>
-  <si>
-    <t>A, Å, Æ =&gt; E | E =&gt; EI | O =&gt; Ø | Ø =&gt; I | EI, I =&gt; Y | U =&gt; U</t>
-  </si>
-  <si>
     <t>antul</t>
   </si>
   <si>
@@ -258,16 +264,22 @@
     <t>any type of fortified structure, mostly used to refer castles</t>
   </si>
   <si>
+    <t>definitive -en</t>
+  </si>
+  <si>
+    <t>add -en to word. if ends with -e, use -n. if ends with other vowel, add -nen</t>
+  </si>
+  <si>
     <t>mirste</t>
   </si>
   <si>
     <t>any type of metal</t>
   </si>
   <si>
-    <t>definitive -en</t>
-  </si>
-  <si>
-    <t>add -en to word. if ends with -e, use -n. if ends with other vowel, add -nen</t>
+    <t>plural -ir</t>
+  </si>
+  <si>
+    <t>add -ir to word. if ends with -e, remove the -e and add -ir. if ends with other vowel, add -nir</t>
   </si>
   <si>
     <t>nem</t>
@@ -276,10 +288,10 @@
     <t>any, some</t>
   </si>
   <si>
-    <t>plural -ir</t>
-  </si>
-  <si>
-    <t>add -ir to word. if ends with -e, remove the -e and add -ir. if ends with other vowel, add -nir</t>
+    <t>past tense -de</t>
+  </si>
+  <si>
+    <t>remove -en, then add -de. if after removing the ending, and it ends with two different consonants (or -t or -d) (excluding consonants are r, n, m, and l), apply i shift and double the consonant | gjårken =&gt; gjårkde | akresten =&gt; akreisdde | hæsten =&gt; hesdde  (-ten is replaced with -den)</t>
   </si>
   <si>
     <t>blogvir</t>
@@ -288,10 +300,10 @@
     <t>around</t>
   </si>
   <si>
-    <t>past tense -de</t>
-  </si>
-  <si>
-    <t>remove -en, then add -de. if after removing the ending, and it ends with two different consonants (or -t or -d) (excluding consonants are r, n, m, and l), apply i shift and double the consonant | gjårken =&gt; gjårkde | akresten =&gt; akreisdde | hæsten =&gt; hesdde  (-ten is replaced with -den)</t>
+    <t>present tense -ete</t>
+  </si>
+  <si>
+    <t>remove -en</t>
   </si>
   <si>
     <t>å</t>
@@ -300,10 +312,10 @@
     <t>at</t>
   </si>
   <si>
-    <t>present tense -ete</t>
-  </si>
-  <si>
-    <t>remove -en</t>
+    <t>past participle -den, -edet</t>
+  </si>
+  <si>
+    <t>remove -en, then add -den. if after removing the ending, and it ends with two different consonants (or -t or -d) (excluding consonants are r, n, m, and l), apply i shift and add -ende | gjårken =&gt; gjårkden | akresten =&gt; akreistende | hæsten =&gt; hestende  (-ten is replaced with -den)</t>
   </si>
   <si>
     <t>væg</t>
@@ -312,10 +324,10 @@
     <t>away</t>
   </si>
   <si>
-    <t>past participle -den, -edet</t>
-  </si>
-  <si>
-    <t>remove -en, then add -den. if after removing the ending, and it ends with two different consonants (or -t or -d) (excluding consonants are r, n, m, and l), apply i shift and add -ende | gjårken =&gt; gjårkden | akresten =&gt; akreistende | hæsten =&gt; hestende  (-ten is replaced with -den)</t>
+    <t>present participle -inde</t>
+  </si>
+  <si>
+    <t>remove -en, then add -inde</t>
   </si>
   <si>
     <t>lybe</t>
@@ -324,10 +336,10 @@
     <t>baby</t>
   </si>
   <si>
-    <t>present participle -inde</t>
-  </si>
-  <si>
-    <t>remove -en, then add -inde</t>
+    <t>noun form of verb -inge</t>
+  </si>
+  <si>
+    <t>remove -en, then add -inge</t>
   </si>
   <si>
     <t>dym</t>
@@ -336,10 +348,10 @@
     <t>bad</t>
   </si>
   <si>
-    <t>noun form of verb -inge</t>
-  </si>
-  <si>
-    <t>remove -en, then add -inge</t>
+    <t>imperative</t>
+  </si>
+  <si>
+    <t>remove the -n</t>
   </si>
   <si>
     <t>bal</t>
@@ -348,10 +360,10 @@
     <t>ball, sphere</t>
   </si>
   <si>
-    <t>imperative</t>
-  </si>
-  <si>
-    <t>remove the -n</t>
+    <t>likeness -likden</t>
+  </si>
+  <si>
+    <t>add -likden</t>
   </si>
   <si>
     <t>bavked</t>
@@ -360,10 +372,13 @@
     <t>bastard (insult)</t>
   </si>
   <si>
-    <t>likeness -likden</t>
-  </si>
-  <si>
-    <t>add -likden</t>
+    <t>Pronunciation</t>
+  </si>
+  <si>
+    <t>Sound</t>
+  </si>
+  <si>
+    <t>Special</t>
   </si>
   <si>
     <t>bagt</t>
@@ -372,13 +387,10 @@
     <t>battle, or any large-scale fight</t>
   </si>
   <si>
-    <t>Pronunciation</t>
-  </si>
-  <si>
-    <t>Sound</t>
-  </si>
-  <si>
-    <t>Special</t>
+    <t>VOWELS</t>
+  </si>
+  <si>
+    <t>A Å Æ E I O Ø U Y</t>
   </si>
   <si>
     <t>dul</t>
@@ -387,10 +399,10 @@
     <t>bean</t>
   </si>
   <si>
-    <t>VOWELS</t>
-  </si>
-  <si>
-    <t>A Å Æ E I O Ø U Y</t>
+    <t>A</t>
+  </si>
+  <si>
+    <t>/a/</t>
   </si>
   <si>
     <t>byr</t>
@@ -399,10 +411,10 @@
     <t>bear</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>/a/</t>
+    <t>Å</t>
+  </si>
+  <si>
+    <t>/ɒ/</t>
   </si>
   <si>
     <t>kødde</t>
@@ -411,10 +423,10 @@
     <t>bed</t>
   </si>
   <si>
-    <t>Å</t>
-  </si>
-  <si>
-    <t>/ɒ/</t>
+    <t>Æ</t>
+  </si>
+  <si>
+    <t>/aː/</t>
   </si>
   <si>
     <t>glof</t>
@@ -423,10 +435,10 @@
     <t>being fat</t>
   </si>
   <si>
-    <t>Æ</t>
-  </si>
-  <si>
-    <t>/aː/</t>
+    <t>E</t>
+  </si>
+  <si>
+    <t>/ɛ/</t>
   </si>
   <si>
     <t>tuvig</t>
@@ -435,10 +447,10 @@
     <t>being heavy</t>
   </si>
   <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>/ɛ/</t>
+    <t>I</t>
+  </si>
+  <si>
+    <t>/ɪ/</t>
   </si>
   <si>
     <t>berre</t>
@@ -447,10 +459,10 @@
     <t>berry</t>
   </si>
   <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>/ɪ/</t>
+    <t>O</t>
+  </si>
+  <si>
+    <t>/ɔ/</t>
   </si>
   <si>
     <t>bag</t>
@@ -459,10 +471,10 @@
     <t>big, vast, massive, or great</t>
   </si>
   <si>
-    <t>O</t>
-  </si>
-  <si>
-    <t>/ɔ/</t>
+    <t>U</t>
+  </si>
+  <si>
+    <t>/u/</t>
   </si>
   <si>
     <t>årke</t>
@@ -471,28 +483,28 @@
     <t>bird</t>
   </si>
   <si>
-    <t>U</t>
-  </si>
-  <si>
-    <t>/u/</t>
-  </si>
-  <si>
     <t>blæke</t>
   </si>
   <si>
     <t>black</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>/i/</t>
+  </si>
+  <si>
     <t>bladd</t>
   </si>
   <si>
     <t>blade</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>/i/</t>
+    <t>EA</t>
+  </si>
+  <si>
+    <t>/aːɒː/</t>
   </si>
   <si>
     <t>blod</t>
@@ -501,10 +513,10 @@
     <t>blood</t>
   </si>
   <si>
-    <t>EA</t>
-  </si>
-  <si>
-    <t>/aːɒː/</t>
+    <t>EO</t>
+  </si>
+  <si>
+    <t>/ɛoː/</t>
   </si>
   <si>
     <t>blor</t>
@@ -513,10 +525,10 @@
     <t>blue</t>
   </si>
   <si>
-    <t>EO</t>
-  </si>
-  <si>
-    <t>/ɛoː/</t>
+    <t>R</t>
+  </si>
+  <si>
+    <t>/r/</t>
   </si>
   <si>
     <t>skått</t>
@@ -525,10 +537,10 @@
     <t>boat</t>
   </si>
   <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>/r/</t>
+    <t>L when its after the vowel in a syllable</t>
+  </si>
+  <si>
+    <t>/l̪/</t>
   </si>
   <si>
     <t>buv</t>
@@ -537,12 +549,6 @@
     <t>bow (weapon)</t>
   </si>
   <si>
-    <t>L when its after the vowel in a syllable</t>
-  </si>
-  <si>
-    <t>/l̪/</t>
-  </si>
-  <si>
     <t>gutte</t>
   </si>
   <si>
@@ -561,13 +567,16 @@
     <t>bread</t>
   </si>
   <si>
+    <t>adjectives go before nouns</t>
+  </si>
+  <si>
     <t>glant</t>
   </si>
   <si>
     <t>bright, shiny</t>
   </si>
   <si>
-    <t>adjectives go before nouns</t>
+    <t>adverbs go after verbs</t>
   </si>
   <si>
     <t>ænne</t>
@@ -576,25 +585,28 @@
     <t>but, still, or yet</t>
   </si>
   <si>
-    <t>adverbs go after verbs</t>
-  </si>
-  <si>
     <t>kogve</t>
   </si>
   <si>
     <t>cart, wagon</t>
   </si>
   <si>
+    <t>question example</t>
+  </si>
+  <si>
+    <t>vil du som matig?</t>
+  </si>
+  <si>
     <t>kåte</t>
   </si>
   <si>
     <t>cat</t>
   </si>
   <si>
-    <t>question example</t>
-  </si>
-  <si>
-    <t>vil du som matig?</t>
+    <t>auxiliary example</t>
+  </si>
+  <si>
+    <t>eg vil eten som matig.</t>
   </si>
   <si>
     <t>kuve</t>
@@ -603,12 +615,6 @@
     <t>cattle, bull, cow</t>
   </si>
   <si>
-    <t>auxiliary example</t>
-  </si>
-  <si>
-    <t>eg vil eten som matig.</t>
-  </si>
-  <si>
     <t>maille</t>
   </si>
   <si>
@@ -693,6 +699,9 @@
     <t>demon</t>
   </si>
   <si>
+    <t>nøkton</t>
+  </si>
+  <si>
     <t>graste</t>
   </si>
   <si>
@@ -783,6 +792,12 @@
     <t>every, or all</t>
   </si>
   <si>
+    <t>juk</t>
+  </si>
+  <si>
+    <t>ew, disgust (interjection)</t>
+  </si>
+  <si>
     <t>tal</t>
   </si>
   <si>
@@ -1119,6 +1134,12 @@
     <t>lady, maiden</t>
   </si>
   <si>
+    <t>tørd</t>
+  </si>
+  <si>
+    <t>lake</t>
+  </si>
+  <si>
     <t>lånde</t>
   </si>
   <si>
@@ -1323,6 +1344,12 @@
     <t>no, none</t>
   </si>
   <si>
+    <t>nord</t>
+  </si>
+  <si>
+    <t>north</t>
+  </si>
+  <si>
     <t>nøbe</t>
   </si>
   <si>
@@ -1473,6 +1500,12 @@
     <t>pink</t>
   </si>
   <si>
+    <t>tjørn</t>
+  </si>
+  <si>
+    <t>pond, puddle, small lake</t>
+  </si>
+  <si>
     <t>pålter</t>
   </si>
   <si>
@@ -1617,6 +1650,12 @@
     <t>slave</t>
   </si>
   <si>
+    <t>naker</t>
+  </si>
+  <si>
+    <t>snake</t>
+  </si>
+  <si>
     <t>snove</t>
   </si>
   <si>
@@ -1695,12 +1734,6 @@
     <t>stupid, dumb</t>
   </si>
   <si>
-    <t>fågen</t>
-  </si>
-  <si>
-    <t>swear word</t>
-  </si>
-  <si>
     <t>sverd</t>
   </si>
   <si>
@@ -2028,7 +2061,7 @@
     <t>mørknen</t>
   </si>
   <si>
-    <t>to fail, to become spoiled</t>
+    <t>to fail, to become spoiled | past participle = mirknende</t>
   </si>
   <si>
     <t>duten</t>
@@ -2377,6 +2410,12 @@
   </si>
   <si>
     <t>to suffer</t>
+  </si>
+  <si>
+    <t>svåttasken</t>
+  </si>
+  <si>
+    <t>to summon, to call</t>
   </si>
   <si>
     <t>taken</t>
@@ -3217,12 +3256,12 @@
         <v>23</v>
       </c>
       <c r="G4" s="14" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:B1000, REGEXMATCH(B2:B1000, H3)), 2, TRUE)"),"reinen")</f>
-        <v>reinen</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:B1000, REGEXMATCH(B2:B1000, H3)), 2, TRUE)"),"mørknen")</f>
+        <v>mørknen</v>
       </c>
       <c r="H4" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"to clean, to wash")</f>
-        <v>to clean, to wash</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"to fail, to become spoiled | past participle = mirknende")</f>
+        <v>to fail, to become spoiled | past participle = mirknende</v>
       </c>
       <c r="I4" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("FILTER(C:C, REGEXMATCH(B:B, H3))"),"")</f>
@@ -3402,7 +3441,7 @@
       <c r="A9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="8" t="s">
         <v>41</v>
       </c>
       <c r="C9" s="7"/>
@@ -3437,7 +3476,7 @@
       <c r="Z9" s="7"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B10" s="11" t="s">
@@ -3475,10 +3514,10 @@
       <c r="Z10" s="7"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C11" s="7"/>
@@ -3516,7 +3555,7 @@
       <c r="A12" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="8" t="s">
         <v>55</v>
       </c>
       <c r="C12" s="7"/>
@@ -3697,7 +3736,7 @@
       <c r="A17" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="11" t="s">
         <v>74</v>
       </c>
       <c r="C17" s="7"/>
@@ -3730,10 +3769,10 @@
       <c r="Z17" s="7"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="8" t="s">
         <v>78</v>
       </c>
       <c r="C18" s="7"/>
@@ -3759,7 +3798,7 @@
       <c r="Z18" s="7"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="11" t="s">
         <v>79</v>
       </c>
       <c r="B19" s="11" t="s">
@@ -3826,10 +3865,10 @@
       <c r="Z20" s="7"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="11" t="s">
         <v>86</v>
       </c>
       <c r="C21" s="7"/>
@@ -3862,10 +3901,10 @@
       <c r="Z21" s="7"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="16" t="s">
         <v>90</v>
       </c>
       <c r="C22" s="7"/>
@@ -3898,10 +3937,10 @@
       <c r="Z22" s="7"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="11" t="s">
         <v>94</v>
       </c>
       <c r="C23" s="7"/>
@@ -3934,10 +3973,10 @@
       <c r="Z23" s="7"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="16" t="s">
         <v>98</v>
       </c>
       <c r="C24" s="7"/>
@@ -3970,10 +4009,10 @@
       <c r="Z24" s="7"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="11" t="s">
         <v>102</v>
       </c>
       <c r="C25" s="7"/>
@@ -4006,10 +4045,10 @@
       <c r="Z25" s="7"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="16" t="s">
         <v>106</v>
       </c>
       <c r="C26" s="7"/>
@@ -4113,10 +4152,10 @@
       <c r="Z28" s="7"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="8" t="s">
         <v>118</v>
       </c>
       <c r="C29" s="7"/>
@@ -4151,10 +4190,10 @@
       <c r="Z29" s="7"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="11" t="s">
         <v>123</v>
       </c>
       <c r="C30" s="7"/>
@@ -4186,10 +4225,10 @@
       <c r="Z30" s="7"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="8" t="s">
         <v>127</v>
       </c>
       <c r="C31" s="7"/>
@@ -4222,10 +4261,10 @@
       <c r="Z31" s="7"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C32" s="7"/>
@@ -4258,10 +4297,10 @@
       <c r="Z32" s="7"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="8" t="s">
         <v>135</v>
       </c>
       <c r="C33" s="7"/>
@@ -4294,7 +4333,7 @@
       <c r="Z33" s="7"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="11" t="s">
         <v>138</v>
       </c>
       <c r="B34" s="11" t="s">
@@ -4333,7 +4372,7 @@
       <c r="A35" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="11" t="s">
         <v>143</v>
       </c>
       <c r="C35" s="7"/>
@@ -4366,10 +4405,10 @@
       <c r="Z35" s="7"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="8" t="s">
         <v>147</v>
       </c>
       <c r="C36" s="7"/>
@@ -4402,10 +4441,10 @@
       <c r="Z36" s="7"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="11" t="s">
         <v>151</v>
       </c>
       <c r="C37" s="7"/>
@@ -4509,7 +4548,7 @@
       <c r="A40" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="8" t="s">
         <v>161</v>
       </c>
       <c r="C40" s="7"/>
@@ -4542,10 +4581,10 @@
       <c r="Z40" s="7"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="11" t="s">
         <v>165</v>
       </c>
       <c r="C41" s="7"/>
@@ -4578,10 +4617,10 @@
       <c r="Z41" s="7"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="16" t="s">
         <v>169</v>
       </c>
       <c r="C42" s="7"/>
@@ -4717,7 +4756,7 @@
       <c r="A46" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="8" t="s">
         <v>181</v>
       </c>
       <c r="C46" s="7"/>
@@ -4749,7 +4788,7 @@
       <c r="A47" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="11" t="s">
         <v>183</v>
       </c>
       <c r="C47" s="7"/>
@@ -4783,7 +4822,7 @@
       <c r="A48" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="8" t="s">
         <v>186</v>
       </c>
       <c r="C48" s="7"/>
@@ -4817,7 +4856,7 @@
       <c r="A49" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="11" t="s">
         <v>189</v>
       </c>
       <c r="C49" s="7"/>
@@ -5014,10 +5053,10 @@
       <c r="Z54" s="7"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="16" t="s">
+      <c r="A55" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="8" t="s">
         <v>205</v>
       </c>
       <c r="C55" s="7"/>
@@ -5046,10 +5085,10 @@
       <c r="Z55" s="7"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="16" t="s">
         <v>207</v>
       </c>
       <c r="C56" s="7"/>
@@ -5081,7 +5120,7 @@
       <c r="A57" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="11" t="s">
         <v>209</v>
       </c>
       <c r="C57" s="7"/>
@@ -5142,10 +5181,10 @@
       <c r="Z58" s="7"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="20" t="s">
+      <c r="A59" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="B59" s="21" t="s">
+      <c r="B59" s="8" t="s">
         <v>213</v>
       </c>
       <c r="C59" s="7"/>
@@ -5174,10 +5213,10 @@
       <c r="Z59" s="7"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="21" t="s">
         <v>215</v>
       </c>
       <c r="C60" s="7"/>
@@ -5206,10 +5245,10 @@
       <c r="Z60" s="7"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="16" t="s">
+      <c r="A61" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="B61" s="8" t="s">
         <v>217</v>
       </c>
       <c r="C61" s="7"/>
@@ -5270,10 +5309,10 @@
       <c r="Z62" s="7"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="16" t="s">
         <v>221</v>
       </c>
       <c r="C63" s="7"/>
@@ -5334,10 +5373,10 @@
       <c r="Z64" s="7"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="11" t="s">
         <v>225</v>
       </c>
       <c r="C65" s="7"/>
@@ -5366,10 +5405,10 @@
       <c r="Z65" s="7"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="8" t="s">
         <v>227</v>
       </c>
       <c r="C66" s="7"/>
@@ -5398,11 +5437,11 @@
       <c r="Z66" s="7"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="11" t="s">
+      <c r="A67" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="B67" s="8" t="s">
-        <v>229</v>
+      <c r="B67" s="16" t="s">
+        <v>227</v>
       </c>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
@@ -5431,10 +5470,10 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="B68" s="11" t="s">
         <v>230</v>
-      </c>
-      <c r="B68" s="8" t="s">
-        <v>231</v>
       </c>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
@@ -5462,11 +5501,11 @@
       <c r="Z68" s="7"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="B69" s="8" t="s">
         <v>232</v>
-      </c>
-      <c r="B69" s="8" t="s">
-        <v>233</v>
       </c>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
@@ -5494,11 +5533,11 @@
       <c r="Z69" s="7"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="16" t="s">
+      <c r="A70" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="B70" s="8" t="s">
         <v>234</v>
-      </c>
-      <c r="B70" s="16" t="s">
-        <v>235</v>
       </c>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
@@ -5526,11 +5565,11 @@
       <c r="Z70" s="7"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="11" t="s">
+      <c r="A71" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B71" s="8" t="s">
         <v>236</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>237</v>
       </c>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
@@ -5558,11 +5597,11 @@
       <c r="Z71" s="7"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B72" s="16" t="s">
         <v>238</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>239</v>
       </c>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
@@ -5590,11 +5629,11 @@
       <c r="Z72" s="7"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="16" t="s">
+      <c r="A73" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="B73" s="8" t="s">
         <v>240</v>
-      </c>
-      <c r="B73" s="16" t="s">
-        <v>241</v>
       </c>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
@@ -5623,10 +5662,10 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="B74" s="11" t="s">
         <v>242</v>
-      </c>
-      <c r="B74" s="11" t="s">
-        <v>243</v>
       </c>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
@@ -5654,11 +5693,11 @@
       <c r="Z74" s="7"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="B75" s="16" t="s">
         <v>244</v>
-      </c>
-      <c r="B75" s="11" t="s">
-        <v>245</v>
       </c>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
@@ -5687,10 +5726,10 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B76" s="11" t="s">
         <v>246</v>
-      </c>
-      <c r="B76" s="11" t="s">
-        <v>247</v>
       </c>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
@@ -5719,10 +5758,10 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B77" s="11" t="s">
         <v>248</v>
-      </c>
-      <c r="B77" s="11" t="s">
-        <v>249</v>
       </c>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
@@ -5751,10 +5790,10 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B78" s="11" t="s">
         <v>250</v>
-      </c>
-      <c r="B78" s="11" t="s">
-        <v>251</v>
       </c>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
@@ -5783,10 +5822,10 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B79" s="11" t="s">
         <v>252</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>253</v>
       </c>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
@@ -5815,10 +5854,10 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="B80" s="11" t="s">
         <v>254</v>
-      </c>
-      <c r="B80" s="11" t="s">
-        <v>255</v>
       </c>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
@@ -5847,10 +5886,10 @@
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="B81" s="11" t="s">
         <v>256</v>
-      </c>
-      <c r="B81" s="11" t="s">
-        <v>257</v>
       </c>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
@@ -5878,13 +5917,13 @@
       <c r="Z81" s="7"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="20" t="s">
+      <c r="A82" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="B82" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="B82" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="C82" s="22"/>
+      <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
       <c r="F82" s="7"/>
@@ -5910,11 +5949,11 @@
       <c r="Z82" s="7"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="8" t="s">
+      <c r="A83" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="B83" s="16" t="s">
         <v>260</v>
-      </c>
-      <c r="B83" s="8" t="s">
-        <v>261</v>
       </c>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
@@ -5943,10 +5982,10 @@
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B84" s="11" t="s">
         <v>262</v>
-      </c>
-      <c r="B84" s="8" t="s">
-        <v>263</v>
       </c>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
@@ -5974,13 +6013,13 @@
       <c r="Z84" s="7"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="8" t="s">
+      <c r="A85" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="B85" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="B85" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="C85" s="7"/>
+      <c r="C85" s="22"/>
       <c r="D85" s="7"/>
       <c r="E85" s="7"/>
       <c r="F85" s="7"/>
@@ -6007,10 +6046,10 @@
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="B86" s="8" t="s">
         <v>266</v>
-      </c>
-      <c r="B86" s="8" t="s">
-        <v>267</v>
       </c>
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
@@ -6039,10 +6078,10 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="B87" s="8" t="s">
         <v>268</v>
-      </c>
-      <c r="B87" s="11" t="s">
-        <v>269</v>
       </c>
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
@@ -6071,10 +6110,10 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B88" s="11" t="s">
         <v>270</v>
-      </c>
-      <c r="B88" s="8" t="s">
-        <v>271</v>
       </c>
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
@@ -6103,10 +6142,10 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="B89" s="8" t="s">
         <v>272</v>
-      </c>
-      <c r="B89" s="8" t="s">
-        <v>273</v>
       </c>
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
@@ -6134,11 +6173,11 @@
       <c r="Z89" s="7"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="11" t="s">
+      <c r="A90" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="B90" s="11" t="s">
         <v>274</v>
-      </c>
-      <c r="B90" s="11" t="s">
-        <v>275</v>
       </c>
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
@@ -6166,11 +6205,11 @@
       <c r="Z90" s="7"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="11" t="s">
+      <c r="A91" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B91" s="8" t="s">
         <v>276</v>
-      </c>
-      <c r="B91" s="8" t="s">
-        <v>277</v>
       </c>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
@@ -6199,10 +6238,10 @@
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="B92" s="8" t="s">
         <v>278</v>
-      </c>
-      <c r="B92" s="8" t="s">
-        <v>279</v>
       </c>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
@@ -6230,11 +6269,11 @@
       <c r="Z92" s="7"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="16" t="s">
+      <c r="A93" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="B93" s="11" t="s">
         <v>280</v>
-      </c>
-      <c r="B93" s="16" t="s">
-        <v>281</v>
       </c>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
@@ -6262,11 +6301,11 @@
       <c r="Z93" s="7"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="8" t="s">
+      <c r="A94" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="B94" s="8" t="s">
         <v>282</v>
-      </c>
-      <c r="B94" s="8" t="s">
-        <v>283</v>
       </c>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
@@ -6295,10 +6334,10 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B95" s="8" t="s">
         <v>284</v>
-      </c>
-      <c r="B95" s="8" t="s">
-        <v>285</v>
       </c>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
@@ -6326,11 +6365,11 @@
       <c r="Z95" s="7"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="8" t="s">
+      <c r="A96" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="B96" s="16" t="s">
         <v>286</v>
-      </c>
-      <c r="B96" s="8" t="s">
-        <v>287</v>
       </c>
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
@@ -6358,11 +6397,11 @@
       <c r="Z96" s="7"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="16" t="s">
+      <c r="A97" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B97" s="8" t="s">
         <v>288</v>
-      </c>
-      <c r="B97" s="16" t="s">
-        <v>289</v>
       </c>
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
@@ -6391,10 +6430,10 @@
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="B98" s="8" t="s">
         <v>290</v>
-      </c>
-      <c r="B98" s="8" t="s">
-        <v>291</v>
       </c>
       <c r="C98" s="7"/>
       <c r="D98" s="7"/>
@@ -6423,10 +6462,10 @@
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="B99" s="8" t="s">
         <v>292</v>
-      </c>
-      <c r="B99" s="11" t="s">
-        <v>293</v>
       </c>
       <c r="C99" s="7"/>
       <c r="D99" s="7"/>
@@ -6454,11 +6493,11 @@
       <c r="Z99" s="7"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="8" t="s">
+      <c r="A100" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="B100" s="16" t="s">
         <v>294</v>
-      </c>
-      <c r="B100" s="8" t="s">
-        <v>295</v>
       </c>
       <c r="C100" s="7"/>
       <c r="D100" s="7"/>
@@ -6487,10 +6526,10 @@
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B101" s="8" t="s">
         <v>296</v>
-      </c>
-      <c r="B101" s="8" t="s">
-        <v>297</v>
       </c>
       <c r="C101" s="7"/>
       <c r="D101" s="7"/>
@@ -6519,10 +6558,10 @@
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="B102" s="11" t="s">
         <v>298</v>
-      </c>
-      <c r="B102" s="11" t="s">
-        <v>299</v>
       </c>
       <c r="C102" s="7"/>
       <c r="D102" s="7"/>
@@ -6551,10 +6590,10 @@
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B103" s="8" t="s">
         <v>300</v>
-      </c>
-      <c r="B103" s="11" t="s">
-        <v>301</v>
       </c>
       <c r="C103" s="7"/>
       <c r="D103" s="7"/>
@@ -6583,10 +6622,10 @@
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B104" s="8" t="s">
         <v>302</v>
-      </c>
-      <c r="B104" s="11" t="s">
-        <v>303</v>
       </c>
       <c r="C104" s="7"/>
       <c r="D104" s="7"/>
@@ -6615,10 +6654,10 @@
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="B105" s="11" t="s">
         <v>304</v>
-      </c>
-      <c r="B105" s="8" t="s">
-        <v>305</v>
       </c>
       <c r="C105" s="7"/>
       <c r="D105" s="7"/>
@@ -6646,11 +6685,11 @@
       <c r="Z105" s="7"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="16" t="s">
+      <c r="A106" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B106" s="11" t="s">
         <v>306</v>
-      </c>
-      <c r="B106" s="16" t="s">
-        <v>307</v>
       </c>
       <c r="C106" s="7"/>
       <c r="D106" s="7"/>
@@ -6679,10 +6718,10 @@
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B107" s="11" t="s">
         <v>308</v>
-      </c>
-      <c r="B107" s="8" t="s">
-        <v>309</v>
       </c>
       <c r="C107" s="7"/>
       <c r="D107" s="7"/>
@@ -6710,11 +6749,11 @@
       <c r="Z107" s="7"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="16" t="s">
+      <c r="A108" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="B108" s="8" t="s">
         <v>310</v>
-      </c>
-      <c r="B108" s="16" t="s">
-        <v>311</v>
       </c>
       <c r="C108" s="7"/>
       <c r="D108" s="7"/>
@@ -6742,11 +6781,11 @@
       <c r="Z108" s="7"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="20" t="s">
+      <c r="A109" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="B109" s="16" t="s">
         <v>312</v>
-      </c>
-      <c r="B109" s="20" t="s">
-        <v>313</v>
       </c>
       <c r="C109" s="7"/>
       <c r="D109" s="7"/>
@@ -6775,10 +6814,10 @@
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="B110" s="8" t="s">
         <v>314</v>
-      </c>
-      <c r="B110" s="16" t="s">
-        <v>315</v>
       </c>
       <c r="C110" s="7"/>
       <c r="D110" s="7"/>
@@ -6806,11 +6845,11 @@
       <c r="Z110" s="7"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="8" t="s">
+      <c r="A111" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="B111" s="16" t="s">
         <v>316</v>
-      </c>
-      <c r="B111" s="11" t="s">
-        <v>317</v>
       </c>
       <c r="C111" s="7"/>
       <c r="D111" s="7"/>
@@ -6838,11 +6877,11 @@
       <c r="Z111" s="7"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="16" t="s">
+      <c r="A112" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="B112" s="20" t="s">
         <v>318</v>
-      </c>
-      <c r="B112" s="16" t="s">
-        <v>319</v>
       </c>
       <c r="C112" s="7"/>
       <c r="D112" s="7"/>
@@ -6871,10 +6910,10 @@
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="B113" s="16" t="s">
         <v>320</v>
-      </c>
-      <c r="B113" s="11" t="s">
-        <v>321</v>
       </c>
       <c r="C113" s="7"/>
       <c r="D113" s="7"/>
@@ -6903,10 +6942,10 @@
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B114" s="11" t="s">
         <v>322</v>
-      </c>
-      <c r="B114" s="8" t="s">
-        <v>323</v>
       </c>
       <c r="C114" s="7"/>
       <c r="D114" s="7"/>
@@ -6934,11 +6973,11 @@
       <c r="Z114" s="7"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="8" t="s">
+      <c r="A115" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="B115" s="16" t="s">
         <v>324</v>
-      </c>
-      <c r="B115" s="8" t="s">
-        <v>325</v>
       </c>
       <c r="C115" s="7"/>
       <c r="D115" s="7"/>
@@ -6967,10 +7006,10 @@
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="B116" s="11" t="s">
         <v>326</v>
-      </c>
-      <c r="B116" s="8" t="s">
-        <v>327</v>
       </c>
       <c r="C116" s="7"/>
       <c r="D116" s="7"/>
@@ -6998,11 +7037,11 @@
       <c r="Z116" s="7"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="11" t="s">
+      <c r="A117" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="B117" s="8" t="s">
         <v>328</v>
-      </c>
-      <c r="B117" s="11" t="s">
-        <v>329</v>
       </c>
       <c r="C117" s="7"/>
       <c r="D117" s="7"/>
@@ -7030,11 +7069,11 @@
       <c r="Z117" s="7"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="16" t="s">
+      <c r="A118" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="B118" s="8" t="s">
         <v>330</v>
-      </c>
-      <c r="B118" s="16" t="s">
-        <v>331</v>
       </c>
       <c r="C118" s="7"/>
       <c r="D118" s="7"/>
@@ -7063,10 +7102,10 @@
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="B119" s="8" t="s">
         <v>332</v>
-      </c>
-      <c r="B119" s="8" t="s">
-        <v>333</v>
       </c>
       <c r="C119" s="7"/>
       <c r="D119" s="7"/>
@@ -7094,11 +7133,11 @@
       <c r="Z119" s="7"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="21" t="s">
+      <c r="A120" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="B120" s="11" t="s">
         <v>334</v>
-      </c>
-      <c r="B120" s="20" t="s">
-        <v>335</v>
       </c>
       <c r="C120" s="7"/>
       <c r="D120" s="7"/>
@@ -7126,11 +7165,11 @@
       <c r="Z120" s="7"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="8" t="s">
+      <c r="A121" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="B121" s="16" t="s">
         <v>336</v>
-      </c>
-      <c r="B121" s="8" t="s">
-        <v>337</v>
       </c>
       <c r="C121" s="7"/>
       <c r="D121" s="7"/>
@@ -7159,10 +7198,10 @@
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="B122" s="8" t="s">
         <v>338</v>
-      </c>
-      <c r="B122" s="11" t="s">
-        <v>339</v>
       </c>
       <c r="C122" s="7"/>
       <c r="D122" s="7"/>
@@ -7190,11 +7229,11 @@
       <c r="Z122" s="7"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="8" t="s">
+      <c r="A123" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="B123" s="20" t="s">
         <v>340</v>
-      </c>
-      <c r="B123" s="11" t="s">
-        <v>341</v>
       </c>
       <c r="C123" s="7"/>
       <c r="D123" s="7"/>
@@ -7223,10 +7262,10 @@
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="B124" s="8" t="s">
         <v>342</v>
-      </c>
-      <c r="B124" s="11" t="s">
-        <v>343</v>
       </c>
       <c r="C124" s="7"/>
       <c r="D124" s="7"/>
@@ -7254,11 +7293,11 @@
       <c r="Z124" s="7"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="20" t="s">
+      <c r="A125" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="B125" s="11" t="s">
         <v>344</v>
-      </c>
-      <c r="B125" s="21" t="s">
-        <v>345</v>
       </c>
       <c r="C125" s="7"/>
       <c r="D125" s="7"/>
@@ -7287,10 +7326,10 @@
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="B126" s="11" t="s">
         <v>346</v>
-      </c>
-      <c r="B126" s="8" t="s">
-        <v>347</v>
       </c>
       <c r="C126" s="7"/>
       <c r="D126" s="7"/>
@@ -7319,10 +7358,10 @@
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="B127" s="11" t="s">
         <v>348</v>
-      </c>
-      <c r="B127" s="11" t="s">
-        <v>349</v>
       </c>
       <c r="C127" s="7"/>
       <c r="D127" s="7"/>
@@ -7350,11 +7389,11 @@
       <c r="Z127" s="7"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="8" t="s">
+      <c r="A128" s="20" t="s">
+        <v>349</v>
+      </c>
+      <c r="B128" s="21" t="s">
         <v>350</v>
-      </c>
-      <c r="B128" s="8" t="s">
-        <v>351</v>
       </c>
       <c r="C128" s="7"/>
       <c r="D128" s="7"/>
@@ -7383,10 +7422,10 @@
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="B129" s="8" t="s">
         <v>352</v>
-      </c>
-      <c r="B129" s="11" t="s">
-        <v>353</v>
       </c>
       <c r="C129" s="7"/>
       <c r="D129" s="7"/>
@@ -7414,11 +7453,11 @@
       <c r="Z129" s="7"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="20" t="s">
+      <c r="A130" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="B130" s="11" t="s">
         <v>354</v>
-      </c>
-      <c r="B130" s="21" t="s">
-        <v>355</v>
       </c>
       <c r="C130" s="7"/>
       <c r="D130" s="7"/>
@@ -7446,11 +7485,11 @@
       <c r="Z130" s="7"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="16" t="s">
+      <c r="A131" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="B131" s="8" t="s">
         <v>356</v>
-      </c>
-      <c r="B131" s="16" t="s">
-        <v>357</v>
       </c>
       <c r="C131" s="7"/>
       <c r="D131" s="7"/>
@@ -7479,10 +7518,10 @@
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="B132" s="11" t="s">
         <v>358</v>
-      </c>
-      <c r="B132" s="8" t="s">
-        <v>359</v>
       </c>
       <c r="C132" s="7"/>
       <c r="D132" s="7"/>
@@ -7510,11 +7549,11 @@
       <c r="Z132" s="7"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="8" t="s">
+      <c r="A133" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="B133" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="B133" s="8" t="s">
-        <v>361</v>
       </c>
       <c r="C133" s="7"/>
       <c r="D133" s="7"/>
@@ -7542,11 +7581,11 @@
       <c r="Z133" s="7"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="8" t="s">
+      <c r="A134" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="B134" s="16" t="s">
         <v>362</v>
-      </c>
-      <c r="B134" s="8" t="s">
-        <v>363</v>
       </c>
       <c r="C134" s="7"/>
       <c r="D134" s="7"/>
@@ -7575,10 +7614,10 @@
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="B135" s="8" t="s">
         <v>364</v>
-      </c>
-      <c r="B135" s="8" t="s">
-        <v>365</v>
       </c>
       <c r="C135" s="7"/>
       <c r="D135" s="7"/>
@@ -7607,10 +7646,10 @@
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="B136" s="8" t="s">
         <v>366</v>
-      </c>
-      <c r="B136" s="8" t="s">
-        <v>367</v>
       </c>
       <c r="C136" s="7"/>
       <c r="D136" s="7"/>
@@ -7639,10 +7678,10 @@
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="B137" s="8" t="s">
         <v>368</v>
-      </c>
-      <c r="B137" s="8" t="s">
-        <v>369</v>
       </c>
       <c r="C137" s="7"/>
       <c r="D137" s="7"/>
@@ -7671,10 +7710,10 @@
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="B138" s="8" t="s">
         <v>370</v>
-      </c>
-      <c r="B138" s="8" t="s">
-        <v>371</v>
       </c>
       <c r="C138" s="7"/>
       <c r="D138" s="7"/>
@@ -7703,10 +7742,10 @@
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="B139" s="8" t="s">
         <v>372</v>
-      </c>
-      <c r="B139" s="11" t="s">
-        <v>373</v>
       </c>
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
@@ -7734,11 +7773,11 @@
       <c r="Z139" s="7"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="11" t="s">
+      <c r="A140" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="B140" s="16" t="s">
         <v>374</v>
-      </c>
-      <c r="B140" s="8" t="s">
-        <v>375</v>
       </c>
       <c r="C140" s="7"/>
       <c r="D140" s="7"/>
@@ -7767,10 +7806,10 @@
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="B141" s="8" t="s">
         <v>376</v>
-      </c>
-      <c r="B141" s="8" t="s">
-        <v>377</v>
       </c>
       <c r="C141" s="7"/>
       <c r="D141" s="7"/>
@@ -7799,10 +7838,10 @@
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="B142" s="8" t="s">
         <v>378</v>
-      </c>
-      <c r="B142" s="8" t="s">
-        <v>379</v>
       </c>
       <c r="C142" s="7"/>
       <c r="D142" s="7"/>
@@ -7831,10 +7870,10 @@
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="B143" s="11" t="s">
         <v>380</v>
-      </c>
-      <c r="B143" s="11" t="s">
-        <v>381</v>
       </c>
       <c r="C143" s="7"/>
       <c r="D143" s="7"/>
@@ -7862,11 +7901,11 @@
       <c r="Z143" s="7"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="16" t="s">
+      <c r="A144" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="B144" s="8" t="s">
         <v>382</v>
-      </c>
-      <c r="B144" s="16" t="s">
-        <v>383</v>
       </c>
       <c r="C144" s="7"/>
       <c r="D144" s="7"/>
@@ -7895,10 +7934,10 @@
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="B145" s="8" t="s">
         <v>384</v>
-      </c>
-      <c r="B145" s="8" t="s">
-        <v>385</v>
       </c>
       <c r="C145" s="7"/>
       <c r="D145" s="7"/>
@@ -7926,11 +7965,11 @@
       <c r="Z145" s="7"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="16" t="s">
+      <c r="A146" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="B146" s="8" t="s">
         <v>386</v>
-      </c>
-      <c r="B146" s="16" t="s">
-        <v>387</v>
       </c>
       <c r="C146" s="7"/>
       <c r="D146" s="7"/>
@@ -7959,10 +7998,10 @@
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="B147" s="11" t="s">
         <v>388</v>
-      </c>
-      <c r="B147" s="8" t="s">
-        <v>389</v>
       </c>
       <c r="C147" s="7"/>
       <c r="D147" s="7"/>
@@ -7990,11 +8029,11 @@
       <c r="Z147" s="7"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="8" t="s">
+      <c r="A148" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="B148" s="16" t="s">
         <v>390</v>
-      </c>
-      <c r="B148" s="8" t="s">
-        <v>391</v>
       </c>
       <c r="C148" s="7"/>
       <c r="D148" s="7"/>
@@ -8023,10 +8062,10 @@
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="B149" s="8" t="s">
         <v>392</v>
-      </c>
-      <c r="B149" s="11" t="s">
-        <v>393</v>
       </c>
       <c r="C149" s="7"/>
       <c r="D149" s="7"/>
@@ -8054,11 +8093,11 @@
       <c r="Z149" s="7"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="11" t="s">
+      <c r="A150" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="B150" s="16" t="s">
         <v>394</v>
-      </c>
-      <c r="B150" s="11" t="s">
-        <v>395</v>
       </c>
       <c r="C150" s="7"/>
       <c r="D150" s="7"/>
@@ -8087,10 +8126,10 @@
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="B151" s="8" t="s">
         <v>396</v>
-      </c>
-      <c r="B151" s="11" t="s">
-        <v>397</v>
       </c>
       <c r="C151" s="7"/>
       <c r="D151" s="7"/>
@@ -8119,10 +8158,10 @@
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="B152" s="8" t="s">
         <v>398</v>
-      </c>
-      <c r="B152" s="11" t="s">
-        <v>399</v>
       </c>
       <c r="C152" s="7"/>
       <c r="D152" s="7"/>
@@ -8151,10 +8190,10 @@
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="B153" s="11" t="s">
         <v>400</v>
-      </c>
-      <c r="B153" s="8" t="s">
-        <v>401</v>
       </c>
       <c r="C153" s="7"/>
       <c r="D153" s="7"/>
@@ -8182,11 +8221,11 @@
       <c r="Z153" s="7"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="16" t="s">
+      <c r="A154" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="B154" s="11" t="s">
         <v>402</v>
-      </c>
-      <c r="B154" s="16" t="s">
-        <v>403</v>
       </c>
       <c r="C154" s="7"/>
       <c r="D154" s="7"/>
@@ -8215,10 +8254,10 @@
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="B155" s="11" t="s">
         <v>404</v>
-      </c>
-      <c r="B155" s="11" t="s">
-        <v>405</v>
       </c>
       <c r="C155" s="7"/>
       <c r="D155" s="7"/>
@@ -8246,11 +8285,11 @@
       <c r="Z155" s="7"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="16" t="s">
+      <c r="A156" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="B156" s="11" t="s">
         <v>406</v>
-      </c>
-      <c r="B156" s="16" t="s">
-        <v>407</v>
       </c>
       <c r="C156" s="7"/>
       <c r="D156" s="7"/>
@@ -8279,10 +8318,10 @@
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="B157" s="8" t="s">
         <v>408</v>
-      </c>
-      <c r="B157" s="8" t="s">
-        <v>409</v>
       </c>
       <c r="C157" s="7"/>
       <c r="D157" s="7"/>
@@ -8310,11 +8349,11 @@
       <c r="Z157" s="7"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="8" t="s">
+      <c r="A158" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="B158" s="16" t="s">
         <v>410</v>
-      </c>
-      <c r="B158" s="8" t="s">
-        <v>411</v>
       </c>
       <c r="C158" s="7"/>
       <c r="D158" s="7"/>
@@ -8342,11 +8381,11 @@
       <c r="Z158" s="7"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="11" t="s">
+      <c r="A159" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="B159" s="11" t="s">
         <v>412</v>
-      </c>
-      <c r="B159" s="11" t="s">
-        <v>413</v>
       </c>
       <c r="C159" s="7"/>
       <c r="D159" s="7"/>
@@ -8374,11 +8413,11 @@
       <c r="Z159" s="7"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="8" t="s">
+      <c r="A160" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="B160" s="16" t="s">
         <v>414</v>
-      </c>
-      <c r="B160" s="8" t="s">
-        <v>415</v>
       </c>
       <c r="C160" s="7"/>
       <c r="D160" s="7"/>
@@ -8406,11 +8445,11 @@
       <c r="Z160" s="7"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="16" t="s">
+      <c r="A161" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="B161" s="8" t="s">
         <v>416</v>
-      </c>
-      <c r="B161" s="16" t="s">
-        <v>417</v>
       </c>
       <c r="C161" s="7"/>
       <c r="D161" s="7"/>
@@ -8438,11 +8477,11 @@
       <c r="Z161" s="7"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="11" t="s">
+      <c r="A162" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="B162" s="8" t="s">
         <v>418</v>
-      </c>
-      <c r="B162" s="8" t="s">
-        <v>419</v>
       </c>
       <c r="C162" s="7"/>
       <c r="D162" s="7"/>
@@ -8471,10 +8510,10 @@
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="B163" s="11" t="s">
         <v>420</v>
-      </c>
-      <c r="B163" s="11" t="s">
-        <v>421</v>
       </c>
       <c r="C163" s="7"/>
       <c r="D163" s="7"/>
@@ -8503,10 +8542,10 @@
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="B164" s="8" t="s">
         <v>422</v>
-      </c>
-      <c r="B164" s="8" t="s">
-        <v>423</v>
       </c>
       <c r="C164" s="7"/>
       <c r="D164" s="7"/>
@@ -8534,11 +8573,11 @@
       <c r="Z164" s="7"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="8" t="s">
+      <c r="A165" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="B165" s="16" t="s">
         <v>424</v>
-      </c>
-      <c r="B165" s="11" t="s">
-        <v>425</v>
       </c>
       <c r="C165" s="7"/>
       <c r="D165" s="7"/>
@@ -8567,10 +8606,10 @@
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="B166" s="8" t="s">
         <v>426</v>
-      </c>
-      <c r="B166" s="11" t="s">
-        <v>427</v>
       </c>
       <c r="C166" s="7"/>
       <c r="D166" s="7"/>
@@ -8598,11 +8637,11 @@
       <c r="Z166" s="7"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="8" t="s">
+      <c r="A167" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="B167" s="11" t="s">
         <v>428</v>
-      </c>
-      <c r="B167" s="8" t="s">
-        <v>429</v>
       </c>
       <c r="C167" s="7"/>
       <c r="D167" s="7"/>
@@ -8631,10 +8670,10 @@
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="B168" s="8" t="s">
         <v>430</v>
-      </c>
-      <c r="B168" s="8" t="s">
-        <v>431</v>
       </c>
       <c r="C168" s="7"/>
       <c r="D168" s="7"/>
@@ -8662,11 +8701,11 @@
       <c r="Z168" s="7"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="11" t="s">
+      <c r="A169" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="B169" s="11" t="s">
         <v>432</v>
-      </c>
-      <c r="B169" s="11" t="s">
-        <v>433</v>
       </c>
       <c r="C169" s="7"/>
       <c r="D169" s="7"/>
@@ -8694,11 +8733,11 @@
       <c r="Z169" s="7"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="20" t="s">
+      <c r="A170" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="B170" s="11" t="s">
         <v>434</v>
-      </c>
-      <c r="B170" s="20" t="s">
-        <v>435</v>
       </c>
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
@@ -8726,11 +8765,11 @@
       <c r="Z170" s="7"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="16" t="s">
+      <c r="A171" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="B171" s="8" t="s">
         <v>436</v>
-      </c>
-      <c r="B171" s="16" t="s">
-        <v>437</v>
       </c>
       <c r="C171" s="7"/>
       <c r="D171" s="7"/>
@@ -8758,11 +8797,11 @@
       <c r="Z171" s="7"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="20" t="s">
+      <c r="A172" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="B172" s="8" t="s">
         <v>438</v>
-      </c>
-      <c r="B172" s="20" t="s">
-        <v>439</v>
       </c>
       <c r="C172" s="7"/>
       <c r="D172" s="7"/>
@@ -8790,11 +8829,11 @@
       <c r="Z172" s="7"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="8" t="s">
+      <c r="A173" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="B173" s="11" t="s">
         <v>440</v>
-      </c>
-      <c r="B173" s="8" t="s">
-        <v>441</v>
       </c>
       <c r="C173" s="7"/>
       <c r="D173" s="7"/>
@@ -8822,11 +8861,11 @@
       <c r="Z173" s="7"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="16" t="s">
+      <c r="A174" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="B174" s="20" t="s">
         <v>442</v>
-      </c>
-      <c r="B174" s="16" t="s">
-        <v>443</v>
       </c>
       <c r="C174" s="7"/>
       <c r="D174" s="7"/>
@@ -8854,11 +8893,11 @@
       <c r="Z174" s="7"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="8" t="s">
+      <c r="A175" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="B175" s="16" t="s">
         <v>444</v>
-      </c>
-      <c r="B175" s="8" t="s">
-        <v>445</v>
       </c>
       <c r="C175" s="7"/>
       <c r="D175" s="7"/>
@@ -8886,11 +8925,11 @@
       <c r="Z175" s="7"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="8" t="s">
+      <c r="A176" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="B176" s="16" t="s">
         <v>446</v>
-      </c>
-      <c r="B176" s="11" t="s">
-        <v>447</v>
       </c>
       <c r="C176" s="7"/>
       <c r="D176" s="7"/>
@@ -8918,11 +8957,11 @@
       <c r="Z176" s="7"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="8" t="s">
+      <c r="A177" s="20" t="s">
+        <v>447</v>
+      </c>
+      <c r="B177" s="20" t="s">
         <v>448</v>
-      </c>
-      <c r="B177" s="11" t="s">
-        <v>449</v>
       </c>
       <c r="C177" s="7"/>
       <c r="D177" s="7"/>
@@ -8951,10 +8990,10 @@
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="B178" s="8" t="s">
         <v>450</v>
-      </c>
-      <c r="B178" s="11" t="s">
-        <v>451</v>
       </c>
       <c r="C178" s="7"/>
       <c r="D178" s="7"/>
@@ -8982,11 +9021,11 @@
       <c r="Z178" s="7"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="8" t="s">
+      <c r="A179" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="B179" s="16" t="s">
         <v>452</v>
-      </c>
-      <c r="B179" s="11" t="s">
-        <v>453</v>
       </c>
       <c r="C179" s="7"/>
       <c r="D179" s="7"/>
@@ -9015,10 +9054,10 @@
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B180" s="8" t="s">
         <v>454</v>
-      </c>
-      <c r="B180" s="11" t="s">
-        <v>455</v>
       </c>
       <c r="C180" s="7"/>
       <c r="D180" s="7"/>
@@ -9047,10 +9086,10 @@
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="B181" s="11" t="s">
         <v>456</v>
-      </c>
-      <c r="B181" s="11" t="s">
-        <v>457</v>
       </c>
       <c r="C181" s="7"/>
       <c r="D181" s="7"/>
@@ -9079,10 +9118,10 @@
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="B182" s="11" t="s">
         <v>458</v>
-      </c>
-      <c r="B182" s="11" t="s">
-        <v>459</v>
       </c>
       <c r="C182" s="7"/>
       <c r="D182" s="7"/>
@@ -9111,10 +9150,10 @@
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="B183" s="11" t="s">
         <v>460</v>
-      </c>
-      <c r="B183" s="11" t="s">
-        <v>461</v>
       </c>
       <c r="C183" s="7"/>
       <c r="D183" s="7"/>
@@ -9142,11 +9181,11 @@
       <c r="Z183" s="7"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="16" t="s">
+      <c r="A184" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="B184" s="11" t="s">
         <v>462</v>
-      </c>
-      <c r="B184" s="16" t="s">
-        <v>463</v>
       </c>
       <c r="C184" s="7"/>
       <c r="D184" s="7"/>
@@ -9175,10 +9214,10 @@
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="B185" s="11" t="s">
         <v>464</v>
-      </c>
-      <c r="B185" s="11" t="s">
-        <v>465</v>
       </c>
       <c r="C185" s="7"/>
       <c r="D185" s="7"/>
@@ -9207,10 +9246,10 @@
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="B186" s="11" t="s">
         <v>466</v>
-      </c>
-      <c r="B186" s="11" t="s">
-        <v>467</v>
       </c>
       <c r="C186" s="7"/>
       <c r="D186" s="7"/>
@@ -9239,10 +9278,10 @@
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="B187" s="11" t="s">
         <v>468</v>
-      </c>
-      <c r="B187" s="11" t="s">
-        <v>469</v>
       </c>
       <c r="C187" s="7"/>
       <c r="D187" s="7"/>
@@ -9270,11 +9309,11 @@
       <c r="Z187" s="7"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="11" t="s">
+      <c r="A188" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="B188" s="11" t="s">
         <v>470</v>
-      </c>
-      <c r="B188" s="11" t="s">
-        <v>471</v>
       </c>
       <c r="C188" s="7"/>
       <c r="D188" s="7"/>
@@ -9302,11 +9341,11 @@
       <c r="Z188" s="7"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="11" t="s">
+      <c r="A189" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="B189" s="16" t="s">
         <v>472</v>
-      </c>
-      <c r="B189" s="11" t="s">
-        <v>473</v>
       </c>
       <c r="C189" s="7"/>
       <c r="D189" s="7"/>
@@ -9335,10 +9374,10 @@
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="B190" s="11" t="s">
         <v>474</v>
-      </c>
-      <c r="B190" s="11" t="s">
-        <v>475</v>
       </c>
       <c r="C190" s="7"/>
       <c r="D190" s="7"/>
@@ -9366,11 +9405,11 @@
       <c r="Z190" s="7"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="16" t="s">
+      <c r="A191" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="B191" s="11" t="s">
         <v>476</v>
-      </c>
-      <c r="B191" s="16" t="s">
-        <v>477</v>
       </c>
       <c r="C191" s="7"/>
       <c r="D191" s="7"/>
@@ -9399,10 +9438,10 @@
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="B192" s="11" t="s">
         <v>478</v>
-      </c>
-      <c r="B192" s="8" t="s">
-        <v>479</v>
       </c>
       <c r="C192" s="7"/>
       <c r="D192" s="7"/>
@@ -9430,11 +9469,11 @@
       <c r="Z192" s="7"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="8" t="s">
+      <c r="A193" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="B193" s="11" t="s">
         <v>480</v>
-      </c>
-      <c r="B193" s="8" t="s">
-        <v>481</v>
       </c>
       <c r="C193" s="7"/>
       <c r="D193" s="7"/>
@@ -9462,11 +9501,11 @@
       <c r="Z193" s="7"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="16" t="s">
+      <c r="A194" s="11" t="s">
+        <v>481</v>
+      </c>
+      <c r="B194" s="11" t="s">
         <v>482</v>
-      </c>
-      <c r="B194" s="16" t="s">
-        <v>483</v>
       </c>
       <c r="C194" s="7"/>
       <c r="D194" s="7"/>
@@ -9494,11 +9533,11 @@
       <c r="Z194" s="7"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="16" t="s">
+      <c r="A195" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="B195" s="11" t="s">
         <v>484</v>
-      </c>
-      <c r="B195" s="16" t="s">
-        <v>485</v>
       </c>
       <c r="C195" s="7"/>
       <c r="D195" s="7"/>
@@ -9526,11 +9565,11 @@
       <c r="Z195" s="7"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="8" t="s">
+      <c r="A196" s="16" t="s">
+        <v>485</v>
+      </c>
+      <c r="B196" s="16" t="s">
         <v>486</v>
-      </c>
-      <c r="B196" s="8" t="s">
-        <v>487</v>
       </c>
       <c r="C196" s="7"/>
       <c r="D196" s="7"/>
@@ -9559,10 +9598,10 @@
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="B197" s="8" t="s">
         <v>488</v>
-      </c>
-      <c r="B197" s="8" t="s">
-        <v>489</v>
       </c>
       <c r="C197" s="7"/>
       <c r="D197" s="7"/>
@@ -9590,11 +9629,11 @@
       <c r="Z197" s="7"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="11" t="s">
+      <c r="A198" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="B198" s="8" t="s">
         <v>490</v>
-      </c>
-      <c r="B198" s="8" t="s">
-        <v>491</v>
       </c>
       <c r="C198" s="7"/>
       <c r="D198" s="7"/>
@@ -9622,11 +9661,11 @@
       <c r="Z198" s="7"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="8" t="s">
+      <c r="A199" s="16" t="s">
+        <v>491</v>
+      </c>
+      <c r="B199" s="16" t="s">
         <v>492</v>
-      </c>
-      <c r="B199" s="11" t="s">
-        <v>493</v>
       </c>
       <c r="C199" s="7"/>
       <c r="D199" s="7"/>
@@ -9654,11 +9693,11 @@
       <c r="Z199" s="7"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="8" t="s">
+      <c r="A200" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="B200" s="16" t="s">
         <v>494</v>
-      </c>
-      <c r="B200" s="11" t="s">
-        <v>495</v>
       </c>
       <c r="C200" s="7"/>
       <c r="D200" s="7"/>
@@ -9686,11 +9725,11 @@
       <c r="Z200" s="7"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="8" t="s">
+      <c r="A201" s="16" t="s">
+        <v>495</v>
+      </c>
+      <c r="B201" s="16" t="s">
         <v>496</v>
-      </c>
-      <c r="B201" s="8" t="s">
-        <v>497</v>
       </c>
       <c r="C201" s="7"/>
       <c r="D201" s="7"/>
@@ -9719,10 +9758,10 @@
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="B202" s="8" t="s">
         <v>498</v>
-      </c>
-      <c r="B202" s="11" t="s">
-        <v>499</v>
       </c>
       <c r="C202" s="7"/>
       <c r="D202" s="7"/>
@@ -9751,10 +9790,10 @@
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="B203" s="8" t="s">
         <v>500</v>
-      </c>
-      <c r="B203" s="8" t="s">
-        <v>501</v>
       </c>
       <c r="C203" s="7"/>
       <c r="D203" s="7"/>
@@ -9782,11 +9821,11 @@
       <c r="Z203" s="7"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="16" t="s">
+      <c r="A204" s="11" t="s">
+        <v>501</v>
+      </c>
+      <c r="B204" s="8" t="s">
         <v>502</v>
-      </c>
-      <c r="B204" s="16" t="s">
-        <v>503</v>
       </c>
       <c r="C204" s="7"/>
       <c r="D204" s="7"/>
@@ -9814,11 +9853,11 @@
       <c r="Z204" s="7"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="11" t="s">
+      <c r="A205" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="B205" s="11" t="s">
         <v>504</v>
-      </c>
-      <c r="B205" s="8" t="s">
-        <v>505</v>
       </c>
       <c r="C205" s="7"/>
       <c r="D205" s="7"/>
@@ -9847,10 +9886,10 @@
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="B206" s="11" t="s">
         <v>506</v>
-      </c>
-      <c r="B206" s="11" t="s">
-        <v>507</v>
       </c>
       <c r="C206" s="7"/>
       <c r="D206" s="7"/>
@@ -9878,11 +9917,11 @@
       <c r="Z206" s="7"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="20" t="s">
+      <c r="A207" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="B207" s="8" t="s">
         <v>508</v>
-      </c>
-      <c r="B207" s="21" t="s">
-        <v>509</v>
       </c>
       <c r="C207" s="7"/>
       <c r="D207" s="7"/>
@@ -9911,10 +9950,10 @@
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="B208" s="11" t="s">
         <v>510</v>
-      </c>
-      <c r="B208" s="8" t="s">
-        <v>511</v>
       </c>
       <c r="C208" s="7"/>
       <c r="D208" s="7"/>
@@ -9943,10 +9982,10 @@
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B209" s="8" t="s">
         <v>512</v>
-      </c>
-      <c r="B209" s="11" t="s">
-        <v>513</v>
       </c>
       <c r="C209" s="7"/>
       <c r="D209" s="7"/>
@@ -9974,11 +10013,11 @@
       <c r="Z209" s="7"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="8" t="s">
+      <c r="A210" s="16" t="s">
+        <v>513</v>
+      </c>
+      <c r="B210" s="16" t="s">
         <v>514</v>
-      </c>
-      <c r="B210" s="8" t="s">
-        <v>515</v>
       </c>
       <c r="C210" s="7"/>
       <c r="D210" s="7"/>
@@ -10006,11 +10045,11 @@
       <c r="Z210" s="7"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="16" t="s">
+      <c r="A211" s="11" t="s">
+        <v>515</v>
+      </c>
+      <c r="B211" s="8" t="s">
         <v>516</v>
-      </c>
-      <c r="B211" s="16" t="s">
-        <v>517</v>
       </c>
       <c r="C211" s="7"/>
       <c r="D211" s="7"/>
@@ -10039,10 +10078,10 @@
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="B212" s="11" t="s">
         <v>518</v>
-      </c>
-      <c r="B212" s="8" t="s">
-        <v>519</v>
       </c>
       <c r="C212" s="7"/>
       <c r="D212" s="7"/>
@@ -10070,11 +10109,11 @@
       <c r="Z212" s="7"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="16" t="s">
+      <c r="A213" s="20" t="s">
+        <v>519</v>
+      </c>
+      <c r="B213" s="21" t="s">
         <v>520</v>
-      </c>
-      <c r="B213" s="16" t="s">
-        <v>521</v>
       </c>
       <c r="C213" s="7"/>
       <c r="D213" s="7"/>
@@ -10103,10 +10142,10 @@
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="B214" s="8" t="s">
         <v>522</v>
-      </c>
-      <c r="B214" s="8" t="s">
-        <v>523</v>
       </c>
       <c r="C214" s="7"/>
       <c r="D214" s="7"/>
@@ -10135,10 +10174,10 @@
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="B215" s="11" t="s">
         <v>524</v>
-      </c>
-      <c r="B215" s="8" t="s">
-        <v>525</v>
       </c>
       <c r="C215" s="7"/>
       <c r="D215" s="7"/>
@@ -10167,10 +10206,10 @@
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="B216" s="8" t="s">
         <v>526</v>
-      </c>
-      <c r="B216" s="11" t="s">
-        <v>527</v>
       </c>
       <c r="C216" s="7"/>
       <c r="D216" s="7"/>
@@ -10198,11 +10237,11 @@
       <c r="Z216" s="7"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="A217" s="11" t="s">
+      <c r="A217" s="16" t="s">
+        <v>527</v>
+      </c>
+      <c r="B217" s="16" t="s">
         <v>528</v>
-      </c>
-      <c r="B217" s="11" t="s">
-        <v>529</v>
       </c>
       <c r="C217" s="7"/>
       <c r="D217" s="7"/>
@@ -10231,10 +10270,10 @@
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="B218" s="8" t="s">
         <v>530</v>
-      </c>
-      <c r="B218" s="11" t="s">
-        <v>531</v>
       </c>
       <c r="C218" s="7"/>
       <c r="D218" s="7"/>
@@ -10263,10 +10302,10 @@
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="16" t="s">
+        <v>531</v>
+      </c>
+      <c r="B219" s="16" t="s">
         <v>532</v>
-      </c>
-      <c r="B219" s="16" t="s">
-        <v>533</v>
       </c>
       <c r="C219" s="7"/>
       <c r="D219" s="7"/>
@@ -10295,10 +10334,10 @@
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="8" t="s">
+        <v>533</v>
+      </c>
+      <c r="B220" s="8" t="s">
         <v>534</v>
-      </c>
-      <c r="B220" s="11" t="s">
-        <v>535</v>
       </c>
       <c r="C220" s="7"/>
       <c r="D220" s="7"/>
@@ -10326,11 +10365,11 @@
       <c r="Z220" s="7"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="16" t="s">
+      <c r="A221" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="B221" s="8" t="s">
         <v>536</v>
-      </c>
-      <c r="B221" s="16" t="s">
-        <v>537</v>
       </c>
       <c r="C221" s="7"/>
       <c r="D221" s="7"/>
@@ -10359,10 +10398,10 @@
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="B222" s="11" t="s">
         <v>538</v>
-      </c>
-      <c r="B222" s="8" t="s">
-        <v>539</v>
       </c>
       <c r="C222" s="7"/>
       <c r="D222" s="7"/>
@@ -10390,11 +10429,11 @@
       <c r="Z222" s="7"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="8" t="s">
+      <c r="A223" s="11" t="s">
+        <v>539</v>
+      </c>
+      <c r="B223" s="11" t="s">
         <v>540</v>
-      </c>
-      <c r="B223" s="11" t="s">
-        <v>541</v>
       </c>
       <c r="C223" s="7"/>
       <c r="D223" s="7"/>
@@ -10423,10 +10462,10 @@
     </row>
     <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="B224" s="11" t="s">
         <v>542</v>
-      </c>
-      <c r="B224" s="8" t="s">
-        <v>543</v>
       </c>
       <c r="C224" s="7"/>
       <c r="D224" s="7"/>
@@ -10454,11 +10493,11 @@
       <c r="Z224" s="7"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="11" t="s">
+      <c r="A225" s="16" t="s">
+        <v>543</v>
+      </c>
+      <c r="B225" s="16" t="s">
         <v>544</v>
-      </c>
-      <c r="B225" s="11" t="s">
-        <v>545</v>
       </c>
       <c r="C225" s="7"/>
       <c r="D225" s="7"/>
@@ -10486,11 +10525,11 @@
       <c r="Z225" s="7"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="8" t="s">
+      <c r="A226" s="16" t="s">
+        <v>545</v>
+      </c>
+      <c r="B226" s="16" t="s">
         <v>546</v>
-      </c>
-      <c r="B226" s="8" t="s">
-        <v>547</v>
       </c>
       <c r="C226" s="7"/>
       <c r="D226" s="7"/>
@@ -10519,10 +10558,10 @@
     </row>
     <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="B227" s="11" t="s">
         <v>548</v>
-      </c>
-      <c r="B227" s="8" t="s">
-        <v>549</v>
       </c>
       <c r="C227" s="7"/>
       <c r="D227" s="7"/>
@@ -10551,10 +10590,10 @@
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="B228" s="16" t="s">
         <v>550</v>
-      </c>
-      <c r="B228" s="16" t="s">
-        <v>551</v>
       </c>
       <c r="C228" s="7"/>
       <c r="D228" s="7"/>
@@ -10583,10 +10622,10 @@
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="B229" s="8" t="s">
         <v>552</v>
-      </c>
-      <c r="B229" s="11" t="s">
-        <v>553</v>
       </c>
       <c r="C229" s="7"/>
       <c r="D229" s="7"/>
@@ -10615,10 +10654,10 @@
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="B230" s="11" t="s">
         <v>554</v>
-      </c>
-      <c r="B230" s="8" t="s">
-        <v>555</v>
       </c>
       <c r="C230" s="7"/>
       <c r="D230" s="7"/>
@@ -10647,10 +10686,10 @@
     </row>
     <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="B231" s="8" t="s">
         <v>556</v>
-      </c>
-      <c r="B231" s="8" t="s">
-        <v>557</v>
       </c>
       <c r="C231" s="7"/>
       <c r="D231" s="7"/>
@@ -10679,10 +10718,10 @@
     </row>
     <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="B232" s="11" t="s">
         <v>558</v>
-      </c>
-      <c r="B232" s="8" t="s">
-        <v>559</v>
       </c>
       <c r="C232" s="7"/>
       <c r="D232" s="7"/>
@@ -10711,10 +10750,10 @@
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="B233" s="8" t="s">
         <v>560</v>
-      </c>
-      <c r="B233" s="8" t="s">
-        <v>561</v>
       </c>
       <c r="C233" s="7"/>
       <c r="D233" s="7"/>
@@ -10743,10 +10782,10 @@
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="B234" s="8" t="s">
         <v>562</v>
-      </c>
-      <c r="B234" s="8" t="s">
-        <v>563</v>
       </c>
       <c r="C234" s="7"/>
       <c r="D234" s="7"/>
@@ -10774,11 +10813,11 @@
       <c r="Z234" s="7"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="8" t="s">
+      <c r="A235" s="16" t="s">
+        <v>563</v>
+      </c>
+      <c r="B235" s="16" t="s">
         <v>564</v>
-      </c>
-      <c r="B235" s="11" t="s">
-        <v>565</v>
       </c>
       <c r="C235" s="7"/>
       <c r="D235" s="7"/>
@@ -10807,10 +10846,10 @@
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="8" t="s">
+        <v>565</v>
+      </c>
+      <c r="B236" s="11" t="s">
         <v>566</v>
-      </c>
-      <c r="B236" s="11" t="s">
-        <v>567</v>
       </c>
       <c r="C236" s="7"/>
       <c r="D236" s="7"/>
@@ -10839,10 +10878,10 @@
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="B237" s="8" t="s">
         <v>568</v>
-      </c>
-      <c r="B237" s="11" t="s">
-        <v>569</v>
       </c>
       <c r="C237" s="7"/>
       <c r="D237" s="7"/>
@@ -10870,11 +10909,11 @@
       <c r="Z237" s="7"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="11" t="s">
+      <c r="A238" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="B238" s="8" t="s">
         <v>570</v>
-      </c>
-      <c r="B238" s="11" t="s">
-        <v>571</v>
       </c>
       <c r="C238" s="7"/>
       <c r="D238" s="7"/>
@@ -10902,11 +10941,11 @@
       <c r="Z238" s="7"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="8" t="s">
+      <c r="A239" s="11" t="s">
+        <v>571</v>
+      </c>
+      <c r="B239" s="8" t="s">
         <v>572</v>
-      </c>
-      <c r="B239" s="11" t="s">
-        <v>573</v>
       </c>
       <c r="C239" s="7"/>
       <c r="D239" s="7"/>
@@ -10935,10 +10974,10 @@
     </row>
     <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="B240" s="8" t="s">
         <v>574</v>
-      </c>
-      <c r="B240" s="8" t="s">
-        <v>575</v>
       </c>
       <c r="C240" s="7"/>
       <c r="D240" s="7"/>
@@ -10967,10 +11006,10 @@
     </row>
     <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="B241" s="11" t="s">
         <v>576</v>
-      </c>
-      <c r="B241" s="11" t="s">
-        <v>577</v>
       </c>
       <c r="C241" s="7"/>
       <c r="D241" s="7"/>
@@ -10999,10 +11038,10 @@
     </row>
     <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="B242" s="11" t="s">
         <v>578</v>
-      </c>
-      <c r="B242" s="11" t="s">
-        <v>579</v>
       </c>
       <c r="C242" s="7"/>
       <c r="D242" s="7"/>
@@ -11031,10 +11070,10 @@
     </row>
     <row r="243" ht="15.75" customHeight="1">
       <c r="A243" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="B243" s="11" t="s">
         <v>580</v>
-      </c>
-      <c r="B243" s="11" t="s">
-        <v>581</v>
       </c>
       <c r="C243" s="7"/>
       <c r="D243" s="7"/>
@@ -11063,10 +11102,10 @@
     </row>
     <row r="244" ht="15.75" customHeight="1">
       <c r="A244" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="B244" s="11" t="s">
         <v>582</v>
-      </c>
-      <c r="B244" s="11" t="s">
-        <v>583</v>
       </c>
       <c r="C244" s="7"/>
       <c r="D244" s="7"/>
@@ -11095,10 +11134,10 @@
     </row>
     <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="B245" s="11" t="s">
         <v>584</v>
-      </c>
-      <c r="B245" s="11" t="s">
-        <v>585</v>
       </c>
       <c r="C245" s="7"/>
       <c r="D245" s="7"/>
@@ -11127,10 +11166,10 @@
     </row>
     <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="B246" s="8" t="s">
         <v>586</v>
-      </c>
-      <c r="B246" s="11" t="s">
-        <v>587</v>
       </c>
       <c r="C246" s="7"/>
       <c r="D246" s="7"/>
@@ -11159,10 +11198,10 @@
     </row>
     <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="B247" s="11" t="s">
         <v>588</v>
-      </c>
-      <c r="B247" s="8" t="s">
-        <v>589</v>
       </c>
       <c r="C247" s="7"/>
       <c r="D247" s="7"/>
@@ -11191,10 +11230,10 @@
     </row>
     <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="8" t="s">
+        <v>589</v>
+      </c>
+      <c r="B248" s="11" t="s">
         <v>590</v>
-      </c>
-      <c r="B248" s="11" t="s">
-        <v>591</v>
       </c>
       <c r="C248" s="7"/>
       <c r="D248" s="7"/>
@@ -11222,11 +11261,11 @@
       <c r="Z248" s="7"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="16" t="s">
+      <c r="A249" s="8" t="s">
+        <v>591</v>
+      </c>
+      <c r="B249" s="11" t="s">
         <v>592</v>
-      </c>
-      <c r="B249" s="16" t="s">
-        <v>593</v>
       </c>
       <c r="C249" s="7"/>
       <c r="D249" s="7"/>
@@ -11254,11 +11293,11 @@
       <c r="Z249" s="7"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="A250" s="8" t="s">
+      <c r="A250" s="11" t="s">
+        <v>593</v>
+      </c>
+      <c r="B250" s="11" t="s">
         <v>594</v>
-      </c>
-      <c r="B250" s="8" t="s">
-        <v>595</v>
       </c>
       <c r="C250" s="7"/>
       <c r="D250" s="7"/>
@@ -11287,10 +11326,10 @@
     </row>
     <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="B251" s="11" t="s">
         <v>596</v>
-      </c>
-      <c r="B251" s="8" t="s">
-        <v>597</v>
       </c>
       <c r="C251" s="7"/>
       <c r="D251" s="7"/>
@@ -11319,10 +11358,10 @@
     </row>
     <row r="252" ht="15.75" customHeight="1">
       <c r="A252" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="B252" s="11" t="s">
         <v>598</v>
-      </c>
-      <c r="B252" s="8" t="s">
-        <v>599</v>
       </c>
       <c r="C252" s="7"/>
       <c r="D252" s="7"/>
@@ -11350,11 +11389,11 @@
       <c r="Z252" s="7"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="A253" s="16" t="s">
+      <c r="A253" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="B253" s="8" t="s">
         <v>600</v>
-      </c>
-      <c r="B253" s="16" t="s">
-        <v>601</v>
       </c>
       <c r="C253" s="7"/>
       <c r="D253" s="7"/>
@@ -11383,10 +11422,10 @@
     </row>
     <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="B254" s="11" t="s">
         <v>602</v>
-      </c>
-      <c r="B254" s="8" t="s">
-        <v>603</v>
       </c>
       <c r="C254" s="7"/>
       <c r="D254" s="7"/>
@@ -11415,10 +11454,10 @@
     </row>
     <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="16" t="s">
+        <v>603</v>
+      </c>
+      <c r="B255" s="16" t="s">
         <v>604</v>
-      </c>
-      <c r="B255" s="16" t="s">
-        <v>605</v>
       </c>
       <c r="C255" s="7"/>
       <c r="D255" s="7"/>
@@ -11446,11 +11485,11 @@
       <c r="Z255" s="7"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="16" t="s">
+      <c r="A256" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="B256" s="8" t="s">
         <v>606</v>
-      </c>
-      <c r="B256" s="16" t="s">
-        <v>607</v>
       </c>
       <c r="C256" s="7"/>
       <c r="D256" s="7"/>
@@ -11478,11 +11517,11 @@
       <c r="Z256" s="7"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="16" t="s">
+      <c r="A257" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="B257" s="8" t="s">
         <v>608</v>
-      </c>
-      <c r="B257" s="16" t="s">
-        <v>609</v>
       </c>
       <c r="C257" s="7"/>
       <c r="D257" s="7"/>
@@ -11511,10 +11550,10 @@
     </row>
     <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="B258" s="8" t="s">
         <v>610</v>
-      </c>
-      <c r="B258" s="11" t="s">
-        <v>611</v>
       </c>
       <c r="C258" s="7"/>
       <c r="D258" s="7"/>
@@ -11542,11 +11581,11 @@
       <c r="Z258" s="7"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="A259" s="8" t="s">
+      <c r="A259" s="16" t="s">
+        <v>611</v>
+      </c>
+      <c r="B259" s="16" t="s">
         <v>612</v>
-      </c>
-      <c r="B259" s="11" t="s">
-        <v>613</v>
       </c>
       <c r="C259" s="7"/>
       <c r="D259" s="7"/>
@@ -11575,10 +11614,10 @@
     </row>
     <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="B260" s="8" t="s">
         <v>614</v>
-      </c>
-      <c r="B260" s="8" t="s">
-        <v>615</v>
       </c>
       <c r="C260" s="7"/>
       <c r="D260" s="7"/>
@@ -11606,11 +11645,11 @@
       <c r="Z260" s="7"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="A261" s="20" t="s">
+      <c r="A261" s="16" t="s">
+        <v>615</v>
+      </c>
+      <c r="B261" s="16" t="s">
         <v>616</v>
-      </c>
-      <c r="B261" s="21" t="s">
-        <v>617</v>
       </c>
       <c r="C261" s="7"/>
       <c r="D261" s="7"/>
@@ -11638,11 +11677,11 @@
       <c r="Z261" s="7"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="A262" s="8" t="s">
+      <c r="A262" s="16" t="s">
+        <v>617</v>
+      </c>
+      <c r="B262" s="16" t="s">
         <v>618</v>
-      </c>
-      <c r="B262" s="11" t="s">
-        <v>619</v>
       </c>
       <c r="C262" s="7"/>
       <c r="D262" s="7"/>
@@ -11670,11 +11709,11 @@
       <c r="Z262" s="7"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="A263" s="8" t="s">
+      <c r="A263" s="16" t="s">
+        <v>619</v>
+      </c>
+      <c r="B263" s="16" t="s">
         <v>620</v>
-      </c>
-      <c r="B263" s="11" t="s">
-        <v>621</v>
       </c>
       <c r="C263" s="7"/>
       <c r="D263" s="7"/>
@@ -11703,10 +11742,10 @@
     </row>
     <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="B264" s="11" t="s">
         <v>622</v>
-      </c>
-      <c r="B264" s="11" t="s">
-        <v>623</v>
       </c>
       <c r="C264" s="7"/>
       <c r="D264" s="7"/>
@@ -11735,10 +11774,10 @@
     </row>
     <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="B265" s="11" t="s">
         <v>624</v>
-      </c>
-      <c r="B265" s="8" t="s">
-        <v>625</v>
       </c>
       <c r="C265" s="7"/>
       <c r="D265" s="7"/>
@@ -11766,11 +11805,11 @@
       <c r="Z265" s="7"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="A266" s="16" t="s">
+      <c r="A266" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="B266" s="8" t="s">
         <v>626</v>
-      </c>
-      <c r="B266" s="16" t="s">
-        <v>627</v>
       </c>
       <c r="C266" s="7"/>
       <c r="D266" s="7"/>
@@ -11798,11 +11837,11 @@
       <c r="Z266" s="7"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="A267" s="16" t="s">
+      <c r="A267" s="20" t="s">
+        <v>627</v>
+      </c>
+      <c r="B267" s="21" t="s">
         <v>628</v>
-      </c>
-      <c r="B267" s="16" t="s">
-        <v>629</v>
       </c>
       <c r="C267" s="7"/>
       <c r="D267" s="7"/>
@@ -11831,10 +11870,10 @@
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="B268" s="11" t="s">
         <v>630</v>
-      </c>
-      <c r="B268" s="11" t="s">
-        <v>631</v>
       </c>
       <c r="C268" s="7"/>
       <c r="D268" s="7"/>
@@ -11863,10 +11902,10 @@
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="B269" s="11" t="s">
         <v>632</v>
-      </c>
-      <c r="B269" s="11" t="s">
-        <v>633</v>
       </c>
       <c r="C269" s="7"/>
       <c r="D269" s="7"/>
@@ -11894,11 +11933,11 @@
       <c r="Z269" s="7"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
-      <c r="A270" s="16" t="s">
+      <c r="A270" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="B270" s="11" t="s">
         <v>634</v>
-      </c>
-      <c r="B270" s="16" t="s">
-        <v>635</v>
       </c>
       <c r="C270" s="7"/>
       <c r="D270" s="7"/>
@@ -11927,10 +11966,10 @@
     </row>
     <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="B271" s="8" t="s">
         <v>636</v>
-      </c>
-      <c r="B271" s="8" t="s">
-        <v>637</v>
       </c>
       <c r="C271" s="7"/>
       <c r="D271" s="7"/>
@@ -11959,10 +11998,10 @@
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="16" t="s">
+        <v>637</v>
+      </c>
+      <c r="B272" s="16" t="s">
         <v>638</v>
-      </c>
-      <c r="B272" s="16" t="s">
-        <v>639</v>
       </c>
       <c r="C272" s="7"/>
       <c r="D272" s="7"/>
@@ -11991,10 +12030,10 @@
     </row>
     <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="16" t="s">
+        <v>639</v>
+      </c>
+      <c r="B273" s="16" t="s">
         <v>640</v>
-      </c>
-      <c r="B273" s="16" t="s">
-        <v>641</v>
       </c>
       <c r="C273" s="7"/>
       <c r="D273" s="7"/>
@@ -12023,10 +12062,10 @@
     </row>
     <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="B274" s="11" t="s">
         <v>642</v>
-      </c>
-      <c r="B274" s="8" t="s">
-        <v>643</v>
       </c>
       <c r="C274" s="7"/>
       <c r="D274" s="7"/>
@@ -12055,10 +12094,10 @@
     </row>
     <row r="275" ht="15.75" customHeight="1">
       <c r="A275" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="B275" s="11" t="s">
         <v>644</v>
-      </c>
-      <c r="B275" s="8" t="s">
-        <v>645</v>
       </c>
       <c r="C275" s="7"/>
       <c r="D275" s="7"/>
@@ -12087,10 +12126,10 @@
     </row>
     <row r="276" ht="15.75" customHeight="1">
       <c r="A276" s="16" t="s">
+        <v>645</v>
+      </c>
+      <c r="B276" s="16" t="s">
         <v>646</v>
-      </c>
-      <c r="B276" s="16" t="s">
-        <v>647</v>
       </c>
       <c r="C276" s="7"/>
       <c r="D276" s="7"/>
@@ -12118,11 +12157,11 @@
       <c r="Z276" s="7"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
-      <c r="A277" s="16" t="s">
+      <c r="A277" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="B277" s="8" t="s">
         <v>648</v>
-      </c>
-      <c r="B277" s="16" t="s">
-        <v>649</v>
       </c>
       <c r="C277" s="7"/>
       <c r="D277" s="7"/>
@@ -12150,11 +12189,11 @@
       <c r="Z277" s="7"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
-      <c r="A278" s="8" t="s">
+      <c r="A278" s="16" t="s">
+        <v>649</v>
+      </c>
+      <c r="B278" s="16" t="s">
         <v>650</v>
-      </c>
-      <c r="B278" s="8" t="s">
-        <v>651</v>
       </c>
       <c r="C278" s="7"/>
       <c r="D278" s="7"/>
@@ -12183,10 +12222,10 @@
     </row>
     <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="16" t="s">
+        <v>651</v>
+      </c>
+      <c r="B279" s="16" t="s">
         <v>652</v>
-      </c>
-      <c r="B279" s="16" t="s">
-        <v>653</v>
       </c>
       <c r="C279" s="7"/>
       <c r="D279" s="7"/>
@@ -12215,10 +12254,10 @@
     </row>
     <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="B280" s="8" t="s">
         <v>654</v>
-      </c>
-      <c r="B280" s="11" t="s">
-        <v>655</v>
       </c>
       <c r="C280" s="7"/>
       <c r="D280" s="7"/>
@@ -12246,11 +12285,11 @@
       <c r="Z280" s="7"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
-      <c r="A281" s="16" t="s">
+      <c r="A281" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="B281" s="8" t="s">
         <v>656</v>
-      </c>
-      <c r="B281" s="11" t="s">
-        <v>657</v>
       </c>
       <c r="C281" s="7"/>
       <c r="D281" s="7"/>
@@ -12278,11 +12317,11 @@
       <c r="Z281" s="7"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="A282" s="8" t="s">
+      <c r="A282" s="16" t="s">
+        <v>657</v>
+      </c>
+      <c r="B282" s="16" t="s">
         <v>658</v>
-      </c>
-      <c r="B282" s="11" t="s">
-        <v>659</v>
       </c>
       <c r="C282" s="7"/>
       <c r="D282" s="7"/>
@@ -12311,10 +12350,10 @@
     </row>
     <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="16" t="s">
+        <v>659</v>
+      </c>
+      <c r="B283" s="16" t="s">
         <v>660</v>
-      </c>
-      <c r="B283" s="16" t="s">
-        <v>661</v>
       </c>
       <c r="C283" s="7"/>
       <c r="D283" s="7"/>
@@ -12343,10 +12382,10 @@
     </row>
     <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="B284" s="8" t="s">
         <v>662</v>
-      </c>
-      <c r="B284" s="11" t="s">
-        <v>663</v>
       </c>
       <c r="C284" s="7"/>
       <c r="D284" s="7"/>
@@ -12374,11 +12413,11 @@
       <c r="Z284" s="7"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="A285" s="8" t="s">
+      <c r="A285" s="16" t="s">
+        <v>663</v>
+      </c>
+      <c r="B285" s="16" t="s">
         <v>664</v>
-      </c>
-      <c r="B285" s="11" t="s">
-        <v>665</v>
       </c>
       <c r="C285" s="7"/>
       <c r="D285" s="7"/>
@@ -12407,10 +12446,10 @@
     </row>
     <row r="286" ht="15.75" customHeight="1">
       <c r="A286" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="B286" s="11" t="s">
         <v>666</v>
-      </c>
-      <c r="B286" s="8" t="s">
-        <v>667</v>
       </c>
       <c r="C286" s="7"/>
       <c r="D286" s="7"/>
@@ -12439,10 +12478,10 @@
     </row>
     <row r="287" ht="15.75" customHeight="1">
       <c r="A287" s="16" t="s">
+        <v>667</v>
+      </c>
+      <c r="B287" s="11" t="s">
         <v>668</v>
-      </c>
-      <c r="B287" s="16" t="s">
-        <v>669</v>
       </c>
       <c r="C287" s="7"/>
       <c r="D287" s="7"/>
@@ -12470,11 +12509,11 @@
       <c r="Z287" s="7"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="A288" s="16" t="s">
+      <c r="A288" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="B288" s="11" t="s">
         <v>670</v>
-      </c>
-      <c r="B288" s="16" t="s">
-        <v>671</v>
       </c>
       <c r="C288" s="7"/>
       <c r="D288" s="7"/>
@@ -12502,11 +12541,11 @@
       <c r="Z288" s="7"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
-      <c r="A289" s="8" t="s">
+      <c r="A289" s="16" t="s">
+        <v>671</v>
+      </c>
+      <c r="B289" s="16" t="s">
         <v>672</v>
-      </c>
-      <c r="B289" s="8" t="s">
-        <v>673</v>
       </c>
       <c r="C289" s="7"/>
       <c r="D289" s="7"/>
@@ -12534,11 +12573,11 @@
       <c r="Z289" s="7"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
-      <c r="A290" s="16" t="s">
+      <c r="A290" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="B290" s="11" t="s">
         <v>674</v>
-      </c>
-      <c r="B290" s="16" t="s">
-        <v>675</v>
       </c>
       <c r="C290" s="7"/>
       <c r="D290" s="7"/>
@@ -12567,10 +12606,10 @@
     </row>
     <row r="291" ht="15.75" customHeight="1">
       <c r="A291" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="B291" s="11" t="s">
         <v>676</v>
-      </c>
-      <c r="B291" s="11" t="s">
-        <v>677</v>
       </c>
       <c r="C291" s="7"/>
       <c r="D291" s="7"/>
@@ -12599,10 +12638,10 @@
     </row>
     <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="B292" s="8" t="s">
         <v>678</v>
-      </c>
-      <c r="B292" s="11" t="s">
-        <v>679</v>
       </c>
       <c r="C292" s="7"/>
       <c r="D292" s="7"/>
@@ -12630,11 +12669,11 @@
       <c r="Z292" s="7"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
-      <c r="A293" s="8" t="s">
+      <c r="A293" s="16" t="s">
+        <v>679</v>
+      </c>
+      <c r="B293" s="16" t="s">
         <v>680</v>
-      </c>
-      <c r="B293" s="8" t="s">
-        <v>681</v>
       </c>
       <c r="C293" s="7"/>
       <c r="D293" s="7"/>
@@ -12662,11 +12701,11 @@
       <c r="Z293" s="7"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
-      <c r="A294" s="8" t="s">
+      <c r="A294" s="16" t="s">
+        <v>681</v>
+      </c>
+      <c r="B294" s="16" t="s">
         <v>682</v>
-      </c>
-      <c r="B294" s="11" t="s">
-        <v>683</v>
       </c>
       <c r="C294" s="7"/>
       <c r="D294" s="7"/>
@@ -12695,10 +12734,10 @@
     </row>
     <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="B295" s="8" t="s">
         <v>684</v>
-      </c>
-      <c r="B295" s="11" t="s">
-        <v>685</v>
       </c>
       <c r="C295" s="7"/>
       <c r="D295" s="7"/>
@@ -12726,11 +12765,11 @@
       <c r="Z295" s="7"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="A296" s="8" t="s">
+      <c r="A296" s="16" t="s">
+        <v>685</v>
+      </c>
+      <c r="B296" s="16" t="s">
         <v>686</v>
-      </c>
-      <c r="B296" s="11" t="s">
-        <v>687</v>
       </c>
       <c r="C296" s="7"/>
       <c r="D296" s="7"/>
@@ -12759,10 +12798,10 @@
     </row>
     <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="8" t="s">
+        <v>687</v>
+      </c>
+      <c r="B297" s="11" t="s">
         <v>688</v>
-      </c>
-      <c r="B297" s="11" t="s">
-        <v>689</v>
       </c>
       <c r="C297" s="7"/>
       <c r="D297" s="7"/>
@@ -12791,10 +12830,10 @@
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="B298" s="11" t="s">
         <v>690</v>
-      </c>
-      <c r="B298" s="8" t="s">
-        <v>691</v>
       </c>
       <c r="C298" s="7"/>
       <c r="D298" s="7"/>
@@ -12822,11 +12861,11 @@
       <c r="Z298" s="7"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
-      <c r="A299" s="20" t="s">
+      <c r="A299" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="B299" s="8" t="s">
         <v>692</v>
-      </c>
-      <c r="B299" s="20" t="s">
-        <v>693</v>
       </c>
       <c r="C299" s="7"/>
       <c r="D299" s="7"/>
@@ -12855,10 +12894,10 @@
     </row>
     <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="8" t="s">
+        <v>693</v>
+      </c>
+      <c r="B300" s="11" t="s">
         <v>694</v>
-      </c>
-      <c r="B300" s="11" t="s">
-        <v>695</v>
       </c>
       <c r="C300" s="7"/>
       <c r="D300" s="7"/>
@@ -12887,10 +12926,10 @@
     </row>
     <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="B301" s="11" t="s">
         <v>696</v>
-      </c>
-      <c r="B301" s="11" t="s">
-        <v>697</v>
       </c>
       <c r="C301" s="7"/>
       <c r="D301" s="7"/>
@@ -12919,10 +12958,10 @@
     </row>
     <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="B302" s="11" t="s">
         <v>698</v>
-      </c>
-      <c r="B302" s="11" t="s">
-        <v>699</v>
       </c>
       <c r="C302" s="7"/>
       <c r="D302" s="7"/>
@@ -12950,11 +12989,11 @@
       <c r="Z302" s="7"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="A303" s="16" t="s">
+      <c r="A303" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="B303" s="11" t="s">
         <v>700</v>
-      </c>
-      <c r="B303" s="16" t="s">
-        <v>701</v>
       </c>
       <c r="C303" s="7"/>
       <c r="D303" s="7"/>
@@ -12983,10 +13022,10 @@
     </row>
     <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="B304" s="8" t="s">
         <v>702</v>
-      </c>
-      <c r="B304" s="11" t="s">
-        <v>703</v>
       </c>
       <c r="C304" s="7"/>
       <c r="D304" s="7"/>
@@ -13014,11 +13053,11 @@
       <c r="Z304" s="7"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="A305" s="8" t="s">
+      <c r="A305" s="20" t="s">
+        <v>703</v>
+      </c>
+      <c r="B305" s="20" t="s">
         <v>704</v>
-      </c>
-      <c r="B305" s="8" t="s">
-        <v>705</v>
       </c>
       <c r="C305" s="7"/>
       <c r="D305" s="7"/>
@@ -13047,10 +13086,10 @@
     </row>
     <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="8" t="s">
+        <v>705</v>
+      </c>
+      <c r="B306" s="11" t="s">
         <v>706</v>
-      </c>
-      <c r="B306" s="11" t="s">
-        <v>707</v>
       </c>
       <c r="C306" s="7"/>
       <c r="D306" s="7"/>
@@ -13079,10 +13118,10 @@
     </row>
     <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="B307" s="11" t="s">
         <v>708</v>
-      </c>
-      <c r="B307" s="11" t="s">
-        <v>709</v>
       </c>
       <c r="C307" s="7"/>
       <c r="D307" s="7"/>
@@ -13111,10 +13150,10 @@
     </row>
     <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="8" t="s">
+        <v>709</v>
+      </c>
+      <c r="B308" s="11" t="s">
         <v>710</v>
-      </c>
-      <c r="B308" s="11" t="s">
-        <v>711</v>
       </c>
       <c r="C308" s="7"/>
       <c r="D308" s="7"/>
@@ -13142,11 +13181,11 @@
       <c r="Z308" s="7"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="A309" s="8" t="s">
+      <c r="A309" s="16" t="s">
+        <v>711</v>
+      </c>
+      <c r="B309" s="16" t="s">
         <v>712</v>
-      </c>
-      <c r="B309" s="11" t="s">
-        <v>713</v>
       </c>
       <c r="C309" s="7"/>
       <c r="D309" s="7"/>
@@ -13175,10 +13214,10 @@
     </row>
     <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="B310" s="11" t="s">
         <v>714</v>
-      </c>
-      <c r="B310" s="11" t="s">
-        <v>715</v>
       </c>
       <c r="C310" s="7"/>
       <c r="D310" s="7"/>
@@ -13206,11 +13245,11 @@
       <c r="Z310" s="7"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="A311" s="20" t="s">
+      <c r="A311" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="B311" s="8" t="s">
         <v>716</v>
-      </c>
-      <c r="B311" s="21" t="s">
-        <v>717</v>
       </c>
       <c r="C311" s="7"/>
       <c r="D311" s="7"/>
@@ -13239,10 +13278,10 @@
     </row>
     <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="8" t="s">
+        <v>717</v>
+      </c>
+      <c r="B312" s="11" t="s">
         <v>718</v>
-      </c>
-      <c r="B312" s="11" t="s">
-        <v>719</v>
       </c>
       <c r="C312" s="7"/>
       <c r="D312" s="7"/>
@@ -13270,11 +13309,11 @@
       <c r="Z312" s="7"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="A313" s="16" t="s">
+      <c r="A313" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="B313" s="11" t="s">
         <v>720</v>
-      </c>
-      <c r="B313" s="16" t="s">
-        <v>721</v>
       </c>
       <c r="C313" s="7"/>
       <c r="D313" s="7"/>
@@ -13302,11 +13341,11 @@
       <c r="Z313" s="7"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="A314" s="16" t="s">
+      <c r="A314" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="B314" s="11" t="s">
         <v>722</v>
-      </c>
-      <c r="B314" s="16" t="s">
-        <v>723</v>
       </c>
       <c r="C314" s="7"/>
       <c r="D314" s="7"/>
@@ -13335,10 +13374,10 @@
     </row>
     <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="B315" s="11" t="s">
         <v>724</v>
-      </c>
-      <c r="B315" s="8" t="s">
-        <v>725</v>
       </c>
       <c r="C315" s="7"/>
       <c r="D315" s="7"/>
@@ -13366,11 +13405,11 @@
       <c r="Z315" s="7"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="A316" s="16" t="s">
+      <c r="A316" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="B316" s="11" t="s">
         <v>726</v>
-      </c>
-      <c r="B316" s="16" t="s">
-        <v>727</v>
       </c>
       <c r="C316" s="7"/>
       <c r="D316" s="7"/>
@@ -13398,11 +13437,11 @@
       <c r="Z316" s="7"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="A317" s="23" t="s">
+      <c r="A317" s="20" t="s">
+        <v>727</v>
+      </c>
+      <c r="B317" s="21" t="s">
         <v>728</v>
-      </c>
-      <c r="B317" s="24" t="s">
-        <v>729</v>
       </c>
       <c r="C317" s="7"/>
       <c r="D317" s="7"/>
@@ -13430,11 +13469,11 @@
       <c r="Z317" s="7"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="A318" s="16" t="s">
+      <c r="A318" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="B318" s="11" t="s">
         <v>730</v>
-      </c>
-      <c r="B318" s="16" t="s">
-        <v>731</v>
       </c>
       <c r="C318" s="7"/>
       <c r="D318" s="7"/>
@@ -13462,11 +13501,11 @@
       <c r="Z318" s="7"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
-      <c r="A319" s="8" t="s">
+      <c r="A319" s="16" t="s">
+        <v>731</v>
+      </c>
+      <c r="B319" s="16" t="s">
         <v>732</v>
-      </c>
-      <c r="B319" s="8" t="s">
-        <v>733</v>
       </c>
       <c r="C319" s="7"/>
       <c r="D319" s="7"/>
@@ -13494,11 +13533,11 @@
       <c r="Z319" s="7"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="A320" s="8" t="s">
+      <c r="A320" s="16" t="s">
+        <v>733</v>
+      </c>
+      <c r="B320" s="16" t="s">
         <v>734</v>
-      </c>
-      <c r="B320" s="8" t="s">
-        <v>735</v>
       </c>
       <c r="C320" s="7"/>
       <c r="D320" s="7"/>
@@ -13527,10 +13566,10 @@
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="B321" s="8" t="s">
         <v>736</v>
-      </c>
-      <c r="B321" s="8" t="s">
-        <v>737</v>
       </c>
       <c r="C321" s="7"/>
       <c r="D321" s="7"/>
@@ -13558,11 +13597,11 @@
       <c r="Z321" s="7"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="A322" s="8" t="s">
+      <c r="A322" s="16" t="s">
+        <v>737</v>
+      </c>
+      <c r="B322" s="16" t="s">
         <v>738</v>
-      </c>
-      <c r="B322" s="11" t="s">
-        <v>739</v>
       </c>
       <c r="C322" s="7"/>
       <c r="D322" s="7"/>
@@ -13590,11 +13629,11 @@
       <c r="Z322" s="7"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="A323" s="8" t="s">
+      <c r="A323" s="23" t="s">
+        <v>739</v>
+      </c>
+      <c r="B323" s="24" t="s">
         <v>740</v>
-      </c>
-      <c r="B323" s="8" t="s">
-        <v>741</v>
       </c>
       <c r="C323" s="7"/>
       <c r="D323" s="7"/>
@@ -13623,10 +13662,10 @@
     </row>
     <row r="324" ht="15.75" customHeight="1">
       <c r="A324" s="16" t="s">
+        <v>741</v>
+      </c>
+      <c r="B324" s="16" t="s">
         <v>742</v>
-      </c>
-      <c r="B324" s="16" t="s">
-        <v>743</v>
       </c>
       <c r="C324" s="7"/>
       <c r="D324" s="7"/>
@@ -13655,10 +13694,10 @@
     </row>
     <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="B325" s="8" t="s">
         <v>744</v>
-      </c>
-      <c r="B325" s="11" t="s">
-        <v>745</v>
       </c>
       <c r="C325" s="7"/>
       <c r="D325" s="7"/>
@@ -13687,10 +13726,10 @@
     </row>
     <row r="326" ht="15.75" customHeight="1">
       <c r="A326" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="B326" s="8" t="s">
         <v>746</v>
-      </c>
-      <c r="B326" s="8" t="s">
-        <v>747</v>
       </c>
       <c r="C326" s="7"/>
       <c r="D326" s="7"/>
@@ -13719,10 +13758,10 @@
     </row>
     <row r="327" ht="15.75" customHeight="1">
       <c r="A327" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="B327" s="8" t="s">
         <v>748</v>
-      </c>
-      <c r="B327" s="11" t="s">
-        <v>749</v>
       </c>
       <c r="C327" s="7"/>
       <c r="D327" s="7"/>
@@ -13751,10 +13790,10 @@
     </row>
     <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="8" t="s">
+        <v>749</v>
+      </c>
+      <c r="B328" s="11" t="s">
         <v>750</v>
-      </c>
-      <c r="B328" s="11" t="s">
-        <v>751</v>
       </c>
       <c r="C328" s="7"/>
       <c r="D328" s="7"/>
@@ -13783,10 +13822,10 @@
     </row>
     <row r="329" ht="15.75" customHeight="1">
       <c r="A329" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="B329" s="8" t="s">
         <v>752</v>
-      </c>
-      <c r="B329" s="8" t="s">
-        <v>753</v>
       </c>
       <c r="C329" s="7"/>
       <c r="D329" s="7"/>
@@ -13815,10 +13854,10 @@
     </row>
     <row r="330" ht="15.75" customHeight="1">
       <c r="A330" s="16" t="s">
+        <v>753</v>
+      </c>
+      <c r="B330" s="16" t="s">
         <v>754</v>
-      </c>
-      <c r="B330" s="16" t="s">
-        <v>755</v>
       </c>
       <c r="C330" s="7"/>
       <c r="D330" s="7"/>
@@ -13847,10 +13886,10 @@
     </row>
     <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="8" t="s">
+        <v>755</v>
+      </c>
+      <c r="B331" s="11" t="s">
         <v>756</v>
-      </c>
-      <c r="B331" s="11" t="s">
-        <v>757</v>
       </c>
       <c r="C331" s="7"/>
       <c r="D331" s="7"/>
@@ -13879,10 +13918,10 @@
     </row>
     <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="B332" s="8" t="s">
         <v>758</v>
-      </c>
-      <c r="B332" s="11" t="s">
-        <v>759</v>
       </c>
       <c r="C332" s="7"/>
       <c r="D332" s="7"/>
@@ -13910,11 +13949,11 @@
       <c r="Z332" s="7"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="A333" s="20" t="s">
+      <c r="A333" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="B333" s="11" t="s">
         <v>760</v>
-      </c>
-      <c r="B333" s="21" t="s">
-        <v>761</v>
       </c>
       <c r="C333" s="7"/>
       <c r="D333" s="7"/>
@@ -13943,10 +13982,10 @@
     </row>
     <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="8" t="s">
+        <v>761</v>
+      </c>
+      <c r="B334" s="11" t="s">
         <v>762</v>
-      </c>
-      <c r="B334" s="11" t="s">
-        <v>763</v>
       </c>
       <c r="C334" s="7"/>
       <c r="D334" s="7"/>
@@ -13975,10 +14014,10 @@
     </row>
     <row r="335" ht="15.75" customHeight="1">
       <c r="A335" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="B335" s="8" t="s">
         <v>764</v>
-      </c>
-      <c r="B335" s="11" t="s">
-        <v>765</v>
       </c>
       <c r="C335" s="7"/>
       <c r="D335" s="7"/>
@@ -14006,11 +14045,11 @@
       <c r="Z335" s="7"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="A336" s="8" t="s">
+      <c r="A336" s="16" t="s">
+        <v>765</v>
+      </c>
+      <c r="B336" s="16" t="s">
         <v>766</v>
-      </c>
-      <c r="B336" s="8" t="s">
-        <v>767</v>
       </c>
       <c r="C336" s="7"/>
       <c r="D336" s="7"/>
@@ -14039,10 +14078,10 @@
     </row>
     <row r="337" ht="15.75" customHeight="1">
       <c r="A337" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="B337" s="11" t="s">
         <v>768</v>
-      </c>
-      <c r="B337" s="11" t="s">
-        <v>769</v>
       </c>
       <c r="C337" s="7"/>
       <c r="D337" s="7"/>
@@ -14071,10 +14110,10 @@
     </row>
     <row r="338" ht="15.75" customHeight="1">
       <c r="A338" s="8" t="s">
+        <v>769</v>
+      </c>
+      <c r="B338" s="11" t="s">
         <v>770</v>
-      </c>
-      <c r="B338" s="8" t="s">
-        <v>771</v>
       </c>
       <c r="C338" s="7"/>
       <c r="D338" s="7"/>
@@ -14102,11 +14141,11 @@
       <c r="Z338" s="7"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="A339" s="8" t="s">
+      <c r="A339" s="20" t="s">
+        <v>771</v>
+      </c>
+      <c r="B339" s="21" t="s">
         <v>772</v>
-      </c>
-      <c r="B339" s="11" t="s">
-        <v>773</v>
       </c>
       <c r="C339" s="7"/>
       <c r="D339" s="7"/>
@@ -14135,10 +14174,10 @@
     </row>
     <row r="340" ht="15.75" customHeight="1">
       <c r="A340" s="8" t="s">
+        <v>773</v>
+      </c>
+      <c r="B340" s="11" t="s">
         <v>774</v>
-      </c>
-      <c r="B340" s="8" t="s">
-        <v>775</v>
       </c>
       <c r="C340" s="7"/>
       <c r="D340" s="7"/>
@@ -14167,10 +14206,10 @@
     </row>
     <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="8" t="s">
+        <v>775</v>
+      </c>
+      <c r="B341" s="11" t="s">
         <v>776</v>
-      </c>
-      <c r="B341" s="8" t="s">
-        <v>777</v>
       </c>
       <c r="C341" s="7"/>
       <c r="D341" s="7"/>
@@ -14199,10 +14238,10 @@
     </row>
     <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="8" t="s">
+        <v>777</v>
+      </c>
+      <c r="B342" s="8" t="s">
         <v>778</v>
-      </c>
-      <c r="B342" s="11" t="s">
-        <v>779</v>
       </c>
       <c r="C342" s="7"/>
       <c r="D342" s="7"/>
@@ -14231,10 +14270,10 @@
     </row>
     <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="8" t="s">
+        <v>779</v>
+      </c>
+      <c r="B343" s="11" t="s">
         <v>780</v>
-      </c>
-      <c r="B343" s="11" t="s">
-        <v>781</v>
       </c>
       <c r="C343" s="7"/>
       <c r="D343" s="7"/>
@@ -14263,10 +14302,10 @@
     </row>
     <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="8" t="s">
+        <v>781</v>
+      </c>
+      <c r="B344" s="8" t="s">
         <v>782</v>
-      </c>
-      <c r="B344" s="8" t="s">
-        <v>783</v>
       </c>
       <c r="C344" s="7"/>
       <c r="D344" s="7"/>
@@ -14295,10 +14334,10 @@
     </row>
     <row r="345" ht="15.75" customHeight="1">
       <c r="A345" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="B345" s="11" t="s">
         <v>784</v>
-      </c>
-      <c r="B345" s="11" t="s">
-        <v>785</v>
       </c>
       <c r="C345" s="7"/>
       <c r="D345" s="7"/>
@@ -14327,10 +14366,10 @@
     </row>
     <row r="346" ht="15.75" customHeight="1">
       <c r="A346" s="8" t="s">
+        <v>785</v>
+      </c>
+      <c r="B346" s="8" t="s">
         <v>786</v>
-      </c>
-      <c r="B346" s="11" t="s">
-        <v>787</v>
       </c>
       <c r="C346" s="7"/>
       <c r="D346" s="7"/>
@@ -14359,10 +14398,10 @@
     </row>
     <row r="347" ht="15.75" customHeight="1">
       <c r="A347" s="8" t="s">
+        <v>787</v>
+      </c>
+      <c r="B347" s="8" t="s">
         <v>788</v>
-      </c>
-      <c r="B347" s="11" t="s">
-        <v>789</v>
       </c>
       <c r="C347" s="7"/>
       <c r="D347" s="7"/>
@@ -14391,10 +14430,10 @@
     </row>
     <row r="348" ht="15.75" customHeight="1">
       <c r="A348" s="8" t="s">
+        <v>789</v>
+      </c>
+      <c r="B348" s="11" t="s">
         <v>790</v>
-      </c>
-      <c r="B348" s="8" t="s">
-        <v>791</v>
       </c>
       <c r="C348" s="7"/>
       <c r="D348" s="7"/>
@@ -14423,10 +14462,10 @@
     </row>
     <row r="349" ht="15.75" customHeight="1">
       <c r="A349" s="8" t="s">
+        <v>791</v>
+      </c>
+      <c r="B349" s="11" t="s">
         <v>792</v>
-      </c>
-      <c r="B349" s="11" t="s">
-        <v>793</v>
       </c>
       <c r="C349" s="7"/>
       <c r="D349" s="7"/>
@@ -14455,10 +14494,10 @@
     </row>
     <row r="350" ht="15.75" customHeight="1">
       <c r="A350" s="8" t="s">
+        <v>793</v>
+      </c>
+      <c r="B350" s="8" t="s">
         <v>794</v>
-      </c>
-      <c r="B350" s="8" t="s">
-        <v>795</v>
       </c>
       <c r="C350" s="7"/>
       <c r="D350" s="7"/>
@@ -14487,10 +14526,10 @@
     </row>
     <row r="351" ht="15.75" customHeight="1">
       <c r="A351" s="8" t="s">
+        <v>795</v>
+      </c>
+      <c r="B351" s="11" t="s">
         <v>796</v>
-      </c>
-      <c r="B351" s="11" t="s">
-        <v>797</v>
       </c>
       <c r="C351" s="7"/>
       <c r="D351" s="7"/>
@@ -14519,10 +14558,10 @@
     </row>
     <row r="352" ht="15.75" customHeight="1">
       <c r="A352" s="8" t="s">
+        <v>797</v>
+      </c>
+      <c r="B352" s="11" t="s">
         <v>798</v>
-      </c>
-      <c r="B352" s="11" t="s">
-        <v>799</v>
       </c>
       <c r="C352" s="7"/>
       <c r="D352" s="7"/>
@@ -14550,11 +14589,11 @@
       <c r="Z352" s="7"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="A353" s="8" t="s">
+      <c r="A353" s="16" t="s">
+        <v>799</v>
+      </c>
+      <c r="B353" s="16" t="s">
         <v>800</v>
-      </c>
-      <c r="B353" s="11" t="s">
-        <v>801</v>
       </c>
       <c r="C353" s="7"/>
       <c r="D353" s="7"/>
@@ -14583,10 +14622,10 @@
     </row>
     <row r="354" ht="15.75" customHeight="1">
       <c r="A354" s="8" t="s">
+        <v>801</v>
+      </c>
+      <c r="B354" s="11" t="s">
         <v>802</v>
-      </c>
-      <c r="B354" s="11" t="s">
-        <v>803</v>
       </c>
       <c r="C354" s="7"/>
       <c r="D354" s="7"/>
@@ -14615,10 +14654,10 @@
     </row>
     <row r="355" ht="15.75" customHeight="1">
       <c r="A355" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="B355" s="8" t="s">
         <v>804</v>
-      </c>
-      <c r="B355" s="11" t="s">
-        <v>805</v>
       </c>
       <c r="C355" s="7"/>
       <c r="D355" s="7"/>
@@ -14646,11 +14685,11 @@
       <c r="Z355" s="7"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="A356" s="16" t="s">
+      <c r="A356" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="B356" s="11" t="s">
         <v>806</v>
-      </c>
-      <c r="B356" s="16" t="s">
-        <v>807</v>
       </c>
       <c r="C356" s="7"/>
       <c r="D356" s="7"/>
@@ -14678,11 +14717,11 @@
       <c r="Z356" s="7"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="A357" s="16" t="s">
+      <c r="A357" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="B357" s="8" t="s">
         <v>808</v>
-      </c>
-      <c r="B357" s="16" t="s">
-        <v>809</v>
       </c>
       <c r="C357" s="7"/>
       <c r="D357" s="7"/>
@@ -14711,10 +14750,10 @@
     </row>
     <row r="358" ht="15.75" customHeight="1">
       <c r="A358" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="B358" s="11" t="s">
         <v>810</v>
-      </c>
-      <c r="B358" s="11" t="s">
-        <v>811</v>
       </c>
       <c r="C358" s="7"/>
       <c r="D358" s="7"/>
@@ -14743,10 +14782,10 @@
     </row>
     <row r="359" ht="15.75" customHeight="1">
       <c r="A359" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="B359" s="11" t="s">
         <v>812</v>
-      </c>
-      <c r="B359" s="8" t="s">
-        <v>813</v>
       </c>
       <c r="C359" s="7"/>
       <c r="D359" s="7"/>
@@ -14774,11 +14813,11 @@
       <c r="Z359" s="7"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="A360" s="16" t="s">
+      <c r="A360" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="B360" s="11" t="s">
         <v>814</v>
-      </c>
-      <c r="B360" s="16" t="s">
-        <v>815</v>
       </c>
       <c r="C360" s="7"/>
       <c r="D360" s="7"/>
@@ -14806,11 +14845,11 @@
       <c r="Z360" s="7"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="11" t="s">
+      <c r="A361" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="B361" s="11" t="s">
         <v>816</v>
-      </c>
-      <c r="B361" s="8" t="s">
-        <v>817</v>
       </c>
       <c r="C361" s="7"/>
       <c r="D361" s="7"/>
@@ -14839,10 +14878,10 @@
     </row>
     <row r="362" ht="15.75" customHeight="1">
       <c r="A362" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="B362" s="11" t="s">
         <v>818</v>
-      </c>
-      <c r="B362" s="8" t="s">
-        <v>819</v>
       </c>
       <c r="C362" s="7"/>
       <c r="D362" s="7"/>
@@ -14871,10 +14910,10 @@
     </row>
     <row r="363" ht="15.75" customHeight="1">
       <c r="A363" s="16" t="s">
+        <v>819</v>
+      </c>
+      <c r="B363" s="16" t="s">
         <v>820</v>
-      </c>
-      <c r="B363" s="16" t="s">
-        <v>821</v>
       </c>
       <c r="C363" s="7"/>
       <c r="D363" s="7"/>
@@ -14902,11 +14941,11 @@
       <c r="Z363" s="7"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="A364" s="11" t="s">
+      <c r="A364" s="16" t="s">
+        <v>821</v>
+      </c>
+      <c r="B364" s="16" t="s">
         <v>822</v>
-      </c>
-      <c r="B364" s="11" t="s">
-        <v>823</v>
       </c>
       <c r="C364" s="7"/>
       <c r="D364" s="7"/>
@@ -14934,11 +14973,11 @@
       <c r="Z364" s="7"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="A365" s="16" t="s">
+      <c r="A365" s="8" t="s">
+        <v>823</v>
+      </c>
+      <c r="B365" s="11" t="s">
         <v>824</v>
-      </c>
-      <c r="B365" s="11" t="s">
-        <v>825</v>
       </c>
       <c r="C365" s="7"/>
       <c r="D365" s="7"/>
@@ -14967,10 +15006,10 @@
     </row>
     <row r="366" ht="15.75" customHeight="1">
       <c r="A366" s="8" t="s">
+        <v>825</v>
+      </c>
+      <c r="B366" s="8" t="s">
         <v>826</v>
-      </c>
-      <c r="B366" s="11" t="s">
-        <v>827</v>
       </c>
       <c r="C366" s="7"/>
       <c r="D366" s="7"/>
@@ -14998,11 +15037,11 @@
       <c r="Z366" s="7"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="A367" s="11" t="s">
+      <c r="A367" s="16" t="s">
+        <v>827</v>
+      </c>
+      <c r="B367" s="16" t="s">
         <v>828</v>
-      </c>
-      <c r="B367" s="11" t="s">
-        <v>829</v>
       </c>
       <c r="C367" s="7"/>
       <c r="D367" s="7"/>
@@ -15030,11 +15069,11 @@
       <c r="Z367" s="7"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="A368" s="8" t="s">
+      <c r="A368" s="11" t="s">
+        <v>829</v>
+      </c>
+      <c r="B368" s="8" t="s">
         <v>830</v>
-      </c>
-      <c r="B368" s="11" t="s">
-        <v>831</v>
       </c>
       <c r="C368" s="7"/>
       <c r="D368" s="7"/>
@@ -15062,11 +15101,11 @@
       <c r="Z368" s="7"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="A369" s="20" t="s">
+      <c r="A369" s="8" t="s">
+        <v>831</v>
+      </c>
+      <c r="B369" s="8" t="s">
         <v>832</v>
-      </c>
-      <c r="B369" s="21" t="s">
-        <v>833</v>
       </c>
       <c r="C369" s="7"/>
       <c r="D369" s="7"/>
@@ -15094,11 +15133,11 @@
       <c r="Z369" s="7"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="A370" s="8" t="s">
+      <c r="A370" s="16" t="s">
+        <v>833</v>
+      </c>
+      <c r="B370" s="16" t="s">
         <v>834</v>
-      </c>
-      <c r="B370" s="8" t="s">
-        <v>835</v>
       </c>
       <c r="C370" s="7"/>
       <c r="D370" s="7"/>
@@ -15126,11 +15165,11 @@
       <c r="Z370" s="7"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="A371" s="8" t="s">
+      <c r="A371" s="11" t="s">
+        <v>835</v>
+      </c>
+      <c r="B371" s="11" t="s">
         <v>836</v>
-      </c>
-      <c r="B371" s="11" t="s">
-        <v>837</v>
       </c>
       <c r="C371" s="7"/>
       <c r="D371" s="7"/>
@@ -15158,11 +15197,11 @@
       <c r="Z371" s="7"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="A372" s="8" t="s">
+      <c r="A372" s="16" t="s">
+        <v>837</v>
+      </c>
+      <c r="B372" s="11" t="s">
         <v>838</v>
-      </c>
-      <c r="B372" s="8" t="s">
-        <v>839</v>
       </c>
       <c r="C372" s="7"/>
       <c r="D372" s="7"/>
@@ -15191,10 +15230,10 @@
     </row>
     <row r="373" ht="15.75" customHeight="1">
       <c r="A373" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="B373" s="11" t="s">
         <v>840</v>
-      </c>
-      <c r="B373" s="11" t="s">
-        <v>841</v>
       </c>
       <c r="C373" s="7"/>
       <c r="D373" s="7"/>
@@ -15223,10 +15262,10 @@
     </row>
     <row r="374" ht="15.75" customHeight="1">
       <c r="A374" s="11" t="s">
+        <v>841</v>
+      </c>
+      <c r="B374" s="11" t="s">
         <v>842</v>
-      </c>
-      <c r="B374" s="11" t="s">
-        <v>843</v>
       </c>
       <c r="C374" s="7"/>
       <c r="D374" s="7"/>
@@ -15255,10 +15294,10 @@
     </row>
     <row r="375" ht="15.75" customHeight="1">
       <c r="A375" s="8" t="s">
+        <v>843</v>
+      </c>
+      <c r="B375" s="11" t="s">
         <v>844</v>
-      </c>
-      <c r="B375" s="8" t="s">
-        <v>845</v>
       </c>
       <c r="C375" s="7"/>
       <c r="D375" s="7"/>
@@ -15286,11 +15325,11 @@
       <c r="Z375" s="7"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="A376" s="8" t="s">
+      <c r="A376" s="20" t="s">
+        <v>845</v>
+      </c>
+      <c r="B376" s="21" t="s">
         <v>846</v>
-      </c>
-      <c r="B376" s="8" t="s">
-        <v>847</v>
       </c>
       <c r="C376" s="7"/>
       <c r="D376" s="7"/>
@@ -15319,10 +15358,10 @@
     </row>
     <row r="377" ht="15.75" customHeight="1">
       <c r="A377" s="8" t="s">
+        <v>847</v>
+      </c>
+      <c r="B377" s="8" t="s">
         <v>848</v>
-      </c>
-      <c r="B377" s="8" t="s">
-        <v>849</v>
       </c>
       <c r="C377" s="7"/>
       <c r="D377" s="7"/>
@@ -15351,10 +15390,10 @@
     </row>
     <row r="378" ht="15.75" customHeight="1">
       <c r="A378" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="B378" s="11" t="s">
         <v>850</v>
-      </c>
-      <c r="B378" s="11" t="s">
-        <v>851</v>
       </c>
       <c r="C378" s="7"/>
       <c r="D378" s="7"/>
@@ -15383,10 +15422,10 @@
     </row>
     <row r="379" ht="15.75" customHeight="1">
       <c r="A379" s="8" t="s">
+        <v>851</v>
+      </c>
+      <c r="B379" s="8" t="s">
         <v>852</v>
-      </c>
-      <c r="B379" s="8" t="s">
-        <v>853</v>
       </c>
       <c r="C379" s="7"/>
       <c r="D379" s="7"/>
@@ -15414,11 +15453,11 @@
       <c r="Z379" s="7"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="A380" s="16" t="s">
+      <c r="A380" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="B380" s="11" t="s">
         <v>854</v>
-      </c>
-      <c r="B380" s="16" t="s">
-        <v>855</v>
       </c>
       <c r="C380" s="7"/>
       <c r="D380" s="7"/>
@@ -15446,11 +15485,11 @@
       <c r="Z380" s="7"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="A381" s="8" t="s">
+      <c r="A381" s="11" t="s">
+        <v>855</v>
+      </c>
+      <c r="B381" s="11" t="s">
         <v>856</v>
-      </c>
-      <c r="B381" s="11" t="s">
-        <v>857</v>
       </c>
       <c r="C381" s="7"/>
       <c r="D381" s="7"/>
@@ -15478,11 +15517,11 @@
       <c r="Z381" s="7"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="A382" s="16" t="s">
+      <c r="A382" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="B382" s="8" t="s">
         <v>858</v>
-      </c>
-      <c r="B382" s="16" t="s">
-        <v>859</v>
       </c>
       <c r="C382" s="7"/>
       <c r="D382" s="7"/>
@@ -15510,11 +15549,11 @@
       <c r="Z382" s="7"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="A383" s="16" t="s">
+      <c r="A383" s="8" t="s">
+        <v>859</v>
+      </c>
+      <c r="B383" s="8" t="s">
         <v>860</v>
-      </c>
-      <c r="B383" s="16" t="s">
-        <v>861</v>
       </c>
       <c r="C383" s="7"/>
       <c r="D383" s="7"/>
@@ -15543,10 +15582,10 @@
     </row>
     <row r="384" ht="15.75" customHeight="1">
       <c r="A384" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="B384" s="8" t="s">
         <v>862</v>
-      </c>
-      <c r="B384" s="11" t="s">
-        <v>863</v>
       </c>
       <c r="C384" s="7"/>
       <c r="D384" s="7"/>
@@ -15574,11 +15613,11 @@
       <c r="Z384" s="7"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="A385" s="16" t="s">
+      <c r="A385" s="8" t="s">
+        <v>863</v>
+      </c>
+      <c r="B385" s="11" t="s">
         <v>864</v>
-      </c>
-      <c r="B385" s="16" t="s">
-        <v>865</v>
       </c>
       <c r="C385" s="7"/>
       <c r="D385" s="7"/>
@@ -15606,11 +15645,11 @@
       <c r="Z385" s="7"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="A386" s="16" t="s">
+      <c r="A386" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="B386" s="8" t="s">
         <v>866</v>
-      </c>
-      <c r="B386" s="16" t="s">
-        <v>867</v>
       </c>
       <c r="C386" s="7"/>
       <c r="D386" s="7"/>
@@ -15638,11 +15677,11 @@
       <c r="Z386" s="7"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
-      <c r="A387" s="8" t="s">
+      <c r="A387" s="16" t="s">
+        <v>867</v>
+      </c>
+      <c r="B387" s="16" t="s">
         <v>868</v>
-      </c>
-      <c r="B387" s="8" t="s">
-        <v>869</v>
       </c>
       <c r="C387" s="7"/>
       <c r="D387" s="7"/>
@@ -15671,10 +15710,10 @@
     </row>
     <row r="388" ht="15.75" customHeight="1">
       <c r="A388" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="B388" s="11" t="s">
         <v>870</v>
-      </c>
-      <c r="B388" s="8" t="s">
-        <v>871</v>
       </c>
       <c r="C388" s="7"/>
       <c r="D388" s="7"/>
@@ -15702,11 +15741,11 @@
       <c r="Z388" s="7"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="A389" s="11" t="s">
+      <c r="A389" s="16" t="s">
+        <v>871</v>
+      </c>
+      <c r="B389" s="16" t="s">
         <v>872</v>
-      </c>
-      <c r="B389" s="11" t="s">
-        <v>873</v>
       </c>
       <c r="C389" s="7"/>
       <c r="D389" s="7"/>
@@ -15734,11 +15773,11 @@
       <c r="Z389" s="7"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="A390" s="8" t="s">
+      <c r="A390" s="16" t="s">
+        <v>873</v>
+      </c>
+      <c r="B390" s="16" t="s">
         <v>874</v>
-      </c>
-      <c r="B390" s="8" t="s">
-        <v>875</v>
       </c>
       <c r="C390" s="7"/>
       <c r="D390" s="7"/>
@@ -15766,11 +15805,11 @@
       <c r="Z390" s="7"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="A391" s="21" t="s">
+      <c r="A391" s="8" t="s">
+        <v>875</v>
+      </c>
+      <c r="B391" s="11" t="s">
         <v>876</v>
-      </c>
-      <c r="B391" s="20" t="s">
-        <v>877</v>
       </c>
       <c r="C391" s="7"/>
       <c r="D391" s="7"/>
@@ -15798,11 +15837,11 @@
       <c r="Z391" s="7"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
-      <c r="A392" s="8" t="s">
+      <c r="A392" s="16" t="s">
+        <v>877</v>
+      </c>
+      <c r="B392" s="16" t="s">
         <v>878</v>
-      </c>
-      <c r="B392" s="8" t="s">
-        <v>879</v>
       </c>
       <c r="C392" s="7"/>
       <c r="D392" s="7"/>
@@ -15830,11 +15869,11 @@
       <c r="Z392" s="7"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="A393" s="8" t="s">
+      <c r="A393" s="16" t="s">
+        <v>879</v>
+      </c>
+      <c r="B393" s="16" t="s">
         <v>880</v>
-      </c>
-      <c r="B393" s="8" t="s">
-        <v>881</v>
       </c>
       <c r="C393" s="7"/>
       <c r="D393" s="7"/>
@@ -15863,10 +15902,10 @@
     </row>
     <row r="394" ht="15.75" customHeight="1">
       <c r="A394" s="8" t="s">
+        <v>881</v>
+      </c>
+      <c r="B394" s="8" t="s">
         <v>882</v>
-      </c>
-      <c r="B394" s="8" t="s">
-        <v>883</v>
       </c>
       <c r="C394" s="7"/>
       <c r="D394" s="7"/>
@@ -15894,6 +15933,12 @@
       <c r="Z394" s="7"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
+      <c r="A395" s="8" t="s">
+        <v>883</v>
+      </c>
+      <c r="B395" s="8" t="s">
+        <v>884</v>
+      </c>
       <c r="C395" s="7"/>
       <c r="D395" s="7"/>
       <c r="E395" s="7"/>
@@ -15920,6 +15965,12 @@
       <c r="Z395" s="7"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
+      <c r="A396" s="11" t="s">
+        <v>885</v>
+      </c>
+      <c r="B396" s="11" t="s">
+        <v>886</v>
+      </c>
       <c r="C396" s="7"/>
       <c r="D396" s="7"/>
       <c r="E396" s="7"/>
@@ -15946,6 +15997,12 @@
       <c r="Z396" s="7"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
+      <c r="A397" s="8" t="s">
+        <v>887</v>
+      </c>
+      <c r="B397" s="8" t="s">
+        <v>888</v>
+      </c>
       <c r="C397" s="7"/>
       <c r="D397" s="7"/>
       <c r="E397" s="7"/>
@@ -15972,6 +16029,12 @@
       <c r="Z397" s="7"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
+      <c r="A398" s="21" t="s">
+        <v>889</v>
+      </c>
+      <c r="B398" s="20" t="s">
+        <v>890</v>
+      </c>
       <c r="C398" s="7"/>
       <c r="D398" s="7"/>
       <c r="E398" s="7"/>
@@ -15998,6 +16061,12 @@
       <c r="Z398" s="7"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
+      <c r="A399" s="8" t="s">
+        <v>891</v>
+      </c>
+      <c r="B399" s="8" t="s">
+        <v>892</v>
+      </c>
       <c r="C399" s="7"/>
       <c r="D399" s="7"/>
       <c r="E399" s="7"/>
@@ -16024,6 +16093,12 @@
       <c r="Z399" s="7"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
+      <c r="A400" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="B400" s="8" t="s">
+        <v>894</v>
+      </c>
       <c r="C400" s="7"/>
       <c r="D400" s="7"/>
       <c r="E400" s="7"/>
@@ -16050,6 +16125,12 @@
       <c r="Z400" s="7"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
+      <c r="A401" s="8" t="s">
+        <v>895</v>
+      </c>
+      <c r="B401" s="8" t="s">
+        <v>896</v>
+      </c>
       <c r="C401" s="7"/>
       <c r="D401" s="7"/>
       <c r="E401" s="7"/>
